--- a/analysis/final_working/free_lit_SM_SF_18F_18O.xlsx
+++ b/analysis/final_working/free_lit_SM_SF_18F_18O.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kawecka/digios/analysis/final_working/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C99A1FD1-A3CC-124B-B3B5-0B7DA5B9F8A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CE60947-7425-7744-BB5D-BAB41D0AD73E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36380" yWindow="3860" windowWidth="29400" windowHeight="17160" activeTab="6" xr2:uid="{FC3CEAA1-A762-5643-8C2C-8E9D51254AD0}"/>
+    <workbookView xWindow="30960" yWindow="2060" windowWidth="36080" windowHeight="17680" activeTab="4" xr2:uid="{FC3CEAA1-A762-5643-8C2C-8E9D51254AD0}"/>
   </bookViews>
   <sheets>
     <sheet name="18O Option 1" sheetId="6" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="113">
   <si>
     <t>unc</t>
   </si>
@@ -283,9 +283,6 @@
     <t>chi2/ndf</t>
   </si>
   <si>
-    <t>d</t>
-  </si>
-  <si>
     <t>unc (15%)</t>
   </si>
   <si>
@@ -313,16 +310,7 @@
     <t>SF literature</t>
   </si>
   <si>
-    <t>wieghted diff</t>
-  </si>
-  <si>
-    <t>summed</t>
-  </si>
-  <si>
     <t>Exp re-norm unc</t>
-  </si>
-  <si>
-    <t>s</t>
   </si>
   <si>
     <t>energy</t>
@@ -362,6 +350,45 @@
   </si>
   <si>
     <t>some of the states are not reproduced with SM so I wouldn't trust this too much</t>
+  </si>
+  <si>
+    <t>&lt;- upper limit rather than a real value</t>
+  </si>
+  <si>
+    <t>(SF_O - SF_F)/sqrt(unc_O^2+unc_F^2)</t>
+  </si>
+  <si>
+    <t>comparing fits with Option 1 (maybe makes more sense since both states are ell=2 and cannot be separated)</t>
+  </si>
+  <si>
+    <t>weighted diff</t>
+  </si>
+  <si>
+    <t>unc. Lit</t>
+  </si>
+  <si>
+    <t>unc norm</t>
+  </si>
+  <si>
+    <t>unc norm inflated</t>
+  </si>
+  <si>
+    <t>unc norm factor</t>
+  </si>
+  <si>
+    <t>unc norm factor 2</t>
+  </si>
+  <si>
+    <t>unc inflated</t>
+  </si>
+  <si>
+    <t>unc final</t>
+  </si>
+  <si>
+    <t>unc final (including sqrt(chi2/ndf) and lit. Uncertainty</t>
+  </si>
+  <si>
+    <t>unc fit</t>
   </si>
 </sst>
 </file>
@@ -716,7 +743,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="166">
+  <cellXfs count="183">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -732,14 +759,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -752,7 +777,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -774,7 +798,6 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -891,15 +914,12 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -907,6 +927,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -939,12 +962,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -971,12 +993,40 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -985,10 +1035,10 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFD8E4FF"/>
+      <color rgb="FFFDFFBB"/>
+      <color rgb="FF7FFFF0"/>
       <color rgb="FFFFECEF"/>
-      <color rgb="FFFDFFBB"/>
-      <color rgb="FFD8E4FF"/>
-      <color rgb="FF7FFFF0"/>
     </mruColors>
   </colors>
   <extLst>
@@ -5851,7 +5901,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G2" t="s">
         <v>1</v>
@@ -5870,7 +5920,7 @@
       <c r="C3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="35">
+      <c r="D3" s="32">
         <v>6.1960600000000001</v>
       </c>
       <c r="E3" s="9">
@@ -5891,13 +5941,13 @@
       </c>
     </row>
     <row r="4" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="125" t="s">
+      <c r="B4" s="118" t="s">
         <v>37</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="38">
+      <c r="D4" s="35">
         <v>0.74325399999999997</v>
       </c>
       <c r="E4" s="2">
@@ -5918,11 +5968,11 @@
       </c>
     </row>
     <row r="5" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="126"/>
+      <c r="B5" s="119"/>
       <c r="C5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="37">
+      <c r="D5" s="34">
         <v>4.9184099999999997</v>
       </c>
       <c r="E5" s="6">
@@ -5940,26 +5990,26 @@
       </c>
     </row>
     <row r="6" spans="2:9" ht="35" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="53" t="s">
+      <c r="B6" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="54" t="s">
+      <c r="C6" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="55">
+      <c r="D6" s="51">
         <v>8.4322099999999995</v>
       </c>
-      <c r="E6" s="56">
+      <c r="E6" s="52">
         <v>0.14779700000000001</v>
       </c>
       <c r="F6" s="9">
         <f t="shared" si="0"/>
         <v>0.46677488986783022</v>
       </c>
-      <c r="G6" s="57">
+      <c r="G6" s="53">
         <v>69.820300000000003</v>
       </c>
-      <c r="H6" s="72">
+      <c r="H6" s="68">
         <v>9.9743300000000001</v>
       </c>
       <c r="I6" t="s">
@@ -5967,13 +6017,13 @@
       </c>
     </row>
     <row r="7" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="125" t="s">
+      <c r="B7" s="118" t="s">
         <v>36</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="38">
+      <c r="D7" s="35">
         <v>1.2651399999999999</v>
       </c>
       <c r="E7" s="2">
@@ -5994,11 +6044,11 @@
       </c>
     </row>
     <row r="8" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="126"/>
+      <c r="B8" s="119"/>
       <c r="C8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="37">
+      <c r="D8" s="34">
         <v>3.4860899999999999</v>
       </c>
       <c r="E8" s="6">
@@ -6016,26 +6066,26 @@
       </c>
     </row>
     <row r="9" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="130" t="s">
+      <c r="B9" s="124" t="s">
         <v>50</v>
       </c>
-      <c r="C9" s="58" t="s">
+      <c r="C9" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="59">
+      <c r="D9" s="55">
         <v>2.8942600000000001</v>
       </c>
-      <c r="E9" s="58">
+      <c r="E9" s="54">
         <v>1.4768600000000001</v>
       </c>
       <c r="F9" s="9">
         <f t="shared" si="0"/>
         <v>1.5356716668556818</v>
       </c>
-      <c r="G9" s="60">
+      <c r="G9" s="56">
         <v>4.3249199999999997</v>
       </c>
-      <c r="H9" s="30">
+      <c r="H9" s="27">
         <v>1.0812299999999999</v>
       </c>
       <c r="I9" t="s">
@@ -6043,35 +6093,35 @@
       </c>
     </row>
     <row r="10" spans="2:9" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="129"/>
-      <c r="C10" s="33" t="s">
+      <c r="B10" s="123"/>
+      <c r="C10" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="44">
+      <c r="D10" s="41">
         <v>4.9315699999999998</v>
       </c>
-      <c r="E10" s="33">
+      <c r="E10" s="30">
         <v>0.476076</v>
       </c>
       <c r="F10" s="9">
         <f t="shared" si="0"/>
         <v>0.49503434616008668</v>
       </c>
-      <c r="G10" s="60">
+      <c r="G10" s="56">
         <v>4.3249199999999997</v>
       </c>
-      <c r="H10" s="30">
+      <c r="H10" s="27">
         <v>1.0812299999999999</v>
       </c>
     </row>
     <row r="11" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="50" t="s">
+      <c r="B11" s="46" t="s">
         <v>43</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="35">
+      <c r="D11" s="32">
         <v>0.28774300000000003</v>
       </c>
       <c r="E11" s="9">
@@ -6098,7 +6148,7 @@
       <c r="C12" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="35">
+      <c r="D12" s="32">
         <v>0.28167199999999998</v>
       </c>
       <c r="E12" s="9">
@@ -6130,13 +6180,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E7DC075-C5D5-7045-BBDD-7E30C0F6925C}">
-  <dimension ref="B2:N21"/>
+  <dimension ref="B2:P21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="14" max="14" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:16" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D2" t="s">
         <v>47</v>
       </c>
@@ -6144,7 +6194,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="G2" t="s">
         <v>1</v>
@@ -6156,55 +6206,65 @@
         <v>32</v>
       </c>
       <c r="J2" t="s">
+        <v>104</v>
+      </c>
+      <c r="K2" t="s">
         <v>3</v>
       </c>
-      <c r="K2" t="s">
-        <v>0</v>
-      </c>
       <c r="L2" t="s">
+        <v>105</v>
+      </c>
+      <c r="M2" t="s">
+        <v>109</v>
+      </c>
+      <c r="N2" t="s">
         <v>46</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="2:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="8" t="s">
+    <row r="3" spans="2:16" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="69" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="35">
         <f>'18O Option 1'!D3</f>
         <v>6.1960600000000001</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="2">
         <f>'18O Option 1'!E3</f>
         <v>0.50926499999999997</v>
       </c>
-      <c r="F3" s="9">
+      <c r="F3" s="2">
         <f>E3*SQRT(H3)</f>
         <v>0.84551640881286871</v>
       </c>
-      <c r="G3" s="10">
+      <c r="G3" s="2">
         <f>'18O Option 1'!G3</f>
         <v>8.2694700000000001</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="3">
         <f>'18O Option 1'!H3</f>
         <v>2.7564899999999999</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3">
+        <f>E3*SQRT(H3)</f>
+        <v>0.84551640881286871</v>
+      </c>
+      <c r="N3" t="s">
         <v>48</v>
       </c>
-      <c r="N3" s="94">
-        <f>D3*$N$21/$D$5</f>
+      <c r="P3" s="90">
+        <f>D3*$P$21/$D$5</f>
         <v>1.5478780585595753</v>
       </c>
     </row>
-    <row r="4" spans="2:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="125" t="s">
+    <row r="4" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B4" s="118" t="s">
         <v>37</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -6214,7 +6274,7 @@
         <f>'18O Option 1'!D4</f>
         <v>0.74325399999999997</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="2">
         <f>'18O Option 1'!E4</f>
         <v>9.4910800000000003E-2</v>
       </c>
@@ -6222,142 +6282,166 @@
         <f>E4*SQRT(H4)</f>
         <v>0.10717148336994237</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G4" s="2">
         <f>'18O Option 1'!G4</f>
         <v>10.2004</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="3">
         <f>'18O Option 1'!H4</f>
         <v>1.27505</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4">
+        <f t="shared" ref="M4:M5" si="0">E4*SQRT(H4)</f>
+        <v>0.10717148336994237</v>
+      </c>
+      <c r="N4" t="s">
         <v>48</v>
       </c>
-      <c r="N4" s="94">
-        <f t="shared" ref="N4:N14" si="0">D4*$N$21/$D$5</f>
+      <c r="P4" s="90">
+        <f>D4*$P$21/$D$5</f>
         <v>0.18567711715778065</v>
       </c>
     </row>
-    <row r="5" spans="2:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="126"/>
+    <row r="5" spans="2:16" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="119"/>
       <c r="C5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="35">
+      <c r="D5" s="34">
         <f>'18O Option 1'!D5</f>
         <v>4.9184099999999997</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="6">
         <f>'18O Option 1'!E5</f>
         <v>0.21648899999999999</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="6">
         <f t="shared" ref="F5:F14" si="1">E5*SQRT(H5)</f>
         <v>0.24445529131853752</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="6">
         <f>'18O Option 1'!G5</f>
         <v>10.2004</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="7">
         <f>'18O Option 1'!H5</f>
         <v>1.27505</v>
       </c>
-      <c r="N5" s="94">
+      <c r="M5">
         <f t="shared" si="0"/>
+        <v>0.24445529131853752</v>
+      </c>
+      <c r="P5" s="90">
+        <f>D5*$P$21/$D$5</f>
         <v>1.2286999999999999</v>
       </c>
     </row>
-    <row r="6" spans="2:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="12" t="s">
+    <row r="6" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B6" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="162" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="61">
-        <f>I6*J6</f>
+      <c r="D6" s="167">
+        <f>I6*K6</f>
         <v>8.2684207000000001</v>
       </c>
-      <c r="E6" s="52">
-        <f>I6*K6</f>
+      <c r="E6" s="162">
+        <f>I6*L6</f>
         <v>0.14492560099999999</v>
       </c>
-      <c r="F6" s="2">
-        <f>E6*SQRT(H6)</f>
-        <v>0.45770639083204728</v>
-      </c>
-      <c r="G6" s="52">
+      <c r="F6" s="162">
+        <f>D6*SQRT(POWER((M6/K6),2)+POWER((J6/I6),2))</f>
+        <v>1.3220240957837115</v>
+      </c>
+      <c r="G6" s="162">
         <v>69.820300000000003</v>
       </c>
-      <c r="H6" s="52">
+      <c r="H6" s="162">
         <v>9.9743300000000001</v>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="48">
         <v>1.57</v>
       </c>
-      <c r="J6" s="13">
+      <c r="J6" s="48">
+        <f>0.15*I6</f>
+        <v>0.23549999999999999</v>
+      </c>
+      <c r="K6" s="48">
         <v>5.2665100000000002</v>
       </c>
-      <c r="K6" s="14">
+      <c r="L6" s="48">
         <v>9.2309299999999997E-2</v>
       </c>
-      <c r="N6" s="94">
-        <f t="shared" si="0"/>
+      <c r="M6" s="71">
+        <f>L6*SQRT(H6)</f>
+        <v>0.29153273301404287</v>
+      </c>
+      <c r="P6" s="90">
+        <f>D6*$P$21/$D$5</f>
         <v>2.0655879672678772</v>
       </c>
     </row>
-    <row r="7" spans="2:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="16" t="s">
+    <row r="7" spans="2:16" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="157" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="39">
-        <f>I7*J7</f>
+      <c r="D7" s="168">
+        <f>I7*K7</f>
         <v>1.4746228000000001</v>
       </c>
-      <c r="E7" s="17">
-        <f>I7*K7</f>
+      <c r="E7" s="157">
+        <f>I7*L7</f>
         <v>2.5846604000000002E-2</v>
       </c>
-      <c r="F7" s="2">
-        <f>E7*SQRT(H7)</f>
-        <v>8.1629165243932017E-2</v>
-      </c>
-      <c r="G7" s="17">
+      <c r="F7" s="157">
+        <f>D7*SQRT(POWER((M7/K7),2)+POWER((J7/I7),2))</f>
+        <v>0.23577499797416512</v>
+      </c>
+      <c r="G7" s="157">
         <v>69.820300000000003</v>
       </c>
-      <c r="H7" s="52">
+      <c r="H7" s="157">
         <v>9.9743300000000001</v>
       </c>
-      <c r="I7" s="17">
+      <c r="I7" s="15">
         <v>0.28000000000000003</v>
       </c>
-      <c r="J7" s="13">
+      <c r="J7" s="15">
+        <f>0.15*I7</f>
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="K7" s="15">
         <v>5.2665100000000002</v>
       </c>
-      <c r="K7" s="14">
+      <c r="L7" s="15">
         <v>9.2309299999999997E-2</v>
       </c>
-      <c r="N7" s="94">
-        <f t="shared" si="0"/>
+      <c r="M7" s="16">
+        <f>L7*SQRT(H7)</f>
+        <v>0.29153273301404287</v>
+      </c>
+      <c r="P7" s="90">
+        <f>D7*$P$21/$D$5</f>
         <v>0.36838511518153222</v>
       </c>
     </row>
-    <row r="8" spans="2:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="128" t="s">
+    <row r="8" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B8" s="118" t="s">
         <v>36</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="36">
+      <c r="D8" s="35">
         <f>'18O Option 1'!D7</f>
         <v>1.2651399999999999</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="2">
         <f>'18O Option 1'!E7</f>
         <v>0.160803</v>
       </c>
@@ -6365,181 +6449,213 @@
         <f t="shared" si="1"/>
         <v>0.43678576450431567</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="2">
         <f>'18O Option 1'!G7</f>
         <v>44.267000000000003</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="3">
         <f>'18O Option 1'!H7</f>
         <v>7.3781699999999999</v>
       </c>
-      <c r="L8" t="s">
+      <c r="M8">
+        <f>E8*SQRT(H8)</f>
+        <v>0.43678576450431567</v>
+      </c>
+      <c r="N8" t="s">
         <v>48</v>
       </c>
-      <c r="N8" s="94">
-        <f t="shared" si="0"/>
+      <c r="P8" s="90">
+        <f>D8*$P$21/$D$5</f>
         <v>0.31605285407275929</v>
       </c>
     </row>
-    <row r="9" spans="2:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="126"/>
+    <row r="9" spans="2:16" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="119"/>
       <c r="C9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="36">
+      <c r="D9" s="34">
         <f>'18O Option 1'!D8</f>
         <v>3.4860899999999999</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="6">
         <f>'18O Option 1'!E8</f>
         <v>0.202874</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="6">
         <f t="shared" si="1"/>
         <v>0.55106232587730664</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="6">
         <f>'18O Option 1'!G8</f>
         <v>44.267000000000003</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="7">
         <f>'18O Option 1'!H8</f>
         <v>7.3781699999999999</v>
       </c>
-      <c r="N9" s="94">
-        <f t="shared" si="0"/>
+      <c r="M9">
+        <f>E9*SQRT(H9)</f>
+        <v>0.55106232587730664</v>
+      </c>
+      <c r="P9" s="90">
+        <f>D9*$P$21/$D$5</f>
         <v>0.87088282249751447</v>
       </c>
     </row>
-    <row r="10" spans="2:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="1" t="s">
+    <row r="10" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B10" s="116" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="132" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="38">
-        <f>I10*J10</f>
+      <c r="D10" s="164">
+        <f>I10*K10</f>
         <v>1.5525124999999997</v>
       </c>
-      <c r="E10" s="2">
-        <f>I10*K10</f>
+      <c r="E10" s="132">
+        <f>I10*L10</f>
         <v>5.8336249999999992E-2</v>
       </c>
-      <c r="F10" s="2">
-        <f t="shared" si="1"/>
-        <v>6.7469599429762148E-2</v>
-      </c>
-      <c r="G10" s="2">
+      <c r="F10" s="132">
+        <f>D10*SQRT(POWER((M10/K10),2)+POWER((J10/I10),2))</f>
+        <v>0.24245367754888389</v>
+      </c>
+      <c r="G10" s="132">
         <v>6.6882200000000003</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="132">
         <v>1.3376399999999999</v>
       </c>
       <c r="I10" s="2">
         <v>0.35</v>
       </c>
       <c r="J10" s="2">
+        <f>0.15*I10</f>
+        <v>5.2499999999999998E-2</v>
+      </c>
+      <c r="K10" s="2">
         <v>4.4357499999999996</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="2">
         <v>0.16667499999999999</v>
       </c>
-      <c r="N10" s="94">
-        <f t="shared" si="0"/>
+      <c r="M10" s="3">
+        <f>L10*SQRT(H10)</f>
+        <v>0.19277028408503472</v>
+      </c>
+      <c r="P10" s="90">
+        <f>D10*$P$21/$D$5</f>
         <v>0.38784324786872171</v>
       </c>
     </row>
-    <row r="11" spans="2:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="26" t="s">
+    <row r="11" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B11" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="27" t="s">
+      <c r="C11" s="163" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="45">
-        <f>I11*J11</f>
+      <c r="D11" s="165">
+        <f>I11*K11</f>
         <v>0.70971999999999991</v>
       </c>
-      <c r="E11" s="27">
-        <f t="shared" ref="E11:E12" si="2">I11*K11</f>
+      <c r="E11" s="163">
+        <f>I11*L11</f>
         <v>2.6667999999999997E-2</v>
       </c>
-      <c r="F11" s="2">
-        <f t="shared" si="1"/>
-        <v>3.0843245453605554E-2</v>
-      </c>
-      <c r="G11" s="27">
+      <c r="F11" s="163">
+        <f>D11*SQRT(POWER((M11/K11),2)+POWER((J11/I11),2))</f>
+        <v>0.11083596687948978</v>
+      </c>
+      <c r="G11" s="163">
         <v>6.6882200000000003</v>
       </c>
-      <c r="H11" s="27">
+      <c r="H11" s="163">
         <v>1.3376399999999999</v>
       </c>
-      <c r="I11" s="27">
+      <c r="I11" s="163">
         <v>0.16</v>
       </c>
-      <c r="J11" s="27">
+      <c r="J11" s="163">
+        <f>0.15*I11</f>
+        <v>2.4E-2</v>
+      </c>
+      <c r="K11" s="163">
         <v>4.4357499999999996</v>
       </c>
-      <c r="K11" s="28">
+      <c r="L11" s="163">
         <v>0.16667499999999999</v>
       </c>
-      <c r="N11" s="94">
-        <f t="shared" si="0"/>
+      <c r="M11" s="25">
+        <f t="shared" ref="M11:M12" si="2">L11*SQRT(H11)</f>
+        <v>0.19277028408503472</v>
+      </c>
+      <c r="P11" s="90">
+        <f>D11*$P$21/$D$5</f>
         <v>0.17729977045427281</v>
       </c>
     </row>
-    <row r="12" spans="2:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="29" t="s">
+    <row r="12" spans="2:16" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="30" t="s">
+      <c r="C12" s="161" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="43">
-        <f>I12*J12</f>
+      <c r="D12" s="166">
+        <f>I12*K12</f>
         <v>4.4801074999999999</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="161">
+        <f>I12*L12</f>
+        <v>0.16834174999999998</v>
+      </c>
+      <c r="F12" s="161">
+        <f>D12*SQRT(POWER((M12/K12),2)+POWER((J12/I12),2))</f>
+        <v>0.69965204092677924</v>
+      </c>
+      <c r="G12" s="161">
+        <v>6.6882200000000003</v>
+      </c>
+      <c r="H12" s="161">
+        <v>1.3376399999999999</v>
+      </c>
+      <c r="I12" s="30">
+        <v>1.01</v>
+      </c>
+      <c r="J12" s="30">
+        <f>0.15*I12</f>
+        <v>0.1515</v>
+      </c>
+      <c r="K12" s="30">
+        <v>4.4357499999999996</v>
+      </c>
+      <c r="L12" s="30">
+        <v>0.16667499999999999</v>
+      </c>
+      <c r="M12" s="31">
         <f t="shared" si="2"/>
-        <v>0.16834174999999998</v>
-      </c>
-      <c r="F12" s="2">
-        <f t="shared" si="1"/>
-        <v>0.19469798692588505</v>
-      </c>
-      <c r="G12" s="30">
-        <v>6.6882200000000003</v>
-      </c>
-      <c r="H12" s="30">
-        <v>1.3376399999999999</v>
-      </c>
-      <c r="I12" s="33">
-        <v>1.01</v>
-      </c>
-      <c r="J12" s="33">
-        <v>4.4357499999999996</v>
-      </c>
-      <c r="K12" s="34">
-        <v>0.16667499999999999</v>
-      </c>
-      <c r="N12" s="94">
-        <f t="shared" si="0"/>
+        <v>0.19277028408503472</v>
+      </c>
+      <c r="P12" s="90">
+        <f>D12*$P$21/$D$5</f>
         <v>1.1192048009925972</v>
       </c>
     </row>
-    <row r="13" spans="2:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="50" t="s">
+    <row r="13" spans="2:16" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="2" t="s">
         <v>42</v>
       </c>
       <c r="D13" s="35">
         <f>'18O Option 1'!D11</f>
         <v>0.28774300000000003</v>
       </c>
-      <c r="E13" s="138">
+      <c r="E13" s="134">
         <f>'18O Option 1'!E11</f>
         <v>3.6374200000000002E-2</v>
       </c>
@@ -6547,42 +6663,46 @@
         <f t="shared" si="1"/>
         <v>7.0891533460457984E-2</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="2">
         <f>'18O Option 1'!G11</f>
         <v>15.1936</v>
       </c>
-      <c r="H13" s="10">
+      <c r="H13" s="3">
         <f>'18O Option 1'!H11</f>
         <v>3.7984100000000001</v>
       </c>
-      <c r="L13" t="s">
+      <c r="M13">
+        <f>E13*SQRT(H13)</f>
+        <v>7.0891533460457984E-2</v>
+      </c>
+      <c r="N13" t="s">
         <v>48</v>
       </c>
-      <c r="N13" s="94">
-        <f t="shared" si="0"/>
+      <c r="P13" s="90">
+        <f>D13*$P$21/$D$5</f>
         <v>7.1882950811339441E-2</v>
       </c>
     </row>
-    <row r="14" spans="2:14" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:16" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B14" s="8" t="s">
         <v>44</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="35">
+      <c r="D14" s="32">
         <f>'18O Option 1'!D12</f>
         <v>0.28167199999999998</v>
       </c>
-      <c r="E14" s="138">
+      <c r="E14" s="133">
         <f>'18O Option 1'!E12</f>
         <v>2.2748000000000001E-2</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="9">
         <f t="shared" si="1"/>
         <v>5.1837596157627529E-2</v>
       </c>
-      <c r="G14" s="10">
+      <c r="G14" s="9">
         <f>'18O Option 1'!G12</f>
         <v>15.5784</v>
       </c>
@@ -6590,21 +6710,25 @@
         <f>'18O Option 1'!H12</f>
         <v>5.1928200000000002</v>
       </c>
-      <c r="L14" t="s">
+      <c r="M14">
+        <f>E14*SQRT(H14)</f>
+        <v>5.1837596157627529E-2</v>
+      </c>
+      <c r="N14" t="s">
         <v>48</v>
       </c>
-      <c r="N14" s="94">
-        <f t="shared" si="0"/>
+      <c r="P14" s="90">
+        <f>D14*$P$21/$D$5</f>
         <v>7.0366314804987784E-2</v>
       </c>
     </row>
-    <row r="20" spans="14:14" x14ac:dyDescent="0.2">
-      <c r="N20" t="s">
+    <row r="20" spans="16:16" x14ac:dyDescent="0.2">
+      <c r="P20" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="21" spans="14:14" x14ac:dyDescent="0.2">
-      <c r="N21">
+    <row r="21" spans="16:16" x14ac:dyDescent="0.2">
+      <c r="P21">
         <v>1.2286999999999999</v>
       </c>
     </row>
@@ -6630,7 +6754,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G2" t="s">
         <v>1</v>
@@ -6658,7 +6782,7 @@
       <c r="C3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="35">
+      <c r="D3" s="32">
         <f>'18O Option 1'!D3</f>
         <v>6.1960600000000001</v>
       </c>
@@ -6683,13 +6807,13 @@
       </c>
     </row>
     <row r="4" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="125" t="s">
+      <c r="B4" s="118" t="s">
         <v>37</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="35">
+      <c r="D4" s="32">
         <f>'18O Option 1'!D4</f>
         <v>0.74325399999999997</v>
       </c>
@@ -6714,11 +6838,11 @@
       </c>
     </row>
     <row r="5" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="126"/>
+      <c r="B5" s="119"/>
       <c r="C5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="35">
+      <c r="D5" s="32">
         <f>'18O Option 1'!D5</f>
         <v>4.9184099999999997</v>
       </c>
@@ -6740,91 +6864,91 @@
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="52" t="s">
+      <c r="C6" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="61">
+      <c r="D6" s="57">
         <f>I6*J6</f>
         <v>8.6018539699999987</v>
       </c>
-      <c r="E6" s="52">
+      <c r="E6" s="48">
         <v>0.13732075073999997</v>
       </c>
-      <c r="F6" s="52"/>
-      <c r="G6" s="52">
+      <c r="F6" s="48"/>
+      <c r="G6" s="48">
         <v>89.231099999999998</v>
       </c>
-      <c r="H6" s="52">
+      <c r="H6" s="48">
         <v>12.747299999999999</v>
       </c>
-      <c r="I6" s="52">
+      <c r="I6" s="48">
         <v>1.8597999999999999</v>
       </c>
-      <c r="J6" s="13">
+      <c r="J6" s="12">
         <v>4.6251499999999997</v>
       </c>
-      <c r="K6" s="14">
+      <c r="K6" s="13">
         <v>7.3836299999999994E-2</v>
       </c>
     </row>
     <row r="7" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="144" t="s">
+      <c r="B7" s="137" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="145" t="s">
+      <c r="C7" s="138" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="146">
+      <c r="D7" s="139">
         <f>I7*J7</f>
         <v>1.5017862049999999</v>
       </c>
-      <c r="E7" s="145">
+      <c r="E7" s="138">
         <v>2.3974646609999997E-2</v>
       </c>
-      <c r="F7" s="145"/>
-      <c r="G7" s="145">
+      <c r="F7" s="138"/>
+      <c r="G7" s="138">
         <v>89.231099999999998</v>
       </c>
-      <c r="H7" s="145">
+      <c r="H7" s="138">
         <v>12.747299999999999</v>
       </c>
-      <c r="I7" s="145">
+      <c r="I7" s="138">
         <v>0.32469999999999999</v>
       </c>
-      <c r="J7" s="145">
+      <c r="J7" s="138">
         <v>4.6251499999999997</v>
       </c>
-      <c r="K7" s="147">
+      <c r="K7" s="140">
         <v>7.3836299999999994E-2</v>
       </c>
     </row>
     <row r="8" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="125" t="s">
+      <c r="B8" s="118" t="s">
         <v>36</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="38">
+      <c r="D8" s="35">
         <f>'18O Option 1'!D7</f>
         <v>1.2651399999999999</v>
       </c>
-      <c r="E8" s="139">
+      <c r="E8" s="134">
         <f>'18O Option 1'!E7</f>
         <v>0.160803</v>
       </c>
-      <c r="F8" s="139">
+      <c r="F8" s="134">
         <f>'18O Option 1'!F7</f>
         <v>0.43678576450431567</v>
       </c>
-      <c r="G8" s="139">
+      <c r="G8" s="134">
         <f>'18O Option 1'!G7</f>
         <v>44.267000000000003</v>
       </c>
-      <c r="H8" s="139">
+      <c r="H8" s="134">
         <f>'18O Option 1'!H7</f>
         <v>7.3781699999999999</v>
       </c>
@@ -6833,184 +6957,184 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="126"/>
+      <c r="B9" s="119"/>
       <c r="C9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="38">
+      <c r="D9" s="35">
         <f>'18O Option 1'!D8</f>
         <v>3.4860899999999999</v>
       </c>
-      <c r="E9" s="139">
+      <c r="E9" s="134">
         <f>'18O Option 1'!E8</f>
         <v>0.202874</v>
       </c>
-      <c r="F9" s="139">
+      <c r="F9" s="134">
         <f>'18O Option 1'!F8</f>
         <v>0.55106232587730664</v>
       </c>
-      <c r="G9" s="139">
+      <c r="G9" s="134">
         <f>'18O Option 1'!G8</f>
         <v>44.267000000000003</v>
       </c>
-      <c r="H9" s="139">
+      <c r="H9" s="134">
         <f>'18O Option 1'!H8</f>
         <v>7.3781699999999999</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B10" s="148" t="s">
+      <c r="B10" s="141" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="149" t="s">
+      <c r="C10" s="142" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="150">
+      <c r="D10" s="143">
         <f>I10*J10</f>
         <v>3.4596450000000001E-2</v>
       </c>
-      <c r="E10" s="149">
+      <c r="E10" s="142">
         <f>I10*K10</f>
         <v>1.4321550000000001E-3</v>
       </c>
-      <c r="F10" s="149"/>
-      <c r="G10" s="149">
+      <c r="F10" s="142"/>
+      <c r="G10" s="142">
         <v>45.520400000000002</v>
       </c>
-      <c r="H10" s="149">
+      <c r="H10" s="142">
         <v>9.1040899999999993</v>
       </c>
-      <c r="I10" s="149">
+      <c r="I10" s="142">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="J10" s="149">
+      <c r="J10" s="142">
         <v>2.3064300000000002</v>
       </c>
-      <c r="K10" s="151">
+      <c r="K10" s="144">
         <v>9.5477000000000006E-2</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B11" s="152"/>
-      <c r="C11" s="153" t="s">
+      <c r="B11" s="145"/>
+      <c r="C11" s="146" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="154">
+      <c r="D11" s="147">
         <f>I11*J11</f>
         <v>2.0605645620000002</v>
       </c>
-      <c r="E11" s="153">
+      <c r="E11" s="146">
         <f>I11*K11</f>
         <v>8.52991518E-2</v>
       </c>
-      <c r="F11" s="153"/>
-      <c r="G11" s="153">
+      <c r="F11" s="146"/>
+      <c r="G11" s="146">
         <v>45.520400000000002</v>
       </c>
-      <c r="H11" s="153">
+      <c r="H11" s="146">
         <v>9.1040899999999993</v>
       </c>
-      <c r="I11" s="153">
+      <c r="I11" s="146">
         <v>0.89339999999999997</v>
       </c>
-      <c r="J11" s="153">
+      <c r="J11" s="146">
         <v>2.3064300000000002</v>
       </c>
-      <c r="K11" s="155">
+      <c r="K11" s="148">
         <v>9.5477000000000006E-2</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B12" s="152"/>
-      <c r="C12" s="153" t="s">
+      <c r="B12" s="145"/>
+      <c r="C12" s="146" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="154">
+      <c r="D12" s="147">
         <f>I12*J12</f>
         <v>2.3064300000000003E-2</v>
       </c>
-      <c r="E12" s="153">
+      <c r="E12" s="146">
         <f>I12*K12</f>
         <v>9.5477000000000008E-4</v>
       </c>
-      <c r="F12" s="153"/>
-      <c r="G12" s="153">
+      <c r="F12" s="146"/>
+      <c r="G12" s="146">
         <v>45.520400000000002</v>
       </c>
-      <c r="H12" s="153">
+      <c r="H12" s="146">
         <v>9.1040899999999993</v>
       </c>
-      <c r="I12" s="153">
+      <c r="I12" s="146">
         <v>0.01</v>
       </c>
-      <c r="J12" s="153">
+      <c r="J12" s="146">
         <v>2.3064300000000002</v>
       </c>
-      <c r="K12" s="155">
+      <c r="K12" s="148">
         <v>9.5477000000000006E-2</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B13" s="156" t="s">
+      <c r="B13" s="149" t="s">
         <v>40</v>
       </c>
-      <c r="C13" s="157" t="s">
+      <c r="C13" s="150" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="158">
+      <c r="D13" s="151">
         <f>I13*J13</f>
         <v>0.301219758</v>
       </c>
-      <c r="E13" s="157">
+      <c r="E13" s="150">
         <f>I13*K13</f>
         <v>1.24692962E-2</v>
       </c>
-      <c r="F13" s="157"/>
-      <c r="G13" s="157">
+      <c r="F13" s="150"/>
+      <c r="G13" s="150">
         <v>45.520400000000002</v>
       </c>
-      <c r="H13" s="157">
+      <c r="H13" s="150">
         <v>9.1040899999999993</v>
       </c>
-      <c r="I13" s="157">
+      <c r="I13" s="150">
         <v>0.13059999999999999</v>
       </c>
-      <c r="J13" s="157">
+      <c r="J13" s="150">
         <v>2.3064300000000002</v>
       </c>
-      <c r="K13" s="159">
+      <c r="K13" s="152">
         <v>9.5477000000000006E-2</v>
       </c>
     </row>
     <row r="14" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="32" t="s">
+      <c r="B14" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="33" t="s">
+      <c r="C14" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="44">
+      <c r="D14" s="41">
         <f>I14*J14</f>
         <v>2.2833657000000001</v>
       </c>
-      <c r="E14" s="33">
+      <c r="E14" s="30">
         <f>I14*K14</f>
         <v>9.4522229999999999E-2</v>
       </c>
-      <c r="F14" s="33"/>
-      <c r="G14" s="33">
+      <c r="F14" s="30"/>
+      <c r="G14" s="30">
         <v>45.520400000000002</v>
       </c>
-      <c r="H14" s="33">
+      <c r="H14" s="30">
         <v>9.1040899999999993</v>
       </c>
-      <c r="I14" s="33">
+      <c r="I14" s="30">
         <v>0.99</v>
       </c>
-      <c r="J14" s="33">
+      <c r="J14" s="30">
         <v>2.3064300000000002</v>
       </c>
-      <c r="K14" s="34">
+      <c r="K14" s="31">
         <v>9.5477000000000006E-2</v>
       </c>
     </row>
@@ -7021,23 +7145,23 @@
       <c r="C15" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D15" s="37">
+      <c r="D15" s="34">
         <f>'18O Option 1'!D11</f>
         <v>0.28774300000000003</v>
       </c>
-      <c r="E15" s="140">
+      <c r="E15" s="135">
         <f>'18O Option 1'!E11</f>
         <v>3.6374200000000002E-2</v>
       </c>
-      <c r="F15" s="140">
+      <c r="F15" s="135">
         <f>'18O Option 1'!F11</f>
         <v>7.0891533460457984E-2</v>
       </c>
-      <c r="G15" s="140">
+      <c r="G15" s="135">
         <f>'18O Option 1'!G11</f>
         <v>15.1936</v>
       </c>
-      <c r="H15" s="140">
+      <c r="H15" s="135">
         <f>'18O Option 1'!H11</f>
         <v>3.7984100000000001</v>
       </c>
@@ -7052,23 +7176,23 @@
       <c r="C16" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="37">
+      <c r="D16" s="34">
         <f>'18O Option 1'!D12</f>
         <v>0.28167199999999998</v>
       </c>
-      <c r="E16" s="140">
+      <c r="E16" s="135">
         <f>'18O Option 1'!E12</f>
         <v>2.2748000000000001E-2</v>
       </c>
-      <c r="F16" s="140">
+      <c r="F16" s="135">
         <f>'18O Option 1'!F12</f>
         <v>5.1837596157627529E-2</v>
       </c>
-      <c r="G16" s="140">
+      <c r="G16" s="135">
         <f>'18O Option 1'!G12</f>
         <v>15.5784</v>
       </c>
-      <c r="H16" s="140">
+      <c r="H16" s="135">
         <f>'18O Option 1'!H12</f>
         <v>5.1928200000000002</v>
       </c>
@@ -7078,7 +7202,7 @@
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -7093,10 +7217,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7253C9-71CE-6148-AA2F-0D73ACAD915E}">
-  <dimension ref="B2:J24"/>
+  <dimension ref="B2:K24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D2" t="s">
         <v>47</v>
       </c>
@@ -7104,10 +7228,10 @@
         <v>54</v>
       </c>
       <c r="F2" t="s">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="G2" t="s">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="H2" t="s">
         <v>1</v>
@@ -7116,10 +7240,13 @@
         <v>76</v>
       </c>
       <c r="J2" t="s">
+        <v>109</v>
+      </c>
+      <c r="K2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B3" s="8" t="s">
         <v>4</v>
       </c>
@@ -7129,85 +7256,97 @@
       <c r="D3" s="9">
         <v>2.2913000000000001</v>
       </c>
-      <c r="E3" s="35">
+      <c r="E3" s="32">
         <f t="shared" ref="E3:E17" si="0">D3*$D$23</f>
         <v>7.4353114331521173</v>
       </c>
       <c r="F3" s="9">
         <v>0.19059799999999999</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3" s="178">
+        <f>E3*SQRT(POWER(($E$23/$D$23),2)+POWER((J3/D3),2))</f>
+        <v>1.2880554729207276</v>
+      </c>
+      <c r="H3" s="10">
+        <v>2.3610099999999998</v>
+      </c>
+      <c r="I3">
+        <v>0.78700300000000001</v>
+      </c>
+      <c r="J3">
         <f>F3</f>
         <v>0.19059799999999999</v>
       </c>
-      <c r="H3" s="10">
-        <v>2.3610099999999998</v>
-      </c>
-      <c r="I3">
-        <v>0.78700300000000001</v>
-      </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="2:10" ht="35" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="51" t="s">
+    <row r="4" spans="2:11" ht="35" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="47" t="s">
         <v>53</v>
       </c>
-      <c r="C4" s="58" t="s">
+      <c r="C4" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="67">
+      <c r="D4" s="63">
         <v>7.8150499999999998E-2</v>
       </c>
-      <c r="E4" s="93">
+      <c r="E4" s="89">
         <f t="shared" si="0"/>
         <v>0.25359983684220944</v>
       </c>
-      <c r="F4" s="58">
+      <c r="F4" s="54">
         <v>0.100659</v>
       </c>
-      <c r="G4" s="58">
+      <c r="G4" s="179">
+        <f>E4*SQRT(POWER(($E$23/$D$23),2)+POWER((J4/D4),2))</f>
+        <v>0.9286430678272074</v>
+      </c>
+      <c r="H4" s="56">
+        <v>80.688100000000006</v>
+      </c>
+      <c r="I4" s="27">
+        <v>8.0688099999999991</v>
+      </c>
+      <c r="J4" s="27">
         <f>F4*SQRT(I4)</f>
         <v>0.28592844085343383</v>
       </c>
-      <c r="H4" s="60">
-        <v>80.688100000000006</v>
-      </c>
-      <c r="I4" s="30">
-        <v>8.0688099999999991</v>
-      </c>
-    </row>
-    <row r="5" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="63" t="s">
+    </row>
+    <row r="5" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="33" t="s">
+      <c r="C5" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="33">
+      <c r="D5" s="30">
         <v>4.5386199999999999</v>
       </c>
-      <c r="E5" s="44">
+      <c r="E5" s="41">
         <f t="shared" si="0"/>
         <v>14.72790694223055</v>
       </c>
-      <c r="F5" s="33">
+      <c r="F5" s="30">
         <v>0.41965799999999998</v>
       </c>
-      <c r="G5" s="58">
-        <f t="shared" ref="G5:G7" si="1">F5*SQRT(I5)</f>
+      <c r="G5" s="179">
+        <f>E5*SQRT(POWER(($E$23/$D$23),2)+POWER((J5/D5),2))</f>
+        <v>4.4690298235219004</v>
+      </c>
+      <c r="H5" s="31">
+        <v>80.688100000000006</v>
+      </c>
+      <c r="I5" s="27">
+        <v>8.0688099999999991</v>
+      </c>
+      <c r="J5" s="27">
+        <f t="shared" ref="J5:J20" si="1">F5*SQRT(I5)</f>
         <v>1.1920658622842499</v>
       </c>
-      <c r="H5" s="34">
-        <v>80.688100000000006</v>
-      </c>
-      <c r="I5" s="30">
-        <v>8.0688099999999991</v>
-      </c>
-    </row>
-    <row r="6" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="125" t="s">
+    </row>
+    <row r="6" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="118" t="s">
         <v>19</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -7216,109 +7355,125 @@
       <c r="D6" s="2">
         <v>0.15563199999999999</v>
       </c>
-      <c r="E6" s="38">
+      <c r="E6" s="35">
         <f t="shared" si="0"/>
         <v>0.50502875614905518</v>
       </c>
       <c r="F6" s="2">
         <v>5.4237800000000003E-2</v>
       </c>
-      <c r="G6" s="58">
+      <c r="G6" s="180">
+        <f t="shared" ref="G6:G7" si="2">F6*SQRT(I6)</f>
+        <v>9.4693203252016286E-2</v>
+      </c>
+      <c r="H6" s="3">
+        <v>24.385100000000001</v>
+      </c>
+      <c r="I6">
+        <v>3.04813</v>
+      </c>
+      <c r="J6" s="155">
         <f t="shared" si="1"/>
         <v>9.4693203252016286E-2</v>
       </c>
-      <c r="H6" s="3">
-        <v>24.385100000000001</v>
-      </c>
-      <c r="I6">
-        <v>3.04813</v>
-      </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="126"/>
+    <row r="7" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="119"/>
       <c r="C7" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D7" s="6">
         <v>1.5156799999999999</v>
       </c>
-      <c r="E7" s="37">
+      <c r="E7" s="34">
         <f t="shared" si="0"/>
         <v>4.9184099999999997</v>
       </c>
       <c r="F7" s="6">
         <v>0.124664</v>
       </c>
-      <c r="G7" s="58">
+      <c r="G7" s="180">
+        <f t="shared" si="2"/>
+        <v>0.21764956340798039</v>
+      </c>
+      <c r="H7" s="7">
+        <v>24.385100000000001</v>
+      </c>
+      <c r="I7">
+        <v>3.04813</v>
+      </c>
+      <c r="J7" s="155">
         <f t="shared" si="1"/>
         <v>0.21764956340798039</v>
       </c>
-      <c r="H7" s="7">
-        <v>24.385100000000001</v>
-      </c>
-      <c r="I7">
-        <v>3.04813</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="131" t="s">
+    </row>
+    <row r="8" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="125" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="17">
         <v>0.69544099999999998</v>
       </c>
-      <c r="E8" s="40">
+      <c r="E8" s="37">
         <f t="shared" si="0"/>
         <v>2.2567190758009605</v>
       </c>
-      <c r="F8" s="19">
+      <c r="F8" s="17">
         <v>0.11036899999999999</v>
       </c>
-      <c r="G8" s="19">
+      <c r="G8" s="181">
         <f>F8</f>
         <v>0.11036899999999999</v>
       </c>
-      <c r="H8" s="20">
+      <c r="H8" s="18">
         <v>3.2037599999999999</v>
       </c>
-      <c r="I8" s="21">
+      <c r="I8" s="19">
         <v>0.457679</v>
       </c>
-    </row>
-    <row r="9" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="127"/>
-      <c r="C9" s="21" t="s">
+      <c r="J8" s="155">
+        <f>F8</f>
+        <v>0.11036899999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="120"/>
+      <c r="C9" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="21">
+      <c r="D9" s="19">
         <v>1.3852199999999999</v>
       </c>
-      <c r="E9" s="41">
+      <c r="E9" s="38">
         <f t="shared" si="0"/>
         <v>4.4950648555103978</v>
       </c>
-      <c r="F9" s="21">
+      <c r="F9" s="19">
         <v>0.206014</v>
       </c>
-      <c r="G9" s="19">
+      <c r="G9" s="181">
         <f>F9</f>
         <v>0.206014</v>
       </c>
-      <c r="H9" s="22">
+      <c r="H9" s="20">
         <v>3.2037599999999999</v>
       </c>
-      <c r="I9" s="21">
+      <c r="I9" s="19">
         <v>0.457679</v>
       </c>
-    </row>
-    <row r="10" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="125" t="s">
+      <c r="J9" s="155">
+        <f>F9</f>
+        <v>0.206014</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="118" t="s">
         <v>23</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -7327,14 +7482,14 @@
       <c r="D10" s="2">
         <v>0.36027500000000001</v>
       </c>
-      <c r="E10" s="38">
+      <c r="E10" s="35">
         <f t="shared" si="0"/>
         <v>1.169099125639977</v>
       </c>
       <c r="F10" s="2">
         <v>6.9371299999999997E-2</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="182">
         <f>F10*SQRT(I10)</f>
         <v>0.10768338664574435</v>
       </c>
@@ -7344,27 +7499,31 @@
       <c r="I10">
         <v>2.4095599999999999</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J10" s="155">
+        <f t="shared" si="1"/>
+        <v>0.10768338664574435</v>
+      </c>
+      <c r="K10" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="126"/>
+    <row r="11" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="119"/>
       <c r="C11" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D11" s="6">
         <v>1.9050400000000001</v>
       </c>
-      <c r="E11" s="37">
+      <c r="E11" s="34">
         <f t="shared" si="0"/>
         <v>6.181890495619129</v>
       </c>
       <c r="F11" s="6">
         <v>0.117092</v>
       </c>
-      <c r="G11" s="2">
-        <f t="shared" ref="G11:G15" si="2">F11*SQRT(I11)</f>
+      <c r="G11" s="182">
+        <f t="shared" ref="G11:G15" si="3">F11*SQRT(I11)</f>
         <v>0.18175907196669946</v>
       </c>
       <c r="H11" s="7">
@@ -7373,9 +7532,13 @@
       <c r="I11">
         <v>2.4095599999999999</v>
       </c>
-    </row>
-    <row r="12" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="50" t="s">
+      <c r="J11" s="155">
+        <f t="shared" si="1"/>
+        <v>0.18175907196669946</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="46" t="s">
         <v>24</v>
       </c>
       <c r="C12" s="9" t="s">
@@ -7384,15 +7547,15 @@
       <c r="D12" s="9">
         <v>0.42468299999999998</v>
       </c>
-      <c r="E12" s="35">
+      <c r="E12" s="32">
         <f t="shared" si="0"/>
         <v>1.3781042924825821</v>
       </c>
       <c r="F12" s="9">
         <v>8.5518999999999998E-2</v>
       </c>
-      <c r="G12" s="2">
-        <f t="shared" si="2"/>
+      <c r="G12" s="182">
+        <f t="shared" si="3"/>
         <v>0.12721651911586365</v>
       </c>
       <c r="H12" s="10">
@@ -7401,40 +7564,48 @@
       <c r="I12">
         <v>2.2128999999999999</v>
       </c>
-      <c r="J12" t="s">
+      <c r="J12" s="155">
+        <f t="shared" si="1"/>
+        <v>0.12721651911586365</v>
+      </c>
+      <c r="K12" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="2:10" ht="35" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="65" t="s">
+    <row r="13" spans="2:11" ht="35" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="61" t="s">
         <v>56</v>
       </c>
-      <c r="C13" s="56" t="s">
+      <c r="C13" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="56">
+      <c r="D13" s="52">
         <v>2.2034099999999999</v>
       </c>
-      <c r="E13" s="55">
+      <c r="E13" s="51">
         <f t="shared" si="0"/>
         <v>7.1501067363163733</v>
       </c>
-      <c r="F13" s="56">
+      <c r="F13" s="52">
         <v>7.1556900000000007E-2</v>
       </c>
-      <c r="G13" s="2">
-        <f t="shared" si="2"/>
+      <c r="G13" s="182">
+        <f>E13*SQRT(POWER((E$23/D$23),2)+POWER((J13/D13),2))</f>
+        <v>1.2684673643870159</v>
+      </c>
+      <c r="H13" s="53">
+        <v>55.631799999999998</v>
+      </c>
+      <c r="I13" s="68">
+        <v>7.9474</v>
+      </c>
+      <c r="J13" s="155">
+        <f t="shared" si="1"/>
         <v>0.20172701105742313</v>
       </c>
-      <c r="H13" s="57">
-        <v>55.631799999999998</v>
-      </c>
-      <c r="I13" s="72">
-        <v>7.9474</v>
-      </c>
-    </row>
-    <row r="14" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="125" t="s">
+    </row>
+    <row r="14" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="118" t="s">
         <v>28</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -7443,16 +7614,16 @@
       <c r="D14" s="2">
         <v>0.38335200000000003</v>
       </c>
-      <c r="E14" s="38">
+      <c r="E14" s="35">
         <f t="shared" si="0"/>
         <v>1.2439844230444423</v>
       </c>
       <c r="F14" s="2">
         <v>9.3142699999999995E-2</v>
       </c>
-      <c r="G14" s="2">
-        <f t="shared" si="2"/>
-        <v>0.14131500430575206</v>
+      <c r="G14" s="182">
+        <f>E14*SQRT(POWER((E$23/D$23),2)+POWER((J14/D14),2))</f>
+        <v>0.49600336979921622</v>
       </c>
       <c r="H14" s="3">
         <v>13.811199999999999</v>
@@ -7460,28 +7631,32 @@
       <c r="I14">
         <v>2.30186</v>
       </c>
-      <c r="J14" t="s">
+      <c r="J14" s="155">
+        <f t="shared" si="1"/>
+        <v>0.14131500430575206</v>
+      </c>
+      <c r="K14" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="126"/>
+    <row r="15" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="119"/>
       <c r="C15" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="6">
         <v>1.15177</v>
       </c>
-      <c r="E15" s="37">
+      <c r="E15" s="34">
         <f t="shared" si="0"/>
         <v>3.7375152312493403</v>
       </c>
       <c r="F15" s="6">
         <v>0.117274</v>
       </c>
-      <c r="G15" s="2">
-        <f t="shared" si="2"/>
-        <v>0.1779267276442788</v>
+      <c r="G15" s="182">
+        <f t="shared" ref="G15:G20" si="4">E15*SQRT(POWER((E$23/D$23),2)+POWER((J15/D15),2))</f>
+        <v>0.80988843614557104</v>
       </c>
       <c r="H15" s="7">
         <v>13.811199999999999</v>
@@ -7489,132 +7664,169 @@
       <c r="I15">
         <v>2.30186</v>
       </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B16" s="46" t="s">
+      <c r="J15" s="155">
+        <f t="shared" si="1"/>
+        <v>0.1779267276442788</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="47" t="s">
+      <c r="C16" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="D16" s="47">
+      <c r="D16" s="43">
         <v>0</v>
       </c>
-      <c r="E16" s="48">
+      <c r="E16" s="44">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F16" s="47">
+      <c r="F16" s="43">
         <v>0.76793</v>
       </c>
-      <c r="G16" s="47"/>
-      <c r="H16" s="49">
+      <c r="G16" s="182"/>
+      <c r="H16" s="45">
         <v>8.1551799999999997</v>
       </c>
-      <c r="I16" s="47">
+      <c r="I16" s="43">
         <v>2.0387900000000001</v>
       </c>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="68" t="s">
+      <c r="J16" s="155">
+        <f t="shared" si="1"/>
+        <v>1.0964980949592529</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="64" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="47" t="s">
+      <c r="C17" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="47">
+      <c r="D17" s="43">
         <v>2.44</v>
       </c>
-      <c r="E17" s="48">
+      <c r="E17" s="44">
         <f t="shared" si="0"/>
         <v>7.9178457194130694</v>
       </c>
-      <c r="F17" s="47">
+      <c r="F17" s="43">
         <v>0.27806199999999998</v>
       </c>
-      <c r="G17" s="47"/>
-      <c r="H17" s="49">
+      <c r="G17" s="182">
+        <f t="shared" si="4"/>
+        <v>1.7628245835591634</v>
+      </c>
+      <c r="H17" s="45">
         <v>8.1551799999999997</v>
       </c>
-      <c r="I17" s="47">
+      <c r="I17" s="43">
         <v>2.0387900000000001</v>
       </c>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B18" s="68" t="s">
+      <c r="J17" s="155">
+        <f t="shared" si="1"/>
+        <v>0.39703417405305141</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="64" t="s">
+        <v>83</v>
+      </c>
+      <c r="C18" s="43" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="43">
+        <v>0</v>
+      </c>
+      <c r="E18" s="44">
+        <f t="shared" ref="E18:E19" si="5">D18*$D$23</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="43"/>
+      <c r="G18" s="182"/>
+      <c r="H18" s="45"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="155">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="64" t="s">
         <v>84</v>
       </c>
-      <c r="C18" s="47" t="s">
-        <v>10</v>
-      </c>
-      <c r="D18" s="47">
+      <c r="C19" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="D19" s="43">
+        <v>0.26</v>
+      </c>
+      <c r="E19" s="44">
+        <f t="shared" si="5"/>
+        <v>0.84370487174073694</v>
+      </c>
+      <c r="F19" s="43"/>
+      <c r="G19" s="182"/>
+      <c r="H19" s="45"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="155">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E18" s="48">
-        <f t="shared" ref="E18:E19" si="3">D18*$D$23</f>
-        <v>0</v>
-      </c>
-      <c r="F18" s="47"/>
-      <c r="G18" s="47"/>
-      <c r="H18" s="49"/>
-      <c r="I18" s="47"/>
-    </row>
-    <row r="19" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="68" t="s">
-        <v>85</v>
-      </c>
-      <c r="C19" s="47" t="s">
-        <v>83</v>
-      </c>
-      <c r="D19" s="47">
-        <v>0.26</v>
-      </c>
-      <c r="E19" s="48">
-        <f t="shared" si="3"/>
-        <v>0.84370487174073694</v>
-      </c>
-      <c r="F19" s="47"/>
-      <c r="G19" s="47"/>
-      <c r="H19" s="49"/>
-      <c r="I19" s="47"/>
-    </row>
-    <row r="20" spans="2:9" ht="35" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="69" t="s">
+    </row>
+    <row r="20" spans="2:10" ht="35" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="54" t="s">
+      <c r="C20" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="54">
+      <c r="D20" s="50">
         <v>0.80409799999999998</v>
       </c>
-      <c r="E20" s="70">
+      <c r="E20" s="66">
         <f>D20*$D$23</f>
         <v>2.6093130767576271</v>
       </c>
-      <c r="F20" s="54">
+      <c r="F20" s="50">
         <v>0.103809</v>
       </c>
-      <c r="G20" s="54"/>
-      <c r="H20" s="71">
+      <c r="G20" s="182">
+        <f t="shared" si="4"/>
+        <v>0.43080050069535031</v>
+      </c>
+      <c r="H20" s="67">
         <v>1.25024</v>
       </c>
-      <c r="I20" s="15">
+      <c r="I20" s="14">
         <v>0.25004900000000002</v>
       </c>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="J20" s="155">
+        <f t="shared" si="1"/>
+        <v>5.1909586391779013E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.2">
       <c r="D22" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="E22" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.2">
       <c r="D23">
         <f>'18O Option 1'!D5/D7</f>
         <v>3.2450187374643726</v>
       </c>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="E23">
+        <f>D23*SQRT(POWER(('18O Option 1'!F5/'18O Option 1'!D5),2)+POWER(('18F norm Option 1'!G7/'18F norm Option 1'!D7),2))</f>
+        <v>0.4931026033780847</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.2">
       <c r="D24" t="s">
         <v>63</v>
       </c>
@@ -7632,761 +7844,922 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{821ECE62-53CE-CB41-9599-014ED0A08C45}">
-  <dimension ref="B2:M39"/>
+  <dimension ref="B2:O39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="2:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D2" t="s">
+    <row r="2" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="132"/>
+      <c r="C2" s="132"/>
+      <c r="D2" s="132" t="s">
         <v>47</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="132" t="s">
         <v>54</v>
       </c>
-      <c r="F2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="F2" s="132" t="s">
+        <v>112</v>
+      </c>
+      <c r="G2" s="132" t="s">
+        <v>110</v>
+      </c>
+      <c r="H2" s="132" t="s">
         <v>1</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="132" t="s">
         <v>76</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="132" t="s">
         <v>32</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="132" t="s">
+        <v>104</v>
+      </c>
+      <c r="L2" s="132" t="s">
         <v>3</v>
       </c>
-      <c r="L2" t="s">
-        <v>0</v>
-      </c>
-      <c r="M2" t="s">
+      <c r="M2" s="132" t="s">
+        <v>105</v>
+      </c>
+      <c r="N2" s="132" t="s">
+        <v>106</v>
+      </c>
+      <c r="O2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="2:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="73" t="s">
+    <row r="3" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="69" t="s">
         <v>4</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D3" s="2">
-        <v>2.3270200000000001</v>
-      </c>
-      <c r="E3" s="38">
-        <f t="shared" ref="E3:E9" si="0">D3*$D$29</f>
-        <v>7.551223502454345</v>
+        <f>'18F norm Option 1'!D3</f>
+        <v>2.2913000000000001</v>
+      </c>
+      <c r="E3" s="35">
+        <f>'18F norm Option 1'!E3</f>
+        <v>7.4353114331521173</v>
       </c>
       <c r="F3" s="2">
         <v>0.32842500000000002</v>
       </c>
-      <c r="G3" s="142"/>
-      <c r="H3" s="3">
+      <c r="G3" s="136"/>
+      <c r="H3" s="2">
         <v>0.870116</v>
       </c>
-      <c r="M3" t="s">
+      <c r="I3" s="3"/>
+      <c r="J3" s="132"/>
+      <c r="K3" s="132"/>
+      <c r="L3" s="132"/>
+      <c r="M3" s="132"/>
+      <c r="N3" s="132"/>
+      <c r="O3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="2:13" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="130" t="s">
+    <row r="4" spans="2:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="124" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="58" t="s">
+      <c r="C4" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="58">
-        <f>J4*K4</f>
+      <c r="D4" s="54">
+        <f>J4*L4</f>
         <v>0.31518917999999996</v>
       </c>
-      <c r="E4" s="59">
-        <f t="shared" si="0"/>
+      <c r="E4" s="55">
+        <f t="shared" ref="E4:E7" si="0">D4*$D$29</f>
         <v>1.0227947949460308</v>
       </c>
-      <c r="F4" s="58">
-        <f>J4*L4</f>
-        <v>1.4414741999999999E-2</v>
-      </c>
-      <c r="G4" s="142">
-        <f>F4*SQRT(I4)</f>
-        <v>4.0392077359350714E-2</v>
-      </c>
-      <c r="H4" s="58">
+      <c r="F4" s="54"/>
+      <c r="G4" s="54">
+        <f>E4*SQRT(POWER(($E$29/$D$29),2)+POWER((N4/L4),2)+POWER((K4/J4),2))</f>
+        <v>0.28840956313475286</v>
+      </c>
+      <c r="H4" s="54">
         <v>86.371700000000004</v>
       </c>
-      <c r="I4" s="58">
+      <c r="I4" s="54">
         <v>7.8519699999999997</v>
       </c>
-      <c r="J4" s="58">
+      <c r="J4" s="54">
         <v>0.10199999999999999</v>
       </c>
-      <c r="K4" s="58">
+      <c r="K4" s="54">
+        <f>0.2*J4</f>
+        <v>2.0400000000000001E-2</v>
+      </c>
+      <c r="L4" s="54">
         <v>3.09009</v>
       </c>
-      <c r="L4" s="60">
+      <c r="M4" s="54">
         <v>0.141321</v>
       </c>
-    </row>
-    <row r="5" spans="2:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="132"/>
-      <c r="C5" s="30" t="s">
+      <c r="N4" s="56">
+        <f>M4*SQRT(I4)</f>
+        <v>0.39600075842500704</v>
+      </c>
+    </row>
+    <row r="5" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B5" s="126"/>
+      <c r="C5" s="161" t="s">
         <v>58</v>
       </c>
-      <c r="D5" s="30">
-        <f>J5*K5</f>
+      <c r="D5" s="161">
+        <f>J5*L5</f>
         <v>0.94556753999999998</v>
       </c>
-      <c r="E5" s="43">
+      <c r="E5" s="166">
         <f t="shared" si="0"/>
         <v>3.0683843848380925</v>
       </c>
-      <c r="F5" s="30">
-        <f t="shared" ref="F5:F7" si="1">J5*L5</f>
-        <v>4.3244225999999997E-2</v>
-      </c>
-      <c r="G5" s="142">
-        <f t="shared" ref="G5:G23" si="2">F5*SQRT(I5)</f>
-        <v>0.12117623207805214</v>
-      </c>
-      <c r="H5" s="30">
+      <c r="F5" s="161"/>
+      <c r="G5" s="161">
+        <f>E5*SQRT(POWER(($E$29/$D$29),2)+POWER((N5/L5),2)+POWER((K5/J5),2))</f>
+        <v>0.86522868940425868</v>
+      </c>
+      <c r="H5" s="161">
         <v>86.371700000000004</v>
       </c>
-      <c r="I5" s="58">
+      <c r="I5" s="161">
         <v>7.8519699999999997</v>
       </c>
-      <c r="J5" s="30">
+      <c r="J5" s="161">
         <v>0.30599999999999999</v>
       </c>
-      <c r="K5" s="30">
+      <c r="K5" s="161">
+        <f t="shared" ref="K5:K7" si="1">0.2*J5</f>
+        <v>6.1200000000000004E-2</v>
+      </c>
+      <c r="L5" s="161">
         <v>3.09009</v>
       </c>
-      <c r="L5" s="31">
+      <c r="M5" s="161">
         <v>0.141321</v>
       </c>
-    </row>
-    <row r="6" spans="2:13" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="66" t="s">
+      <c r="N5" s="28">
+        <f t="shared" ref="N5:N7" si="2">M5*SQRT(I5)</f>
+        <v>0.39600075842500704</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" ht="17" x14ac:dyDescent="0.2">
+      <c r="B6" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="161" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="30">
-        <f>J6*K6</f>
+      <c r="D6" s="161">
+        <f>J6*L6</f>
         <v>2.9664864</v>
       </c>
-      <c r="E6" s="43">
+      <c r="E6" s="166">
         <f t="shared" si="0"/>
         <v>9.626303952433231</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="161"/>
+      <c r="G6" s="161">
+        <f>E6*SQRT(POWER(($E$29/$D$29),2)+POWER((N6/L6),2)+POWER((K6/J6),2))</f>
+        <v>2.7144429471506153</v>
+      </c>
+      <c r="H6" s="161">
+        <v>86.371700000000004</v>
+      </c>
+      <c r="I6" s="161">
+        <v>7.8519699999999997</v>
+      </c>
+      <c r="J6" s="161">
+        <v>0.96</v>
+      </c>
+      <c r="K6" s="161">
         <f t="shared" si="1"/>
-        <v>0.13566816000000001</v>
-      </c>
-      <c r="G6" s="142">
+        <v>0.192</v>
+      </c>
+      <c r="L6" s="161">
+        <v>3.09009</v>
+      </c>
+      <c r="M6" s="161">
+        <v>0.141321</v>
+      </c>
+      <c r="N6" s="28">
         <f t="shared" si="2"/>
-        <v>0.38016072808800677</v>
-      </c>
-      <c r="H6" s="30">
-        <v>86.371700000000004</v>
-      </c>
-      <c r="I6" s="58">
-        <v>7.8519699999999997</v>
-      </c>
-      <c r="J6" s="30">
-        <v>0.96</v>
-      </c>
-      <c r="K6" s="30">
-        <v>3.09009</v>
-      </c>
-      <c r="L6" s="31">
-        <v>0.141321</v>
-      </c>
-    </row>
-    <row r="7" spans="2:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="63" t="s">
+        <v>0.39600075842500704</v>
+      </c>
+    </row>
+    <row r="7" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="33" t="s">
+      <c r="C7" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="33">
-        <f>J7*K7</f>
+      <c r="D7" s="30">
+        <f>J7*L7</f>
         <v>2.7501801000000001</v>
       </c>
-      <c r="E7" s="44">
+      <c r="E7" s="41">
         <f t="shared" si="0"/>
         <v>8.9243859559016432</v>
       </c>
-      <c r="F7" s="33">
+      <c r="F7" s="30"/>
+      <c r="G7" s="30">
+        <f>E7*SQRT(POWER(($E$29/$D$29),2)+POWER((N7/L7),2)+POWER((K7/J7),2))</f>
+        <v>2.5165148155875503</v>
+      </c>
+      <c r="H7" s="30">
+        <v>86.371700000000004</v>
+      </c>
+      <c r="I7" s="30">
+        <v>7.8519699999999997</v>
+      </c>
+      <c r="J7" s="30">
+        <v>0.89</v>
+      </c>
+      <c r="K7" s="30">
         <f t="shared" si="1"/>
-        <v>0.12577569</v>
-      </c>
-      <c r="G7" s="142">
+        <v>0.17800000000000002</v>
+      </c>
+      <c r="L7" s="30">
+        <v>3.09009</v>
+      </c>
+      <c r="M7" s="30">
+        <v>0.141321</v>
+      </c>
+      <c r="N7" s="31">
         <f t="shared" si="2"/>
-        <v>0.35244067499825621</v>
-      </c>
-      <c r="H7" s="33">
-        <v>86.371700000000004</v>
-      </c>
-      <c r="I7" s="58">
-        <v>7.8519699999999997</v>
-      </c>
-      <c r="J7" s="33">
-        <v>0.89</v>
-      </c>
-      <c r="K7" s="33">
-        <v>3.09009</v>
-      </c>
-      <c r="L7" s="34">
-        <v>0.141321</v>
-      </c>
-    </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B8" s="128" t="s">
+        <v>0.39600075842500704</v>
+      </c>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B8" s="118" t="s">
         <v>19</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="2">
         <f>'18F norm Option 1'!D6</f>
         <v>0.15563199999999999</v>
       </c>
-      <c r="E8" s="36">
+      <c r="E8" s="35">
         <f>'18F norm Option 1'!E6</f>
         <v>0.50502875614905518</v>
       </c>
-      <c r="F8" s="141">
+      <c r="F8" s="134">
         <f>'18F norm Option 1'!F6</f>
         <v>5.4237800000000003E-2</v>
       </c>
-      <c r="G8" s="143">
+      <c r="G8" s="169">
         <f>'18F norm Option 1'!G6</f>
         <v>9.4693203252016286E-2</v>
       </c>
-      <c r="H8" s="141">
+      <c r="H8" s="134">
         <f>'18F norm Option 1'!H6</f>
         <v>24.385100000000001</v>
       </c>
-      <c r="I8" s="141">
+      <c r="I8" s="170">
         <f>'18F norm Option 1'!I6</f>
         <v>3.04813</v>
       </c>
-      <c r="M8" t="s">
+      <c r="J8" s="132"/>
+      <c r="K8" s="132"/>
+      <c r="L8" s="132"/>
+      <c r="M8" s="132"/>
+      <c r="N8" s="132"/>
+      <c r="O8" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="2:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="126"/>
+    <row r="9" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="119"/>
       <c r="C9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="6">
         <f>'18F norm Option 1'!D7</f>
         <v>1.5156799999999999</v>
       </c>
-      <c r="E9" s="36">
+      <c r="E9" s="34">
         <f>'18F norm Option 1'!E7</f>
         <v>4.9184099999999997</v>
       </c>
-      <c r="F9" s="141">
+      <c r="F9" s="135">
         <f>'18F norm Option 1'!F7</f>
         <v>0.124664</v>
       </c>
-      <c r="G9" s="143">
+      <c r="G9" s="171">
         <f>'18F norm Option 1'!G7</f>
         <v>0.21764956340798039</v>
       </c>
-      <c r="H9" s="141">
+      <c r="H9" s="135">
         <f>'18F norm Option 1'!H7</f>
         <v>24.385100000000001</v>
       </c>
-      <c r="I9" s="141">
+      <c r="I9" s="172">
         <f>'18F norm Option 1'!I7</f>
         <v>3.04813</v>
       </c>
-    </row>
-    <row r="10" spans="2:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="131" t="s">
+      <c r="J9" s="132"/>
+      <c r="K9" s="132"/>
+      <c r="L9" s="132"/>
+      <c r="M9" s="132"/>
+      <c r="N9" s="132"/>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B10" s="125" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="17" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="2"/>
-      <c r="E10" s="38"/>
+      <c r="E10" s="35"/>
       <c r="F10" s="2"/>
-      <c r="G10" s="142">
-        <f t="shared" si="2"/>
+      <c r="G10" s="136">
+        <f t="shared" ref="G10:G23" si="3">F10*SQRT(I10)</f>
         <v>0</v>
       </c>
       <c r="H10" s="2"/>
-      <c r="M10" t="s">
+      <c r="I10" s="3"/>
+      <c r="J10" s="132"/>
+      <c r="K10" s="132"/>
+      <c r="L10" s="132"/>
+      <c r="M10" s="132"/>
+      <c r="N10" s="132"/>
+      <c r="O10" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="2:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="127"/>
-      <c r="C11" s="21" t="s">
+    <row r="11" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="121"/>
+      <c r="C11" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="36"/>
-      <c r="G11" s="142">
-        <f t="shared" si="2"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="173">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="2:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="125" t="s">
+      <c r="H11" s="6"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="132"/>
+      <c r="K11" s="132"/>
+      <c r="L11" s="132"/>
+      <c r="M11" s="132"/>
+      <c r="N11" s="132"/>
+    </row>
+    <row r="12" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="118" t="s">
         <v>23</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="2">
-        <v>0.36342999999999998</v>
-      </c>
-      <c r="E12" s="38">
-        <f t="shared" ref="E12:E21" si="3">D12*$D$29</f>
-        <v>1.1793371597566769</v>
+        <f>'18F norm Option 1'!D10</f>
+        <v>0.36027500000000001</v>
+      </c>
+      <c r="E12" s="35">
+        <f t="shared" ref="E12:E21" si="4">D12*$D$29</f>
+        <v>1.169099125639977</v>
       </c>
       <c r="F12" s="2">
-        <v>5.6393199999999997E-2</v>
-      </c>
-      <c r="G12" s="142">
-        <f t="shared" si="2"/>
-        <v>0.1020109188029327</v>
-      </c>
-      <c r="H12" s="3">
-        <v>21.1067</v>
-      </c>
-      <c r="I12">
-        <v>3.2722000000000002</v>
-      </c>
-      <c r="M12" t="s">
+        <f>'18F norm Option 1'!F10</f>
+        <v>6.9371299999999997E-2</v>
+      </c>
+      <c r="G12" s="2">
+        <f>'18F norm Option 1'!G10</f>
+        <v>0.10768338664574435</v>
+      </c>
+      <c r="H12" s="2">
+        <f>'18F norm Option 1'!H10</f>
+        <v>14.4574</v>
+      </c>
+      <c r="I12" s="2">
+        <f>'18F norm Option 1'!I10</f>
+        <v>2.4095599999999999</v>
+      </c>
+      <c r="J12" s="132"/>
+      <c r="K12" s="132"/>
+      <c r="L12" s="132"/>
+      <c r="M12" s="132"/>
+      <c r="N12" s="132"/>
+      <c r="O12" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="2:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="126"/>
+    <row r="13" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="119"/>
       <c r="C13" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D13" s="6">
-        <v>1.8707499999999999</v>
-      </c>
-      <c r="E13" s="37">
-        <f t="shared" si="3"/>
-        <v>6.0706188031114747</v>
-      </c>
-      <c r="F13" s="6">
-        <v>0.114702</v>
-      </c>
-      <c r="G13" s="142">
-        <f t="shared" si="2"/>
-        <v>0.20748700922334584</v>
-      </c>
-      <c r="H13" s="7">
-        <v>21.1067</v>
-      </c>
-      <c r="I13">
-        <v>3.2722000000000002</v>
-      </c>
-    </row>
-    <row r="14" spans="2:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+        <f>'18F norm Option 1'!D11</f>
+        <v>1.9050400000000001</v>
+      </c>
+      <c r="E13" s="34">
+        <f t="shared" si="4"/>
+        <v>6.181890495619129</v>
+      </c>
+      <c r="F13" s="2">
+        <f>'18F norm Option 1'!F11</f>
+        <v>0.117092</v>
+      </c>
+      <c r="G13" s="2">
+        <f>'18F norm Option 1'!G11</f>
+        <v>0.18175907196669946</v>
+      </c>
+      <c r="H13" s="2">
+        <f>'18F norm Option 1'!H11</f>
+        <v>14.4574</v>
+      </c>
+      <c r="I13" s="2">
+        <f>'18F norm Option 1'!I11</f>
+        <v>2.4095599999999999</v>
+      </c>
+      <c r="J13" s="132"/>
+      <c r="K13" s="132"/>
+      <c r="L13" s="132"/>
+      <c r="M13" s="132"/>
+      <c r="N13" s="132"/>
+    </row>
+    <row r="14" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D14" s="2">
-        <v>0.45706400000000003</v>
-      </c>
-      <c r="E14" s="38">
-        <f t="shared" si="3"/>
-        <v>1.4831812442204162</v>
+      <c r="D14" s="6">
+        <f>'18F norm Option 1'!D12</f>
+        <v>0.42468299999999998</v>
+      </c>
+      <c r="E14" s="35">
+        <f t="shared" si="4"/>
+        <v>1.3781042924825821</v>
       </c>
       <c r="F14" s="2">
-        <v>8.3333199999999996E-2</v>
-      </c>
-      <c r="G14" s="142">
-        <f t="shared" si="2"/>
-        <v>0.14544973958820406</v>
-      </c>
-      <c r="H14" s="3">
-        <v>15.232100000000001</v>
-      </c>
-      <c r="I14">
-        <v>3.0464199999999999</v>
-      </c>
-      <c r="M14" t="s">
+        <f>'18F norm Option 1'!F12</f>
+        <v>8.5518999999999998E-2</v>
+      </c>
+      <c r="G14" s="2">
+        <f>'18F norm Option 1'!G12</f>
+        <v>0.12721651911586365</v>
+      </c>
+      <c r="H14" s="2">
+        <f>'18F norm Option 1'!H12</f>
+        <v>11.064500000000001</v>
+      </c>
+      <c r="I14" s="2">
+        <f>'18F norm Option 1'!I12</f>
+        <v>2.2128999999999999</v>
+      </c>
+      <c r="J14" s="132"/>
+      <c r="K14" s="132"/>
+      <c r="L14" s="132"/>
+      <c r="M14" s="132"/>
+      <c r="N14" s="132"/>
+      <c r="O14" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="2:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="74" t="s">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B15" s="70" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="52" t="s">
+      <c r="C15" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="52">
-        <f>J15*K15</f>
+      <c r="D15" s="48">
+        <f>J15*L15</f>
         <v>2.1618688000000001</v>
       </c>
-      <c r="E15" s="61">
+      <c r="E15" s="57">
         <f>D15*$D$29</f>
         <v>7.0153047639396187</v>
       </c>
-      <c r="F15" s="52">
-        <f>J15*L15</f>
-        <v>7.0206448000000005E-2</v>
-      </c>
-      <c r="G15" s="142">
-        <f>F15*SQRT(I15)</f>
-        <v>0.19791993381488582</v>
-      </c>
-      <c r="H15" s="52">
+      <c r="F15" s="48"/>
+      <c r="G15" s="48">
+        <f>E15*SQRT(POWER(($E$29/$D$29),2)+POWER((N15/L15),2)+POWER((K15/J15),2))</f>
+        <v>1.875493381034588</v>
+      </c>
+      <c r="H15" s="48">
         <v>55.631799999999998</v>
       </c>
-      <c r="I15" s="52">
+      <c r="I15" s="48">
         <v>7.9474</v>
       </c>
-      <c r="J15" s="52">
+      <c r="J15" s="48">
         <v>1.04</v>
       </c>
-      <c r="K15" s="52">
+      <c r="K15" s="48">
+        <f>0.2*J15</f>
+        <v>0.20800000000000002</v>
+      </c>
+      <c r="L15" s="48">
         <v>2.0787200000000001</v>
       </c>
-      <c r="L15" s="75">
+      <c r="M15" s="48">
         <v>6.7506200000000002E-2</v>
       </c>
-      <c r="M15" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="16" spans="2:13" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="77" t="s">
+      <c r="N15" s="71">
+        <f>M15*SQRT(I15)</f>
+        <v>0.19030762866815942</v>
+      </c>
+      <c r="O15" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="73" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="78" t="s">
+      <c r="C16" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="D16" s="78">
-        <f>J16*K16</f>
+      <c r="D16" s="74">
+        <f>J16*L16</f>
         <v>0.37416959999999999</v>
       </c>
-      <c r="E16" s="79">
+      <c r="E16" s="75">
         <f>D16*$D$29</f>
         <v>1.2141873629895492</v>
       </c>
-      <c r="F16" s="78">
-        <f>J16*L16</f>
-        <v>1.2151116E-2</v>
-      </c>
-      <c r="G16" s="142">
-        <f t="shared" si="2"/>
-        <v>3.4255373160268693E-2</v>
-      </c>
-      <c r="H16" s="78">
+      <c r="F16" s="74"/>
+      <c r="G16" s="74">
+        <f>E16*SQRT(POWER(($E$29/$D$29),2)+POWER((N16/L16),2)+POWER((K16/J16),2))</f>
+        <v>0.32460462364060161</v>
+      </c>
+      <c r="H16" s="74">
         <v>55.631799999999998</v>
       </c>
-      <c r="I16" s="52">
+      <c r="I16" s="74">
         <v>7.9474</v>
       </c>
-      <c r="J16" s="78">
+      <c r="J16" s="74">
         <v>0.18</v>
       </c>
-      <c r="K16" s="78">
+      <c r="K16" s="74">
+        <f>0.2*J16</f>
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="L16" s="74">
         <v>2.0787200000000001</v>
       </c>
-      <c r="L16" s="80">
+      <c r="M16" s="74">
         <v>6.7506200000000002E-2</v>
       </c>
-    </row>
-    <row r="17" spans="2:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="128" t="s">
+      <c r="N16" s="76">
+        <f t="shared" ref="N16:N21" si="5">M16*SQRT(I16)</f>
+        <v>0.19030762866815942</v>
+      </c>
+    </row>
+    <row r="17" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="118" t="s">
         <v>28</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D17">
-        <v>0.43999500000000002</v>
-      </c>
-      <c r="E17" s="36">
-        <f t="shared" si="3"/>
-        <v>1.4277920193906368</v>
-      </c>
-      <c r="F17">
-        <v>7.8331999999999999E-2</v>
-      </c>
-      <c r="G17" s="142">
-        <f t="shared" si="2"/>
-        <v>0.13028121158114489</v>
-      </c>
-      <c r="H17" s="4">
-        <v>17.810700000000001</v>
-      </c>
-      <c r="I17">
-        <v>2.7662100000000001</v>
-      </c>
-      <c r="M17" t="s">
+      <c r="D17" s="2">
+        <f>'18F norm Option 1'!D14</f>
+        <v>0.38335200000000003</v>
+      </c>
+      <c r="E17" s="35">
+        <f>'18F norm Option 1'!E14</f>
+        <v>1.2439844230444423</v>
+      </c>
+      <c r="F17" s="2">
+        <f>'18F norm Option 1'!F14</f>
+        <v>9.3142699999999995E-2</v>
+      </c>
+      <c r="G17" s="2">
+        <f>'18F norm Option 1'!G14</f>
+        <v>0.49600336979921622</v>
+      </c>
+      <c r="H17" s="2">
+        <f>'18F norm Option 1'!H14</f>
+        <v>13.811199999999999</v>
+      </c>
+      <c r="I17" s="2">
+        <f>'18F norm Option 1'!I14</f>
+        <v>2.30186</v>
+      </c>
+      <c r="J17" s="132"/>
+      <c r="K17" s="132"/>
+      <c r="L17" s="132"/>
+      <c r="M17" s="132"/>
+      <c r="N17" s="153"/>
+      <c r="O17" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="2:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="128"/>
-      <c r="C18" t="s">
+    <row r="18" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="122"/>
+      <c r="C18" s="132" t="s">
         <v>11</v>
       </c>
-      <c r="D18">
-        <v>1.1331500000000001</v>
-      </c>
-      <c r="E18" s="36">
-        <f t="shared" si="3"/>
-        <v>3.6770929823577543</v>
-      </c>
-      <c r="F18">
-        <v>0.112195</v>
-      </c>
-      <c r="G18" s="142">
-        <f t="shared" si="2"/>
-        <v>0.18660190641559707</v>
-      </c>
-      <c r="H18" s="4">
-        <v>17.810700000000001</v>
-      </c>
-      <c r="I18">
-        <v>2.7662100000000001</v>
-      </c>
-    </row>
-    <row r="19" spans="2:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="85" t="s">
+      <c r="D18" s="2">
+        <f>'18F norm Option 1'!D15</f>
+        <v>1.15177</v>
+      </c>
+      <c r="E18" s="35">
+        <f>'18F norm Option 1'!E15</f>
+        <v>3.7375152312493403</v>
+      </c>
+      <c r="F18" s="2">
+        <f>'18F norm Option 1'!F15</f>
+        <v>0.117274</v>
+      </c>
+      <c r="G18" s="2">
+        <f>'18F norm Option 1'!G15</f>
+        <v>0.80988843614557104</v>
+      </c>
+      <c r="H18" s="2">
+        <f>'18F norm Option 1'!H15</f>
+        <v>13.811199999999999</v>
+      </c>
+      <c r="I18" s="2">
+        <f>'18F norm Option 1'!I15</f>
+        <v>2.30186</v>
+      </c>
+      <c r="J18" s="132"/>
+      <c r="K18" s="132"/>
+      <c r="L18" s="132"/>
+      <c r="M18" s="132"/>
+      <c r="N18" s="153"/>
+    </row>
+    <row r="19" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="81" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="62" t="s">
+      <c r="C19" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="D19" s="62">
+      <c r="D19" s="58">
         <f>0.2*1.42</f>
         <v>0.28399999999999997</v>
       </c>
-      <c r="E19" s="86">
-        <f t="shared" si="3"/>
+      <c r="E19" s="82">
+        <f t="shared" si="4"/>
         <v>0.9215853214398817</v>
       </c>
-      <c r="F19" s="62">
-        <v>0</v>
-      </c>
-      <c r="G19" s="142">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H19" s="62">
+      <c r="F19" s="58"/>
+      <c r="G19" s="58">
+        <f>E19*SQRT(POWER(($E$29/$D$29),2)+POWER((N19/L19),2)+POWER((K19/J19),2))</f>
+        <v>0.25725005957972208</v>
+      </c>
+      <c r="H19" s="58">
         <v>13.728</v>
       </c>
-      <c r="I19" s="62">
+      <c r="I19" s="58">
         <v>2.74559</v>
       </c>
-      <c r="J19" s="62">
+      <c r="J19" s="58">
         <v>0.16</v>
       </c>
-      <c r="K19" s="62">
+      <c r="K19" s="58">
+        <f>0.2*J19</f>
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="L19" s="58">
         <v>2.4052099999999998</v>
       </c>
-      <c r="L19" s="87">
+      <c r="M19" s="58">
         <v>0.17675399999999999</v>
       </c>
-      <c r="M19" t="s">
+      <c r="N19" s="83">
+        <f t="shared" si="5"/>
+        <v>0.29287823118587092</v>
+      </c>
+      <c r="O19" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="20" spans="2:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="88" t="s">
+    <row r="20" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="64" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C20" s="157" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="17">
+      <c r="D20" s="157">
         <f>0.75*1.42</f>
         <v>1.0649999999999999</v>
       </c>
-      <c r="E20" s="39">
+      <c r="E20" s="168">
         <f>D20*$D$29</f>
         <v>3.4559449553995565</v>
       </c>
-      <c r="F20" s="17">
-        <f>J20*L20*1.42</f>
-        <v>0.25350058679999998</v>
-      </c>
-      <c r="G20" s="142">
-        <f t="shared" si="2"/>
-        <v>0.42004595916677601</v>
-      </c>
-      <c r="H20" s="62">
+      <c r="F20" s="157"/>
+      <c r="G20" s="58">
+        <f t="shared" ref="G20:G21" si="6">E20*SQRT(POWER(($E$29/$D$29),2)+POWER((N20/L20),2)+POWER((K20/J20),2))</f>
+        <v>0.96468772342395792</v>
+      </c>
+      <c r="H20" s="157">
         <v>13.728</v>
       </c>
-      <c r="I20" s="62">
+      <c r="I20" s="157">
         <v>2.74559</v>
       </c>
-      <c r="J20" s="17">
+      <c r="J20" s="157">
         <v>1.01</v>
       </c>
-      <c r="K20" s="62">
+      <c r="K20" s="157">
+        <f t="shared" ref="K20:K21" si="7">0.2*J20</f>
+        <v>0.20200000000000001</v>
+      </c>
+      <c r="L20" s="157">
         <v>2.4052099999999998</v>
       </c>
-      <c r="L20" s="87">
+      <c r="M20" s="157">
         <v>0.17675399999999999</v>
       </c>
-    </row>
-    <row r="21" spans="2:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="88" t="s">
+      <c r="N20" s="45">
+        <f t="shared" si="5"/>
+        <v>0.29287823118587092</v>
+      </c>
+    </row>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B21" s="64" t="s">
+        <v>80</v>
+      </c>
+      <c r="C21" s="157" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="157">
+        <v>0</v>
+      </c>
+      <c r="E21" s="168">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F21" s="157"/>
+      <c r="G21" s="58">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H21" s="157">
+        <v>13.728</v>
+      </c>
+      <c r="I21" s="157">
+        <v>2.74559</v>
+      </c>
+      <c r="J21" s="157">
+        <v>0.35</v>
+      </c>
+      <c r="K21" s="157">
+        <f t="shared" si="7"/>
+        <v>6.9999999999999993E-2</v>
+      </c>
+      <c r="L21" s="157">
+        <v>2.4052099999999998</v>
+      </c>
+      <c r="M21" s="157">
+        <v>0.17675399999999999</v>
+      </c>
+      <c r="N21" s="45">
+        <f t="shared" si="5"/>
+        <v>0.29287823118587092</v>
+      </c>
+    </row>
+    <row r="22" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="84" t="s">
         <v>81</v>
       </c>
-      <c r="C21" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="D21" s="17">
-        <v>0</v>
-      </c>
-      <c r="E21" s="39">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F21" s="17">
-        <f>J21*L21</f>
-        <v>6.1863899999999993E-2</v>
-      </c>
-      <c r="G21" s="142">
-        <f t="shared" si="2"/>
-        <v>0.1025073809150548</v>
-      </c>
-      <c r="H21" s="62">
-        <v>13.728</v>
-      </c>
-      <c r="I21" s="62">
-        <v>2.74559</v>
-      </c>
-      <c r="J21" s="47">
-        <v>0.35</v>
-      </c>
-      <c r="K21" s="62">
-        <v>2.4052099999999998</v>
-      </c>
-      <c r="L21" s="87">
-        <v>0.17675399999999999</v>
-      </c>
-    </row>
-    <row r="22" spans="2:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="88" t="s">
+      <c r="C22" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="C22" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="D22" s="17">
+      <c r="D22" s="15">
         <v>0.03</v>
       </c>
-      <c r="E22" s="39"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="142"/>
-      <c r="H22" s="47"/>
-      <c r="I22" s="47"/>
-      <c r="J22" s="47"/>
-      <c r="K22" s="47"/>
-      <c r="L22" s="47"/>
-    </row>
-    <row r="23" spans="2:13" ht="35" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="81" t="s">
+      <c r="E22" s="36"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="15"/>
+      <c r="M22" s="15"/>
+      <c r="N22" s="16"/>
+    </row>
+    <row r="23" spans="2:15" ht="35" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="C23" s="82" t="s">
+      <c r="C23" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="D23" s="82">
+      <c r="D23" s="50">
+        <f>'18F norm Option 1'!D20</f>
         <v>0.80409799999999998</v>
       </c>
-      <c r="E23" s="83">
-        <f>D23*D29</f>
+      <c r="E23" s="66">
+        <f>'18F norm Option 1'!E20</f>
         <v>2.6093130767576271</v>
       </c>
-      <c r="F23" s="82">
+      <c r="F23" s="50">
+        <f>'18F norm Option 1'!F20</f>
         <v>0.103809</v>
       </c>
-      <c r="G23" s="142">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H23" s="84">
+      <c r="G23" s="50">
+        <f>'18F norm Option 1'!G20</f>
+        <v>0.43080050069535031</v>
+      </c>
+      <c r="H23" s="50">
+        <f>'18F norm Option 1'!H20</f>
         <v>1.25024</v>
       </c>
-      <c r="I23" s="15"/>
-      <c r="M23" t="s">
+      <c r="I23" s="50">
+        <f>'18F norm Option 1'!I20</f>
+        <v>0.25004900000000002</v>
+      </c>
+      <c r="J23" s="132"/>
+      <c r="K23" s="132"/>
+      <c r="L23" s="132"/>
+      <c r="M23" s="132"/>
+      <c r="N23" s="132"/>
+      <c r="O23" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="2:13" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="165" t="s">
-        <v>100</v>
-      </c>
-      <c r="C24" s="160" t="s">
-        <v>101</v>
-      </c>
-      <c r="D24" s="160"/>
-      <c r="E24" s="161"/>
-      <c r="F24" s="160"/>
-      <c r="G24" s="160"/>
-      <c r="H24" s="160"/>
-      <c r="I24" s="162"/>
-      <c r="J24" s="162"/>
-      <c r="K24" s="162"/>
-      <c r="L24" s="162"/>
-    </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B25" s="164"/>
-      <c r="C25" s="160" t="s">
-        <v>102</v>
-      </c>
-      <c r="D25" s="160">
-        <f>1.46*1.42</f>
-        <v>2.0731999999999999</v>
-      </c>
-      <c r="E25" s="161"/>
-      <c r="F25" s="160"/>
-      <c r="G25" s="160"/>
-      <c r="H25" s="160"/>
-      <c r="I25" s="162"/>
-      <c r="J25" s="162"/>
-      <c r="K25" s="162"/>
-      <c r="L25" s="162"/>
-    </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B26" s="163"/>
-      <c r="C26" s="160"/>
-      <c r="D26" s="160"/>
-      <c r="E26" s="161"/>
-      <c r="F26" s="160"/>
-      <c r="G26" s="160"/>
-      <c r="H26" s="160"/>
-      <c r="I26" s="162"/>
-    </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:15" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="174" t="s">
+        <v>96</v>
+      </c>
+      <c r="C24" s="136" t="s">
+        <v>97</v>
+      </c>
+      <c r="D24" s="136">
+        <v>0.6</v>
+      </c>
+      <c r="E24" s="136">
+        <f>D24*D29</f>
+        <v>1.9470112424786234</v>
+      </c>
+      <c r="F24" s="136"/>
+      <c r="G24" s="136"/>
+      <c r="H24" s="136"/>
+      <c r="I24" s="175"/>
+      <c r="J24" s="155"/>
+      <c r="K24" s="155"/>
+      <c r="L24" s="155"/>
+      <c r="M24" s="155"/>
+      <c r="N24" s="155"/>
+    </row>
+    <row r="25" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="176"/>
+      <c r="C25" s="173" t="s">
+        <v>98</v>
+      </c>
+      <c r="D25" s="173">
+        <f>1.47*1.42</f>
+        <v>2.0873999999999997</v>
+      </c>
+      <c r="E25" s="173">
+        <f>D25*D29</f>
+        <v>6.7736521125831306</v>
+      </c>
+      <c r="F25" s="173">
+        <v>0.16</v>
+      </c>
+      <c r="G25" s="173"/>
+      <c r="H25" s="173"/>
+      <c r="I25" s="177"/>
+      <c r="J25" s="155"/>
+      <c r="K25" s="155"/>
+      <c r="L25" s="155"/>
+      <c r="M25" s="155"/>
+      <c r="N25" s="155"/>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B26" s="156"/>
+      <c r="C26" s="153"/>
+      <c r="D26" s="153"/>
+      <c r="E26" s="154"/>
+      <c r="F26" s="153"/>
+      <c r="G26" s="153"/>
+      <c r="H26" s="153"/>
+      <c r="I26" s="155"/>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
         <v>45</v>
       </c>
       <c r="D28" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="E28" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B29">
         <v>3.6014013985414599</v>
       </c>
@@ -8394,8 +8767,12 @@
         <f>'18F norm Option 1'!D23</f>
         <v>3.2450187374643726</v>
       </c>
-    </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="E29">
+        <f>'18F norm Option 1'!E23</f>
+        <v>0.4931026033780847</v>
+      </c>
+    </row>
+    <row r="30" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
         <v>62</v>
       </c>
@@ -8405,7 +8782,7 @@
     </row>
     <row r="39" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E39" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -8456,7 +8833,7 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="73" t="s">
+      <c r="B3" s="69" t="s">
         <v>4</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -8465,7 +8842,7 @@
       <c r="D3" s="2">
         <v>2.3270200000000001</v>
       </c>
-      <c r="E3" s="38">
+      <c r="E3" s="35">
         <f t="shared" ref="E3:E27" si="0">D3*$D$31</f>
         <v>7.9657627397373192</v>
       </c>
@@ -8480,178 +8857,178 @@
       </c>
     </row>
     <row r="4" spans="2:12" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="130" t="s">
+      <c r="B4" s="124" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="58" t="s">
+      <c r="C4" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="58">
+      <c r="D4" s="54">
         <f>I4*J4</f>
         <v>0.53477599500000006</v>
       </c>
-      <c r="E4" s="59">
+      <c r="E4" s="55">
         <f t="shared" si="0"/>
         <v>1.8306240148674919</v>
       </c>
-      <c r="F4" s="58">
+      <c r="F4" s="54">
         <f>I4*K4</f>
         <v>2.4061307399999999E-2</v>
       </c>
-      <c r="G4" s="58">
+      <c r="G4" s="54">
         <v>158.19300000000001</v>
       </c>
-      <c r="H4" s="58">
+      <c r="H4" s="54">
         <v>14.3811</v>
       </c>
-      <c r="I4" s="58">
+      <c r="I4" s="54">
         <v>0.3211</v>
       </c>
-      <c r="J4" s="58">
+      <c r="J4" s="54">
         <v>1.6654500000000001</v>
       </c>
-      <c r="K4" s="60">
+      <c r="K4" s="56">
         <v>7.4934000000000001E-2</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="132"/>
-      <c r="C5" s="30" t="s">
+      <c r="B5" s="126"/>
+      <c r="C5" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="27">
         <f t="shared" ref="D5:D8" si="1">I5*J5</f>
         <v>4.8964230000000004E-2</v>
       </c>
-      <c r="E5" s="43">
+      <c r="E5" s="40">
         <f t="shared" si="0"/>
         <v>0.16761241369387811</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="27">
         <f t="shared" ref="F5:F8" si="2">I5*K5</f>
         <v>2.2030596E-3</v>
       </c>
-      <c r="G5" s="30">
+      <c r="G5" s="27">
         <v>158.19300000000001</v>
       </c>
-      <c r="H5" s="58">
+      <c r="H5" s="54">
         <v>14.3811</v>
       </c>
-      <c r="I5" s="30">
+      <c r="I5" s="27">
         <v>2.9399999999999999E-2</v>
       </c>
-      <c r="J5" s="30">
+      <c r="J5" s="27">
         <v>1.6654500000000001</v>
       </c>
-      <c r="K5" s="31">
+      <c r="K5" s="28">
         <v>7.4934000000000001E-2</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="132"/>
-      <c r="C6" s="30" t="s">
+      <c r="B6" s="126"/>
+      <c r="C6" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="27">
         <f t="shared" si="1"/>
         <v>0.43967880000000004</v>
       </c>
-      <c r="E6" s="43">
+      <c r="E6" s="40">
         <f t="shared" si="0"/>
         <v>1.5050910617409463</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="27">
         <f t="shared" si="2"/>
         <v>1.9782576E-2</v>
       </c>
-      <c r="G6" s="30">
+      <c r="G6" s="27">
         <v>158.19300000000001</v>
       </c>
-      <c r="H6" s="58">
+      <c r="H6" s="54">
         <v>14.3811</v>
       </c>
-      <c r="I6" s="30">
+      <c r="I6" s="27">
         <v>0.26400000000000001</v>
       </c>
-      <c r="J6" s="30">
+      <c r="J6" s="27">
         <v>1.6654500000000001</v>
       </c>
-      <c r="K6" s="31">
+      <c r="K6" s="28">
         <v>7.4934000000000001E-2</v>
       </c>
     </row>
     <row r="7" spans="2:12" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="66" t="s">
+      <c r="B7" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="30" t="s">
+      <c r="C7" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="27">
         <f t="shared" si="1"/>
         <v>1.2514191299999999</v>
       </c>
-      <c r="E7" s="43">
+      <c r="E7" s="40">
         <f t="shared" si="0"/>
         <v>4.2838084234551017</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="27">
         <f t="shared" si="2"/>
         <v>5.6305407599999996E-2</v>
       </c>
-      <c r="G7" s="30">
+      <c r="G7" s="27">
         <v>158.19300000000001</v>
       </c>
-      <c r="H7" s="58">
+      <c r="H7" s="54">
         <v>14.3811</v>
       </c>
-      <c r="I7" s="30">
+      <c r="I7" s="27">
         <v>0.75139999999999996</v>
       </c>
-      <c r="J7" s="30">
+      <c r="J7" s="27">
         <v>1.6654500000000001</v>
       </c>
-      <c r="K7" s="31">
+      <c r="K7" s="28">
         <v>7.4934000000000001E-2</v>
       </c>
     </row>
     <row r="8" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="63" t="s">
+      <c r="B8" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="33" t="s">
+      <c r="C8" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="33">
+      <c r="D8" s="30">
         <f t="shared" si="1"/>
         <v>1.6654500000000001</v>
       </c>
-      <c r="E8" s="44">
+      <c r="E8" s="41">
         <f t="shared" si="0"/>
         <v>5.701102506594494</v>
       </c>
-      <c r="F8" s="33">
+      <c r="F8" s="30">
         <f t="shared" si="2"/>
         <v>7.4934000000000001E-2</v>
       </c>
-      <c r="G8" s="33">
+      <c r="G8" s="30">
         <v>158.19300000000001</v>
       </c>
-      <c r="H8" s="58">
+      <c r="H8" s="54">
         <v>14.3811</v>
       </c>
-      <c r="I8" s="33">
+      <c r="I8" s="30">
         <v>1</v>
       </c>
-      <c r="J8" s="33">
+      <c r="J8" s="30">
         <v>1.6654500000000001</v>
       </c>
-      <c r="K8" s="34">
+      <c r="K8" s="31">
         <v>7.4934000000000001E-2</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B9" s="128" t="s">
+      <c r="B9" s="122" t="s">
         <v>19</v>
       </c>
       <c r="C9" t="s">
@@ -8660,7 +9037,7 @@
       <c r="D9">
         <v>0.17736399999999999</v>
       </c>
-      <c r="E9" s="36">
+      <c r="E9" s="33">
         <f t="shared" si="0"/>
         <v>0.60714542314667252</v>
       </c>
@@ -8678,14 +9055,14 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="128"/>
+      <c r="B10" s="122"/>
       <c r="C10" t="s">
         <v>11</v>
       </c>
       <c r="D10">
         <v>1.4557599999999999</v>
       </c>
-      <c r="E10" s="36">
+      <c r="E10" s="33">
         <f t="shared" si="0"/>
         <v>4.9832999999999998</v>
       </c>
@@ -8700,176 +9077,176 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="64" t="s">
+      <c r="B11" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="17">
         <f>I11*J11</f>
         <v>0.25210164000000002</v>
       </c>
-      <c r="E11" s="40">
+      <c r="E11" s="37">
         <f t="shared" si="0"/>
         <v>0.86298435361048531</v>
       </c>
-      <c r="F11" s="19">
+      <c r="F11" s="17">
         <f>I11*K11</f>
         <v>1.5407612999999999E-2</v>
       </c>
-      <c r="G11" s="19">
+      <c r="G11" s="17">
         <v>21.929400000000001</v>
       </c>
-      <c r="H11" s="19">
+      <c r="H11" s="17">
         <v>2.7411699999999999</v>
       </c>
-      <c r="I11" s="19">
+      <c r="I11" s="17">
         <v>8.6999999999999994E-2</v>
       </c>
-      <c r="J11" s="19">
+      <c r="J11" s="17">
         <v>2.8977200000000001</v>
       </c>
-      <c r="K11" s="20">
+      <c r="K11" s="18">
         <v>0.17709900000000001</v>
       </c>
     </row>
     <row r="12" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="90"/>
-      <c r="C12" s="21" t="s">
+      <c r="B12" s="86"/>
+      <c r="C12" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="D12" s="21">
+      <c r="D12" s="19">
         <f t="shared" ref="D12:D15" si="3">I12*J12</f>
         <v>0.28600496399999997</v>
       </c>
-      <c r="E12" s="41">
+      <c r="E12" s="38">
         <f t="shared" si="0"/>
         <v>0.97904087013051588</v>
       </c>
-      <c r="F12" s="21">
+      <c r="F12" s="19">
         <f t="shared" ref="F12:F15" si="4">I12*K12</f>
         <v>1.7479671299999999E-2</v>
       </c>
-      <c r="G12" s="21">
+      <c r="G12" s="19">
         <v>21.929400000000001</v>
       </c>
-      <c r="H12" s="19">
+      <c r="H12" s="17">
         <v>2.7411699999999999</v>
       </c>
-      <c r="I12" s="21">
+      <c r="I12" s="19">
         <v>9.8699999999999996E-2</v>
       </c>
-      <c r="J12" s="21">
+      <c r="J12" s="19">
         <v>2.8977200000000001</v>
       </c>
-      <c r="K12" s="22">
+      <c r="K12" s="20">
         <v>0.17709900000000001</v>
       </c>
     </row>
     <row r="13" spans="2:12" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="89" t="s">
+      <c r="B13" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="21">
+      <c r="D13" s="19">
         <f t="shared" si="3"/>
         <v>0.97247483200000007</v>
       </c>
-      <c r="E13" s="41">
+      <c r="E13" s="38">
         <f t="shared" si="0"/>
         <v>3.328937345651481</v>
       </c>
-      <c r="F13" s="21">
+      <c r="F13" s="19">
         <f t="shared" si="4"/>
         <v>5.9434424400000005E-2</v>
       </c>
-      <c r="G13" s="21">
+      <c r="G13" s="19">
         <v>21.929400000000001</v>
       </c>
-      <c r="H13" s="19">
+      <c r="H13" s="17">
         <v>2.7411699999999999</v>
       </c>
-      <c r="I13" s="21">
+      <c r="I13" s="19">
         <v>0.33560000000000001</v>
       </c>
-      <c r="J13" s="21">
+      <c r="J13" s="19">
         <v>2.8977200000000001</v>
       </c>
-      <c r="K13" s="22">
+      <c r="K13" s="20">
         <v>0.17709900000000001</v>
       </c>
     </row>
     <row r="14" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="89"/>
-      <c r="C14" s="21" t="s">
+      <c r="B14" s="85"/>
+      <c r="C14" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="21">
+      <c r="D14" s="19">
         <f t="shared" si="3"/>
         <v>0.20370971600000001</v>
       </c>
-      <c r="E14" s="41">
+      <c r="E14" s="38">
         <f t="shared" si="0"/>
         <v>0.69733103515881745</v>
       </c>
-      <c r="F14" s="21">
+      <c r="F14" s="19">
         <f t="shared" si="4"/>
         <v>1.24500597E-2</v>
       </c>
-      <c r="G14" s="21">
+      <c r="G14" s="19">
         <v>21.929400000000001</v>
       </c>
-      <c r="H14" s="19">
+      <c r="H14" s="17">
         <v>2.7411699999999999</v>
       </c>
-      <c r="I14" s="21">
+      <c r="I14" s="19">
         <v>7.0300000000000001E-2</v>
       </c>
-      <c r="J14" s="21">
+      <c r="J14" s="19">
         <v>2.8977200000000001</v>
       </c>
-      <c r="K14" s="22">
+      <c r="K14" s="20">
         <v>0.17709900000000001</v>
       </c>
     </row>
     <row r="15" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="23"/>
-      <c r="C15" s="24" t="s">
+      <c r="B15" s="21"/>
+      <c r="C15" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="24">
+      <c r="D15" s="22">
         <f t="shared" si="3"/>
         <v>2.7528339999999998E-2</v>
       </c>
-      <c r="E15" s="42">
+      <c r="E15" s="39">
         <f t="shared" si="0"/>
         <v>9.423392367011045E-2</v>
       </c>
-      <c r="F15" s="24">
+      <c r="F15" s="22">
         <f t="shared" si="4"/>
         <v>1.6824405000000001E-3</v>
       </c>
-      <c r="G15" s="24">
+      <c r="G15" s="22">
         <v>21.929400000000001</v>
       </c>
-      <c r="H15" s="19">
+      <c r="H15" s="17">
         <v>2.7411699999999999</v>
       </c>
-      <c r="I15" s="24">
+      <c r="I15" s="22">
         <v>9.4999999999999998E-3</v>
       </c>
-      <c r="J15" s="24">
+      <c r="J15" s="22">
         <v>2.8977200000000001</v>
       </c>
-      <c r="K15" s="25">
+      <c r="K15" s="23">
         <v>0.17709900000000001</v>
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B16" s="128" t="s">
+      <c r="B16" s="122" t="s">
         <v>23</v>
       </c>
       <c r="C16" t="s">
@@ -8878,7 +9255,7 @@
       <c r="D16">
         <v>0.36342999999999998</v>
       </c>
-      <c r="E16" s="36">
+      <c r="E16" s="33">
         <f t="shared" si="0"/>
         <v>1.244079188190361</v>
       </c>
@@ -8896,14 +9273,14 @@
       </c>
     </row>
     <row r="17" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="126"/>
+      <c r="B17" s="119"/>
       <c r="C17" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D17" s="6">
         <v>1.8707499999999999</v>
       </c>
-      <c r="E17" s="37">
+      <c r="E17" s="34">
         <f t="shared" si="0"/>
         <v>6.4038773389844472</v>
       </c>
@@ -8927,7 +9304,7 @@
       <c r="D18" s="2">
         <v>0.45706400000000003</v>
       </c>
-      <c r="E18" s="38">
+      <c r="E18" s="35">
         <f t="shared" si="0"/>
         <v>1.5646033901192504</v>
       </c>
@@ -8945,110 +9322,110 @@
       </c>
     </row>
     <row r="19" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="74" t="s">
+      <c r="B19" s="70" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="52" t="s">
+      <c r="C19" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="D19" s="52">
+      <c r="D19" s="48">
         <f>I19*J19</f>
         <v>8.0849340000000006E-2</v>
       </c>
-      <c r="E19" s="61">
+      <c r="E19" s="57">
         <f t="shared" si="0"/>
         <v>0.27676025994806835</v>
       </c>
-      <c r="F19" s="52">
+      <c r="F19" s="48">
         <f>I19*K19</f>
         <v>2.4430000000000003E-3</v>
       </c>
-      <c r="G19" s="52">
+      <c r="G19" s="48">
         <v>58.458599999999997</v>
       </c>
-      <c r="H19" s="52">
+      <c r="H19" s="48">
         <v>8.3512299999999993</v>
       </c>
-      <c r="I19" s="52">
+      <c r="I19" s="48">
         <v>3.49E-2</v>
       </c>
-      <c r="J19" s="52">
+      <c r="J19" s="48">
         <v>2.3166000000000002</v>
       </c>
-      <c r="K19" s="75">
+      <c r="K19" s="71">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="20" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="91"/>
-      <c r="C20" s="72" t="s">
+      <c r="B20" s="87"/>
+      <c r="C20" s="68" t="s">
         <v>12</v>
       </c>
-      <c r="D20" s="72">
+      <c r="D20" s="68">
         <f t="shared" ref="D20:D21" si="5">I20*J20</f>
         <v>2.1407700600000004</v>
       </c>
-      <c r="E20" s="76">
+      <c r="E20" s="72">
         <f t="shared" si="0"/>
         <v>7.3281993185676217</v>
       </c>
-      <c r="F20" s="72">
+      <c r="F20" s="68">
         <f t="shared" ref="F20:F21" si="6">I20*K20</f>
         <v>6.4687000000000008E-2</v>
       </c>
-      <c r="G20" s="72">
+      <c r="G20" s="68">
         <v>58.458599999999997</v>
       </c>
-      <c r="H20" s="52">
+      <c r="H20" s="48">
         <v>8.3512299999999993</v>
       </c>
-      <c r="I20" s="72">
+      <c r="I20" s="68">
         <v>0.92410000000000003</v>
       </c>
-      <c r="J20" s="72">
+      <c r="J20" s="68">
         <v>2.3166000000000002</v>
       </c>
-      <c r="K20" s="92">
+      <c r="K20" s="88">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="21" spans="2:12" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="77" t="s">
+      <c r="B21" s="73" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="78" t="s">
+      <c r="C21" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="D21" s="78">
+      <c r="D21" s="74">
         <f t="shared" si="5"/>
         <v>0.41559804000000006</v>
       </c>
-      <c r="E21" s="79">
+      <c r="E21" s="75">
         <f t="shared" si="0"/>
         <v>1.4226587574407872</v>
       </c>
-      <c r="F21" s="78">
+      <c r="F21" s="74">
         <f t="shared" si="6"/>
         <v>1.2558000000000001E-2</v>
       </c>
-      <c r="G21" s="78">
+      <c r="G21" s="74">
         <v>58.458599999999997</v>
       </c>
-      <c r="H21" s="52">
+      <c r="H21" s="48">
         <v>8.3512299999999993</v>
       </c>
-      <c r="I21" s="78">
+      <c r="I21" s="74">
         <v>0.1794</v>
       </c>
-      <c r="J21" s="78">
+      <c r="J21" s="74">
         <v>2.3166000000000002</v>
       </c>
-      <c r="K21" s="80">
+      <c r="K21" s="76">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B22" s="128" t="s">
+      <c r="B22" s="122" t="s">
         <v>28</v>
       </c>
       <c r="C22" t="s">
@@ -9057,7 +9434,7 @@
       <c r="D22">
         <v>0.43999500000000002</v>
       </c>
-      <c r="E22" s="36">
+      <c r="E22" s="33">
         <f t="shared" si="0"/>
         <v>1.5061734650629226</v>
       </c>
@@ -9075,14 +9452,14 @@
       </c>
     </row>
     <row r="23" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="128"/>
+      <c r="B23" s="122"/>
       <c r="C23" t="s">
         <v>11</v>
       </c>
       <c r="D23">
         <v>1.1331500000000001</v>
       </c>
-      <c r="E23" s="36">
+      <c r="E23" s="33">
         <f t="shared" si="0"/>
         <v>3.8789542197889766</v>
       </c>
@@ -9097,162 +9474,162 @@
       </c>
     </row>
     <row r="24" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="85" t="s">
+      <c r="B24" s="81" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="62" t="s">
+      <c r="C24" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="D24" s="62">
+      <c r="D24" s="58">
         <f>I24*J24</f>
         <v>0.38584674400000002</v>
       </c>
-      <c r="E24" s="86">
+      <c r="E24" s="82">
         <f t="shared" si="0"/>
         <v>1.3208152987959554</v>
       </c>
-      <c r="F24" s="62">
+      <c r="F24" s="58">
         <f>I24*K24</f>
         <v>2.8167167999999999E-2</v>
       </c>
-      <c r="G24" s="62">
+      <c r="G24" s="58">
         <v>11.266400000000001</v>
       </c>
-      <c r="H24" s="62">
+      <c r="H24" s="58">
         <v>2.2532800000000002</v>
       </c>
-      <c r="I24" s="62">
+      <c r="I24" s="58">
         <v>6.9199999999999998E-2</v>
       </c>
-      <c r="J24" s="86">
+      <c r="J24" s="82">
         <v>5.5758200000000002</v>
       </c>
-      <c r="K24" s="87">
+      <c r="K24" s="83">
         <v>0.40704000000000001</v>
       </c>
     </row>
     <row r="25" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="46"/>
-      <c r="C25" s="47" t="s">
+      <c r="B25" s="42"/>
+      <c r="C25" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="D25" s="47">
+      <c r="D25" s="43">
         <f t="shared" ref="D25:D27" si="7">I25*J25</f>
         <v>2.9496087800000002</v>
       </c>
-      <c r="E25" s="48">
+      <c r="E25" s="44">
         <f t="shared" si="0"/>
         <v>10.096984003801451</v>
       </c>
-      <c r="F25" s="47">
+      <c r="F25" s="43">
         <f t="shared" ref="F25:F27" si="8">I25*K25</f>
         <v>0.21532416000000001</v>
       </c>
-      <c r="G25" s="47">
+      <c r="G25" s="43">
         <v>11.266400000000001</v>
       </c>
-      <c r="H25" s="62">
+      <c r="H25" s="58">
         <v>2.2532800000000002</v>
       </c>
-      <c r="I25" s="47">
+      <c r="I25" s="43">
         <v>0.52900000000000003</v>
       </c>
-      <c r="J25" s="48">
+      <c r="J25" s="44">
         <v>5.5758200000000002</v>
       </c>
-      <c r="K25" s="49">
+      <c r="K25" s="45">
         <v>0.40704000000000001</v>
       </c>
     </row>
     <row r="26" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="46"/>
-      <c r="C26" s="47" t="s">
+      <c r="B26" s="42"/>
+      <c r="C26" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="D26" s="47">
+      <c r="D26" s="43">
         <f t="shared" si="7"/>
         <v>2.0630534000000002E-2</v>
       </c>
-      <c r="E26" s="48">
+      <c r="E26" s="44">
         <f t="shared" si="0"/>
         <v>7.0621627247760624E-2</v>
       </c>
-      <c r="F26" s="47">
+      <c r="F26" s="43">
         <f t="shared" si="8"/>
         <v>1.5060480000000001E-3</v>
       </c>
-      <c r="G26" s="47">
+      <c r="G26" s="43">
         <v>11.266400000000001</v>
       </c>
-      <c r="H26" s="62">
+      <c r="H26" s="58">
         <v>2.2532800000000002</v>
       </c>
-      <c r="I26" s="47">
+      <c r="I26" s="43">
         <v>3.7000000000000002E-3</v>
       </c>
-      <c r="J26" s="48">
+      <c r="J26" s="44">
         <v>5.5758200000000002</v>
       </c>
-      <c r="K26" s="49">
+      <c r="K26" s="45">
         <v>0.40704000000000001</v>
       </c>
     </row>
     <row r="27" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="88" t="s">
+      <c r="B27" s="84" t="s">
         <v>30</v>
       </c>
-      <c r="C27" s="17" t="s">
+      <c r="C27" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="D27" s="17">
+      <c r="D27" s="15">
         <f t="shared" si="7"/>
         <v>1.6727459999999999E-3</v>
       </c>
-      <c r="E27" s="39">
+      <c r="E27" s="36">
         <f t="shared" si="0"/>
         <v>5.7260778849535631E-3</v>
       </c>
-      <c r="F27" s="17">
+      <c r="F27" s="15">
         <f t="shared" si="8"/>
         <v>1.2211199999999999E-4</v>
       </c>
-      <c r="G27" s="17">
+      <c r="G27" s="15">
         <v>11.266400000000001</v>
       </c>
-      <c r="H27" s="62">
+      <c r="H27" s="58">
         <v>2.2532800000000002</v>
       </c>
-      <c r="I27" s="17">
+      <c r="I27" s="15">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="J27" s="39">
+      <c r="J27" s="36">
         <v>5.5758200000000002</v>
       </c>
-      <c r="K27" s="18">
+      <c r="K27" s="16">
         <v>0.40704000000000001</v>
       </c>
     </row>
     <row r="28" spans="2:12" ht="35" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="81" t="s">
+      <c r="B28" s="77" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="82" t="s">
+      <c r="C28" s="78" t="s">
         <v>13</v>
       </c>
-      <c r="D28" s="82">
+      <c r="D28" s="78">
         <v>0.80409799999999998</v>
       </c>
-      <c r="E28" s="83">
+      <c r="E28" s="79">
         <f>D28*D31</f>
         <v>2.7525564402099247</v>
       </c>
-      <c r="F28" s="82">
+      <c r="F28" s="78">
         <v>0.103809</v>
       </c>
-      <c r="G28" s="84">
+      <c r="G28" s="80">
         <v>1.25024</v>
       </c>
-      <c r="H28" s="62"/>
+      <c r="H28" s="58"/>
       <c r="L28" t="s">
         <v>48</v>
       </c>
@@ -9283,7 +9660,7 @@
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B34" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -9299,7 +9676,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E379A37-1643-1048-AB5D-38CA5C6FAEF5}">
-  <dimension ref="A1:Y71"/>
+  <dimension ref="A1:Y56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="7" max="8" width="15.33203125" customWidth="1"/>
@@ -9326,7 +9703,7 @@
         <v>69</v>
       </c>
       <c r="K2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="N2" t="s">
         <v>67</v>
@@ -9338,16 +9715,16 @@
         <v>69</v>
       </c>
       <c r="R2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="S2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="T2" t="s">
         <v>2</v>
       </c>
       <c r="V2" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.2">
@@ -9355,7 +9732,7 @@
         <v>74</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E3" t="s">
         <v>75</v>
@@ -9364,7 +9741,7 @@
         <v>72</v>
       </c>
       <c r="H3" t="s">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="I3" t="s">
         <v>71</v>
@@ -9373,31 +9750,31 @@
         <v>72</v>
       </c>
       <c r="O3" t="s">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="P3" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="L4" s="105"/>
-      <c r="M4" s="96" t="s">
+      <c r="L4" s="101"/>
+      <c r="M4" s="92" t="s">
         <v>20</v>
       </c>
-      <c r="N4" s="96">
+      <c r="N4" s="92">
         <f>'18F norm Option 2 lit'!E3</f>
-        <v>7.551223502454345</v>
-      </c>
-      <c r="O4" s="96">
+        <v>7.4353114331521173</v>
+      </c>
+      <c r="O4" s="92">
         <f>'18F norm Option 2 lit'!F3</f>
         <v>0.32842500000000002</v>
       </c>
-      <c r="P4" s="96">
+      <c r="P4" s="92">
         <v>0.18529999999999999</v>
       </c>
-      <c r="Q4" s="97">
+      <c r="Q4" s="93">
         <f>N4*$P$12/$N$12</f>
-        <v>0.88156793254512855</v>
+        <v>0.86803577272247467</v>
       </c>
       <c r="R4">
         <f>O4*$P$12/$N$12</f>
@@ -9405,92 +9782,92 @@
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A5" s="112" t="s">
+      <c r="A5" s="108" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="110" t="s">
+      <c r="B5" s="106" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="110">
+      <c r="C5" s="106">
         <v>1.22</v>
       </c>
-      <c r="D5" s="110">
+      <c r="D5" s="106">
         <f>0.15*C5</f>
         <v>0.183</v>
       </c>
-      <c r="E5" s="110">
+      <c r="E5" s="106">
         <f>$G$12/$C$12*C5</f>
         <v>7.2294701204819276</v>
       </c>
-      <c r="F5" s="110">
+      <c r="F5" s="106">
         <f>0.15*E5</f>
         <v>1.084420518072289</v>
       </c>
-      <c r="G5" s="113">
+      <c r="G5" s="109">
         <f>'18O Option 2 lit'!D3</f>
         <v>6.1960600000000001</v>
       </c>
-      <c r="H5" s="113">
+      <c r="H5" s="109">
         <f>'18O Option 2 lit'!F3</f>
         <v>0.84551640881286871</v>
       </c>
-      <c r="I5" s="113">
+      <c r="I5" s="109">
         <v>1.5448</v>
       </c>
-      <c r="J5" s="114">
+      <c r="J5" s="110">
         <f>G5*$I$12/$G$12</f>
         <v>1.5478780585595753</v>
       </c>
-      <c r="K5" s="117">
+      <c r="K5" s="113">
         <f>H5*$I$12/$G$12</f>
         <v>0.21122395479603609</v>
       </c>
-      <c r="L5" s="104" t="s">
+      <c r="L5" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="M5" s="102" t="s">
+      <c r="M5" s="98" t="s">
         <v>5</v>
       </c>
-      <c r="N5" s="102"/>
-      <c r="O5" s="102"/>
-      <c r="P5" s="102">
+      <c r="N5" s="98"/>
+      <c r="O5" s="98"/>
+      <c r="P5" s="98">
         <v>0.31640000000000001</v>
       </c>
-      <c r="Q5" s="103"/>
+      <c r="Q5" s="99"/>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="D6" s="110"/>
-      <c r="E6" s="110"/>
-      <c r="F6" s="110"/>
-      <c r="G6" s="94"/>
-      <c r="H6" s="94"/>
-      <c r="I6" s="94"/>
-      <c r="J6" s="94"/>
-      <c r="K6" s="117"/>
-      <c r="L6" s="135" t="s">
+      <c r="D6" s="106"/>
+      <c r="E6" s="106"/>
+      <c r="F6" s="106"/>
+      <c r="G6" s="90"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
+      <c r="J6" s="90"/>
+      <c r="K6" s="113"/>
+      <c r="L6" s="129" t="s">
         <v>15</v>
       </c>
-      <c r="M6" s="96" t="s">
+      <c r="M6" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="N6" s="96">
+      <c r="N6" s="92">
         <f>'18F norm Option 2 lit'!E4</f>
         <v>1.0227947949460308</v>
       </c>
-      <c r="O6" s="96">
+      <c r="O6" s="92">
         <f>'18F norm Option 2 lit'!G4</f>
-        <v>4.0392077359350714E-2</v>
-      </c>
-      <c r="P6" s="96">
+        <v>0.28840956313475286</v>
+      </c>
+      <c r="P6" s="92">
         <v>0.3211</v>
       </c>
-      <c r="Q6" s="97">
+      <c r="Q6" s="93">
         <f t="shared" ref="Q6:Q39" si="0">N6*$P$12/$N$12</f>
         <v>0.11940622503166896</v>
       </c>
       <c r="R6">
         <f t="shared" ref="R6:R36" si="1">O6*$P$12/$N$12</f>
-        <v>4.7155749154176212E-3</v>
+        <v>3.3670387615504831E-2</v>
       </c>
       <c r="S6">
         <v>0.10199999999999999</v>
@@ -9501,29 +9878,29 @@
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="D7" s="110"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="110"/>
-      <c r="G7" s="94"/>
-      <c r="H7" s="94"/>
-      <c r="I7" s="94"/>
-      <c r="J7" s="94"/>
-      <c r="K7" s="117"/>
-      <c r="L7" s="136"/>
+      <c r="D7" s="106"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="106"/>
+      <c r="G7" s="90"/>
+      <c r="H7" s="90"/>
+      <c r="I7" s="90"/>
+      <c r="J7" s="90"/>
+      <c r="K7" s="113"/>
+      <c r="L7" s="130"/>
       <c r="M7" t="s">
         <v>60</v>
       </c>
-      <c r="O7" s="96">
+      <c r="O7" s="92">
         <f>'18F norm Option 2 lit'!G5</f>
-        <v>0.12117623207805214</v>
+        <v>0.86522868940425868</v>
       </c>
       <c r="P7">
         <v>2.9399999999999999E-2</v>
       </c>
-      <c r="Q7" s="99"/>
+      <c r="Q7" s="95"/>
       <c r="R7">
         <f t="shared" si="1"/>
-        <v>1.4146724746252863E-2</v>
+        <v>0.1010111628465145</v>
       </c>
       <c r="T7">
         <f t="shared" ref="T7:T11" si="2">$N$12/$S$12*S7</f>
@@ -9531,15 +9908,15 @@
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="D8" s="110"/>
-      <c r="E8" s="110"/>
-      <c r="F8" s="110"/>
-      <c r="G8" s="94"/>
-      <c r="H8" s="94"/>
-      <c r="I8" s="94"/>
-      <c r="J8" s="94"/>
-      <c r="K8" s="117"/>
-      <c r="L8" s="136"/>
+      <c r="D8" s="106"/>
+      <c r="E8" s="106"/>
+      <c r="F8" s="106"/>
+      <c r="G8" s="90"/>
+      <c r="H8" s="90"/>
+      <c r="I8" s="90"/>
+      <c r="J8" s="90"/>
+      <c r="K8" s="113"/>
+      <c r="L8" s="130"/>
       <c r="M8" t="s">
         <v>58</v>
       </c>
@@ -9549,18 +9926,18 @@
       </c>
       <c r="O8">
         <f>'18F norm Option 2 lit'!G5</f>
-        <v>0.12117623207805214</v>
+        <v>0.86522868940425868</v>
       </c>
       <c r="P8">
         <v>0.26400000000000001</v>
       </c>
-      <c r="Q8" s="99">
+      <c r="Q8" s="95">
         <f t="shared" si="0"/>
         <v>0.35821867509500693</v>
       </c>
       <c r="R8">
         <f t="shared" si="1"/>
-        <v>1.4146724746252863E-2</v>
+        <v>0.1010111628465145</v>
       </c>
       <c r="S8">
         <v>0.30599999999999999</v>
@@ -9571,15 +9948,15 @@
       </c>
     </row>
     <row r="9" spans="1:25" ht="17" x14ac:dyDescent="0.2">
-      <c r="D9" s="110"/>
-      <c r="E9" s="110"/>
-      <c r="F9" s="110"/>
-      <c r="G9" s="94"/>
-      <c r="H9" s="94"/>
-      <c r="I9" s="94"/>
-      <c r="J9" s="94"/>
-      <c r="K9" s="117"/>
-      <c r="L9" s="100" t="s">
+      <c r="D9" s="106"/>
+      <c r="E9" s="106"/>
+      <c r="F9" s="106"/>
+      <c r="G9" s="90"/>
+      <c r="H9" s="90"/>
+      <c r="I9" s="90"/>
+      <c r="J9" s="90"/>
+      <c r="K9" s="113"/>
+      <c r="L9" s="96" t="s">
         <v>16</v>
       </c>
       <c r="M9" t="s">
@@ -9591,18 +9968,18 @@
       </c>
       <c r="O9">
         <f>'18F norm Option 2 lit'!G6</f>
-        <v>0.38016072808800677</v>
+        <v>2.7144429471506153</v>
       </c>
       <c r="P9">
         <v>0.75139999999999996</v>
       </c>
-      <c r="Q9" s="99">
+      <c r="Q9" s="95">
         <f t="shared" si="0"/>
         <v>1.1238232944157081</v>
       </c>
       <c r="R9">
         <f t="shared" si="1"/>
-        <v>4.4381881556871734E-2</v>
+        <v>0.31689776579298662</v>
       </c>
       <c r="S9">
         <v>0.96</v>
@@ -9611,40 +9988,44 @@
         <f t="shared" si="2"/>
         <v>7.6156025806451613</v>
       </c>
+      <c r="V9">
+        <f>(G5-N9)/SQRT(H5*H5+O9*O9)</f>
+        <v>-1.2065242951441306</v>
+      </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="D10" s="110"/>
-      <c r="E10" s="110"/>
-      <c r="F10" s="110"/>
-      <c r="G10" s="94"/>
-      <c r="H10" s="94"/>
-      <c r="I10" s="94"/>
-      <c r="J10" s="94"/>
-      <c r="K10" s="117"/>
-      <c r="L10" s="104" t="s">
+      <c r="D10" s="106"/>
+      <c r="E10" s="106"/>
+      <c r="F10" s="106"/>
+      <c r="G10" s="90"/>
+      <c r="H10" s="90"/>
+      <c r="I10" s="90"/>
+      <c r="J10" s="90"/>
+      <c r="K10" s="113"/>
+      <c r="L10" s="100" t="s">
         <v>17</v>
       </c>
-      <c r="M10" s="102" t="s">
+      <c r="M10" s="98" t="s">
         <v>9</v>
       </c>
-      <c r="N10" s="102">
+      <c r="N10" s="98">
         <f>'18F norm Option 2 lit'!E7</f>
         <v>8.9243859559016432</v>
       </c>
       <c r="O10">
-        <f>'18F norm Option 2 lit'!F7</f>
-        <v>0.12577569</v>
-      </c>
-      <c r="P10" s="102">
+        <f>'18F norm Option 2 lit'!G7</f>
+        <v>2.5165148155875503</v>
+      </c>
+      <c r="P10" s="98">
         <v>1</v>
       </c>
-      <c r="Q10" s="103">
+      <c r="Q10" s="99">
         <f t="shared" si="0"/>
         <v>1.0418778458645628</v>
       </c>
       <c r="R10">
         <f t="shared" si="1"/>
-        <v>1.468368867133891E-2</v>
+        <v>0.29379063703724811</v>
       </c>
       <c r="S10">
         <v>0.89</v>
@@ -9655,64 +10036,64 @@
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A11" s="133" t="s">
+      <c r="A11" s="127" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="96" t="s">
+      <c r="B11" s="92" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="96">
+      <c r="C11" s="92">
         <v>0.21</v>
       </c>
-      <c r="D11" s="110">
+      <c r="D11" s="106">
         <f t="shared" ref="D11:D32" si="3">0.15*C11</f>
         <v>3.15E-2</v>
       </c>
-      <c r="E11" s="110">
+      <c r="E11" s="106">
         <f>$G$12/$C$12*C11</f>
         <v>1.2444169879518072</v>
       </c>
-      <c r="F11" s="110">
+      <c r="F11" s="106">
         <f t="shared" ref="F11:F32" si="4">0.15*E11</f>
         <v>0.18666254819277109</v>
       </c>
-      <c r="G11" s="115">
+      <c r="G11" s="111">
         <f>'18O Option 2 lit'!D4</f>
         <v>0.74325399999999997</v>
       </c>
-      <c r="H11" s="115">
+      <c r="H11" s="111">
         <f>'18O Option 2 lit'!F4</f>
         <v>0.10717148336994237</v>
       </c>
-      <c r="I11" s="115">
+      <c r="I11" s="111">
         <v>0.32819999999999999</v>
       </c>
-      <c r="J11" s="116">
+      <c r="J11" s="112">
         <f>G11*$I$12/$G$12</f>
         <v>0.18567711715778065</v>
       </c>
-      <c r="K11" s="117">
+      <c r="K11" s="113">
         <f t="shared" ref="K11:K39" si="5">H11*$I$12/$G$12</f>
         <v>2.6773205490524008E-2</v>
       </c>
-      <c r="L11" s="133" t="s">
+      <c r="L11" s="127" t="s">
         <v>19</v>
       </c>
-      <c r="M11" s="96" t="s">
+      <c r="M11" s="92" t="s">
         <v>10</v>
       </c>
-      <c r="N11" s="96">
+      <c r="N11" s="92">
         <f>'18F norm Option 2 lit'!E8</f>
         <v>0.50502875614905518</v>
       </c>
-      <c r="O11" s="96">
+      <c r="O11" s="92">
         <f>'18F norm Option 2 lit'!G8</f>
         <v>9.4693203252016286E-2</v>
       </c>
-      <c r="P11" s="96">
+      <c r="P11" s="92">
         <v>0.14710000000000001</v>
       </c>
-      <c r="Q11" s="97">
+      <c r="Q11" s="93">
         <f t="shared" si="0"/>
         <v>5.8959605193708443E-2</v>
       </c>
@@ -9733,60 +10114,60 @@
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A12" s="137"/>
-      <c r="B12" s="102" t="s">
+      <c r="A12" s="131"/>
+      <c r="B12" s="98" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="102">
+      <c r="C12" s="98">
         <v>0.83</v>
       </c>
-      <c r="D12" s="110">
+      <c r="D12" s="106">
         <f t="shared" si="3"/>
         <v>0.12449999999999999</v>
       </c>
-      <c r="E12" s="110">
+      <c r="E12" s="106">
         <f>$G$12/$C$12*C12</f>
         <v>4.9184099999999997</v>
       </c>
-      <c r="F12" s="110">
+      <c r="F12" s="106">
         <f t="shared" si="4"/>
         <v>0.73776149999999996</v>
       </c>
-      <c r="G12" s="117">
+      <c r="G12" s="113">
         <f>'18O Option 2 lit'!D5</f>
         <v>4.9184099999999997</v>
       </c>
-      <c r="H12" s="115">
+      <c r="H12" s="111">
         <f>'18O Option 2 lit'!F5</f>
         <v>0.24445529131853752</v>
       </c>
-      <c r="I12" s="117">
+      <c r="I12" s="113">
         <v>1.2286999999999999</v>
       </c>
-      <c r="J12" s="118">
+      <c r="J12" s="114">
         <f>G12*$I$12/$G$12</f>
         <v>1.2286999999999999</v>
       </c>
-      <c r="K12" s="117">
+      <c r="K12" s="113">
         <f t="shared" si="5"/>
         <v>6.1068966687016141E-2</v>
       </c>
-      <c r="L12" s="137"/>
-      <c r="M12" s="102" t="s">
+      <c r="L12" s="131"/>
+      <c r="M12" s="98" t="s">
         <v>11</v>
       </c>
-      <c r="N12" s="102">
+      <c r="N12" s="98">
         <f>'18F norm Option 2 lit'!E9</f>
         <v>4.9184099999999997</v>
       </c>
-      <c r="O12" s="96">
+      <c r="O12" s="92">
         <f>'18F norm Option 2 lit'!G9</f>
         <v>0.21764956340798039</v>
       </c>
-      <c r="P12" s="102">
+      <c r="P12" s="98">
         <v>0.57420000000000004</v>
       </c>
-      <c r="Q12" s="103">
+      <c r="Q12" s="99">
         <f t="shared" si="0"/>
         <v>0.57420000000000004</v>
       </c>
@@ -9807,58 +10188,58 @@
       </c>
     </row>
     <row r="13" spans="1:25" ht="17" x14ac:dyDescent="0.2">
-      <c r="D13" s="110"/>
-      <c r="E13" s="110"/>
-      <c r="F13" s="110"/>
-      <c r="G13" s="94"/>
-      <c r="H13" s="94"/>
-      <c r="I13" s="94"/>
-      <c r="J13" s="94"/>
-      <c r="K13" s="117"/>
-      <c r="L13" s="95" t="s">
+      <c r="D13" s="106"/>
+      <c r="E13" s="106"/>
+      <c r="F13" s="106"/>
+      <c r="G13" s="90"/>
+      <c r="H13" s="90"/>
+      <c r="I13" s="90"/>
+      <c r="J13" s="90"/>
+      <c r="K13" s="113"/>
+      <c r="L13" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="M13" s="96" t="s">
+      <c r="M13" s="92" t="s">
         <v>20</v>
       </c>
-      <c r="N13" s="96"/>
-      <c r="O13" s="96"/>
-      <c r="P13" s="96">
+      <c r="N13" s="92"/>
+      <c r="O13" s="92"/>
+      <c r="P13" s="92">
         <v>8.6999999999999994E-2</v>
       </c>
-      <c r="Q13" s="97"/>
+      <c r="Q13" s="93"/>
       <c r="Y13" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="D14" s="110"/>
-      <c r="E14" s="110"/>
-      <c r="F14" s="110"/>
-      <c r="G14" s="94"/>
-      <c r="H14" s="94"/>
-      <c r="I14" s="94"/>
-      <c r="J14" s="94"/>
-      <c r="K14" s="117"/>
-      <c r="L14" s="98"/>
+      <c r="D14" s="106"/>
+      <c r="E14" s="106"/>
+      <c r="F14" s="106"/>
+      <c r="G14" s="90"/>
+      <c r="H14" s="90"/>
+      <c r="I14" s="90"/>
+      <c r="J14" s="90"/>
+      <c r="K14" s="113"/>
+      <c r="L14" s="94"/>
       <c r="M14" t="s">
         <v>5</v>
       </c>
       <c r="P14">
         <v>9.8699999999999996E-2</v>
       </c>
-      <c r="Q14" s="99"/>
+      <c r="Q14" s="95"/>
     </row>
     <row r="15" spans="1:25" ht="17" x14ac:dyDescent="0.2">
-      <c r="D15" s="110"/>
-      <c r="E15" s="110"/>
-      <c r="F15" s="110"/>
-      <c r="G15" s="94"/>
-      <c r="H15" s="94"/>
-      <c r="I15" s="94"/>
-      <c r="J15" s="94"/>
-      <c r="K15" s="117"/>
-      <c r="L15" s="100" t="s">
+      <c r="D15" s="106"/>
+      <c r="E15" s="106"/>
+      <c r="F15" s="106"/>
+      <c r="G15" s="90"/>
+      <c r="H15" s="90"/>
+      <c r="I15" s="90"/>
+      <c r="J15" s="90"/>
+      <c r="K15" s="113"/>
+      <c r="L15" s="96" t="s">
         <v>22</v>
       </c>
       <c r="M15" t="s">
@@ -9875,7 +10256,7 @@
       <c r="P15">
         <v>0.33560000000000001</v>
       </c>
-      <c r="Q15" s="99">
+      <c r="Q15" s="95">
         <f t="shared" si="0"/>
         <v>0.26346077153488867</v>
       </c>
@@ -9885,48 +10266,48 @@
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="D16" s="110"/>
-      <c r="E16" s="110"/>
-      <c r="F16" s="110"/>
-      <c r="G16" s="94"/>
-      <c r="H16" s="94"/>
-      <c r="I16" s="94"/>
-      <c r="J16" s="94"/>
-      <c r="K16" s="117"/>
-      <c r="L16" s="100"/>
+      <c r="D16" s="106"/>
+      <c r="E16" s="106"/>
+      <c r="F16" s="106"/>
+      <c r="G16" s="90"/>
+      <c r="H16" s="90"/>
+      <c r="I16" s="90"/>
+      <c r="J16" s="90"/>
+      <c r="K16" s="113"/>
+      <c r="L16" s="96"/>
       <c r="M16" t="s">
         <v>18</v>
       </c>
       <c r="P16">
         <v>7.0300000000000001E-2</v>
       </c>
-      <c r="Q16" s="99"/>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="D17" s="110"/>
-      <c r="E17" s="110"/>
-      <c r="F17" s="110"/>
-      <c r="G17" s="94"/>
-      <c r="H17" s="94"/>
-      <c r="I17" s="94"/>
-      <c r="J17" s="94"/>
-      <c r="K17" s="117"/>
-      <c r="L17" s="101"/>
-      <c r="M17" s="102" t="s">
+      <c r="Q16" s="95"/>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="D17" s="106"/>
+      <c r="E17" s="106"/>
+      <c r="F17" s="106"/>
+      <c r="G17" s="90"/>
+      <c r="H17" s="90"/>
+      <c r="I17" s="90"/>
+      <c r="J17" s="90"/>
+      <c r="K17" s="113"/>
+      <c r="L17" s="97"/>
+      <c r="M17" s="98" t="s">
         <v>11</v>
       </c>
-      <c r="N17" s="102">
+      <c r="N17" s="98">
         <f>'18F norm Option 1'!E9</f>
         <v>4.4950648555103978</v>
       </c>
-      <c r="O17" s="102">
+      <c r="O17" s="98">
         <f>'18F norm Option 1'!F9</f>
         <v>0.206014</v>
       </c>
-      <c r="P17" s="102">
+      <c r="P17" s="98">
         <v>9.4999999999999998E-3</v>
       </c>
-      <c r="Q17" s="103">
+      <c r="Q17" s="99">
         <f t="shared" si="0"/>
         <v>0.52477655177873961</v>
       </c>
@@ -9935,39 +10316,39 @@
         <v>2.4051113835568814E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="D18" s="110"/>
-      <c r="E18" s="110"/>
-      <c r="F18" s="110"/>
-      <c r="G18" s="94"/>
-      <c r="H18" s="94"/>
-      <c r="I18" s="94"/>
-      <c r="J18" s="94"/>
-      <c r="K18" s="117"/>
-      <c r="L18" s="133" t="s">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="D18" s="106"/>
+      <c r="E18" s="106"/>
+      <c r="F18" s="106"/>
+      <c r="G18" s="90"/>
+      <c r="H18" s="90"/>
+      <c r="I18" s="90"/>
+      <c r="J18" s="90"/>
+      <c r="K18" s="113"/>
+      <c r="L18" s="127" t="s">
         <v>23</v>
       </c>
-      <c r="M18" s="96" t="s">
+      <c r="M18" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="N18" s="96">
+      <c r="N18" s="92">
         <f>'18F norm Option 2 lit'!E12</f>
-        <v>1.1793371597566769</v>
-      </c>
-      <c r="O18" s="96">
+        <v>1.169099125639977</v>
+      </c>
+      <c r="O18" s="92">
         <f>'18F norm Option 2 lit'!F12</f>
-        <v>5.6393199999999997E-2</v>
-      </c>
-      <c r="P18" s="96">
+        <v>6.9371299999999997E-2</v>
+      </c>
+      <c r="P18" s="92">
         <v>0.13789999999999999</v>
       </c>
-      <c r="Q18" s="97">
+      <c r="Q18" s="93">
         <f t="shared" si="0"/>
-        <v>0.13768177055842923</v>
+        <v>0.13648653079805767</v>
       </c>
       <c r="R18">
         <f t="shared" si="1"/>
-        <v>6.5836267086314482E-3</v>
+        <v>8.0987555856465825E-3</v>
       </c>
       <c r="S18">
         <v>0.17</v>
@@ -9977,55 +10358,55 @@
         <v>1.3485962903225808</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="D19" s="110"/>
-      <c r="E19" s="110"/>
-      <c r="F19" s="110"/>
-      <c r="G19" s="94"/>
-      <c r="H19" s="94"/>
-      <c r="I19" s="94"/>
-      <c r="J19" s="94"/>
-      <c r="K19" s="117"/>
-      <c r="L19" s="134"/>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="D19" s="106"/>
+      <c r="E19" s="106"/>
+      <c r="F19" s="106"/>
+      <c r="G19" s="90"/>
+      <c r="H19" s="90"/>
+      <c r="I19" s="90"/>
+      <c r="J19" s="90"/>
+      <c r="K19" s="113"/>
+      <c r="L19" s="128"/>
       <c r="M19" t="s">
         <v>14</v>
       </c>
       <c r="P19">
         <v>1.44E-2</v>
       </c>
-      <c r="Q19" s="99"/>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="D20" s="110"/>
-      <c r="E20" s="110"/>
-      <c r="F20" s="110"/>
-      <c r="G20" s="94"/>
-      <c r="H20" s="94"/>
-      <c r="I20" s="94"/>
-      <c r="J20" s="94"/>
-      <c r="K20" s="117"/>
-      <c r="L20" s="137"/>
-      <c r="M20" s="102" t="s">
+      <c r="Q19" s="95"/>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="D20" s="106"/>
+      <c r="E20" s="106"/>
+      <c r="F20" s="106"/>
+      <c r="G20" s="90"/>
+      <c r="H20" s="90"/>
+      <c r="I20" s="90"/>
+      <c r="J20" s="90"/>
+      <c r="K20" s="113"/>
+      <c r="L20" s="131"/>
+      <c r="M20" s="98" t="s">
         <v>6</v>
       </c>
-      <c r="N20" s="102">
+      <c r="N20" s="98">
         <f>'18F norm Option 2 lit'!E13</f>
-        <v>6.0706188031114747</v>
-      </c>
-      <c r="O20" s="102">
+        <v>6.181890495619129</v>
+      </c>
+      <c r="O20" s="98">
         <f>'18F norm Option 2 lit'!F13</f>
-        <v>0.114702</v>
-      </c>
-      <c r="P20" s="102">
+        <v>0.117092</v>
+      </c>
+      <c r="P20" s="98">
         <v>0.65269999999999995</v>
       </c>
-      <c r="Q20" s="103">
+      <c r="Q20" s="99">
         <f t="shared" si="0"/>
-        <v>0.70871466932334015</v>
+        <v>0.72170508814525514</v>
       </c>
       <c r="R20">
         <f t="shared" si="1"/>
-        <v>1.3390890226719611E-2</v>
+        <v>1.3669910885835057E-2</v>
       </c>
       <c r="S20">
         <v>0.68</v>
@@ -10035,59 +10416,59 @@
         <v>5.3943851612903231</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="D21" s="110"/>
-      <c r="E21" s="110"/>
-      <c r="F21" s="110"/>
-      <c r="G21" s="94"/>
-      <c r="H21" s="94"/>
-      <c r="I21" s="94"/>
-      <c r="J21" s="94"/>
-      <c r="K21" s="117"/>
-      <c r="L21" s="106"/>
-      <c r="M21" s="96" t="s">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="D21" s="106"/>
+      <c r="E21" s="106"/>
+      <c r="F21" s="106"/>
+      <c r="G21" s="90"/>
+      <c r="H21" s="90"/>
+      <c r="I21" s="90"/>
+      <c r="J21" s="90"/>
+      <c r="K21" s="113"/>
+      <c r="L21" s="102"/>
+      <c r="M21" s="92" t="s">
         <v>20</v>
       </c>
-      <c r="N21" s="96"/>
-      <c r="O21" s="96"/>
-      <c r="P21" s="96">
+      <c r="N21" s="92"/>
+      <c r="O21" s="92"/>
+      <c r="P21" s="92">
         <v>0.1908</v>
       </c>
-      <c r="Q21" s="97"/>
-    </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="D22" s="110"/>
-      <c r="E22" s="110"/>
-      <c r="F22" s="110"/>
-      <c r="G22" s="94"/>
-      <c r="H22" s="94"/>
-      <c r="I22" s="94"/>
-      <c r="J22" s="94"/>
-      <c r="K22" s="117"/>
-      <c r="L22" s="101" t="s">
+      <c r="Q21" s="93"/>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="D22" s="106"/>
+      <c r="E22" s="106"/>
+      <c r="F22" s="106"/>
+      <c r="G22" s="90"/>
+      <c r="H22" s="90"/>
+      <c r="I22" s="90"/>
+      <c r="J22" s="90"/>
+      <c r="K22" s="113"/>
+      <c r="L22" s="97" t="s">
         <v>24</v>
       </c>
-      <c r="M22" s="102" t="s">
+      <c r="M22" s="98" t="s">
         <v>5</v>
       </c>
-      <c r="N22" s="102">
+      <c r="N22" s="98">
         <f>'18F norm Option 2 lit'!E14</f>
-        <v>1.4831812442204162</v>
-      </c>
-      <c r="O22" s="102">
+        <v>1.3781042924825821</v>
+      </c>
+      <c r="O22" s="98">
         <f>'18F norm Option 2 lit'!F14</f>
-        <v>8.3333199999999996E-2</v>
-      </c>
-      <c r="P22" s="102">
+        <v>8.5518999999999998E-2</v>
+      </c>
+      <c r="P22" s="98">
         <v>0.186</v>
       </c>
-      <c r="Q22" s="103">
+      <c r="Q22" s="99">
         <f t="shared" si="0"/>
-        <v>0.17315406207114964</v>
+        <v>0.16088684854322816</v>
       </c>
       <c r="R22">
         <f t="shared" si="1"/>
-        <v>9.7287382385771032E-3</v>
+        <v>9.9839195593697978E-3</v>
       </c>
       <c r="S22">
         <v>7.3999999999999996E-2</v>
@@ -10097,70 +10478,70 @@
         <v>0.58703603225806444</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="D23" s="110"/>
-      <c r="E23" s="110"/>
-      <c r="F23" s="110"/>
-      <c r="G23" s="94"/>
-      <c r="H23" s="94"/>
-      <c r="I23" s="94"/>
-      <c r="J23" s="94"/>
-      <c r="K23" s="117"/>
-      <c r="L23" s="106" t="s">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="D23" s="106"/>
+      <c r="E23" s="106"/>
+      <c r="F23" s="106"/>
+      <c r="G23" s="90"/>
+      <c r="H23" s="90"/>
+      <c r="I23" s="90"/>
+      <c r="J23" s="90"/>
+      <c r="K23" s="113"/>
+      <c r="L23" s="102" t="s">
         <v>25</v>
       </c>
-      <c r="M23" s="96" t="s">
+      <c r="M23" s="92" t="s">
         <v>26</v>
       </c>
-      <c r="N23" s="96"/>
-      <c r="O23" s="96"/>
-      <c r="P23" s="96">
+      <c r="N23" s="92"/>
+      <c r="O23" s="92"/>
+      <c r="P23" s="92">
         <v>3.49E-2</v>
       </c>
-      <c r="Q23" s="97"/>
-    </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A24" s="106" t="s">
+      <c r="Q23" s="93"/>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A24" s="102" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="96" t="s">
+      <c r="B24" s="92" t="s">
         <v>12</v>
       </c>
-      <c r="C24" s="96">
+      <c r="C24" s="92">
         <v>1.57</v>
       </c>
-      <c r="D24" s="110">
+      <c r="D24" s="106">
         <f t="shared" si="3"/>
         <v>0.23549999999999999</v>
       </c>
-      <c r="E24" s="110">
+      <c r="E24" s="106">
         <f>$G$12/$C$12*C24</f>
         <v>9.3034984337349407</v>
       </c>
-      <c r="F24" s="110">
+      <c r="F24" s="106">
         <f t="shared" si="4"/>
         <v>1.3955247650602411</v>
       </c>
-      <c r="G24" s="115">
+      <c r="G24" s="111">
         <f>'18O Option 2 lit'!D6</f>
         <v>8.2684207000000001</v>
       </c>
-      <c r="H24" s="115">
+      <c r="H24" s="111">
         <f>'18O Option 2 lit'!F6</f>
-        <v>0.45770639083204728</v>
-      </c>
-      <c r="I24" s="115">
+        <v>1.3220240957837115</v>
+      </c>
+      <c r="I24" s="111">
         <v>1.8597999999999999</v>
       </c>
-      <c r="J24" s="116">
+      <c r="J24" s="112">
         <f>G24*$I$12/$G$12</f>
         <v>2.0655879672678772</v>
       </c>
-      <c r="K24" s="117">
+      <c r="K24" s="113">
         <f t="shared" si="5"/>
-        <v>0.1143426112128384</v>
-      </c>
-      <c r="L24" s="107"/>
+        <v>0.33026344011366399</v>
+      </c>
+      <c r="L24" s="103"/>
       <c r="M24" t="s">
         <v>12</v>
       </c>
@@ -10170,18 +10551,18 @@
       </c>
       <c r="O24">
         <f>'18F norm Option 2 lit'!G15</f>
-        <v>0.19791993381488582</v>
+        <v>1.875493381034588</v>
       </c>
       <c r="P24">
         <v>0.92410000000000003</v>
       </c>
-      <c r="Q24" s="99">
+      <c r="Q24" s="95">
         <f t="shared" si="0"/>
         <v>0.81900207494985777</v>
       </c>
       <c r="R24">
         <f t="shared" si="1"/>
-        <v>2.3106171709253082E-2</v>
+        <v>0.21895456039453004</v>
       </c>
       <c r="S24">
         <v>1.04</v>
@@ -10192,74 +10573,72 @@
       </c>
       <c r="V24">
         <f t="shared" ref="V24:V31" si="6">(G24-N24)/SQRT(H24*H24+O24*O24)</f>
-        <v>2.5129381000389164</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22" ht="17" x14ac:dyDescent="0.2">
-      <c r="A25" s="104" t="s">
+        <v>0.54611343737150353</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" ht="17" x14ac:dyDescent="0.2">
+      <c r="A25" s="100" t="s">
         <v>35</v>
       </c>
-      <c r="B25" s="102" t="s">
+      <c r="B25" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="102">
+      <c r="C25" s="98">
         <v>0.28000000000000003</v>
       </c>
-      <c r="D25" s="110">
+      <c r="D25" s="106">
         <f t="shared" si="3"/>
         <v>4.2000000000000003E-2</v>
       </c>
-      <c r="E25" s="110">
+      <c r="E25" s="106">
         <f>$G$12/$C$12*C25</f>
         <v>1.6592226506024099</v>
       </c>
-      <c r="F25" s="110">
+      <c r="F25" s="106">
         <f t="shared" si="4"/>
         <v>0.24888339759036149</v>
       </c>
-      <c r="G25" s="117">
+      <c r="G25" s="113">
         <f>'18O Option 2 lit'!D7</f>
         <v>1.4746228000000001</v>
       </c>
-      <c r="H25" s="115">
+      <c r="H25" s="111">
         <f>'18O Option 2 lit'!F7</f>
-        <v>8.1629165243932017E-2</v>
-      </c>
-      <c r="I25" s="117">
-        <v>0.32469999999999999</v>
-      </c>
-      <c r="J25" s="118">
+        <v>0.23577499797416512</v>
+      </c>
+      <c r="I25" s="113"/>
+      <c r="J25" s="114">
         <f>G25*$I$12/$G$12</f>
         <v>0.36838511518153222</v>
       </c>
-      <c r="K25" s="117">
+      <c r="K25" s="113">
         <f t="shared" si="5"/>
-        <v>2.0392312827767361E-2</v>
-      </c>
-      <c r="L25" s="108" t="s">
+        <v>5.8900486134920972E-2</v>
+      </c>
+      <c r="L25" s="104" t="s">
         <v>27</v>
       </c>
-      <c r="M25" s="102" t="s">
+      <c r="M25" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="N25" s="102">
+      <c r="N25" s="98">
         <f>'18F norm Option 2 lit'!E16</f>
         <v>1.2141873629895492</v>
       </c>
-      <c r="O25" s="102">
+      <c r="O25" s="98">
         <f>'18F norm Option 2 lit'!G16</f>
-        <v>3.4255373160268693E-2</v>
-      </c>
-      <c r="P25" s="102">
+        <v>0.32460462364060161</v>
+      </c>
+      <c r="P25" s="98">
         <v>0.1794</v>
       </c>
-      <c r="Q25" s="103">
+      <c r="Q25" s="99">
         <f t="shared" si="0"/>
         <v>0.14175035912593689</v>
       </c>
       <c r="R25">
         <f t="shared" si="1"/>
-        <v>3.9991451035245708E-3</v>
+        <v>3.7895981606745566E-2</v>
       </c>
       <c r="S25">
         <v>0.18</v>
@@ -10270,74 +10649,74 @@
       </c>
       <c r="V25">
         <f t="shared" si="6"/>
-        <v>2.9419280551899707</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A26" s="133" t="s">
+        <v>0.64914808281115821</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A26" s="127" t="s">
         <v>36</v>
       </c>
-      <c r="B26" s="96" t="s">
+      <c r="B26" s="92" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="96">
+      <c r="C26" s="92">
         <v>0.35</v>
       </c>
-      <c r="D26" s="110">
+      <c r="D26" s="106">
         <f t="shared" si="3"/>
         <v>5.2499999999999998E-2</v>
       </c>
-      <c r="E26" s="110">
+      <c r="E26" s="106">
         <f>$G$12/$C$12*C26</f>
         <v>2.0740283132530122</v>
       </c>
-      <c r="F26" s="110">
+      <c r="F26" s="106">
         <f t="shared" si="4"/>
         <v>0.3111042469879518</v>
       </c>
-      <c r="G26" s="115">
+      <c r="G26" s="111">
         <f>'18O Option 2 lit'!D8</f>
         <v>1.2651399999999999</v>
       </c>
-      <c r="H26" s="115">
+      <c r="H26" s="111">
         <f>'18O Option 2 lit'!F8</f>
         <v>0.43678576450431567</v>
       </c>
-      <c r="I26" s="115">
+      <c r="I26" s="111">
         <v>0.62080000000000002</v>
       </c>
-      <c r="J26" s="116">
+      <c r="J26" s="112">
         <f>G26*$I$12/$G$12</f>
         <v>0.31605285407275929</v>
       </c>
-      <c r="K26" s="117">
+      <c r="K26" s="113">
         <f t="shared" si="5"/>
         <v>0.10911629344573809</v>
       </c>
-      <c r="L26" s="133" t="s">
+      <c r="L26" s="127" t="s">
         <v>28</v>
       </c>
-      <c r="M26" s="96" t="s">
+      <c r="M26" s="92" t="s">
         <v>10</v>
       </c>
-      <c r="N26" s="96">
+      <c r="N26" s="92">
         <f>'18F norm Option 2 lit'!E17</f>
-        <v>1.4277920193906368</v>
-      </c>
-      <c r="O26" s="96">
+        <v>1.2439844230444423</v>
+      </c>
+      <c r="O26" s="92">
         <f>'18F norm Option 2 lit'!G17</f>
-        <v>0.13028121158114489</v>
-      </c>
-      <c r="P26" s="96">
+        <v>0.49600336979921622</v>
+      </c>
+      <c r="P26" s="92">
         <v>0.33700000000000002</v>
       </c>
-      <c r="Q26" s="97">
+      <c r="Q26" s="93">
         <f t="shared" si="0"/>
-        <v>0.16668764448960208</v>
+        <v>0.14522901826243012</v>
       </c>
       <c r="R26">
         <f t="shared" si="1"/>
-        <v>1.5209685994029252E-2</v>
+        <v>5.7905936052242486E-2</v>
       </c>
       <c r="S26">
         <v>0.17</v>
@@ -10348,70 +10727,70 @@
       </c>
       <c r="V26">
         <f t="shared" si="6"/>
-        <v>-0.35684837150975007</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A27" s="137"/>
-      <c r="B27" s="102" t="s">
+        <v>3.2009802082717455E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A27" s="131"/>
+      <c r="B27" s="98" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="102">
+      <c r="C27" s="98">
         <v>0.66</v>
       </c>
-      <c r="D27" s="110">
+      <c r="D27" s="106">
         <f t="shared" si="3"/>
         <v>9.9000000000000005E-2</v>
       </c>
-      <c r="E27" s="110">
+      <c r="E27" s="106">
         <f>$G$12/$C$12*C27</f>
         <v>3.9110248192771087</v>
       </c>
-      <c r="F27" s="110">
+      <c r="F27" s="106">
         <f t="shared" si="4"/>
         <v>0.58665372289156625</v>
       </c>
-      <c r="G27" s="117">
+      <c r="G27" s="113">
         <f>'18O Option 2 lit'!D9</f>
         <v>3.4860899999999999</v>
       </c>
-      <c r="H27" s="115">
+      <c r="H27" s="111">
         <f>'18O Option 2 lit'!F9</f>
         <v>0.55106232587730664</v>
       </c>
-      <c r="I27" s="117">
+      <c r="I27" s="113">
         <v>0.72740000000000005</v>
       </c>
-      <c r="J27" s="118">
+      <c r="J27" s="114">
         <f>G27*$I$12/$G$12</f>
         <v>0.87088282249751447</v>
       </c>
-      <c r="K27" s="117">
+      <c r="K27" s="113">
         <f t="shared" si="5"/>
         <v>0.13766446469599863</v>
       </c>
-      <c r="L27" s="137"/>
-      <c r="M27" s="102" t="s">
+      <c r="L27" s="131"/>
+      <c r="M27" s="98" t="s">
         <v>11</v>
       </c>
-      <c r="N27" s="102">
+      <c r="N27" s="98">
         <f>'18F norm Option 2 lit'!E18</f>
-        <v>3.6770929823577543</v>
-      </c>
-      <c r="O27" s="102">
+        <v>3.7375152312493403</v>
+      </c>
+      <c r="O27" s="98">
         <f>'18F norm Option 2 lit'!G18</f>
-        <v>0.18660190641559707</v>
-      </c>
-      <c r="P27" s="102">
+        <v>0.80988843614557104</v>
+      </c>
+      <c r="P27" s="98">
         <v>0.39240000000000003</v>
       </c>
-      <c r="Q27" s="103">
+      <c r="Q27" s="99">
         <f t="shared" si="0"/>
-        <v>0.42928238810302977</v>
+        <v>0.43633638630845573</v>
       </c>
       <c r="R27">
         <f t="shared" si="1"/>
-        <v>2.1784848083798596E-2</v>
+        <v>9.4550462453269854E-2</v>
       </c>
       <c r="S27">
         <v>0.51</v>
@@ -10422,85 +10801,79 @@
       </c>
       <c r="V27">
         <f t="shared" si="6"/>
-        <v>-0.32829725666110343</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A28" s="133" t="s">
+        <v>-0.25666475481903567</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A28" s="127" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="96" t="s">
+      <c r="B28" s="92" t="s">
         <v>10</v>
       </c>
-      <c r="C28" s="96">
+      <c r="C28" s="92">
         <v>0.35</v>
       </c>
-      <c r="D28" s="110">
+      <c r="D28" s="106">
         <f t="shared" si="3"/>
         <v>5.2499999999999998E-2</v>
       </c>
-      <c r="E28" s="110">
+      <c r="E28" s="106">
         <f>$G$12/$C$12*C28</f>
         <v>2.0740283132530122</v>
       </c>
-      <c r="F28" s="110">
+      <c r="F28" s="106">
         <f t="shared" si="4"/>
         <v>0.3111042469879518</v>
       </c>
-      <c r="G28" s="115">
+      <c r="G28" s="111">
         <f>'18O Option 2 lit'!D10</f>
         <v>1.5525124999999997</v>
       </c>
-      <c r="H28" s="115">
+      <c r="H28" s="111">
         <f>'18O Option 2 lit'!F10</f>
-        <v>6.7469599429762148E-2</v>
-      </c>
-      <c r="I28" s="115">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="J28" s="116">
+        <v>0.24245367754888389</v>
+      </c>
+      <c r="I28" s="111"/>
+      <c r="J28" s="112">
         <f>G28*$I$12/$G$12</f>
         <v>0.38784324786872171</v>
       </c>
-      <c r="K28" s="117">
+      <c r="K28" s="113">
         <f t="shared" si="5"/>
-        <v>1.6855019573266308E-2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A29" s="134"/>
+        <v>6.0568930529238847E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A29" s="128"/>
       <c r="B29" t="s">
         <v>18</v>
       </c>
-      <c r="D29" s="110"/>
-      <c r="E29" s="110"/>
-      <c r="F29" s="110"/>
-      <c r="G29" s="94"/>
-      <c r="H29" s="94"/>
-      <c r="I29" s="94">
-        <v>0.89339999999999997</v>
-      </c>
-      <c r="J29" s="119"/>
-      <c r="K29" s="117"/>
-    </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A30" s="134"/>
+      <c r="D29" s="106"/>
+      <c r="E29" s="106"/>
+      <c r="F29" s="106"/>
+      <c r="G29" s="90"/>
+      <c r="H29" s="90"/>
+      <c r="I29" s="90"/>
+      <c r="J29" s="115"/>
+      <c r="K29" s="113"/>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A30" s="128"/>
       <c r="B30" t="s">
         <v>11</v>
       </c>
-      <c r="D30" s="110"/>
-      <c r="E30" s="110"/>
-      <c r="F30" s="110"/>
-      <c r="G30" s="94"/>
-      <c r="H30" s="94"/>
-      <c r="I30" s="94">
-        <v>1.0800000000000001E-2</v>
-      </c>
-      <c r="J30" s="119"/>
-      <c r="K30" s="117"/>
-    </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A31" s="98" t="s">
+      <c r="D30" s="106"/>
+      <c r="E30" s="106"/>
+      <c r="F30" s="106"/>
+      <c r="G30" s="90"/>
+      <c r="H30" s="90"/>
+      <c r="I30" s="90"/>
+      <c r="J30" s="115"/>
+      <c r="K30" s="113"/>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A31" s="94" t="s">
         <v>40</v>
       </c>
       <c r="B31" t="s">
@@ -10509,230 +10882,231 @@
       <c r="C31">
         <v>0.16</v>
       </c>
-      <c r="D31" s="110">
+      <c r="D31" s="106">
         <f t="shared" si="3"/>
         <v>2.4E-2</v>
       </c>
-      <c r="E31" s="110">
+      <c r="E31" s="106">
         <f>$G$12/$C$12*C31</f>
         <v>0.9481272289156627</v>
       </c>
-      <c r="F31" s="110">
+      <c r="F31" s="106">
         <f t="shared" si="4"/>
         <v>0.14221908433734939</v>
       </c>
-      <c r="G31" s="94">
+      <c r="G31" s="90">
         <f>'18O Option 2 lit'!D11</f>
         <v>0.70971999999999991</v>
       </c>
-      <c r="H31" s="94">
+      <c r="H31" s="90">
         <f>'18O Option 2 lit'!F11</f>
-        <v>3.0843245453605554E-2</v>
-      </c>
-      <c r="I31" s="94">
-        <v>0.13059999999999999</v>
-      </c>
-      <c r="J31" s="119">
+        <v>0.11083596687948978</v>
+      </c>
+      <c r="I31" s="90"/>
+      <c r="J31" s="115">
         <f>G31*$I$12/$G$12</f>
         <v>0.17729977045427281</v>
       </c>
-      <c r="K31" s="117">
+      <c r="K31" s="113">
         <f t="shared" si="5"/>
-        <v>7.7051518049217416E-3</v>
-      </c>
-      <c r="L31" s="96" t="s">
+        <v>2.7688653956223469E-2</v>
+      </c>
+      <c r="L31" s="92" t="s">
         <v>29</v>
       </c>
-      <c r="M31" s="96" t="s">
+      <c r="M31" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="N31" s="96">
-        <f>'18F norm Option 2 lit'!E19</f>
-        <v>0.9215853214398817</v>
-      </c>
-      <c r="O31" s="96">
+      <c r="N31" s="92">
+        <f>'18F norm Option 2 lit'!E24</f>
+        <v>1.9470112424786234</v>
+      </c>
+      <c r="O31" s="92">
         <f>'18F norm Option 2 lit'!G19</f>
-        <v>0</v>
-      </c>
-      <c r="P31" s="96">
+        <v>0.25725005957972208</v>
+      </c>
+      <c r="P31" s="92">
         <v>6.9199999999999998E-2</v>
       </c>
-      <c r="Q31" s="97">
+      <c r="Q31" s="93">
         <f t="shared" si="0"/>
-        <v>0.10759052042647525</v>
+        <v>0.22730391639396183</v>
       </c>
       <c r="R31">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3.0032669950385685E-2</v>
       </c>
       <c r="V31">
         <f t="shared" si="6"/>
-        <v>-6.8690994843123709</v>
-      </c>
-    </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A32" s="101" t="s">
+        <v>-4.4171452999701799</v>
+      </c>
+      <c r="W31" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A32" s="97" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="102" t="s">
+      <c r="B32" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="C32" s="102">
+      <c r="C32" s="98">
         <v>1.01</v>
       </c>
-      <c r="D32" s="110">
+      <c r="D32" s="106">
         <f t="shared" si="3"/>
         <v>0.1515</v>
       </c>
-      <c r="E32" s="110">
+      <c r="E32" s="106">
         <f>$G$12/$C$12*C32</f>
         <v>5.9850531325301208</v>
       </c>
-      <c r="F32" s="110">
+      <c r="F32" s="106">
         <f t="shared" si="4"/>
         <v>0.89775796987951806</v>
       </c>
-      <c r="G32" s="117">
+      <c r="G32" s="113">
         <f>'18O Option 2 lit'!D12</f>
         <v>4.4801074999999999</v>
       </c>
-      <c r="H32" s="117">
+      <c r="H32" s="113">
         <f>'18O Option 2 lit'!F12</f>
-        <v>0.19469798692588505</v>
-      </c>
-      <c r="I32" s="117">
+        <v>0.69965204092677924</v>
+      </c>
+      <c r="I32" s="113">
         <v>0.99</v>
       </c>
-      <c r="J32" s="118">
+      <c r="J32" s="114">
         <f>G32*$I$12/$G$12</f>
         <v>1.1192048009925972</v>
       </c>
-      <c r="K32" s="117">
+      <c r="K32" s="113">
         <f t="shared" si="5"/>
-        <v>4.8638770768568491E-2</v>
+        <v>0.17478462809866069</v>
       </c>
       <c r="M32" t="s">
         <v>7</v>
       </c>
       <c r="N32">
-        <f>'18F norm Option 2 lit'!D25</f>
-        <v>2.0731999999999999</v>
+        <f>'18F norm Option 2 lit'!E25</f>
+        <v>6.7736521125831306</v>
       </c>
       <c r="O32">
-        <f>'18F norm Option 2 lit'!G20</f>
-        <v>0.42004595916677601</v>
+        <f>'18F norm Option 2 lit'!F25</f>
+        <v>0.16</v>
       </c>
       <c r="P32">
         <v>0.52900000000000003</v>
       </c>
-      <c r="Q32" s="99">
+      <c r="Q32" s="95">
         <f t="shared" si="0"/>
-        <v>0.2420358286519424</v>
+        <v>0.79079032513459302</v>
       </c>
       <c r="R32">
         <f t="shared" si="1"/>
-        <v>4.9038284680122807E-2</v>
+        <v>1.8679207304799723E-2</v>
       </c>
       <c r="V32">
         <f>(G32-N32)/SQRT(H32*H32+O32*O32)</f>
-        <v>5.1987842639402384</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="D33" s="110"/>
-      <c r="E33" s="110"/>
-      <c r="F33" s="110"/>
-      <c r="G33" s="94"/>
-      <c r="H33" s="94"/>
-      <c r="I33" s="94"/>
-      <c r="J33" s="94"/>
-      <c r="K33" s="117"/>
-      <c r="L33" s="98"/>
+        <v>-3.1956260009000808</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="D33" s="106"/>
+      <c r="E33" s="106"/>
+      <c r="F33" s="106"/>
+      <c r="G33" s="90"/>
+      <c r="H33" s="90"/>
+      <c r="I33" s="90"/>
+      <c r="J33" s="90"/>
+      <c r="K33" s="113"/>
+      <c r="L33" s="94"/>
       <c r="M33" t="s">
         <v>14</v>
       </c>
       <c r="P33">
         <v>3.7000000000000002E-3</v>
       </c>
-      <c r="Q33" s="99"/>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="D34" s="110"/>
-      <c r="E34" s="110"/>
-      <c r="F34" s="110"/>
-      <c r="G34" s="94"/>
-      <c r="H34" s="94"/>
-      <c r="I34" s="94"/>
-      <c r="J34" s="94"/>
-      <c r="K34" s="117"/>
-      <c r="L34" s="101" t="s">
+      <c r="Q33" s="95"/>
+    </row>
+    <row r="34" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="D34" s="106"/>
+      <c r="E34" s="106"/>
+      <c r="F34" s="106"/>
+      <c r="G34" s="90"/>
+      <c r="H34" s="90"/>
+      <c r="I34" s="90"/>
+      <c r="J34" s="90"/>
+      <c r="K34" s="113"/>
+      <c r="L34" s="97" t="s">
         <v>30</v>
       </c>
-      <c r="M34" s="102" t="s">
+      <c r="M34" s="98" t="s">
         <v>6</v>
       </c>
-      <c r="N34" s="102"/>
-      <c r="O34" s="102"/>
-      <c r="P34" s="102">
+      <c r="N34" s="98"/>
+      <c r="O34" s="98"/>
+      <c r="P34" s="98">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="Q34" s="103"/>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="D35" s="110"/>
-      <c r="E35" s="110"/>
-      <c r="F35" s="110"/>
-      <c r="G35" s="94"/>
-      <c r="H35" s="94"/>
-      <c r="I35" s="94"/>
-      <c r="J35" s="94"/>
-      <c r="K35" s="117"/>
-      <c r="L35" s="120" t="s">
-        <v>80</v>
-      </c>
-      <c r="M35" s="102" t="s">
+      <c r="Q34" s="99"/>
+    </row>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="D35" s="106"/>
+      <c r="E35" s="106"/>
+      <c r="F35" s="106"/>
+      <c r="G35" s="90"/>
+      <c r="H35" s="90"/>
+      <c r="I35" s="90"/>
+      <c r="J35" s="90"/>
+      <c r="K35" s="113"/>
+      <c r="L35" s="117" t="s">
+        <v>79</v>
+      </c>
+      <c r="M35" s="98" t="s">
         <v>10</v>
       </c>
-      <c r="N35" s="102">
+      <c r="N35" s="98">
         <f>'18F norm Option 2 lit'!E21</f>
         <v>0</v>
       </c>
-      <c r="O35" s="102">
+      <c r="O35" s="98">
         <f>'18F norm Option 2 lit'!G21</f>
-        <v>0.1025073809150548</v>
-      </c>
-      <c r="P35" s="102"/>
-      <c r="Q35" s="103"/>
+        <v>0</v>
+      </c>
+      <c r="P35" s="98"/>
+      <c r="Q35" s="99"/>
       <c r="R35">
         <f t="shared" si="1"/>
-        <v>1.1967228864902374E-2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:20" ht="34" x14ac:dyDescent="0.2">
-      <c r="D36" s="110"/>
-      <c r="E36" s="110"/>
-      <c r="F36" s="110"/>
-      <c r="G36" s="94"/>
-      <c r="H36" s="94"/>
-      <c r="I36" s="94"/>
-      <c r="J36" s="94"/>
-      <c r="K36" s="117"/>
-      <c r="L36" s="109" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" ht="34" x14ac:dyDescent="0.2">
+      <c r="D36" s="106"/>
+      <c r="E36" s="106"/>
+      <c r="F36" s="106"/>
+      <c r="G36" s="90"/>
+      <c r="H36" s="90"/>
+      <c r="I36" s="90"/>
+      <c r="J36" s="90"/>
+      <c r="K36" s="113"/>
+      <c r="L36" s="105" t="s">
         <v>31</v>
       </c>
-      <c r="M36" s="110" t="s">
+      <c r="M36" s="106" t="s">
         <v>13</v>
       </c>
-      <c r="N36" s="110">
+      <c r="N36" s="106">
         <f>'18F norm Option 2 SM'!E28</f>
         <v>2.7525564402099247</v>
       </c>
-      <c r="O36" s="110">
+      <c r="O36" s="106">
         <f>'18F norm Option 2 SM'!F28</f>
         <v>0.103809</v>
       </c>
-      <c r="P36" s="110"/>
-      <c r="Q36" s="111">
+      <c r="P36" s="106"/>
+      <c r="Q36" s="107">
         <f t="shared" si="0"/>
         <v>0.32134732728026721</v>
       </c>
@@ -10741,653 +11115,386 @@
         <v>1.2119186444399717E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A37" s="106" t="s">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A37" s="102" t="s">
         <v>43</v>
       </c>
-      <c r="B37" s="96" t="s">
+      <c r="B37" s="92" t="s">
         <v>42</v>
       </c>
-      <c r="C37" s="96"/>
-      <c r="D37" s="110"/>
-      <c r="E37" s="110"/>
-      <c r="F37" s="110"/>
-      <c r="G37" s="115">
+      <c r="C37" s="92"/>
+      <c r="D37" s="106"/>
+      <c r="E37" s="106"/>
+      <c r="F37" s="106"/>
+      <c r="G37" s="111">
         <f>'18O Option 2 lit'!D13</f>
         <v>0.28774300000000003</v>
       </c>
-      <c r="H37" s="115">
+      <c r="H37" s="111">
         <f>'18O Option 2 lit'!E13</f>
         <v>3.6374200000000002E-2</v>
       </c>
-      <c r="I37" s="115"/>
-      <c r="J37" s="116">
+      <c r="I37" s="111"/>
+      <c r="J37" s="112">
         <f>G37*$I$12/$G$12</f>
         <v>7.1882950811339441E-2</v>
       </c>
-      <c r="K37" s="117">
+      <c r="K37" s="113">
         <f t="shared" si="5"/>
         <v>9.0868755431125093E-3</v>
       </c>
-      <c r="Q37" s="111">
+      <c r="Q37" s="107">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A38" s="101"/>
-      <c r="B38" s="102" t="s">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A38" s="97"/>
+      <c r="B38" s="98" t="s">
         <v>26</v>
       </c>
-      <c r="C38" s="102"/>
-      <c r="D38" s="110"/>
-      <c r="E38" s="110"/>
-      <c r="F38" s="110"/>
-      <c r="G38" s="117"/>
-      <c r="H38" s="117"/>
-      <c r="I38" s="117">
+      <c r="C38" s="98"/>
+      <c r="D38" s="106"/>
+      <c r="E38" s="106"/>
+      <c r="F38" s="106"/>
+      <c r="G38" s="113"/>
+      <c r="H38" s="113"/>
+      <c r="I38" s="113">
         <v>0.92989999999999995</v>
       </c>
-      <c r="J38" s="118"/>
-      <c r="K38" s="117"/>
+      <c r="J38" s="114"/>
+      <c r="K38" s="113"/>
       <c r="L38" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="N38">
         <v>0.28289999999999998</v>
       </c>
-      <c r="Q38" s="111">
+      <c r="Q38" s="107">
         <f t="shared" si="0"/>
         <v>3.3027173415799006E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A39" s="112" t="s">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A39" s="108" t="s">
         <v>44</v>
       </c>
-      <c r="B39" s="110" t="s">
+      <c r="B39" s="106" t="s">
         <v>12</v>
       </c>
-      <c r="C39" s="110"/>
-      <c r="D39" s="110"/>
-      <c r="E39" s="110"/>
-      <c r="F39" s="110"/>
-      <c r="G39" s="113">
+      <c r="C39" s="106"/>
+      <c r="D39" s="106"/>
+      <c r="E39" s="106"/>
+      <c r="F39" s="106"/>
+      <c r="G39" s="109">
         <f>'18O Option 2 lit'!D14</f>
         <v>0.28167199999999998</v>
       </c>
-      <c r="H39" s="113">
+      <c r="H39" s="109">
         <f>'18O Option 2 lit'!E14</f>
         <v>2.2748000000000001E-2</v>
       </c>
-      <c r="I39" s="113">
+      <c r="I39" s="109">
         <v>0.14019999999999999</v>
       </c>
-      <c r="J39" s="114">
+      <c r="J39" s="110">
         <f>G39*$I$12/$G$12</f>
         <v>7.0366314804987784E-2</v>
       </c>
-      <c r="K39" s="117">
+      <c r="K39" s="113">
         <f t="shared" si="5"/>
         <v>5.6828258725889055E-3</v>
       </c>
       <c r="L39" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="N39">
         <v>0.33</v>
       </c>
-      <c r="Q39" s="111">
+      <c r="Q39" s="107">
         <f t="shared" si="0"/>
         <v>3.8525865066149433E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="T41">
-        <f>SUM(P4:P5)</f>
-        <v>0.50170000000000003</v>
-      </c>
-    </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="43" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="121" t="s">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="L41" s="155"/>
+      <c r="M41" s="155"/>
+      <c r="N41" s="155"/>
+      <c r="O41" s="155"/>
+      <c r="P41" s="155"/>
+      <c r="Q41" s="155"/>
+      <c r="R41" s="155"/>
+      <c r="S41" s="155"/>
+    </row>
+    <row r="42" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A42" s="153" t="s">
+        <v>102</v>
+      </c>
+      <c r="B42" s="153"/>
+      <c r="C42" s="153"/>
+      <c r="D42" s="153"/>
+      <c r="E42" s="153"/>
+      <c r="F42" s="153"/>
+      <c r="G42" s="153"/>
+      <c r="H42" s="153"/>
+      <c r="I42" s="153"/>
+      <c r="J42" s="153"/>
+      <c r="K42" s="153"/>
+      <c r="L42" s="155"/>
+      <c r="M42" s="155"/>
+      <c r="N42" s="155"/>
+      <c r="O42" s="155"/>
+      <c r="P42" s="155"/>
+      <c r="Q42" s="155"/>
+      <c r="R42" s="155"/>
+      <c r="S42" s="155"/>
+    </row>
+    <row r="43" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="158"/>
+      <c r="B43" s="153"/>
+      <c r="C43" s="153"/>
+      <c r="D43" s="153"/>
+      <c r="E43" s="153"/>
+      <c r="F43" s="153"/>
+      <c r="G43" s="153" t="s">
+        <v>47</v>
+      </c>
+      <c r="H43" t="s">
+        <v>78</v>
+      </c>
+      <c r="I43" s="159"/>
+      <c r="J43" s="159"/>
+      <c r="K43" s="159"/>
+      <c r="L43" s="155"/>
+      <c r="M43" s="155"/>
+      <c r="N43" s="155" t="s">
+        <v>54</v>
+      </c>
+      <c r="O43" t="s">
+        <v>78</v>
+      </c>
+      <c r="P43" s="155"/>
+      <c r="Q43" s="155"/>
+      <c r="R43" s="155"/>
+      <c r="S43" s="155"/>
+      <c r="V43" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="44" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A44" s="102" t="s">
         <v>34</v>
       </c>
-      <c r="G43">
-        <v>8.5994395000000008</v>
-      </c>
-      <c r="H43">
-        <v>1.7499635444921997</v>
-      </c>
-      <c r="I43" s="115">
-        <v>1.8597999999999999</v>
-      </c>
-      <c r="J43" s="116">
-        <f>G43*$I$12/$G$12</f>
-        <v>2.1482819272183491</v>
-      </c>
-      <c r="K43" s="117">
-        <f t="shared" ref="K43:K44" si="7">H43*$I$12/$G$12</f>
-        <v>0.43716977785860994</v>
-      </c>
-      <c r="L43" t="s">
-        <v>15</v>
-      </c>
-      <c r="M43" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="N43" s="11">
-        <v>0.98622305775952057</v>
-      </c>
-      <c r="O43" s="11">
-        <v>4.2165840840068108E-2</v>
-      </c>
-      <c r="P43" s="11">
-        <v>0.3211</v>
-      </c>
-      <c r="Q43" s="11">
-        <v>0.11363740488542066</v>
-      </c>
-      <c r="R43" s="11">
-        <v>4.8585527281855617E-3</v>
-      </c>
-    </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A44" s="122" t="s">
+      <c r="B44" s="92" t="s">
+        <v>12</v>
+      </c>
+      <c r="C44" s="153"/>
+      <c r="D44" s="153"/>
+      <c r="E44" s="153"/>
+      <c r="F44" s="153"/>
+      <c r="G44" s="153">
+        <f>'18O Option 1'!D6</f>
+        <v>8.4322099999999995</v>
+      </c>
+      <c r="H44" s="153">
+        <f>'18O Option 1'!F6</f>
+        <v>0.46677488986783022</v>
+      </c>
+      <c r="I44" s="153"/>
+      <c r="J44" s="153"/>
+      <c r="L44" s="102" t="s">
+        <v>25</v>
+      </c>
+      <c r="M44" s="92" t="s">
+        <v>12</v>
+      </c>
+      <c r="N44" s="155">
+        <f>'18F norm Option 1'!E13</f>
+        <v>7.1501067363163733</v>
+      </c>
+      <c r="O44" s="155">
+        <f>'18F norm Option 1'!G13</f>
+        <v>1.2684673643870159</v>
+      </c>
+      <c r="P44" s="155"/>
+      <c r="Q44" s="155"/>
+      <c r="R44" s="155"/>
+      <c r="S44" s="155"/>
+      <c r="V44">
+        <f>(G44-N44)/SQRT(H44*H44+O44*O44)</f>
+        <v>0.94856482107387652</v>
+      </c>
+    </row>
+    <row r="45" spans="1:22" ht="17" x14ac:dyDescent="0.2">
+      <c r="A45" s="100" t="s">
         <v>35</v>
       </c>
-      <c r="G44">
-        <v>1.5336580000000002</v>
-      </c>
-      <c r="H44">
-        <v>0.31209540920879997</v>
-      </c>
-      <c r="I44" s="117">
-        <v>0.32469999999999999</v>
-      </c>
-      <c r="J44" s="118">
-        <f>G44*$I$12/$G$12</f>
-        <v>0.38313308256123424</v>
-      </c>
-      <c r="K44" s="117">
-        <f t="shared" si="7"/>
-        <v>7.7966584586248916E-2</v>
-      </c>
-      <c r="M44" t="s">
-        <v>60</v>
-      </c>
-      <c r="O44">
-        <v>0.12649752252020433</v>
-      </c>
-      <c r="P44">
-        <v>2.9399999999999999E-2</v>
-      </c>
-      <c r="R44">
-        <v>1.4575658184556688E-2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="G45">
-        <f>SUM(G43:G44)</f>
-        <v>10.133097500000002</v>
-      </c>
-      <c r="H45">
-        <f>SQRT(H43*H43+H44*H44)</f>
-        <v>1.7775758637821653</v>
-      </c>
-      <c r="I45" s="94">
-        <f>SUM(I43:I44)</f>
-        <v>2.1844999999999999</v>
-      </c>
-      <c r="J45" s="94">
-        <f>SUM(J43:J44)</f>
-        <v>2.5314150097795833</v>
-      </c>
-      <c r="K45">
-        <f>SQRT(K43*K43+K44*K44)</f>
-        <v>0.44406779097902499</v>
-      </c>
-      <c r="M45" t="s">
-        <v>58</v>
-      </c>
-      <c r="N45">
-        <v>2.9586691732785622</v>
-      </c>
-      <c r="O45">
-        <v>0.12649752252020433</v>
-      </c>
-      <c r="P45">
-        <v>0.26400000000000001</v>
-      </c>
-      <c r="Q45">
-        <v>0.34091221465626204</v>
-      </c>
-      <c r="R45">
-        <v>1.4575658184556688E-2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="L46" t="s">
-        <v>16</v>
-      </c>
-      <c r="M46" t="s">
-        <v>8</v>
-      </c>
-      <c r="N46">
-        <v>9.2820993671484313</v>
-      </c>
-      <c r="O46">
-        <v>0.39685497261240571</v>
-      </c>
-      <c r="P46">
-        <v>0.75139999999999996</v>
-      </c>
-      <c r="Q46">
-        <v>1.0695285165686652</v>
-      </c>
-      <c r="R46">
-        <v>4.5727555088805286E-2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A47" s="133" t="s">
-        <v>39</v>
-      </c>
-      <c r="B47" s="123" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47" s="11"/>
-      <c r="D47" s="11"/>
-      <c r="E47" s="11"/>
-      <c r="F47" s="11"/>
-      <c r="G47" s="11">
-        <v>1.4409675</v>
-      </c>
-      <c r="H47" s="11">
-        <v>4.7135959677690638E-2</v>
-      </c>
-      <c r="I47" s="115">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="J47" s="116">
-        <f>G47*$I$12/$G$12</f>
-        <v>0.35997746573587802</v>
-      </c>
-      <c r="K47" s="117">
-        <f t="shared" ref="K47" si="8">H47*$I$12/$G$12</f>
-        <v>1.1775340741414092E-2</v>
-      </c>
-      <c r="L47" t="s">
-        <v>17</v>
-      </c>
-      <c r="M47" t="s">
-        <v>9</v>
-      </c>
-      <c r="N47">
-        <v>8.6052796216271918</v>
-      </c>
-      <c r="O47">
-        <v>0.10942372</v>
-      </c>
-      <c r="P47">
-        <v>1</v>
-      </c>
-      <c r="Q47">
-        <v>0.99154206223553354</v>
-      </c>
-      <c r="R47">
-        <v>1.2608331833122632E-2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A48" s="134"/>
-      <c r="B48" t="s">
-        <v>18</v>
-      </c>
-      <c r="I48" s="94">
-        <v>0.89339999999999997</v>
-      </c>
-      <c r="J48" s="119"/>
-      <c r="K48" s="117"/>
-      <c r="O48" t="s">
-        <v>77</v>
-      </c>
-      <c r="P48">
-        <f>SUM(P44:P47)</f>
-        <v>2.0448</v>
-      </c>
-      <c r="Q48">
-        <f>SUM(Q44:Q47)</f>
-        <v>2.4019827934604607</v>
-      </c>
-      <c r="R48">
-        <f>SQRT(R44*R44+R45*R45+R46*R46+R47*R47)</f>
-        <v>5.1719231906902141E-2</v>
-      </c>
-    </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A49" s="134"/>
-      <c r="B49" t="s">
-        <v>11</v>
-      </c>
-      <c r="I49" s="94">
-        <v>1.0800000000000001E-2</v>
-      </c>
-      <c r="J49" s="119"/>
-      <c r="K49" s="117"/>
-    </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A50" s="98" t="s">
-        <v>40</v>
-      </c>
-      <c r="B50" t="s">
-        <v>8</v>
-      </c>
-      <c r="G50">
-        <v>0.65872799999999998</v>
-      </c>
-      <c r="H50">
-        <v>2.154786728123001E-2</v>
-      </c>
-      <c r="I50" s="94">
-        <v>0.13059999999999999</v>
-      </c>
-      <c r="J50" s="119">
-        <f>G50*$I$12/$G$12</f>
-        <v>0.16456112719354424</v>
-      </c>
-      <c r="K50" s="117">
-        <f t="shared" ref="K50:K51" si="9">H50*$I$12/$G$12</f>
-        <v>5.383012910360729E-3</v>
-      </c>
-    </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A51" s="101" t="s">
-        <v>41</v>
-      </c>
-      <c r="B51" s="124" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" s="11"/>
-      <c r="D51" s="11"/>
-      <c r="E51" s="11"/>
-      <c r="F51" s="11"/>
-      <c r="G51" s="11">
-        <v>4.1582204999999997</v>
-      </c>
-      <c r="H51" s="11">
-        <v>0.13602091221276444</v>
-      </c>
-      <c r="I51" s="117">
-        <v>0.99</v>
-      </c>
-      <c r="J51" s="118">
-        <f>G51*$I$12/$G$12</f>
-        <v>1.0387921154092481</v>
-      </c>
-      <c r="K51" s="117">
-        <f t="shared" si="9"/>
-        <v>3.3980268996652102E-2</v>
-      </c>
-    </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="G52">
-        <f>SUM(G47,G51)</f>
-        <v>5.5991879999999998</v>
-      </c>
-      <c r="H52">
-        <f>SQRT(H47*H47+H51*H51)</f>
-        <v>0.14395654640873212</v>
-      </c>
-      <c r="I52" s="94">
-        <f>SUM(I47,I51)</f>
-        <v>1.0049999999999999</v>
-      </c>
-      <c r="J52" s="94">
-        <f>SUM(J47,J51)</f>
-        <v>1.3987695811451262</v>
-      </c>
-      <c r="K52">
-        <f>SQRT(K47*K47+K51*K51)</f>
-        <v>3.5962721402324975E-2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="I53" s="94">
-        <f>SUM(I48:I50)</f>
-        <v>1.0347999999999999</v>
-      </c>
-      <c r="L53" t="s">
-        <v>25</v>
-      </c>
-      <c r="M53" t="s">
-        <v>26</v>
-      </c>
-      <c r="P53">
-        <v>3.49E-2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="M54" t="s">
-        <v>12</v>
-      </c>
-      <c r="N54">
-        <v>7.6052057037492435</v>
-      </c>
-      <c r="O54">
-        <v>0.19360551136048537</v>
-      </c>
-      <c r="P54">
-        <v>0.92410000000000003</v>
-      </c>
-      <c r="Q54">
-        <v>0.87630869405671263</v>
-      </c>
-      <c r="R54">
-        <v>2.2308166199745294E-2</v>
-      </c>
-    </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="L55" t="s">
+      <c r="B45" s="153"/>
+      <c r="C45" s="153"/>
+      <c r="D45" s="153"/>
+      <c r="E45" s="153"/>
+      <c r="F45" s="153"/>
+      <c r="G45" s="153"/>
+      <c r="H45" s="153"/>
+      <c r="I45" s="159"/>
+      <c r="J45" s="159"/>
+      <c r="L45" s="104" t="s">
         <v>27</v>
       </c>
-      <c r="M55" t="s">
-        <v>8</v>
-      </c>
-      <c r="N55">
-        <v>1.3563424185030499</v>
-      </c>
-      <c r="O55">
-        <v>3.4528371452825418E-2</v>
-      </c>
-      <c r="P55">
-        <v>0.1794</v>
-      </c>
-      <c r="Q55">
-        <v>0.15628435308017807</v>
-      </c>
-      <c r="R55">
-        <v>3.9785264560055307E-3</v>
-      </c>
-    </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="P56">
-        <f>SUM(P53:P55)</f>
-        <v>1.1384000000000001</v>
-      </c>
-      <c r="Q56">
-        <f>SUM(Q54:Q55)</f>
-        <v>1.0325930471368907</v>
-      </c>
-      <c r="R56">
-        <f>SQRT(R54*R54+R55*R55)</f>
-        <v>2.2660162222645146E-2</v>
-      </c>
-    </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="L59" t="s">
-        <v>21</v>
-      </c>
-      <c r="M59" t="s">
-        <v>20</v>
-      </c>
-      <c r="P59">
-        <v>8.6999999999999994E-2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="M60" t="s">
-        <v>5</v>
-      </c>
-      <c r="P60">
-        <v>9.8699999999999996E-2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="L61" t="s">
-        <v>22</v>
-      </c>
-      <c r="M61" t="s">
-        <v>10</v>
-      </c>
-      <c r="N61">
-        <v>2.3322128806946201</v>
-      </c>
-      <c r="O61">
-        <v>9.0212000000000001E-2</v>
-      </c>
-      <c r="P61">
-        <v>0.33560000000000001</v>
-      </c>
-      <c r="Q61">
-        <v>0.26872888168379411</v>
-      </c>
-      <c r="R61">
-        <v>1.0394664258623806E-2</v>
-      </c>
-    </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="M62" t="s">
-        <v>18</v>
-      </c>
-      <c r="P62">
-        <v>7.0300000000000001E-2</v>
-      </c>
-    </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="M63" t="s">
-        <v>11</v>
-      </c>
-      <c r="N63">
-        <v>4.7650735237951309</v>
-      </c>
-      <c r="O63">
-        <v>0.20165</v>
-      </c>
-      <c r="P63">
-        <v>9.4999999999999998E-3</v>
-      </c>
-      <c r="Q63">
-        <v>0.54905488679452663</v>
-      </c>
-      <c r="R63">
-        <v>2.3235091204623446E-2</v>
-      </c>
-    </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="O64" t="s">
-        <v>77</v>
-      </c>
-      <c r="P64">
-        <f>SUM(P59,P60,P62,P63)</f>
-        <v>0.26550000000000001</v>
-      </c>
-    </row>
-    <row r="65" spans="12:18" x14ac:dyDescent="0.2">
-      <c r="O65" t="s">
-        <v>90</v>
-      </c>
-      <c r="P65">
-        <f>P61</f>
-        <v>0.33560000000000001</v>
-      </c>
-    </row>
-    <row r="67" spans="12:18" x14ac:dyDescent="0.2">
-      <c r="L67" t="s">
-        <v>29</v>
-      </c>
-      <c r="M67" t="s">
-        <v>8</v>
-      </c>
-      <c r="N67">
-        <v>1.3173471443644555</v>
-      </c>
-      <c r="O67">
-        <v>4.6860516989739344E-2</v>
-      </c>
-      <c r="P67">
-        <v>6.9199999999999998E-2</v>
-      </c>
-      <c r="Q67">
-        <v>0.15179112842776282</v>
-      </c>
-      <c r="R67">
-        <v>5.3994960880357056E-3</v>
-      </c>
-    </row>
-    <row r="68" spans="12:18" x14ac:dyDescent="0.2">
-      <c r="M68" t="s">
-        <v>7</v>
-      </c>
-      <c r="N68">
-        <v>8.3157538488006253</v>
-      </c>
-      <c r="O68">
-        <v>0.29580701349772964</v>
-      </c>
-      <c r="P68">
-        <v>0.52900000000000003</v>
-      </c>
-      <c r="Q68">
-        <v>0.95818149820025278</v>
-      </c>
-      <c r="R68">
-        <v>3.4084319055725398E-2</v>
-      </c>
-    </row>
-    <row r="69" spans="12:18" x14ac:dyDescent="0.2">
-      <c r="M69" t="s">
-        <v>14</v>
-      </c>
-      <c r="P69">
-        <v>3.7000000000000002E-3</v>
-      </c>
-    </row>
-    <row r="70" spans="12:18" x14ac:dyDescent="0.2">
-      <c r="L70" t="s">
-        <v>30</v>
-      </c>
-      <c r="M70" t="s">
-        <v>6</v>
-      </c>
-      <c r="P70">
-        <v>2.9999999999999997E-4</v>
-      </c>
-    </row>
-    <row r="71" spans="12:18" x14ac:dyDescent="0.2">
-      <c r="P71">
-        <f>SUM(P67:P70)-P68</f>
-        <v>7.3200000000000043E-2</v>
-      </c>
+      <c r="M45" s="155"/>
+      <c r="N45" s="155"/>
+      <c r="O45" s="155"/>
+      <c r="P45" s="155"/>
+      <c r="Q45" s="155"/>
+      <c r="R45" s="155"/>
+      <c r="S45" s="155"/>
+    </row>
+    <row r="46" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A46" s="153"/>
+      <c r="B46" s="153"/>
+      <c r="C46" s="153"/>
+      <c r="D46" s="153"/>
+      <c r="E46" s="153"/>
+      <c r="F46" s="153"/>
+      <c r="G46" s="153"/>
+      <c r="H46" s="153"/>
+      <c r="I46" s="153"/>
+      <c r="J46" s="153"/>
+      <c r="K46" s="153"/>
+    </row>
+    <row r="47" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A47" s="160"/>
+      <c r="B47" s="153"/>
+      <c r="C47" s="153"/>
+      <c r="D47" s="153"/>
+      <c r="E47" s="153"/>
+      <c r="F47" s="153"/>
+      <c r="G47" s="153"/>
+      <c r="H47" s="153"/>
+      <c r="I47" s="159"/>
+      <c r="J47" s="159"/>
+      <c r="K47" s="159"/>
+    </row>
+    <row r="48" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A48" s="160"/>
+      <c r="B48" s="153"/>
+      <c r="C48" s="153"/>
+      <c r="D48" s="153"/>
+      <c r="E48" s="153"/>
+      <c r="F48" s="153"/>
+      <c r="G48" s="153"/>
+      <c r="H48" s="153"/>
+      <c r="I48" s="159"/>
+      <c r="J48" s="159"/>
+      <c r="K48" s="159"/>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A49" s="160"/>
+      <c r="B49" s="153"/>
+      <c r="C49" s="153"/>
+      <c r="D49" s="153"/>
+      <c r="E49" s="153"/>
+      <c r="F49" s="153"/>
+      <c r="G49" s="153"/>
+      <c r="H49" s="153"/>
+      <c r="I49" s="159"/>
+      <c r="J49" s="159"/>
+      <c r="K49" s="159"/>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A50" s="153"/>
+      <c r="B50" s="153"/>
+      <c r="C50" s="153"/>
+      <c r="D50" s="153"/>
+      <c r="E50" s="153"/>
+      <c r="F50" s="153"/>
+      <c r="G50" s="153"/>
+      <c r="H50" s="153"/>
+      <c r="I50" s="159"/>
+      <c r="J50" s="159"/>
+      <c r="K50" s="159"/>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A51" s="160"/>
+      <c r="B51" s="153"/>
+      <c r="C51" s="153"/>
+      <c r="D51" s="153"/>
+      <c r="E51" s="153"/>
+      <c r="F51" s="153"/>
+      <c r="G51" s="153"/>
+      <c r="H51" s="153"/>
+      <c r="I51" s="159"/>
+      <c r="J51" s="159"/>
+      <c r="K51" s="159"/>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A52" s="153"/>
+      <c r="B52" s="153"/>
+      <c r="C52" s="153"/>
+      <c r="D52" s="153"/>
+      <c r="E52" s="153"/>
+      <c r="F52" s="153"/>
+      <c r="G52" s="153"/>
+      <c r="H52" s="153"/>
+      <c r="I52" s="159"/>
+      <c r="J52" s="159"/>
+      <c r="K52" s="153"/>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A53" s="153"/>
+      <c r="B53" s="153"/>
+      <c r="C53" s="153"/>
+      <c r="D53" s="153"/>
+      <c r="E53" s="153"/>
+      <c r="F53" s="153"/>
+      <c r="G53" s="153"/>
+      <c r="H53" s="153"/>
+      <c r="I53" s="159"/>
+      <c r="J53" s="153"/>
+      <c r="K53" s="153"/>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A54" s="153"/>
+      <c r="B54" s="153"/>
+      <c r="C54" s="153"/>
+      <c r="D54" s="153"/>
+      <c r="E54" s="153"/>
+      <c r="F54" s="153"/>
+      <c r="G54" s="153"/>
+      <c r="H54" s="153"/>
+      <c r="I54" s="153"/>
+      <c r="J54" s="153"/>
+      <c r="K54" s="153"/>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A55" s="153"/>
+      <c r="B55" s="153"/>
+      <c r="C55" s="153"/>
+      <c r="D55" s="153"/>
+      <c r="E55" s="153"/>
+      <c r="F55" s="153"/>
+      <c r="G55" s="153"/>
+      <c r="H55" s="153"/>
+      <c r="I55" s="153"/>
+      <c r="J55" s="153"/>
+      <c r="K55" s="153"/>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A56" s="153"/>
+      <c r="B56" s="153"/>
+      <c r="C56" s="153"/>
+      <c r="D56" s="153"/>
+      <c r="E56" s="153"/>
+      <c r="F56" s="153"/>
+      <c r="G56" s="153"/>
+      <c r="H56" s="153"/>
+      <c r="I56" s="153"/>
+      <c r="J56" s="153"/>
+      <c r="K56" s="153"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="A28:A30"/>
-    <mergeCell ref="A47:A49"/>
     <mergeCell ref="L6:L8"/>
     <mergeCell ref="L11:L12"/>
     <mergeCell ref="L18:L20"/>
@@ -11406,7 +11513,7 @@
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C2">
         <v>6.1494999999999997</v>
@@ -11520,7 +11627,7 @@
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C5">
         <v>0.27305800000000002</v>
@@ -11558,7 +11665,7 @@
     </row>
     <row r="51" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B51" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C51">
         <v>6.1494999999999997</v>
@@ -11672,7 +11779,7 @@
     </row>
     <row r="54" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B54" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C54">
         <v>0.27</v>
@@ -11710,7 +11817,7 @@
     </row>
     <row r="55" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B55" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C55">
         <v>0.35</v>
@@ -11748,7 +11855,7 @@
     </row>
     <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B66" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C66">
         <v>6.1494999999999997</v>
@@ -11824,7 +11931,7 @@
     </row>
     <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B68" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C68">
         <v>0.27</v>
@@ -11862,7 +11969,7 @@
     </row>
     <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B69" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C69">
         <v>0.38</v>
@@ -11900,7 +12007,7 @@
     </row>
     <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B70" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C70">
         <v>6.9000000000000006E-2</v>

--- a/analysis/final_working/free_lit_SM_SF_18F_18O.xlsx
+++ b/analysis/final_working/free_lit_SM_SF_18F_18O.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kawecka/digios/analysis/final_working/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CE60947-7425-7744-BB5D-BAB41D0AD73E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AC726B1-0169-0E4B-84A0-CD6C27B2ECB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30960" yWindow="2060" windowWidth="36080" windowHeight="17680" activeTab="4" xr2:uid="{FC3CEAA1-A762-5643-8C2C-8E9D51254AD0}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="17240" activeTab="4" xr2:uid="{FC3CEAA1-A762-5643-8C2C-8E9D51254AD0}"/>
   </bookViews>
   <sheets>
     <sheet name="18O Option 1" sheetId="6" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="118">
   <si>
     <t>unc</t>
   </si>
@@ -390,15 +390,33 @@
   <si>
     <t>unc fit</t>
   </si>
+  <si>
+    <t>SF re-norm to lit</t>
+  </si>
+  <si>
+    <t>unc re-norm to lit</t>
+  </si>
+  <si>
+    <t>lit</t>
+  </si>
+  <si>
+    <t>what to do about lit SF for this state?</t>
+  </si>
+  <si>
+    <t>unc lit</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.00000"/>
+    <numFmt numFmtId="169" formatCode="0.00000000"/>
+    <numFmt numFmtId="171" formatCode="0.000000"/>
+    <numFmt numFmtId="172" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -423,6 +441,13 @@
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -743,7 +768,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="183">
+  <cellXfs count="191">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -963,30 +988,30 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
@@ -1009,10 +1034,10 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1027,6 +1052,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5887,292 +5920,471 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CADDBF61-7143-F246-8310-61B610542A2A}">
-  <dimension ref="B2:I12"/>
+  <dimension ref="A2:T14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="6" max="6" width="14.1640625" customWidth="1"/>
+    <col min="9" max="9" width="14.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D2" t="s">
+    <row r="2" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="183" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" s="183" t="s">
+        <v>117</v>
+      </c>
+      <c r="C2" s="183" t="s">
+        <v>113</v>
+      </c>
+      <c r="D2" s="183" t="s">
+        <v>114</v>
+      </c>
+      <c r="G2" t="s">
         <v>47</v>
       </c>
-      <c r="E2" t="s">
+      <c r="H2" t="s">
         <v>0</v>
       </c>
-      <c r="F2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
+        <v>110</v>
+      </c>
+      <c r="J2" t="s">
         <v>1</v>
       </c>
-      <c r="H2" t="s">
+      <c r="K2" t="s">
         <v>76</v>
       </c>
-      <c r="I2" t="s">
+      <c r="L2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="8" t="s">
+    <row r="3" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="183">
+        <v>1.22</v>
+      </c>
+      <c r="B3" s="189">
+        <f>A3*0.15</f>
+        <v>0.183</v>
+      </c>
+      <c r="C3" s="188">
+        <f>G3*$A$5/$G$5</f>
+        <v>1.045608194518147</v>
+      </c>
+      <c r="D3" s="189">
+        <f>I3*$A$5/$G$5</f>
+        <v>0.14268404206129237</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="F3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="32">
+      <c r="G3" s="32">
         <v>6.1960600000000001</v>
       </c>
-      <c r="E3" s="9">
+      <c r="H3" s="9">
         <v>0.50926499999999997</v>
       </c>
-      <c r="F3" s="9">
-        <f>E3*SQRT(H3)</f>
+      <c r="I3" s="9">
+        <f>H3*SQRT(K3)</f>
         <v>0.84551640881286871</v>
       </c>
-      <c r="G3" s="10">
+      <c r="J3" s="10">
         <v>8.2694700000000001</v>
       </c>
-      <c r="H3">
+      <c r="K3">
         <v>2.7564899999999999</v>
       </c>
-      <c r="I3" t="s">
+      <c r="L3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="118" t="s">
+    <row r="4" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="183">
+        <v>0.21</v>
+      </c>
+      <c r="B4" s="189">
+        <f t="shared" ref="B4:B12" si="0">A4*0.15</f>
+        <v>3.15E-2</v>
+      </c>
+      <c r="C4" s="188">
+        <f t="shared" ref="C4:C12" si="1">G4*$A$5/$G$5</f>
+        <v>0.12542687982498407</v>
+      </c>
+      <c r="D4" s="189">
+        <f t="shared" ref="D4:D12" si="2">I4*$A$5/$G$5</f>
+        <v>1.808558684555622E-2</v>
+      </c>
+      <c r="E4" s="118" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="35">
+      <c r="G4" s="35">
         <v>0.74325399999999997</v>
       </c>
-      <c r="E4" s="2">
+      <c r="H4" s="2">
         <v>9.4910800000000003E-2</v>
       </c>
-      <c r="F4" s="9">
-        <f t="shared" ref="F4:F12" si="0">E4*SQRT(H4)</f>
+      <c r="I4" s="9">
+        <f t="shared" ref="I4:I12" si="3">H4*SQRT(K4)</f>
         <v>0.10717148336994237</v>
       </c>
-      <c r="G4" s="3">
+      <c r="J4" s="3">
         <v>10.2004</v>
       </c>
-      <c r="H4">
+      <c r="K4">
         <v>1.27505</v>
       </c>
-      <c r="I4" t="s">
+      <c r="L4" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="119"/>
-      <c r="C5" s="6" t="s">
+    <row r="5" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="183">
+        <v>0.83</v>
+      </c>
+      <c r="B5" s="189">
+        <f t="shared" si="0"/>
+        <v>0.12449999999999999</v>
+      </c>
+      <c r="C5" s="188">
+        <f t="shared" si="1"/>
+        <v>0.83000000000000007</v>
+      </c>
+      <c r="D5" s="189">
+        <f t="shared" si="2"/>
+        <v>4.1252740579656055E-2</v>
+      </c>
+      <c r="E5" s="119"/>
+      <c r="F5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="34">
+      <c r="G5" s="34">
         <v>4.9184099999999997</v>
       </c>
-      <c r="E5" s="6">
+      <c r="H5" s="6">
         <v>0.21648899999999999</v>
       </c>
-      <c r="F5" s="9">
+      <c r="I5" s="9">
+        <f t="shared" si="3"/>
+        <v>0.24445529131853752</v>
+      </c>
+      <c r="J5" s="3">
+        <v>10.2004</v>
+      </c>
+      <c r="K5">
+        <v>1.27505</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="35" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="183">
+        <f>1.57+0.28</f>
+        <v>1.85</v>
+      </c>
+      <c r="B6" s="189">
         <f t="shared" si="0"/>
-        <v>0.24445529131853752</v>
-      </c>
-      <c r="G5" s="3">
-        <v>10.2004</v>
-      </c>
-      <c r="H5">
-        <v>1.27505</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" ht="35" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="49" t="s">
+        <v>0.27750000000000002</v>
+      </c>
+      <c r="C6" s="188">
+        <f t="shared" si="1"/>
+        <v>1.4229668327772591</v>
+      </c>
+      <c r="D6" s="189">
+        <f t="shared" si="2"/>
+        <v>7.8770000587649075E-2</v>
+      </c>
+      <c r="E6" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="50" t="s">
+      <c r="F6" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="51">
+      <c r="G6" s="51">
         <v>8.4322099999999995</v>
       </c>
-      <c r="E6" s="52">
+      <c r="H6" s="52">
         <v>0.14779700000000001</v>
       </c>
-      <c r="F6" s="9">
+      <c r="I6" s="9">
+        <f t="shared" si="3"/>
+        <v>0.46677488986783022</v>
+      </c>
+      <c r="J6" s="53">
+        <v>69.820300000000003</v>
+      </c>
+      <c r="K6" s="68">
+        <v>9.9743300000000001</v>
+      </c>
+      <c r="L6" t="s">
+        <v>51</v>
+      </c>
+      <c r="T6" s="187" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="132">
+        <v>0.35</v>
+      </c>
+      <c r="B7" s="189">
         <f t="shared" si="0"/>
-        <v>0.46677488986783022</v>
-      </c>
-      <c r="G6" s="53">
-        <v>69.820300000000003</v>
-      </c>
-      <c r="H6" s="68">
-        <v>9.9743300000000001</v>
-      </c>
-      <c r="I6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="118" t="s">
+        <v>5.2499999999999998E-2</v>
+      </c>
+      <c r="C7" s="188">
+        <f t="shared" si="1"/>
+        <v>0.21349708544021337</v>
+      </c>
+      <c r="D7" s="189">
+        <f t="shared" si="2"/>
+        <v>7.3709224025362258E-2</v>
+      </c>
+      <c r="E7" s="118" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="35">
+      <c r="G7" s="35">
         <v>1.2651399999999999</v>
       </c>
-      <c r="E7" s="2">
+      <c r="H7" s="2">
         <v>0.160803</v>
       </c>
-      <c r="F7" s="9">
+      <c r="I7" s="9">
+        <f t="shared" si="3"/>
+        <v>0.43678576450431567</v>
+      </c>
+      <c r="J7" s="3">
+        <v>44.267000000000003</v>
+      </c>
+      <c r="K7">
+        <v>7.3781699999999999</v>
+      </c>
+      <c r="L7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="132">
+        <v>0.66</v>
+      </c>
+      <c r="B8" s="189">
         <f t="shared" si="0"/>
-        <v>0.43678576450431567</v>
-      </c>
-      <c r="G7" s="3">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="C8" s="188">
+        <f t="shared" si="1"/>
+        <v>0.588290667105833</v>
+      </c>
+      <c r="D8" s="189">
+        <f t="shared" si="2"/>
+        <v>9.2993819237957895E-2</v>
+      </c>
+      <c r="E8" s="119"/>
+      <c r="F8" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="34">
+        <v>3.4860899999999999</v>
+      </c>
+      <c r="H8" s="6">
+        <v>0.202874</v>
+      </c>
+      <c r="I8" s="9">
+        <f t="shared" si="3"/>
+        <v>0.55106232587730664</v>
+      </c>
+      <c r="J8" s="3">
         <v>44.267000000000003</v>
       </c>
-      <c r="H7">
+      <c r="K8">
         <v>7.3781699999999999</v>
       </c>
-      <c r="I7" t="s">
+    </row>
+    <row r="9" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="183">
+        <f>0.16</f>
+        <v>0.16</v>
+      </c>
+      <c r="B9" s="189">
+        <f t="shared" si="0"/>
+        <v>2.4E-2</v>
+      </c>
+      <c r="C9" s="188">
+        <f t="shared" si="1"/>
+        <v>0.48841715107117956</v>
+      </c>
+      <c r="D9" s="189">
+        <f t="shared" si="2"/>
+        <v>0.25915031148078665</v>
+      </c>
+      <c r="E9" s="124" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" s="54" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="55">
+        <v>2.8942600000000001</v>
+      </c>
+      <c r="H9" s="54">
+        <v>1.4768600000000001</v>
+      </c>
+      <c r="I9" s="9">
+        <f t="shared" si="3"/>
+        <v>1.5356716668556818</v>
+      </c>
+      <c r="J9" s="56">
+        <v>4.3249199999999997</v>
+      </c>
+      <c r="K9" s="27">
+        <v>1.0812299999999999</v>
+      </c>
+      <c r="L9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="183">
+        <v>1.36</v>
+      </c>
+      <c r="B10" s="189">
+        <f t="shared" si="0"/>
+        <v>0.20400000000000001</v>
+      </c>
+      <c r="C10" s="188">
+        <f t="shared" si="1"/>
+        <v>0.83222079899805013</v>
+      </c>
+      <c r="D10" s="189">
+        <f t="shared" si="2"/>
+        <v>8.3538889054160168E-2</v>
+      </c>
+      <c r="E10" s="123"/>
+      <c r="F10" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="G10" s="41">
+        <v>4.9315699999999998</v>
+      </c>
+      <c r="H10" s="30">
+        <v>0.476076</v>
+      </c>
+      <c r="I10" s="9">
+        <f t="shared" si="3"/>
+        <v>0.49503434616008668</v>
+      </c>
+      <c r="J10" s="56">
+        <v>4.3249199999999997</v>
+      </c>
+      <c r="K10" s="27">
+        <v>1.0812299999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="153">
+        <v>0.03</v>
+      </c>
+      <c r="B11" s="189">
+        <f t="shared" si="0"/>
+        <v>4.4999999999999997E-3</v>
+      </c>
+      <c r="C11" s="188">
+        <f t="shared" si="1"/>
+        <v>4.8557702590877952E-2</v>
+      </c>
+      <c r="D11" s="189">
+        <f t="shared" si="2"/>
+        <v>1.1963210218786179E-2</v>
+      </c>
+      <c r="E11" s="46" t="s">
+        <v>43</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="G11" s="32">
+        <v>0.28774300000000003</v>
+      </c>
+      <c r="H11" s="9">
+        <v>3.6374200000000002E-2</v>
+      </c>
+      <c r="I11" s="9">
+        <f t="shared" si="3"/>
+        <v>7.0891533460457984E-2</v>
+      </c>
+      <c r="J11" s="10">
+        <v>15.1936</v>
+      </c>
+      <c r="K11">
+        <v>3.7984100000000001</v>
+      </c>
+      <c r="L11" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="119"/>
-      <c r="C8" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="34">
-        <v>3.4860899999999999</v>
-      </c>
-      <c r="E8" s="6">
-        <v>0.202874</v>
-      </c>
-      <c r="F8" s="9">
+    <row r="12" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="153">
+        <v>0.03</v>
+      </c>
+      <c r="B12" s="189">
         <f t="shared" si="0"/>
-        <v>0.55106232587730664</v>
-      </c>
-      <c r="G8" s="3">
-        <v>44.267000000000003</v>
-      </c>
-      <c r="H8">
-        <v>7.3781699999999999</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="124" t="s">
-        <v>50</v>
-      </c>
-      <c r="C9" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="55">
-        <v>2.8942600000000001</v>
-      </c>
-      <c r="E9" s="54">
-        <v>1.4768600000000001</v>
-      </c>
-      <c r="F9" s="9">
-        <f t="shared" si="0"/>
-        <v>1.5356716668556818</v>
-      </c>
-      <c r="G9" s="56">
-        <v>4.3249199999999997</v>
-      </c>
-      <c r="H9" s="27">
-        <v>1.0812299999999999</v>
-      </c>
-      <c r="I9" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="123"/>
-      <c r="C10" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="41">
-        <v>4.9315699999999998</v>
-      </c>
-      <c r="E10" s="30">
-        <v>0.476076</v>
-      </c>
-      <c r="F10" s="9">
-        <f t="shared" si="0"/>
-        <v>0.49503434616008668</v>
-      </c>
-      <c r="G10" s="56">
-        <v>4.3249199999999997</v>
-      </c>
-      <c r="H10" s="27">
-        <v>1.0812299999999999</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="46" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" s="32">
-        <v>0.28774300000000003</v>
-      </c>
-      <c r="E11" s="9">
-        <v>3.6374200000000002E-2</v>
-      </c>
-      <c r="F11" s="9">
-        <f t="shared" si="0"/>
-        <v>7.0891533460457984E-2</v>
-      </c>
-      <c r="G11" s="10">
-        <v>15.1936</v>
-      </c>
-      <c r="H11">
-        <v>3.7984100000000001</v>
-      </c>
-      <c r="I11" t="s">
+        <v>4.4999999999999997E-3</v>
+      </c>
+      <c r="C12" s="188">
+        <f t="shared" si="1"/>
+        <v>4.7533198736990204E-2</v>
+      </c>
+      <c r="D12" s="189">
+        <f t="shared" si="2"/>
+        <v>8.7477873562453821E-3</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="32">
+        <v>0.28167199999999998</v>
+      </c>
+      <c r="H12" s="9">
+        <v>2.2748000000000001E-2</v>
+      </c>
+      <c r="I12" s="9">
+        <f t="shared" si="3"/>
+        <v>5.1837596157627529E-2</v>
+      </c>
+      <c r="J12" s="10">
+        <v>15.5784</v>
+      </c>
+      <c r="K12">
+        <v>5.1928200000000002</v>
+      </c>
+      <c r="L12" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" s="32">
-        <v>0.28167199999999998</v>
-      </c>
-      <c r="E12" s="9">
-        <v>2.2748000000000001E-2</v>
-      </c>
-      <c r="F12" s="9">
-        <f t="shared" si="0"/>
-        <v>5.1837596157627529E-2</v>
-      </c>
-      <c r="G12" s="10">
-        <v>15.5784</v>
-      </c>
-      <c r="H12">
-        <v>5.1928200000000002</v>
-      </c>
-      <c r="I12" t="s">
-        <v>48</v>
-      </c>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A13" s="183"/>
+      <c r="B13" s="183"/>
+      <c r="C13" s="183"/>
+      <c r="D13" s="183"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A14" s="183"/>
+      <c r="B14" s="183"/>
+      <c r="C14" s="183"/>
+      <c r="D14" s="183"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="E7:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6180,562 +6392,756 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E7DC075-C5D5-7045-BBDD-7E30C0F6925C}">
-  <dimension ref="B2:P21"/>
+  <dimension ref="A2:S21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="16" max="16" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" customWidth="1"/>
+    <col min="4" max="4" width="9.83203125" customWidth="1"/>
+    <col min="19" max="19" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C2" t="s">
+        <v>113</v>
+      </c>
       <c r="D2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G2" t="s">
         <v>47</v>
       </c>
-      <c r="E2" t="s">
+      <c r="H2" t="s">
         <v>0</v>
       </c>
-      <c r="F2" t="s">
+      <c r="I2" t="s">
         <v>110</v>
       </c>
-      <c r="G2" t="s">
+      <c r="J2" t="s">
         <v>1</v>
       </c>
-      <c r="H2" t="s">
+      <c r="K2" t="s">
         <v>76</v>
       </c>
-      <c r="I2" t="s">
+      <c r="L2" t="s">
         <v>32</v>
       </c>
-      <c r="J2" t="s">
+      <c r="M2" t="s">
         <v>104</v>
       </c>
-      <c r="K2" t="s">
+      <c r="N2" t="s">
         <v>3</v>
       </c>
-      <c r="L2" t="s">
+      <c r="O2" t="s">
         <v>105</v>
       </c>
-      <c r="M2" t="s">
+      <c r="P2" t="s">
         <v>109</v>
       </c>
-      <c r="N2" t="s">
+      <c r="Q2" t="s">
         <v>46</v>
       </c>
-      <c r="P2" t="s">
+      <c r="S2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="2:16" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="69" t="s">
+    <row r="3" spans="1:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="132">
+        <v>1.22</v>
+      </c>
+      <c r="B3" s="190">
+        <f>A3*0.15</f>
+        <v>0.183</v>
+      </c>
+      <c r="C3" s="186">
+        <f>G3*$A$5/$G$5</f>
+        <v>1.045608194518147</v>
+      </c>
+      <c r="D3" s="186">
+        <f>I3*$A$5/$G$5</f>
+        <v>0.14268404206129237</v>
+      </c>
+      <c r="E3" s="69" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="35">
-        <f>'18O Option 1'!D3</f>
+      <c r="G3" s="35">
+        <f>'18O Option 1'!G3</f>
         <v>6.1960600000000001</v>
       </c>
-      <c r="E3" s="2">
-        <f>'18O Option 1'!E3</f>
+      <c r="H3" s="2">
+        <f>'18O Option 1'!H3</f>
         <v>0.50926499999999997</v>
       </c>
-      <c r="F3" s="2">
-        <f>E3*SQRT(H3)</f>
+      <c r="I3" s="2">
+        <f>H3*SQRT(K3)</f>
         <v>0.84551640881286871</v>
       </c>
-      <c r="G3" s="2">
-        <f>'18O Option 1'!G3</f>
+      <c r="J3" s="2">
+        <f>'18O Option 1'!J3</f>
         <v>8.2694700000000001</v>
       </c>
-      <c r="H3" s="3">
-        <f>'18O Option 1'!H3</f>
+      <c r="K3" s="3">
+        <f>'18O Option 1'!K3</f>
         <v>2.7564899999999999</v>
       </c>
-      <c r="M3">
-        <f>E3*SQRT(H3)</f>
+      <c r="P3">
+        <f>H3*SQRT(K3)</f>
         <v>0.84551640881286871</v>
       </c>
-      <c r="N3" t="s">
+      <c r="Q3" t="s">
         <v>48</v>
       </c>
-      <c r="P3" s="90">
-        <f>D3*$P$21/$D$5</f>
+      <c r="S3" s="90">
+        <f>G3*$S$21/$G$5</f>
         <v>1.5478780585595753</v>
       </c>
     </row>
-    <row r="4" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B4" s="118" t="s">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A4" s="132">
+        <v>0.21</v>
+      </c>
+      <c r="B4" s="190">
+        <f t="shared" ref="B4:B14" si="0">A4*0.15</f>
+        <v>3.15E-2</v>
+      </c>
+      <c r="C4" s="186">
+        <f t="shared" ref="C4:C5" si="1">G4*$A$5/$G$5</f>
+        <v>0.12542687982498407</v>
+      </c>
+      <c r="D4" s="186">
+        <f t="shared" ref="D4:D14" si="2">I4*$A$5/$G$5</f>
+        <v>1.808558684555622E-2</v>
+      </c>
+      <c r="E4" s="118" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="35">
-        <f>'18O Option 1'!D4</f>
+      <c r="G4" s="35">
+        <f>'18O Option 1'!G4</f>
         <v>0.74325399999999997</v>
       </c>
-      <c r="E4" s="2">
-        <f>'18O Option 1'!E4</f>
+      <c r="H4" s="2">
+        <f>'18O Option 1'!H4</f>
         <v>9.4910800000000003E-2</v>
       </c>
-      <c r="F4" s="2">
-        <f>E4*SQRT(H4)</f>
+      <c r="I4" s="2">
+        <f>H4*SQRT(K4)</f>
         <v>0.10717148336994237</v>
       </c>
-      <c r="G4" s="2">
-        <f>'18O Option 1'!G4</f>
+      <c r="J4" s="2">
+        <f>'18O Option 1'!J4</f>
         <v>10.2004</v>
       </c>
-      <c r="H4" s="3">
-        <f>'18O Option 1'!H4</f>
+      <c r="K4" s="3">
+        <f>'18O Option 1'!K4</f>
         <v>1.27505</v>
       </c>
-      <c r="M4">
-        <f t="shared" ref="M4:M5" si="0">E4*SQRT(H4)</f>
+      <c r="P4">
+        <f t="shared" ref="P4:P5" si="3">H4*SQRT(K4)</f>
         <v>0.10717148336994237</v>
       </c>
-      <c r="N4" t="s">
+      <c r="Q4" t="s">
         <v>48</v>
       </c>
-      <c r="P4" s="90">
-        <f>D4*$P$21/$D$5</f>
+      <c r="S4" s="90">
+        <f>G4*$S$21/$G$5</f>
         <v>0.18567711715778065</v>
       </c>
     </row>
-    <row r="5" spans="2:16" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="119"/>
-      <c r="C5" s="6" t="s">
+    <row r="5" spans="1:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="132">
+        <v>0.83</v>
+      </c>
+      <c r="B5" s="190">
+        <f t="shared" si="0"/>
+        <v>0.12449999999999999</v>
+      </c>
+      <c r="C5" s="186">
+        <f t="shared" si="1"/>
+        <v>0.83000000000000007</v>
+      </c>
+      <c r="D5" s="186">
+        <f t="shared" si="2"/>
+        <v>4.1252740579656055E-2</v>
+      </c>
+      <c r="E5" s="119"/>
+      <c r="F5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="34">
-        <f>'18O Option 1'!D5</f>
+      <c r="G5" s="34">
+        <f>'18O Option 1'!G5</f>
         <v>4.9184099999999997</v>
       </c>
-      <c r="E5" s="6">
-        <f>'18O Option 1'!E5</f>
+      <c r="H5" s="6">
+        <f>'18O Option 1'!H5</f>
         <v>0.21648899999999999</v>
       </c>
-      <c r="F5" s="6">
-        <f t="shared" ref="F5:F14" si="1">E5*SQRT(H5)</f>
+      <c r="I5" s="6">
+        <f t="shared" ref="I5:I14" si="4">H5*SQRT(K5)</f>
         <v>0.24445529131853752</v>
       </c>
-      <c r="G5" s="6">
-        <f>'18O Option 1'!G5</f>
+      <c r="J5" s="6">
+        <f>'18O Option 1'!J5</f>
         <v>10.2004</v>
       </c>
-      <c r="H5" s="7">
-        <f>'18O Option 1'!H5</f>
+      <c r="K5" s="7">
+        <f>'18O Option 1'!K5</f>
         <v>1.27505</v>
       </c>
-      <c r="M5">
+      <c r="P5">
+        <f t="shared" si="3"/>
+        <v>0.24445529131853752</v>
+      </c>
+      <c r="S5" s="90">
+        <f>G5*$S$21/$G$5</f>
+        <v>1.2286999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A6" s="132">
+        <v>1.57</v>
+      </c>
+      <c r="B6" s="190">
         <f t="shared" si="0"/>
-        <v>0.24445529131853752</v>
-      </c>
-      <c r="P5" s="90">
-        <f>D5*$P$21/$D$5</f>
-        <v>1.2286999999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B6" s="87" t="s">
+        <v>0.23549999999999999</v>
+      </c>
+      <c r="C6" s="186">
+        <f t="shared" ref="C6:C14" si="5">G6*$A$5/$G$5</f>
+        <v>1.3953267785727503</v>
+      </c>
+      <c r="D6" s="186">
+        <f t="shared" si="2"/>
+        <v>0.22309648839777094</v>
+      </c>
+      <c r="E6" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="162" t="s">
+      <c r="F6" s="162" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="167">
-        <f>I6*K6</f>
+      <c r="G6" s="167">
+        <f>L6*N6</f>
         <v>8.2684207000000001</v>
       </c>
-      <c r="E6" s="162">
-        <f>I6*L6</f>
+      <c r="H6" s="162">
+        <f>L6*O6</f>
         <v>0.14492560099999999</v>
       </c>
-      <c r="F6" s="162">
-        <f>D6*SQRT(POWER((M6/K6),2)+POWER((J6/I6),2))</f>
+      <c r="I6" s="162">
+        <f>G6*SQRT(POWER((P6/N6),2)+POWER((M6/L6),2))</f>
         <v>1.3220240957837115</v>
       </c>
-      <c r="G6" s="162">
+      <c r="J6" s="162">
         <v>69.820300000000003</v>
       </c>
-      <c r="H6" s="162">
+      <c r="K6" s="162">
         <v>9.9743300000000001</v>
       </c>
-      <c r="I6" s="48">
+      <c r="L6" s="48">
         <v>1.57</v>
       </c>
-      <c r="J6" s="48">
-        <f>0.15*I6</f>
+      <c r="M6" s="48">
+        <f>0.15*L6</f>
         <v>0.23549999999999999</v>
       </c>
-      <c r="K6" s="48">
+      <c r="N6" s="48">
         <v>5.2665100000000002</v>
       </c>
-      <c r="L6" s="48">
+      <c r="O6" s="48">
         <v>9.2309299999999997E-2</v>
       </c>
-      <c r="M6" s="71">
-        <f>L6*SQRT(H6)</f>
+      <c r="P6" s="71">
+        <f>O6*SQRT(K6)</f>
         <v>0.29153273301404287</v>
       </c>
-      <c r="P6" s="90">
-        <f>D6*$P$21/$D$5</f>
+      <c r="S6" s="90">
+        <f>G6*$S$21/$G$5</f>
         <v>2.0655879672678772</v>
       </c>
     </row>
-    <row r="7" spans="2:16" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="42" t="s">
+    <row r="7" spans="1:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="132">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="B7" s="190">
+        <f t="shared" si="0"/>
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="C7" s="186">
+        <f t="shared" si="5"/>
+        <v>0.24884808789832488</v>
+      </c>
+      <c r="D7" s="186">
+        <f t="shared" si="2"/>
+        <v>3.9787908758838135E-2</v>
+      </c>
+      <c r="E7" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="157" t="s">
+      <c r="F7" s="157" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="168">
-        <f>I7*K7</f>
+      <c r="G7" s="168">
+        <f>L7*N7</f>
         <v>1.4746228000000001</v>
       </c>
-      <c r="E7" s="157">
-        <f>I7*L7</f>
+      <c r="H7" s="157">
+        <f>L7*O7</f>
         <v>2.5846604000000002E-2</v>
       </c>
-      <c r="F7" s="157">
-        <f>D7*SQRT(POWER((M7/K7),2)+POWER((J7/I7),2))</f>
+      <c r="I7" s="157">
+        <f>G7*SQRT(POWER((P7/N7),2)+POWER((M7/L7),2))</f>
         <v>0.23577499797416512</v>
       </c>
-      <c r="G7" s="157">
+      <c r="J7" s="157">
         <v>69.820300000000003</v>
       </c>
-      <c r="H7" s="157">
+      <c r="K7" s="157">
         <v>9.9743300000000001</v>
       </c>
-      <c r="I7" s="15">
+      <c r="L7" s="15">
         <v>0.28000000000000003</v>
       </c>
-      <c r="J7" s="15">
-        <f>0.15*I7</f>
+      <c r="M7" s="15">
+        <f>0.15*L7</f>
         <v>4.2000000000000003E-2</v>
       </c>
-      <c r="K7" s="15">
+      <c r="N7" s="15">
         <v>5.2665100000000002</v>
       </c>
-      <c r="L7" s="15">
+      <c r="O7" s="15">
         <v>9.2309299999999997E-2</v>
       </c>
-      <c r="M7" s="16">
-        <f>L7*SQRT(H7)</f>
+      <c r="P7" s="16">
+        <f>O7*SQRT(K7)</f>
         <v>0.29153273301404287</v>
       </c>
-      <c r="P7" s="90">
-        <f>D7*$P$21/$D$5</f>
+      <c r="S7" s="90">
+        <f>G7*$S$21/$G$5</f>
         <v>0.36838511518153222</v>
       </c>
     </row>
-    <row r="8" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B8" s="118" t="s">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A8" s="132">
+        <v>0.35</v>
+      </c>
+      <c r="B8" s="190">
+        <f t="shared" si="0"/>
+        <v>5.2499999999999998E-2</v>
+      </c>
+      <c r="C8" s="186">
+        <f t="shared" si="5"/>
+        <v>0.21349708544021337</v>
+      </c>
+      <c r="D8" s="186">
+        <f t="shared" si="2"/>
+        <v>7.3709224025362258E-2</v>
+      </c>
+      <c r="E8" s="118" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="35">
-        <f>'18O Option 1'!D7</f>
+      <c r="G8" s="35">
+        <f>'18O Option 1'!G7</f>
         <v>1.2651399999999999</v>
       </c>
-      <c r="E8" s="2">
-        <f>'18O Option 1'!E7</f>
+      <c r="H8" s="2">
+        <f>'18O Option 1'!H7</f>
         <v>0.160803</v>
       </c>
-      <c r="F8" s="2">
-        <f t="shared" si="1"/>
+      <c r="I8" s="2">
+        <f t="shared" si="4"/>
         <v>0.43678576450431567</v>
       </c>
-      <c r="G8" s="2">
-        <f>'18O Option 1'!G7</f>
+      <c r="J8" s="2">
+        <f>'18O Option 1'!J7</f>
         <v>44.267000000000003</v>
       </c>
-      <c r="H8" s="3">
-        <f>'18O Option 1'!H7</f>
+      <c r="K8" s="3">
+        <f>'18O Option 1'!K7</f>
         <v>7.3781699999999999</v>
       </c>
-      <c r="M8">
-        <f>E8*SQRT(H8)</f>
+      <c r="P8">
+        <f>H8*SQRT(K8)</f>
         <v>0.43678576450431567</v>
       </c>
-      <c r="N8" t="s">
+      <c r="Q8" t="s">
         <v>48</v>
       </c>
-      <c r="P8" s="90">
-        <f>D8*$P$21/$D$5</f>
+      <c r="S8" s="90">
+        <f>G8*$S$21/$G$5</f>
         <v>0.31605285407275929</v>
       </c>
     </row>
-    <row r="9" spans="2:16" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="119"/>
-      <c r="C9" s="6" t="s">
+    <row r="9" spans="1:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="132">
+        <v>0.66</v>
+      </c>
+      <c r="B9" s="190">
+        <f t="shared" si="0"/>
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="C9" s="186">
+        <f t="shared" si="5"/>
+        <v>0.588290667105833</v>
+      </c>
+      <c r="D9" s="186">
+        <f t="shared" si="2"/>
+        <v>9.2993819237957895E-2</v>
+      </c>
+      <c r="E9" s="119"/>
+      <c r="F9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="34">
-        <f>'18O Option 1'!D8</f>
+      <c r="G9" s="34">
+        <f>'18O Option 1'!G8</f>
         <v>3.4860899999999999</v>
       </c>
-      <c r="E9" s="6">
-        <f>'18O Option 1'!E8</f>
+      <c r="H9" s="6">
+        <f>'18O Option 1'!H8</f>
         <v>0.202874</v>
       </c>
-      <c r="F9" s="6">
-        <f t="shared" si="1"/>
+      <c r="I9" s="6">
+        <f t="shared" si="4"/>
         <v>0.55106232587730664</v>
       </c>
-      <c r="G9" s="6">
-        <f>'18O Option 1'!G8</f>
+      <c r="J9" s="6">
+        <f>'18O Option 1'!J8</f>
         <v>44.267000000000003</v>
       </c>
-      <c r="H9" s="7">
-        <f>'18O Option 1'!H8</f>
+      <c r="K9" s="7">
+        <f>'18O Option 1'!K8</f>
         <v>7.3781699999999999</v>
       </c>
-      <c r="M9">
-        <f>E9*SQRT(H9)</f>
+      <c r="P9">
+        <f>H9*SQRT(K9)</f>
         <v>0.55106232587730664</v>
       </c>
-      <c r="P9" s="90">
-        <f>D9*$P$21/$D$5</f>
+      <c r="S9" s="90">
+        <f>G9*$S$21/$G$5</f>
         <v>0.87088282249751447</v>
       </c>
     </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B10" s="116" t="s">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A10" s="132">
+        <v>0.35</v>
+      </c>
+      <c r="B10" s="190">
+        <f t="shared" si="0"/>
+        <v>5.2499999999999998E-2</v>
+      </c>
+      <c r="C10" s="186">
+        <f t="shared" si="5"/>
+        <v>0.26199226477662496</v>
+      </c>
+      <c r="D10" s="186">
+        <f t="shared" si="2"/>
+        <v>4.0914960803506338E-2</v>
+      </c>
+      <c r="E10" s="116" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="132" t="s">
+      <c r="F10" s="132" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="164">
-        <f>I10*K10</f>
+      <c r="G10" s="164">
+        <f>L10*N10</f>
         <v>1.5525124999999997</v>
       </c>
-      <c r="E10" s="132">
-        <f>I10*L10</f>
+      <c r="H10" s="132">
+        <f>L10*O10</f>
         <v>5.8336249999999992E-2</v>
       </c>
-      <c r="F10" s="132">
-        <f>D10*SQRT(POWER((M10/K10),2)+POWER((J10/I10),2))</f>
+      <c r="I10" s="132">
+        <f>G10*SQRT(POWER((P10/N10),2)+POWER((M10/L10),2))</f>
         <v>0.24245367754888389</v>
       </c>
-      <c r="G10" s="132">
+      <c r="J10" s="132">
         <v>6.6882200000000003</v>
       </c>
-      <c r="H10" s="132">
+      <c r="K10" s="132">
         <v>1.3376399999999999</v>
       </c>
-      <c r="I10" s="2">
+      <c r="L10" s="2">
         <v>0.35</v>
       </c>
-      <c r="J10" s="2">
-        <f>0.15*I10</f>
+      <c r="M10" s="2">
+        <f>0.15*L10</f>
         <v>5.2499999999999998E-2</v>
       </c>
-      <c r="K10" s="2">
+      <c r="N10" s="2">
         <v>4.4357499999999996</v>
       </c>
-      <c r="L10" s="2">
+      <c r="O10" s="2">
         <v>0.16667499999999999</v>
       </c>
-      <c r="M10" s="3">
-        <f>L10*SQRT(H10)</f>
+      <c r="P10" s="3">
+        <f>O10*SQRT(K10)</f>
         <v>0.19277028408503472</v>
       </c>
-      <c r="P10" s="90">
-        <f>D10*$P$21/$D$5</f>
+      <c r="S10" s="90">
+        <f>G10*$S$21/$G$5</f>
         <v>0.38784324786872171</v>
       </c>
     </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B11" s="24" t="s">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A11" s="153">
+        <v>0.16</v>
+      </c>
+      <c r="B11" s="190">
+        <f t="shared" si="0"/>
+        <v>2.4E-2</v>
+      </c>
+      <c r="C11" s="186">
+        <f t="shared" si="5"/>
+        <v>0.11976789246931425</v>
+      </c>
+      <c r="D11" s="186">
+        <f t="shared" si="2"/>
+        <v>1.8703982081602902E-2</v>
+      </c>
+      <c r="E11" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="163" t="s">
+      <c r="F11" s="163" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="165">
-        <f>I11*K11</f>
+      <c r="G11" s="165">
+        <f>L11*N11</f>
         <v>0.70971999999999991</v>
       </c>
-      <c r="E11" s="163">
-        <f>I11*L11</f>
+      <c r="H11" s="163">
+        <f>L11*O11</f>
         <v>2.6667999999999997E-2</v>
       </c>
-      <c r="F11" s="163">
-        <f>D11*SQRT(POWER((M11/K11),2)+POWER((J11/I11),2))</f>
+      <c r="I11" s="163">
+        <f>G11*SQRT(POWER((P11/N11),2)+POWER((M11/L11),2))</f>
         <v>0.11083596687948978</v>
       </c>
-      <c r="G11" s="163">
+      <c r="J11" s="163">
         <v>6.6882200000000003</v>
       </c>
-      <c r="H11" s="163">
+      <c r="K11" s="163">
         <v>1.3376399999999999</v>
       </c>
-      <c r="I11" s="163">
+      <c r="L11" s="163">
         <v>0.16</v>
       </c>
-      <c r="J11" s="163">
-        <f>0.15*I11</f>
+      <c r="M11" s="163">
+        <f>0.15*L11</f>
         <v>2.4E-2</v>
       </c>
-      <c r="K11" s="163">
+      <c r="N11" s="163">
         <v>4.4357499999999996</v>
       </c>
-      <c r="L11" s="163">
+      <c r="O11" s="163">
         <v>0.16667499999999999</v>
       </c>
-      <c r="M11" s="25">
-        <f t="shared" ref="M11:M12" si="2">L11*SQRT(H11)</f>
+      <c r="P11" s="25">
+        <f t="shared" ref="P11:P12" si="6">O11*SQRT(K11)</f>
         <v>0.19277028408503472</v>
       </c>
-      <c r="P11" s="90">
-        <f>D11*$P$21/$D$5</f>
+      <c r="S11" s="90">
+        <f>G11*$S$21/$G$5</f>
         <v>0.17729977045427281</v>
       </c>
     </row>
-    <row r="12" spans="2:16" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="26" t="s">
+    <row r="12" spans="1:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="153">
+        <v>1.01</v>
+      </c>
+      <c r="B12" s="190">
+        <f t="shared" si="0"/>
+        <v>0.1515</v>
+      </c>
+      <c r="C12" s="186">
+        <f t="shared" si="5"/>
+        <v>0.75603482121254639</v>
+      </c>
+      <c r="D12" s="186">
+        <f t="shared" si="2"/>
+        <v>0.11806888689011831</v>
+      </c>
+      <c r="E12" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="161" t="s">
+      <c r="F12" s="161" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="166">
-        <f>I12*K12</f>
+      <c r="G12" s="166">
+        <f>L12*N12</f>
         <v>4.4801074999999999</v>
       </c>
-      <c r="E12" s="161">
-        <f>I12*L12</f>
+      <c r="H12" s="161">
+        <f>L12*O12</f>
         <v>0.16834174999999998</v>
       </c>
-      <c r="F12" s="161">
-        <f>D12*SQRT(POWER((M12/K12),2)+POWER((J12/I12),2))</f>
+      <c r="I12" s="161">
+        <f>G12*SQRT(POWER((P12/N12),2)+POWER((M12/L12),2))</f>
         <v>0.69965204092677924</v>
       </c>
-      <c r="G12" s="161">
+      <c r="J12" s="161">
         <v>6.6882200000000003</v>
       </c>
-      <c r="H12" s="161">
+      <c r="K12" s="161">
         <v>1.3376399999999999</v>
       </c>
-      <c r="I12" s="30">
+      <c r="L12" s="30">
         <v>1.01</v>
       </c>
-      <c r="J12" s="30">
-        <f>0.15*I12</f>
+      <c r="M12" s="30">
+        <f>0.15*L12</f>
         <v>0.1515</v>
       </c>
-      <c r="K12" s="30">
+      <c r="N12" s="30">
         <v>4.4357499999999996</v>
       </c>
-      <c r="L12" s="30">
+      <c r="O12" s="30">
         <v>0.16667499999999999</v>
       </c>
-      <c r="M12" s="31">
+      <c r="P12" s="31">
+        <f t="shared" si="6"/>
+        <v>0.19277028408503472</v>
+      </c>
+      <c r="S12" s="90">
+        <f>G12*$S$21/$G$5</f>
+        <v>1.1192048009925972</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="153">
+        <v>0.03</v>
+      </c>
+      <c r="B13" s="190">
+        <f t="shared" si="0"/>
+        <v>4.4999999999999997E-3</v>
+      </c>
+      <c r="C13" s="186">
+        <f t="shared" si="5"/>
+        <v>4.8557702590877952E-2</v>
+      </c>
+      <c r="D13" s="186">
         <f t="shared" si="2"/>
-        <v>0.19277028408503472</v>
-      </c>
-      <c r="P12" s="90">
-        <f>D12*$P$21/$D$5</f>
-        <v>1.1192048009925972</v>
-      </c>
-    </row>
-    <row r="13" spans="2:16" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="1" t="s">
+        <v>1.1963210218786179E-2</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="35">
-        <f>'18O Option 1'!D11</f>
+      <c r="G13" s="35">
+        <f>'18O Option 1'!G11</f>
         <v>0.28774300000000003</v>
       </c>
-      <c r="E13" s="134">
-        <f>'18O Option 1'!E11</f>
+      <c r="H13" s="134">
+        <f>'18O Option 1'!H11</f>
         <v>3.6374200000000002E-2</v>
       </c>
-      <c r="F13" s="2">
-        <f t="shared" si="1"/>
+      <c r="I13" s="2">
+        <f t="shared" si="4"/>
         <v>7.0891533460457984E-2</v>
       </c>
-      <c r="G13" s="2">
-        <f>'18O Option 1'!G11</f>
+      <c r="J13" s="2">
+        <f>'18O Option 1'!J11</f>
         <v>15.1936</v>
       </c>
-      <c r="H13" s="3">
-        <f>'18O Option 1'!H11</f>
+      <c r="K13" s="3">
+        <f>'18O Option 1'!K11</f>
         <v>3.7984100000000001</v>
       </c>
-      <c r="M13">
-        <f>E13*SQRT(H13)</f>
+      <c r="P13">
+        <f>H13*SQRT(K13)</f>
         <v>7.0891533460457984E-2</v>
       </c>
-      <c r="N13" t="s">
+      <c r="Q13" t="s">
         <v>48</v>
       </c>
-      <c r="P13" s="90">
-        <f>D13*$P$21/$D$5</f>
+      <c r="S13" s="90">
+        <f>G13*$S$21/$G$5</f>
         <v>7.1882950811339441E-2</v>
       </c>
     </row>
-    <row r="14" spans="2:16" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="8" t="s">
+    <row r="14" spans="1:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="153">
+        <v>0.03</v>
+      </c>
+      <c r="B14" s="190">
+        <f t="shared" si="0"/>
+        <v>4.4999999999999997E-3</v>
+      </c>
+      <c r="C14" s="186">
+        <f t="shared" si="5"/>
+        <v>4.7533198736990204E-2</v>
+      </c>
+      <c r="D14" s="186">
+        <f t="shared" si="2"/>
+        <v>8.7477873562453821E-3</v>
+      </c>
+      <c r="E14" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="F14" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="32">
-        <f>'18O Option 1'!D12</f>
+      <c r="G14" s="32">
+        <f>'18O Option 1'!G12</f>
         <v>0.28167199999999998</v>
       </c>
-      <c r="E14" s="133">
-        <f>'18O Option 1'!E12</f>
+      <c r="H14" s="133">
+        <f>'18O Option 1'!H12</f>
         <v>2.2748000000000001E-2</v>
       </c>
-      <c r="F14" s="9">
-        <f t="shared" si="1"/>
+      <c r="I14" s="9">
+        <f t="shared" si="4"/>
         <v>5.1837596157627529E-2</v>
       </c>
-      <c r="G14" s="9">
-        <f>'18O Option 1'!G12</f>
+      <c r="J14" s="9">
+        <f>'18O Option 1'!J12</f>
         <v>15.5784</v>
       </c>
-      <c r="H14" s="10">
-        <f>'18O Option 1'!H12</f>
+      <c r="K14" s="10">
+        <f>'18O Option 1'!K12</f>
         <v>5.1928200000000002</v>
       </c>
-      <c r="M14">
-        <f>E14*SQRT(H14)</f>
+      <c r="P14">
+        <f>H14*SQRT(K14)</f>
         <v>5.1837596157627529E-2</v>
       </c>
-      <c r="N14" t="s">
+      <c r="Q14" t="s">
         <v>48</v>
       </c>
-      <c r="P14" s="90">
-        <f>D14*$P$21/$D$5</f>
+      <c r="S14" s="90">
+        <f>G14*$S$21/$G$5</f>
         <v>7.0366314804987784E-2</v>
       </c>
     </row>
-    <row r="20" spans="16:16" x14ac:dyDescent="0.2">
-      <c r="P20" t="s">
+    <row r="20" spans="19:19" x14ac:dyDescent="0.2">
+      <c r="S20" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="21" spans="16:16" x14ac:dyDescent="0.2">
-      <c r="P21">
+    <row r="21" spans="19:19" x14ac:dyDescent="0.2">
+      <c r="S21">
         <v>1.2286999999999999</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="E8:E9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6783,23 +7189,23 @@
         <v>8</v>
       </c>
       <c r="D3" s="32">
-        <f>'18O Option 1'!D3</f>
+        <f>'18O Option 1'!G3</f>
         <v>6.1960600000000001</v>
       </c>
       <c r="E3" s="9">
-        <f>'18O Option 1'!E3</f>
+        <f>'18O Option 1'!H3</f>
         <v>0.50926499999999997</v>
       </c>
       <c r="F3" s="9">
-        <f>'18O Option 1'!F3</f>
+        <f>'18O Option 1'!I3</f>
         <v>0.84551640881286871</v>
       </c>
       <c r="G3" s="10">
-        <f>'18O Option 1'!G3</f>
+        <f>'18O Option 1'!J3</f>
         <v>8.2694700000000001</v>
       </c>
       <c r="H3">
-        <f>'18O Option 1'!H3</f>
+        <f>'18O Option 1'!K3</f>
         <v>2.7564899999999999</v>
       </c>
       <c r="L3" t="s">
@@ -6814,23 +7220,23 @@
         <v>10</v>
       </c>
       <c r="D4" s="32">
-        <f>'18O Option 1'!D4</f>
+        <f>'18O Option 1'!G4</f>
         <v>0.74325399999999997</v>
       </c>
       <c r="E4" s="9">
-        <f>'18O Option 1'!E4</f>
+        <f>'18O Option 1'!H4</f>
         <v>9.4910800000000003E-2</v>
       </c>
       <c r="F4" s="9">
-        <f>'18O Option 1'!F4</f>
+        <f>'18O Option 1'!I4</f>
         <v>0.10717148336994237</v>
       </c>
       <c r="G4" s="10">
-        <f>'18O Option 1'!G4</f>
+        <f>'18O Option 1'!J4</f>
         <v>10.2004</v>
       </c>
       <c r="H4">
-        <f>'18O Option 1'!H4</f>
+        <f>'18O Option 1'!K4</f>
         <v>1.27505</v>
       </c>
       <c r="L4" t="s">
@@ -6843,23 +7249,23 @@
         <v>11</v>
       </c>
       <c r="D5" s="32">
-        <f>'18O Option 1'!D5</f>
+        <f>'18O Option 1'!G5</f>
         <v>4.9184099999999997</v>
       </c>
       <c r="E5" s="9">
-        <f>'18O Option 1'!E5</f>
+        <f>'18O Option 1'!H5</f>
         <v>0.21648899999999999</v>
       </c>
       <c r="F5" s="9">
-        <f>'18O Option 1'!F5</f>
+        <f>'18O Option 1'!I5</f>
         <v>0.24445529131853752</v>
       </c>
       <c r="G5" s="10">
-        <f>'18O Option 1'!G5</f>
+        <f>'18O Option 1'!J5</f>
         <v>10.2004</v>
       </c>
       <c r="H5">
-        <f>'18O Option 1'!H5</f>
+        <f>'18O Option 1'!K5</f>
         <v>1.27505</v>
       </c>
     </row>
@@ -6933,23 +7339,23 @@
         <v>10</v>
       </c>
       <c r="D8" s="35">
-        <f>'18O Option 1'!D7</f>
+        <f>'18O Option 1'!G7</f>
         <v>1.2651399999999999</v>
       </c>
       <c r="E8" s="134">
-        <f>'18O Option 1'!E7</f>
+        <f>'18O Option 1'!H7</f>
         <v>0.160803</v>
       </c>
       <c r="F8" s="134">
-        <f>'18O Option 1'!F7</f>
+        <f>'18O Option 1'!I7</f>
         <v>0.43678576450431567</v>
       </c>
       <c r="G8" s="134">
-        <f>'18O Option 1'!G7</f>
+        <f>'18O Option 1'!J7</f>
         <v>44.267000000000003</v>
       </c>
       <c r="H8" s="134">
-        <f>'18O Option 1'!H7</f>
+        <f>'18O Option 1'!K7</f>
         <v>7.3781699999999999</v>
       </c>
       <c r="L8" t="s">
@@ -6962,23 +7368,23 @@
         <v>11</v>
       </c>
       <c r="D9" s="35">
-        <f>'18O Option 1'!D8</f>
+        <f>'18O Option 1'!G8</f>
         <v>3.4860899999999999</v>
       </c>
       <c r="E9" s="134">
-        <f>'18O Option 1'!E8</f>
+        <f>'18O Option 1'!H8</f>
         <v>0.202874</v>
       </c>
       <c r="F9" s="134">
-        <f>'18O Option 1'!F8</f>
+        <f>'18O Option 1'!I8</f>
         <v>0.55106232587730664</v>
       </c>
       <c r="G9" s="134">
-        <f>'18O Option 1'!G8</f>
+        <f>'18O Option 1'!J8</f>
         <v>44.267000000000003</v>
       </c>
       <c r="H9" s="134">
-        <f>'18O Option 1'!H8</f>
+        <f>'18O Option 1'!K8</f>
         <v>7.3781699999999999</v>
       </c>
     </row>
@@ -7146,23 +7552,23 @@
         <v>42</v>
       </c>
       <c r="D15" s="34">
-        <f>'18O Option 1'!D11</f>
+        <f>'18O Option 1'!G11</f>
         <v>0.28774300000000003</v>
       </c>
       <c r="E15" s="135">
-        <f>'18O Option 1'!E11</f>
+        <f>'18O Option 1'!H11</f>
         <v>3.6374200000000002E-2</v>
       </c>
       <c r="F15" s="135">
-        <f>'18O Option 1'!F11</f>
+        <f>'18O Option 1'!I11</f>
         <v>7.0891533460457984E-2</v>
       </c>
       <c r="G15" s="135">
-        <f>'18O Option 1'!G11</f>
+        <f>'18O Option 1'!J11</f>
         <v>15.1936</v>
       </c>
       <c r="H15" s="135">
-        <f>'18O Option 1'!H11</f>
+        <f>'18O Option 1'!K11</f>
         <v>3.7984100000000001</v>
       </c>
       <c r="L15" t="s">
@@ -7177,23 +7583,23 @@
         <v>12</v>
       </c>
       <c r="D16" s="34">
-        <f>'18O Option 1'!D12</f>
+        <f>'18O Option 1'!G12</f>
         <v>0.28167199999999998</v>
       </c>
       <c r="E16" s="135">
-        <f>'18O Option 1'!E12</f>
+        <f>'18O Option 1'!H12</f>
         <v>2.2748000000000001E-2</v>
       </c>
       <c r="F16" s="135">
-        <f>'18O Option 1'!F12</f>
+        <f>'18O Option 1'!I12</f>
         <v>5.1837596157627529E-2</v>
       </c>
       <c r="G16" s="135">
-        <f>'18O Option 1'!G12</f>
+        <f>'18O Option 1'!J12</f>
         <v>15.5784</v>
       </c>
       <c r="H16" s="135">
-        <f>'18O Option 1'!H12</f>
+        <f>'18O Option 1'!K12</f>
         <v>5.1928200000000002</v>
       </c>
       <c r="L16" t="s">
@@ -7217,626 +7623,821 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7253C9-71CE-6148-AA2F-0D73ACAD915E}">
-  <dimension ref="B2:K24"/>
+  <dimension ref="A2:O24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="13.1640625" customWidth="1"/>
+    <col min="4" max="4" width="13.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D2" t="s">
+    <row r="2" spans="1:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="183" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" s="183" t="s">
+        <v>117</v>
+      </c>
+      <c r="C2" s="183" t="s">
+        <v>113</v>
+      </c>
+      <c r="D2" s="183" t="s">
+        <v>114</v>
+      </c>
+      <c r="G2" t="s">
         <v>47</v>
       </c>
-      <c r="E2" t="s">
+      <c r="H2" t="s">
         <v>54</v>
       </c>
-      <c r="F2" t="s">
+      <c r="I2" t="s">
         <v>112</v>
       </c>
-      <c r="G2" t="s">
+      <c r="J2" t="s">
         <v>110</v>
       </c>
-      <c r="H2" t="s">
+      <c r="K2" t="s">
         <v>1</v>
       </c>
-      <c r="I2" t="s">
+      <c r="L2" t="s">
         <v>76</v>
       </c>
-      <c r="J2" t="s">
+      <c r="M2" t="s">
         <v>109</v>
       </c>
-      <c r="K2" t="s">
+      <c r="N2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="8" t="s">
+    <row r="3" spans="1:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C3" s="185">
+        <f>H3*A$7/H$7</f>
+        <v>0.93727303916393978</v>
+      </c>
+      <c r="D3" s="184">
+        <f>J3*A$7/H$7</f>
+        <v>0.16236840629611016</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="F3" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="9">
+      <c r="G3" s="9">
         <v>2.2913000000000001</v>
       </c>
-      <c r="E3" s="32">
-        <f t="shared" ref="E3:E17" si="0">D3*$D$23</f>
+      <c r="H3" s="32">
+        <f t="shared" ref="H3:H17" si="0">G3*$G$23</f>
         <v>7.4353114331521173</v>
       </c>
-      <c r="F3" s="9">
+      <c r="I3" s="9">
         <v>0.19059799999999999</v>
       </c>
-      <c r="G3" s="178">
-        <f>E3*SQRT(POWER(($E$23/$D$23),2)+POWER((J3/D3),2))</f>
+      <c r="J3" s="178">
+        <f>H3*SQRT(POWER(($H$23/$G$23),2)+POWER((M3/G3),2))</f>
         <v>1.2880554729207276</v>
       </c>
-      <c r="H3" s="10">
+      <c r="K3" s="10">
         <v>2.3610099999999998</v>
       </c>
-      <c r="I3">
+      <c r="L3">
         <v>0.78700300000000001</v>
       </c>
-      <c r="J3">
-        <f>F3</f>
+      <c r="M3">
+        <f>I3</f>
         <v>0.19059799999999999</v>
       </c>
-      <c r="K3" t="s">
+      <c r="N3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="2:11" ht="35" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="47" t="s">
+    <row r="4" spans="1:15" ht="35" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="B4">
+        <f>0.2*A4</f>
+        <v>2.0400000000000001E-2</v>
+      </c>
+      <c r="C4" s="185">
+        <f>H4*A$7/H$7</f>
+        <v>3.1968034149688587E-2</v>
+      </c>
+      <c r="D4" s="184">
+        <f>J4*A$7/H$7</f>
+        <v>0.11706195743194826</v>
+      </c>
+      <c r="E4" s="47" t="s">
         <v>53</v>
       </c>
-      <c r="C4" s="54" t="s">
+      <c r="F4" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="63">
+      <c r="G4" s="63">
         <v>7.8150499999999998E-2</v>
       </c>
-      <c r="E4" s="89">
+      <c r="H4" s="89">
         <f t="shared" si="0"/>
         <v>0.25359983684220944</v>
       </c>
-      <c r="F4" s="54">
+      <c r="I4" s="54">
         <v>0.100659</v>
       </c>
-      <c r="G4" s="179">
-        <f>E4*SQRT(POWER(($E$23/$D$23),2)+POWER((J4/D4),2))</f>
+      <c r="J4" s="179">
+        <f>H4*SQRT(POWER(($H$23/$G$23),2)+POWER((M4/G4),2))</f>
         <v>0.9286430678272074</v>
       </c>
-      <c r="H4" s="56">
+      <c r="K4" s="56">
         <v>80.688100000000006</v>
       </c>
-      <c r="I4" s="27">
+      <c r="L4" s="27">
         <v>8.0688099999999991</v>
       </c>
-      <c r="J4" s="27">
-        <f>F4*SQRT(I4)</f>
+      <c r="M4" s="27">
+        <f>I4*SQRT(L4)</f>
         <v>0.28592844085343383</v>
       </c>
     </row>
-    <row r="5" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="59" t="s">
+    <row r="5" spans="1:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <f>0.306+0.96+0.89</f>
+        <v>2.1560000000000001</v>
+      </c>
+      <c r="B5">
+        <f t="shared" ref="B5:B15" si="1">0.2*A5</f>
+        <v>0.43120000000000003</v>
+      </c>
+      <c r="C5" s="185">
+        <f t="shared" ref="C5:C15" si="2">H5*A$7/H$7</f>
+        <v>1.8565557373588095</v>
+      </c>
+      <c r="D5" s="184">
+        <f t="shared" ref="D5:D15" si="3">J5*A$7/H$7</f>
+        <v>0.56335248394980864</v>
+      </c>
+      <c r="E5" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="30" t="s">
+      <c r="F5" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="30">
+      <c r="G5" s="30">
         <v>4.5386199999999999</v>
       </c>
-      <c r="E5" s="41">
+      <c r="H5" s="41">
         <f t="shared" si="0"/>
         <v>14.72790694223055</v>
       </c>
-      <c r="F5" s="30">
+      <c r="I5" s="30">
         <v>0.41965799999999998</v>
       </c>
-      <c r="G5" s="179">
-        <f>E5*SQRT(POWER(($E$23/$D$23),2)+POWER((J5/D5),2))</f>
+      <c r="J5" s="179">
+        <f>H5*SQRT(POWER(($H$23/$G$23),2)+POWER((M5/G5),2))</f>
         <v>4.4690298235219004</v>
       </c>
-      <c r="H5" s="31">
+      <c r="K5" s="31">
         <v>80.688100000000006</v>
       </c>
-      <c r="I5" s="27">
+      <c r="L5" s="27">
         <v>8.0688099999999991</v>
       </c>
-      <c r="J5" s="27">
-        <f t="shared" ref="J5:J20" si="1">F5*SQRT(I5)</f>
+      <c r="M5" s="27">
+        <f t="shared" ref="M5:M20" si="4">I5*SQRT(L5)</f>
         <v>1.1920658622842499</v>
       </c>
     </row>
-    <row r="6" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="118" t="s">
+    <row r="6" spans="1:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>0.21</v>
+      </c>
+      <c r="B6">
+        <f t="shared" si="1"/>
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="C6" s="185">
+        <f t="shared" si="2"/>
+        <v>6.3662408951757635E-2</v>
+      </c>
+      <c r="D6" s="184">
+        <f t="shared" si="3"/>
+        <v>3.9924694264318557E-2</v>
+      </c>
+      <c r="E6" s="118" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="2">
+      <c r="G6" s="2">
         <v>0.15563199999999999</v>
       </c>
-      <c r="E6" s="35">
+      <c r="H6" s="35">
         <f t="shared" si="0"/>
         <v>0.50502875614905518</v>
       </c>
-      <c r="F6" s="2">
+      <c r="I6" s="2">
         <v>5.4237800000000003E-2</v>
       </c>
-      <c r="G6" s="180">
-        <f t="shared" ref="G6:G7" si="2">F6*SQRT(I6)</f>
+      <c r="J6" s="180">
+        <f>H6*SQRT(POWER(($H$23/$G$23),2)+POWER((M6/G6),2))</f>
+        <v>0.31671937986543069</v>
+      </c>
+      <c r="K6" s="3">
+        <v>24.385100000000001</v>
+      </c>
+      <c r="L6">
+        <v>3.04813</v>
+      </c>
+      <c r="M6" s="155">
+        <f t="shared" si="4"/>
         <v>9.4693203252016286E-2</v>
       </c>
-      <c r="H6" s="3">
-        <v>24.385100000000001</v>
-      </c>
-      <c r="I6">
-        <v>3.04813</v>
-      </c>
-      <c r="J6" s="155">
+      <c r="N6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>0.62</v>
+      </c>
+      <c r="B7">
         <f t="shared" si="1"/>
-        <v>9.4693203252016286E-2</v>
-      </c>
-      <c r="K6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="119"/>
-      <c r="C7" s="6" t="s">
+        <v>0.124</v>
+      </c>
+      <c r="C7" s="185">
+        <f t="shared" si="2"/>
+        <v>0.62</v>
+      </c>
+      <c r="D7" s="184">
+        <f>O7*A$7/H$7</f>
+        <v>0.12962512526033068</v>
+      </c>
+      <c r="E7" s="119"/>
+      <c r="F7" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="6">
+      <c r="G7" s="6">
         <v>1.5156799999999999</v>
       </c>
-      <c r="E7" s="34">
+      <c r="H7" s="34">
         <f t="shared" si="0"/>
         <v>4.9184099999999997</v>
       </c>
-      <c r="F7" s="6">
+      <c r="I7" s="6">
         <v>0.124664</v>
       </c>
-      <c r="G7" s="180">
+      <c r="J7" s="180">
+        <f t="shared" ref="J7" si="5">I7*SQRT(L7)</f>
+        <v>0.21764956340798039</v>
+      </c>
+      <c r="K7" s="7">
+        <v>24.385100000000001</v>
+      </c>
+      <c r="L7">
+        <v>3.04813</v>
+      </c>
+      <c r="M7" s="155">
+        <f t="shared" si="4"/>
+        <v>0.21764956340798039</v>
+      </c>
+      <c r="O7">
+        <f>H7*SQRT(POWER(($H$23/$G$23),2)+POWER((M7/G7),2))</f>
+        <v>1.0283056650510694</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C8" s="185">
         <f t="shared" si="2"/>
-        <v>0.21764956340798039</v>
-      </c>
-      <c r="H7" s="7">
-        <v>24.385100000000001</v>
-      </c>
-      <c r="I7">
-        <v>3.04813</v>
-      </c>
-      <c r="J7" s="155">
-        <f t="shared" si="1"/>
-        <v>0.21764956340798039</v>
-      </c>
-    </row>
-    <row r="8" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="125" t="s">
+        <v>0.28447523223899501</v>
+      </c>
+      <c r="D8" s="184">
+        <f t="shared" si="3"/>
+        <v>6.250543024555423E-2</v>
+      </c>
+      <c r="E8" s="125" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="F8" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="17">
+      <c r="G8" s="17">
         <v>0.69544099999999998</v>
       </c>
-      <c r="E8" s="37">
+      <c r="H8" s="37">
         <f t="shared" si="0"/>
         <v>2.2567190758009605</v>
       </c>
-      <c r="F8" s="17">
+      <c r="I8" s="17">
         <v>0.11036899999999999</v>
       </c>
-      <c r="G8" s="181">
-        <f>F8</f>
+      <c r="J8" s="181">
+        <f>H8*SQRT(POWER(($H$23/$G$23),2)+POWER((M8/G8),2))</f>
+        <v>0.49585053737747803</v>
+      </c>
+      <c r="K8" s="18">
+        <v>3.2037599999999999</v>
+      </c>
+      <c r="L8" s="19">
+        <v>0.457679</v>
+      </c>
+      <c r="M8" s="155">
+        <f>I8</f>
         <v>0.11036899999999999</v>
       </c>
-      <c r="H8" s="18">
-        <v>3.2037599999999999</v>
-      </c>
-      <c r="I8" s="19">
-        <v>0.457679</v>
-      </c>
-      <c r="J8" s="155">
-        <f>F8</f>
-        <v>0.11036899999999999</v>
-      </c>
-    </row>
-    <row r="9" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="120"/>
-      <c r="C9" s="19" t="s">
+    </row>
+    <row r="9" spans="1:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C9" s="185">
+        <f t="shared" si="2"/>
+        <v>0.56663438192758364</v>
+      </c>
+      <c r="D9" s="184">
+        <f t="shared" si="3"/>
+        <v>0.12048061901042045</v>
+      </c>
+      <c r="E9" s="120"/>
+      <c r="F9" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="19">
+      <c r="G9" s="19">
         <v>1.3852199999999999</v>
       </c>
-      <c r="E9" s="38">
+      <c r="H9" s="38">
         <f t="shared" si="0"/>
         <v>4.4950648555103978</v>
       </c>
-      <c r="F9" s="19">
+      <c r="I9" s="19">
         <v>0.206014</v>
       </c>
-      <c r="G9" s="181">
-        <f>F9</f>
+      <c r="J9" s="181">
+        <f>H9*SQRT(POWER(($H$23/$G$23),2)+POWER((M9/G9),2))</f>
+        <v>0.95576303443071298</v>
+      </c>
+      <c r="K9" s="20">
+        <v>3.2037599999999999</v>
+      </c>
+      <c r="L9" s="19">
+        <v>0.457679</v>
+      </c>
+      <c r="M9" s="155">
+        <f>I9</f>
         <v>0.206014</v>
       </c>
-      <c r="H9" s="20">
-        <v>3.2037599999999999</v>
-      </c>
-      <c r="I9" s="19">
-        <v>0.457679</v>
-      </c>
-      <c r="J9" s="155">
-        <f>F9</f>
-        <v>0.206014</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="118" t="s">
+    </row>
+    <row r="10" spans="1:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>0.17</v>
+      </c>
+      <c r="B10">
+        <f t="shared" si="1"/>
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="C10" s="185">
+        <f t="shared" si="2"/>
+        <v>0.14737312625356278</v>
+      </c>
+      <c r="D10" s="184">
+        <f t="shared" si="3"/>
+        <v>4.9414499209281496E-2</v>
+      </c>
+      <c r="E10" s="118" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="2">
+      <c r="G10" s="2">
         <v>0.36027500000000001</v>
       </c>
-      <c r="E10" s="35">
+      <c r="H10" s="35">
         <f t="shared" si="0"/>
         <v>1.169099125639977</v>
       </c>
-      <c r="F10" s="2">
+      <c r="I10" s="2">
         <v>6.9371299999999997E-2</v>
       </c>
-      <c r="G10" s="182">
-        <f>F10*SQRT(I10)</f>
+      <c r="J10" s="181">
+        <f t="shared" ref="J10:J17" si="6">H10*SQRT(POWER(($H$23/$G$23),2)+POWER((M10/G10),2))</f>
+        <v>0.39200123718697127</v>
+      </c>
+      <c r="K10" s="3">
+        <v>14.4574</v>
+      </c>
+      <c r="L10">
+        <v>2.4095599999999999</v>
+      </c>
+      <c r="M10" s="155">
+        <f t="shared" si="4"/>
         <v>0.10768338664574435</v>
       </c>
-      <c r="H10" s="3">
-        <v>14.4574</v>
-      </c>
-      <c r="I10">
-        <v>2.4095599999999999</v>
-      </c>
-      <c r="J10" s="155">
+      <c r="N10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>0.68</v>
+      </c>
+      <c r="B11">
         <f t="shared" si="1"/>
-        <v>0.10768338664574435</v>
-      </c>
-      <c r="K10" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="119"/>
-      <c r="C11" s="6" t="s">
+        <v>0.13600000000000001</v>
+      </c>
+      <c r="C11" s="185">
+        <f t="shared" si="2"/>
+        <v>0.77927055842921999</v>
+      </c>
+      <c r="D11" s="184">
+        <f t="shared" si="3"/>
+        <v>0.1398217521058201</v>
+      </c>
+      <c r="E11" s="119"/>
+      <c r="F11" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="6">
+      <c r="G11" s="6">
         <v>1.9050400000000001</v>
       </c>
-      <c r="E11" s="34">
+      <c r="H11" s="34">
         <f t="shared" si="0"/>
         <v>6.181890495619129</v>
       </c>
-      <c r="F11" s="6">
+      <c r="I11" s="6">
         <v>0.117092</v>
       </c>
-      <c r="G11" s="182">
-        <f t="shared" ref="G11:G15" si="3">F11*SQRT(I11)</f>
+      <c r="J11" s="181">
+        <f t="shared" si="6"/>
+        <v>1.1091946835077204</v>
+      </c>
+      <c r="K11" s="7">
+        <v>14.4574</v>
+      </c>
+      <c r="L11">
+        <v>2.4095599999999999</v>
+      </c>
+      <c r="M11" s="155">
+        <f t="shared" si="4"/>
         <v>0.18175907196669946</v>
       </c>
-      <c r="H11" s="7">
-        <v>14.4574</v>
-      </c>
-      <c r="I11">
-        <v>2.4095599999999999</v>
-      </c>
-      <c r="J11" s="155">
+    </row>
+    <row r="12" spans="1:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="B12">
         <f t="shared" si="1"/>
-        <v>0.18175907196669946</v>
-      </c>
-    </row>
-    <row r="12" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="46" t="s">
+        <v>1.4800000000000001E-2</v>
+      </c>
+      <c r="C12" s="185">
+        <f t="shared" si="2"/>
+        <v>0.17371969017206801</v>
+      </c>
+      <c r="D12" s="184">
+        <f t="shared" si="3"/>
+        <v>5.8351435999446651E-2</v>
+      </c>
+      <c r="E12" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="F12" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D12" s="9">
+      <c r="G12" s="9">
         <v>0.42468299999999998</v>
       </c>
-      <c r="E12" s="32">
+      <c r="H12" s="32">
         <f t="shared" si="0"/>
         <v>1.3781042924825821</v>
       </c>
-      <c r="F12" s="9">
+      <c r="I12" s="9">
         <v>8.5518999999999998E-2</v>
       </c>
-      <c r="G12" s="182">
+      <c r="J12" s="181">
+        <f t="shared" si="6"/>
+        <v>0.46289723602264254</v>
+      </c>
+      <c r="K12" s="10">
+        <v>11.064500000000001</v>
+      </c>
+      <c r="L12">
+        <v>2.2128999999999999</v>
+      </c>
+      <c r="M12" s="155">
+        <f t="shared" si="4"/>
+        <v>0.12721651911586365</v>
+      </c>
+      <c r="N12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="35" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>1.22</v>
+      </c>
+      <c r="B13">
+        <f t="shared" si="1"/>
+        <v>0.24399999999999999</v>
+      </c>
+      <c r="C13" s="185">
+        <f t="shared" si="2"/>
+        <v>0.90132099123825615</v>
+      </c>
+      <c r="D13" s="184">
         <f t="shared" si="3"/>
-        <v>0.12721651911586365</v>
-      </c>
-      <c r="H12" s="10">
-        <v>11.064500000000001</v>
-      </c>
-      <c r="I12">
-        <v>2.2128999999999999</v>
-      </c>
-      <c r="J12" s="155">
-        <f t="shared" si="1"/>
-        <v>0.12721651911586365</v>
-      </c>
-      <c r="K12" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="13" spans="2:11" ht="35" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="61" t="s">
+        <v>0.1598991881359931</v>
+      </c>
+      <c r="E13" s="61" t="s">
         <v>56</v>
       </c>
-      <c r="C13" s="52" t="s">
+      <c r="F13" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="52">
+      <c r="G13" s="52">
         <v>2.2034099999999999</v>
       </c>
-      <c r="E13" s="51">
+      <c r="H13" s="51">
         <f t="shared" si="0"/>
         <v>7.1501067363163733</v>
       </c>
-      <c r="F13" s="52">
+      <c r="I13" s="52">
         <v>7.1556900000000007E-2</v>
       </c>
-      <c r="G13" s="182">
-        <f>E13*SQRT(POWER((E$23/D$23),2)+POWER((J13/D13),2))</f>
+      <c r="J13" s="181">
+        <f t="shared" si="6"/>
         <v>1.2684673643870159</v>
       </c>
-      <c r="H13" s="53">
+      <c r="K13" s="53">
         <v>55.631799999999998</v>
       </c>
-      <c r="I13" s="68">
+      <c r="L13" s="68">
         <v>7.9474</v>
       </c>
-      <c r="J13" s="155">
+      <c r="M13" s="155">
+        <f t="shared" si="4"/>
+        <v>0.20172701105742313</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>0.17</v>
+      </c>
+      <c r="B14">
         <f t="shared" si="1"/>
-        <v>0.20172701105742313</v>
-      </c>
-    </row>
-    <row r="14" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="118" t="s">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="C14" s="185">
+        <f t="shared" si="2"/>
+        <v>0.15681294204581445</v>
+      </c>
+      <c r="D14" s="184">
+        <f t="shared" si="3"/>
+        <v>6.2524695841850123E-2</v>
+      </c>
+      <c r="E14" s="118" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="F14" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="2">
+      <c r="G14" s="2">
         <v>0.38335200000000003</v>
       </c>
-      <c r="E14" s="35">
+      <c r="H14" s="35">
         <f t="shared" si="0"/>
         <v>1.2439844230444423</v>
       </c>
-      <c r="F14" s="2">
+      <c r="I14" s="2">
         <v>9.3142699999999995E-2</v>
       </c>
-      <c r="G14" s="182">
-        <f>E14*SQRT(POWER((E$23/D$23),2)+POWER((J14/D14),2))</f>
+      <c r="J14" s="181">
+        <f t="shared" si="6"/>
         <v>0.49600336979921622</v>
       </c>
-      <c r="H14" s="3">
+      <c r="K14" s="3">
         <v>13.811199999999999</v>
       </c>
-      <c r="I14">
+      <c r="L14">
         <v>2.30186</v>
       </c>
-      <c r="J14" s="155">
+      <c r="M14" s="155">
+        <f t="shared" si="4"/>
+        <v>0.14131500430575206</v>
+      </c>
+      <c r="N14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>0.51</v>
+      </c>
+      <c r="B15">
         <f t="shared" si="1"/>
-        <v>0.14131500430575206</v>
-      </c>
-      <c r="K14" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="119"/>
-      <c r="C15" s="6" t="s">
+        <v>0.10200000000000001</v>
+      </c>
+      <c r="C15" s="185">
+        <f t="shared" si="2"/>
+        <v>0.47113995038530559</v>
+      </c>
+      <c r="D15" s="184">
+        <f t="shared" si="3"/>
+        <v>0.10209210505229416</v>
+      </c>
+      <c r="E15" s="119"/>
+      <c r="F15" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="6">
+      <c r="G15" s="6">
         <v>1.15177</v>
       </c>
-      <c r="E15" s="34">
+      <c r="H15" s="34">
         <f t="shared" si="0"/>
         <v>3.7375152312493403</v>
       </c>
-      <c r="F15" s="6">
+      <c r="I15" s="6">
         <v>0.117274</v>
       </c>
-      <c r="G15" s="182">
-        <f t="shared" ref="G15:G20" si="4">E15*SQRT(POWER((E$23/D$23),2)+POWER((J15/D15),2))</f>
+      <c r="J15" s="181">
+        <f t="shared" si="6"/>
         <v>0.80988843614557104</v>
       </c>
-      <c r="H15" s="7">
+      <c r="K15" s="7">
         <v>13.811199999999999</v>
       </c>
-      <c r="I15">
+      <c r="L15">
         <v>2.30186</v>
       </c>
-      <c r="J15" s="155">
-        <f t="shared" si="1"/>
+      <c r="M15" s="155">
+        <f t="shared" si="4"/>
         <v>0.1779267276442788</v>
       </c>
     </row>
-    <row r="16" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="42" t="s">
+    <row r="16" spans="1:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E16" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="43" t="s">
+      <c r="F16" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="D16" s="43">
+      <c r="G16" s="43">
         <v>0</v>
       </c>
-      <c r="E16" s="44">
+      <c r="H16" s="44">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F16" s="43">
+      <c r="I16" s="43">
         <v>0.76793</v>
       </c>
-      <c r="G16" s="182"/>
-      <c r="H16" s="45">
+      <c r="J16" s="181"/>
+      <c r="K16" s="45">
         <v>8.1551799999999997</v>
       </c>
-      <c r="I16" s="43">
+      <c r="L16" s="43">
         <v>2.0387900000000001</v>
       </c>
-      <c r="J16" s="155">
-        <f t="shared" si="1"/>
+      <c r="M16" s="155">
+        <f t="shared" si="4"/>
         <v>1.0964980949592529</v>
       </c>
     </row>
-    <row r="17" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="64" t="s">
+    <row r="17" spans="5:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E17" s="64" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="43" t="s">
+      <c r="F17" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="43">
+      <c r="G17" s="43">
         <v>2.44</v>
       </c>
-      <c r="E17" s="44">
+      <c r="H17" s="44">
         <f t="shared" si="0"/>
         <v>7.9178457194130694</v>
       </c>
-      <c r="F17" s="43">
+      <c r="I17" s="43">
         <v>0.27806199999999998</v>
       </c>
-      <c r="G17" s="182">
+      <c r="J17" s="181">
+        <f t="shared" si="6"/>
+        <v>1.7628245835591634</v>
+      </c>
+      <c r="K17" s="45">
+        <v>8.1551799999999997</v>
+      </c>
+      <c r="L17" s="43">
+        <v>2.0387900000000001</v>
+      </c>
+      <c r="M17" s="155">
         <f t="shared" si="4"/>
-        <v>1.7628245835591634</v>
-      </c>
-      <c r="H17" s="45">
-        <v>8.1551799999999997</v>
-      </c>
-      <c r="I17" s="43">
-        <v>2.0387900000000001</v>
-      </c>
-      <c r="J17" s="155">
-        <f t="shared" si="1"/>
         <v>0.39703417405305141</v>
       </c>
     </row>
-    <row r="18" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="64" t="s">
+    <row r="18" spans="5:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E18" s="64" t="s">
         <v>83</v>
       </c>
-      <c r="C18" s="43" t="s">
+      <c r="F18" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="43">
+      <c r="G18" s="43">
         <v>0</v>
       </c>
-      <c r="E18" s="44">
-        <f t="shared" ref="E18:E19" si="5">D18*$D$23</f>
+      <c r="H18" s="44">
+        <f t="shared" ref="H18:H19" si="7">G18*$G$23</f>
         <v>0</v>
       </c>
-      <c r="F18" s="43"/>
-      <c r="G18" s="182"/>
-      <c r="H18" s="45"/>
       <c r="I18" s="43"/>
-      <c r="J18" s="155">
-        <f t="shared" si="1"/>
+      <c r="J18" s="182"/>
+      <c r="K18" s="45"/>
+      <c r="L18" s="43"/>
+      <c r="M18" s="155">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="64" t="s">
+    <row r="19" spans="5:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E19" s="64" t="s">
         <v>84</v>
       </c>
-      <c r="C19" s="43" t="s">
+      <c r="F19" s="43" t="s">
         <v>82</v>
       </c>
-      <c r="D19" s="43">
+      <c r="G19" s="43">
         <v>0.26</v>
       </c>
-      <c r="E19" s="44">
-        <f t="shared" si="5"/>
+      <c r="H19" s="44">
+        <f t="shared" si="7"/>
         <v>0.84370487174073694</v>
       </c>
-      <c r="F19" s="43"/>
-      <c r="G19" s="182"/>
-      <c r="H19" s="45"/>
       <c r="I19" s="43"/>
-      <c r="J19" s="155">
-        <f t="shared" si="1"/>
+      <c r="J19" s="182"/>
+      <c r="K19" s="45"/>
+      <c r="L19" s="43"/>
+      <c r="M19" s="155">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:10" ht="35" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="65" t="s">
+    <row r="20" spans="5:13" ht="35" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E20" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="50" t="s">
+      <c r="F20" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="50">
+      <c r="G20" s="50">
         <v>0.80409799999999998</v>
       </c>
-      <c r="E20" s="66">
-        <f>D20*$D$23</f>
+      <c r="H20" s="66">
+        <f>G20*$G$23</f>
         <v>2.6093130767576271</v>
       </c>
-      <c r="F20" s="50">
+      <c r="I20" s="50">
         <v>0.103809</v>
       </c>
-      <c r="G20" s="182">
+      <c r="J20" s="182">
+        <f t="shared" ref="J15:J20" si="8">H20*SQRT(POWER((H$23/G$23),2)+POWER((M20/G20),2))</f>
+        <v>0.43080050069535031</v>
+      </c>
+      <c r="K20" s="67">
+        <v>1.25024</v>
+      </c>
+      <c r="L20" s="14">
+        <v>0.25004900000000002</v>
+      </c>
+      <c r="M20" s="155">
         <f t="shared" si="4"/>
-        <v>0.43080050069535031</v>
-      </c>
-      <c r="H20" s="67">
-        <v>1.25024</v>
-      </c>
-      <c r="I20" s="14">
-        <v>0.25004900000000002</v>
-      </c>
-      <c r="J20" s="155">
-        <f t="shared" si="1"/>
         <v>5.1909586391779013E-2</v>
       </c>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="D22" t="s">
+    <row r="22" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="G22" t="s">
         <v>61</v>
       </c>
-      <c r="E22" t="s">
+      <c r="H22" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="D23">
-        <f>'18O Option 1'!D5/D7</f>
+    <row r="23" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="G23">
+        <f>'18O Option 1'!G5/G7</f>
         <v>3.2450187374643726</v>
       </c>
-      <c r="E23">
-        <f>D23*SQRT(POWER(('18O Option 1'!F5/'18O Option 1'!D5),2)+POWER(('18F norm Option 1'!G7/'18F norm Option 1'!D7),2))</f>
+      <c r="H23">
+        <f>G23*SQRT(POWER(('18O Option 1'!I5/'18O Option 1'!G5),2)+POWER(('18F norm Option 1'!J7/'18F norm Option 1'!G7),2))</f>
         <v>0.4931026033780847</v>
       </c>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="D24" t="s">
+    <row r="24" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="G24" t="s">
         <v>63</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="E10:E11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7844,955 +8445,1202 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{821ECE62-53CE-CB41-9599-014ED0A08C45}">
-  <dimension ref="B2:O39"/>
+  <dimension ref="A2:R39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="132"/>
-      <c r="C2" s="132"/>
-      <c r="D2" s="132" t="s">
+    <row r="2" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="183" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" s="183" t="s">
+        <v>117</v>
+      </c>
+      <c r="C2" s="183" t="s">
+        <v>113</v>
+      </c>
+      <c r="D2" s="183" t="s">
+        <v>114</v>
+      </c>
+      <c r="E2" s="132"/>
+      <c r="F2" s="132"/>
+      <c r="G2" s="132" t="s">
         <v>47</v>
       </c>
-      <c r="E2" s="132" t="s">
+      <c r="H2" s="132" t="s">
         <v>54</v>
       </c>
-      <c r="F2" s="132" t="s">
+      <c r="I2" s="132" t="s">
         <v>112</v>
       </c>
-      <c r="G2" s="132" t="s">
+      <c r="J2" s="132" t="s">
         <v>110</v>
       </c>
-      <c r="H2" s="132" t="s">
+      <c r="K2" s="132" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="132" t="s">
+      <c r="L2" s="132" t="s">
         <v>76</v>
       </c>
-      <c r="J2" s="132" t="s">
+      <c r="M2" s="132" t="s">
         <v>32</v>
       </c>
-      <c r="K2" s="132" t="s">
+      <c r="N2" s="132" t="s">
         <v>104</v>
       </c>
-      <c r="L2" s="132" t="s">
+      <c r="O2" s="132" t="s">
         <v>3</v>
       </c>
-      <c r="M2" s="132" t="s">
+      <c r="P2" s="132" t="s">
         <v>105</v>
       </c>
-      <c r="N2" s="132" t="s">
+      <c r="Q2" s="132" t="s">
         <v>106</v>
       </c>
-      <c r="O2" t="s">
+      <c r="R2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="69" t="s">
+    <row r="3" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C3" s="90">
+        <f>H3*$A$9/$H$9</f>
+        <v>0.93727303916393978</v>
+      </c>
+      <c r="D3" s="90">
+        <f>J3*$A$9/$H$9</f>
+        <v>0.16236840629611016</v>
+      </c>
+      <c r="E3" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="2">
-        <f>'18F norm Option 1'!D3</f>
+      <c r="G3" s="2">
+        <f>'18F norm Option 1'!G3</f>
         <v>2.2913000000000001</v>
       </c>
-      <c r="E3" s="35">
-        <f>'18F norm Option 1'!E3</f>
+      <c r="H3" s="35">
+        <f>'18F norm Option 1'!H3</f>
         <v>7.4353114331521173</v>
       </c>
-      <c r="F3" s="2">
-        <v>0.32842500000000002</v>
-      </c>
-      <c r="G3" s="136"/>
-      <c r="H3" s="2">
-        <v>0.870116</v>
-      </c>
-      <c r="I3" s="3"/>
-      <c r="J3" s="132"/>
-      <c r="K3" s="132"/>
-      <c r="L3" s="132"/>
+      <c r="I3" s="134">
+        <f>'18F norm Option 1'!I3</f>
+        <v>0.19059799999999999</v>
+      </c>
+      <c r="J3" s="134">
+        <f>'18F norm Option 1'!J3</f>
+        <v>1.2880554729207276</v>
+      </c>
+      <c r="K3" s="134">
+        <f>'18F norm Option 1'!K3</f>
+        <v>2.3610099999999998</v>
+      </c>
+      <c r="L3" s="134">
+        <f>'18F norm Option 1'!L3</f>
+        <v>0.78700300000000001</v>
+      </c>
       <c r="M3" s="132"/>
       <c r="N3" s="132"/>
-      <c r="O3" t="s">
+      <c r="O3" s="132"/>
+      <c r="P3" s="132"/>
+      <c r="Q3" s="132"/>
+      <c r="R3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="2:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="124" t="s">
+    <row r="4" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="B4">
+        <f>0.2*A4</f>
+        <v>2.0400000000000001E-2</v>
+      </c>
+      <c r="C4" s="90">
+        <f>H4*$A$9/$H$9</f>
+        <v>0.12893044151799851</v>
+      </c>
+      <c r="D4" s="90">
+        <f>J4*$A$9/$H$9</f>
+        <v>3.6356043750632172E-2</v>
+      </c>
+      <c r="E4" s="124" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="54" t="s">
+      <c r="F4" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="54">
-        <f>J4*L4</f>
+      <c r="G4" s="54">
+        <f>M4*O4</f>
         <v>0.31518917999999996</v>
       </c>
-      <c r="E4" s="55">
-        <f t="shared" ref="E4:E7" si="0">D4*$D$29</f>
+      <c r="H4" s="55">
+        <f>G4*$G$29</f>
         <v>1.0227947949460308</v>
       </c>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54">
-        <f>E4*SQRT(POWER(($E$29/$D$29),2)+POWER((N4/L4),2)+POWER((K4/J4),2))</f>
+      <c r="I4" s="54"/>
+      <c r="J4" s="54">
+        <f>H4*SQRT(POWER(($H$29/$G$29),2)+POWER((Q4/O4),2)+POWER((N4/M4),2))</f>
         <v>0.28840956313475286</v>
       </c>
-      <c r="H4" s="54">
+      <c r="K4" s="54">
         <v>86.371700000000004</v>
       </c>
-      <c r="I4" s="54">
+      <c r="L4" s="54">
         <v>7.8519699999999997</v>
       </c>
-      <c r="J4" s="54">
+      <c r="M4" s="54">
         <v>0.10199999999999999</v>
       </c>
-      <c r="K4" s="54">
-        <f>0.2*J4</f>
+      <c r="N4" s="54">
+        <f>0.2*M4</f>
         <v>2.0400000000000001E-2</v>
       </c>
-      <c r="L4" s="54">
+      <c r="O4" s="54">
         <v>3.09009</v>
       </c>
-      <c r="M4" s="54">
+      <c r="P4" s="54">
         <v>0.141321</v>
       </c>
-      <c r="N4" s="56">
-        <f>M4*SQRT(I4)</f>
+      <c r="Q4" s="56">
+        <f>P4*SQRT(L4)</f>
         <v>0.39600075842500704</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B5" s="126"/>
-      <c r="C5" s="161" t="s">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>0.30599999999999999</v>
+      </c>
+      <c r="B5">
+        <f t="shared" ref="B5:B18" si="0">0.2*A5</f>
+        <v>6.1200000000000004E-2</v>
+      </c>
+      <c r="C5" s="90">
+        <f t="shared" ref="C5:C25" si="1">H5*$A$9/$H$9</f>
+        <v>0.38679132455399562</v>
+      </c>
+      <c r="D5" s="90">
+        <f t="shared" ref="D5:D18" si="2">J5*$A$9/$H$9</f>
+        <v>0.10906813125189653</v>
+      </c>
+      <c r="E5" s="126"/>
+      <c r="F5" s="161" t="s">
         <v>58</v>
       </c>
-      <c r="D5" s="161">
-        <f>J5*L5</f>
+      <c r="G5" s="161">
+        <f>M5*O5</f>
         <v>0.94556753999999998</v>
       </c>
-      <c r="E5" s="166">
+      <c r="H5" s="166">
+        <f>G5*$G$29</f>
+        <v>3.0683843848380925</v>
+      </c>
+      <c r="I5" s="161"/>
+      <c r="J5" s="161">
+        <f>H5*SQRT(POWER(($H$29/$G$29),2)+POWER((Q5/O5),2)+POWER((N5/M5),2))</f>
+        <v>0.86522868940425868</v>
+      </c>
+      <c r="K5" s="161">
+        <v>86.371700000000004</v>
+      </c>
+      <c r="L5" s="161">
+        <v>7.8519699999999997</v>
+      </c>
+      <c r="M5" s="161">
+        <v>0.30599999999999999</v>
+      </c>
+      <c r="N5" s="161">
+        <f t="shared" ref="N5:N7" si="3">0.2*M5</f>
+        <v>6.1200000000000004E-2</v>
+      </c>
+      <c r="O5" s="161">
+        <v>3.09009</v>
+      </c>
+      <c r="P5" s="161">
+        <v>0.141321</v>
+      </c>
+      <c r="Q5" s="28">
+        <f t="shared" ref="Q5:Q7" si="4">P5*SQRT(L5)</f>
+        <v>0.39600075842500704</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="17" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>0.96</v>
+      </c>
+      <c r="B6">
         <f t="shared" si="0"/>
-        <v>3.0683843848380925</v>
-      </c>
-      <c r="F5" s="161"/>
-      <c r="G5" s="161">
-        <f>E5*SQRT(POWER(($E$29/$D$29),2)+POWER((N5/L5),2)+POWER((K5/J5),2))</f>
-        <v>0.86522868940425868</v>
-      </c>
-      <c r="H5" s="161">
+        <v>0.192</v>
+      </c>
+      <c r="C6" s="90">
+        <f t="shared" si="1"/>
+        <v>1.2134629789929272</v>
+      </c>
+      <c r="D6" s="90">
+        <f t="shared" si="2"/>
+        <v>0.34217452941771459</v>
+      </c>
+      <c r="E6" s="62" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="161" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" s="161">
+        <f>M6*O6</f>
+        <v>2.9664864</v>
+      </c>
+      <c r="H6" s="166">
+        <f>G6*$G$29</f>
+        <v>9.626303952433231</v>
+      </c>
+      <c r="I6" s="161"/>
+      <c r="J6" s="161">
+        <f>H6*SQRT(POWER(($H$29/$G$29),2)+POWER((Q6/O6),2)+POWER((N6/M6),2))</f>
+        <v>2.7144429471506153</v>
+      </c>
+      <c r="K6" s="161">
         <v>86.371700000000004</v>
       </c>
-      <c r="I5" s="161">
+      <c r="L6" s="161">
         <v>7.8519699999999997</v>
       </c>
-      <c r="J5" s="161">
-        <v>0.30599999999999999</v>
-      </c>
-      <c r="K5" s="161">
-        <f t="shared" ref="K5:K7" si="1">0.2*J5</f>
-        <v>6.1200000000000004E-2</v>
-      </c>
-      <c r="L5" s="161">
+      <c r="M6" s="161">
+        <v>0.96</v>
+      </c>
+      <c r="N6" s="161">
+        <f t="shared" si="3"/>
+        <v>0.192</v>
+      </c>
+      <c r="O6" s="161">
         <v>3.09009</v>
       </c>
-      <c r="M5" s="161">
+      <c r="P6" s="161">
         <v>0.141321</v>
       </c>
-      <c r="N5" s="28">
-        <f t="shared" ref="N5:N7" si="2">M5*SQRT(I5)</f>
+      <c r="Q6" s="28">
+        <f t="shared" si="4"/>
         <v>0.39600075842500704</v>
       </c>
     </row>
-    <row r="6" spans="2:15" ht="17" x14ac:dyDescent="0.2">
-      <c r="B6" s="62" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="161" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="161">
-        <f>J6*L6</f>
-        <v>2.9664864</v>
-      </c>
-      <c r="E6" s="166">
+    <row r="7" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>0.89</v>
+      </c>
+      <c r="B7">
         <f t="shared" si="0"/>
-        <v>9.626303952433231</v>
-      </c>
-      <c r="F6" s="161"/>
-      <c r="G6" s="161">
-        <f>E6*SQRT(POWER(($E$29/$D$29),2)+POWER((N6/L6),2)+POWER((K6/J6),2))</f>
-        <v>2.7144429471506153</v>
-      </c>
-      <c r="H6" s="161">
+        <v>0.17800000000000002</v>
+      </c>
+      <c r="C7" s="90">
+        <f t="shared" si="1"/>
+        <v>1.12498130344136</v>
+      </c>
+      <c r="D7" s="90">
+        <f t="shared" si="2"/>
+        <v>0.31722430331433965</v>
+      </c>
+      <c r="E7" s="59" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" s="30">
+        <f>M7*O7</f>
+        <v>2.7501801000000001</v>
+      </c>
+      <c r="H7" s="41">
+        <f>G7*$G$29</f>
+        <v>8.9243859559016432</v>
+      </c>
+      <c r="I7" s="30"/>
+      <c r="J7" s="30">
+        <f>H7*SQRT(POWER(($H$29/$G$29),2)+POWER((Q7/O7),2)+POWER((N7/M7),2))</f>
+        <v>2.5165148155875503</v>
+      </c>
+      <c r="K7" s="30">
         <v>86.371700000000004</v>
       </c>
-      <c r="I6" s="161">
+      <c r="L7" s="30">
         <v>7.8519699999999997</v>
       </c>
-      <c r="J6" s="161">
-        <v>0.96</v>
-      </c>
-      <c r="K6" s="161">
+      <c r="M7" s="30">
+        <v>0.89</v>
+      </c>
+      <c r="N7" s="30">
+        <f t="shared" si="3"/>
+        <v>0.17800000000000002</v>
+      </c>
+      <c r="O7" s="30">
+        <v>3.09009</v>
+      </c>
+      <c r="P7" s="30">
+        <v>0.141321</v>
+      </c>
+      <c r="Q7" s="31">
+        <f t="shared" si="4"/>
+        <v>0.39600075842500704</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>0.21</v>
+      </c>
+      <c r="B8">
+        <f t="shared" si="0"/>
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="C8" s="90">
         <f t="shared" si="1"/>
-        <v>0.192</v>
-      </c>
-      <c r="L6" s="161">
-        <v>3.09009</v>
-      </c>
-      <c r="M6" s="161">
-        <v>0.141321</v>
-      </c>
-      <c r="N6" s="28">
+        <v>6.3662408951757635E-2</v>
+      </c>
+      <c r="D8" s="90">
         <f t="shared" si="2"/>
-        <v>0.39600075842500704</v>
-      </c>
-    </row>
-    <row r="7" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="59" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="30">
-        <f>J7*L7</f>
-        <v>2.7501801000000001</v>
-      </c>
-      <c r="E7" s="41">
-        <f t="shared" si="0"/>
-        <v>8.9243859559016432</v>
-      </c>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30">
-        <f>E7*SQRT(POWER(($E$29/$D$29),2)+POWER((N7/L7),2)+POWER((K7/J7),2))</f>
-        <v>2.5165148155875503</v>
-      </c>
-      <c r="H7" s="30">
-        <v>86.371700000000004</v>
-      </c>
-      <c r="I7" s="30">
-        <v>7.8519699999999997</v>
-      </c>
-      <c r="J7" s="30">
-        <v>0.89</v>
-      </c>
-      <c r="K7" s="30">
-        <f t="shared" si="1"/>
-        <v>0.17800000000000002</v>
-      </c>
-      <c r="L7" s="30">
-        <v>3.09009</v>
-      </c>
-      <c r="M7" s="30">
-        <v>0.141321</v>
-      </c>
-      <c r="N7" s="31">
-        <f t="shared" si="2"/>
-        <v>0.39600075842500704</v>
-      </c>
-    </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B8" s="118" t="s">
+        <v>3.9924694264318557E-2</v>
+      </c>
+      <c r="E8" s="118" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="2">
-        <f>'18F norm Option 1'!D6</f>
+      <c r="G8" s="2">
+        <f>'18F norm Option 1'!G6</f>
         <v>0.15563199999999999</v>
       </c>
-      <c r="E8" s="35">
-        <f>'18F norm Option 1'!E6</f>
+      <c r="H8" s="35">
+        <f>'18F norm Option 1'!H6</f>
         <v>0.50502875614905518</v>
       </c>
-      <c r="F8" s="134">
-        <f>'18F norm Option 1'!F6</f>
+      <c r="I8" s="134">
+        <f>'18F norm Option 1'!I6</f>
         <v>5.4237800000000003E-2</v>
       </c>
-      <c r="G8" s="169">
-        <f>'18F norm Option 1'!G6</f>
-        <v>9.4693203252016286E-2</v>
-      </c>
-      <c r="H8" s="134">
-        <f>'18F norm Option 1'!H6</f>
+      <c r="J8" s="169">
+        <f>'18F norm Option 1'!J6</f>
+        <v>0.31671937986543069</v>
+      </c>
+      <c r="K8" s="134">
+        <f>'18F norm Option 1'!K6</f>
         <v>24.385100000000001</v>
       </c>
-      <c r="I8" s="170">
-        <f>'18F norm Option 1'!I6</f>
+      <c r="L8" s="170">
+        <f>'18F norm Option 1'!L6</f>
         <v>3.04813</v>
       </c>
-      <c r="J8" s="132"/>
-      <c r="K8" s="132"/>
-      <c r="L8" s="132"/>
       <c r="M8" s="132"/>
       <c r="N8" s="132"/>
-      <c r="O8" t="s">
+      <c r="O8" s="132"/>
+      <c r="P8" s="132"/>
+      <c r="Q8" s="132"/>
+      <c r="R8" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="119"/>
-      <c r="C9" s="6" t="s">
+    <row r="9" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>0.62</v>
+      </c>
+      <c r="B9">
+        <f t="shared" si="0"/>
+        <v>0.124</v>
+      </c>
+      <c r="C9" s="90">
+        <f t="shared" si="1"/>
+        <v>0.62</v>
+      </c>
+      <c r="D9" s="90">
+        <f t="shared" si="2"/>
+        <v>0.12962512526033068</v>
+      </c>
+      <c r="E9" s="119"/>
+      <c r="F9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="6">
-        <f>'18F norm Option 1'!D7</f>
+      <c r="G9" s="6">
+        <f>'18F norm Option 1'!G7</f>
         <v>1.5156799999999999</v>
       </c>
-      <c r="E9" s="34">
-        <f>'18F norm Option 1'!E7</f>
+      <c r="H9" s="34">
+        <f>'18F norm Option 1'!H7</f>
         <v>4.9184099999999997</v>
       </c>
-      <c r="F9" s="135">
-        <f>'18F norm Option 1'!F7</f>
+      <c r="I9" s="135">
+        <f>'18F norm Option 1'!I7</f>
         <v>0.124664</v>
       </c>
-      <c r="G9" s="171">
-        <f>'18F norm Option 1'!G7</f>
-        <v>0.21764956340798039</v>
-      </c>
-      <c r="H9" s="135">
-        <f>'18F norm Option 1'!H7</f>
+      <c r="J9" s="171">
+        <f>'18F norm Option 1'!O7</f>
+        <v>1.0283056650510694</v>
+      </c>
+      <c r="K9" s="135">
+        <f>'18F norm Option 1'!K7</f>
         <v>24.385100000000001</v>
       </c>
-      <c r="I9" s="172">
-        <f>'18F norm Option 1'!I7</f>
+      <c r="L9" s="172">
+        <f>'18F norm Option 1'!L7</f>
         <v>3.04813</v>
       </c>
-      <c r="J9" s="132"/>
-      <c r="K9" s="132"/>
-      <c r="L9" s="132"/>
       <c r="M9" s="132"/>
       <c r="N9" s="132"/>
-    </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B10" s="125" t="s">
+      <c r="O9" s="132"/>
+      <c r="P9" s="132"/>
+      <c r="Q9" s="132"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="C10" s="90"/>
+      <c r="D10" s="90"/>
+      <c r="E10" s="125" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="F10" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="2"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="136">
-        <f t="shared" ref="G10:G23" si="3">F10*SQRT(I10)</f>
+      <c r="G10" s="2"/>
+      <c r="H10" s="35"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="136">
+        <f t="shared" ref="J10:J11" si="5">I10*SQRT(L10)</f>
         <v>0</v>
       </c>
-      <c r="H10" s="2"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="132"/>
-      <c r="K10" s="132"/>
-      <c r="L10" s="132"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="3"/>
       <c r="M10" s="132"/>
       <c r="N10" s="132"/>
-      <c r="O10" t="s">
+      <c r="O10" s="132"/>
+      <c r="P10" s="132"/>
+      <c r="Q10" s="132"/>
+      <c r="R10" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="121"/>
-      <c r="C11" s="22" t="s">
+    <row r="11" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C11" s="90"/>
+      <c r="D11" s="90"/>
+      <c r="E11" s="121"/>
+      <c r="F11" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="6"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="173">
-        <f t="shared" si="3"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="34"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="173">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="H11" s="6"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="132"/>
-      <c r="K11" s="132"/>
-      <c r="L11" s="132"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="7"/>
       <c r="M11" s="132"/>
       <c r="N11" s="132"/>
-    </row>
-    <row r="12" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="118" t="s">
+      <c r="O11" s="132"/>
+      <c r="P11" s="132"/>
+      <c r="Q11" s="132"/>
+    </row>
+    <row r="12" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>0.17</v>
+      </c>
+      <c r="B12">
+        <f t="shared" si="0"/>
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="C12" s="90">
+        <f t="shared" si="1"/>
+        <v>0.14737312625356278</v>
+      </c>
+      <c r="D12" s="90">
+        <f t="shared" si="2"/>
+        <v>4.9414499209281496E-2</v>
+      </c>
+      <c r="E12" s="118" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="F12" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="D12" s="2">
-        <f>'18F norm Option 1'!D10</f>
-        <v>0.36027500000000001</v>
-      </c>
-      <c r="E12" s="35">
-        <f t="shared" ref="E12:E21" si="4">D12*$D$29</f>
-        <v>1.169099125639977</v>
-      </c>
-      <c r="F12" s="2">
-        <f>'18F norm Option 1'!F10</f>
-        <v>6.9371299999999997E-2</v>
       </c>
       <c r="G12" s="2">
         <f>'18F norm Option 1'!G10</f>
-        <v>0.10768338664574435</v>
-      </c>
-      <c r="H12" s="2">
-        <f>'18F norm Option 1'!H10</f>
-        <v>14.4574</v>
+        <v>0.36027500000000001</v>
+      </c>
+      <c r="H12" s="35">
+        <f>G12*$G$29</f>
+        <v>1.169099125639977</v>
       </c>
       <c r="I12" s="2">
         <f>'18F norm Option 1'!I10</f>
+        <v>6.9371299999999997E-2</v>
+      </c>
+      <c r="J12" s="2">
+        <f>'18F norm Option 1'!J10</f>
+        <v>0.39200123718697127</v>
+      </c>
+      <c r="K12" s="2">
+        <f>'18F norm Option 1'!K10</f>
+        <v>14.4574</v>
+      </c>
+      <c r="L12" s="2">
+        <f>'18F norm Option 1'!L10</f>
         <v>2.4095599999999999</v>
       </c>
-      <c r="J12" s="132"/>
-      <c r="K12" s="132"/>
-      <c r="L12" s="132"/>
       <c r="M12" s="132"/>
       <c r="N12" s="132"/>
-      <c r="O12" t="s">
+      <c r="O12" s="132"/>
+      <c r="P12" s="132"/>
+      <c r="Q12" s="132"/>
+      <c r="R12" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="119"/>
-      <c r="C13" s="6" t="s">
+    <row r="13" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>0.68</v>
+      </c>
+      <c r="B13">
+        <f t="shared" si="0"/>
+        <v>0.13600000000000001</v>
+      </c>
+      <c r="C13" s="90">
+        <f t="shared" si="1"/>
+        <v>0.77927055842921999</v>
+      </c>
+      <c r="D13" s="90">
+        <f t="shared" si="2"/>
+        <v>0.1398217521058201</v>
+      </c>
+      <c r="E13" s="119"/>
+      <c r="F13" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D13" s="6">
-        <f>'18F norm Option 1'!D11</f>
+      <c r="G13" s="6">
+        <f>'18F norm Option 1'!G11</f>
         <v>1.9050400000000001</v>
       </c>
-      <c r="E13" s="34">
-        <f t="shared" si="4"/>
+      <c r="H13" s="34">
+        <f>G13*$G$29</f>
         <v>6.181890495619129</v>
-      </c>
-      <c r="F13" s="2">
-        <f>'18F norm Option 1'!F11</f>
-        <v>0.117092</v>
-      </c>
-      <c r="G13" s="2">
-        <f>'18F norm Option 1'!G11</f>
-        <v>0.18175907196669946</v>
-      </c>
-      <c r="H13" s="2">
-        <f>'18F norm Option 1'!H11</f>
-        <v>14.4574</v>
       </c>
       <c r="I13" s="2">
         <f>'18F norm Option 1'!I11</f>
+        <v>0.117092</v>
+      </c>
+      <c r="J13" s="2">
+        <f>'18F norm Option 1'!J11</f>
+        <v>1.1091946835077204</v>
+      </c>
+      <c r="K13" s="2">
+        <f>'18F norm Option 1'!K11</f>
+        <v>14.4574</v>
+      </c>
+      <c r="L13" s="2">
+        <f>'18F norm Option 1'!L11</f>
         <v>2.4095599999999999</v>
       </c>
-      <c r="J13" s="132"/>
-      <c r="K13" s="132"/>
-      <c r="L13" s="132"/>
       <c r="M13" s="132"/>
       <c r="N13" s="132"/>
-    </row>
-    <row r="14" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="1" t="s">
+      <c r="O13" s="132"/>
+      <c r="P13" s="132"/>
+      <c r="Q13" s="132"/>
+    </row>
+    <row r="14" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="B14">
+        <f t="shared" si="0"/>
+        <v>1.4800000000000001E-2</v>
+      </c>
+      <c r="C14" s="90">
+        <f t="shared" si="1"/>
+        <v>0.17371969017206801</v>
+      </c>
+      <c r="D14" s="90">
+        <f t="shared" si="2"/>
+        <v>5.8351435999446651E-2</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="F14" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D14" s="6">
-        <f>'18F norm Option 1'!D12</f>
+      <c r="G14" s="6">
+        <f>'18F norm Option 1'!G12</f>
         <v>0.42468299999999998</v>
       </c>
-      <c r="E14" s="35">
-        <f t="shared" si="4"/>
+      <c r="H14" s="35">
+        <f>G14*$G$29</f>
         <v>1.3781042924825821</v>
-      </c>
-      <c r="F14" s="2">
-        <f>'18F norm Option 1'!F12</f>
-        <v>8.5518999999999998E-2</v>
-      </c>
-      <c r="G14" s="2">
-        <f>'18F norm Option 1'!G12</f>
-        <v>0.12721651911586365</v>
-      </c>
-      <c r="H14" s="2">
-        <f>'18F norm Option 1'!H12</f>
-        <v>11.064500000000001</v>
       </c>
       <c r="I14" s="2">
         <f>'18F norm Option 1'!I12</f>
+        <v>8.5518999999999998E-2</v>
+      </c>
+      <c r="J14" s="2">
+        <f>'18F norm Option 1'!J12</f>
+        <v>0.46289723602264254</v>
+      </c>
+      <c r="K14" s="2">
+        <f>'18F norm Option 1'!K12</f>
+        <v>11.064500000000001</v>
+      </c>
+      <c r="L14" s="2">
+        <f>'18F norm Option 1'!L12</f>
         <v>2.2128999999999999</v>
       </c>
-      <c r="J14" s="132"/>
-      <c r="K14" s="132"/>
-      <c r="L14" s="132"/>
       <c r="M14" s="132"/>
       <c r="N14" s="132"/>
-      <c r="O14" t="s">
+      <c r="O14" s="132"/>
+      <c r="P14" s="132"/>
+      <c r="Q14" s="132"/>
+      <c r="R14" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B15" s="70" t="s">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>1.04</v>
+      </c>
+      <c r="B15">
+        <f t="shared" si="0"/>
+        <v>0.20800000000000002</v>
+      </c>
+      <c r="C15" s="90">
+        <f t="shared" si="1"/>
+        <v>0.88432825926316905</v>
+      </c>
+      <c r="D15" s="90">
+        <f t="shared" si="2"/>
+        <v>0.23641906556009859</v>
+      </c>
+      <c r="E15" s="70" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="48" t="s">
+      <c r="F15" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="48">
-        <f>J15*L15</f>
+      <c r="G15" s="48">
+        <f>M15*O15</f>
         <v>2.1618688000000001</v>
       </c>
-      <c r="E15" s="57">
-        <f>D15*$D$29</f>
+      <c r="H15" s="57">
+        <f>G15*$G$29</f>
         <v>7.0153047639396187</v>
       </c>
-      <c r="F15" s="48"/>
-      <c r="G15" s="48">
-        <f>E15*SQRT(POWER(($E$29/$D$29),2)+POWER((N15/L15),2)+POWER((K15/J15),2))</f>
+      <c r="I15" s="48"/>
+      <c r="J15" s="48">
+        <f>H15*SQRT(POWER(($H$29/$G$29),2)+POWER((Q15/O15),2)+POWER((N15/M15),2))</f>
         <v>1.875493381034588</v>
       </c>
-      <c r="H15" s="48">
+      <c r="K15" s="48">
         <v>55.631799999999998</v>
       </c>
-      <c r="I15" s="48">
+      <c r="L15" s="48">
         <v>7.9474</v>
       </c>
-      <c r="J15" s="48">
+      <c r="M15" s="48">
         <v>1.04</v>
       </c>
-      <c r="K15" s="48">
-        <f>0.2*J15</f>
+      <c r="N15" s="48">
+        <f>0.2*M15</f>
         <v>0.20800000000000002</v>
       </c>
-      <c r="L15" s="48">
+      <c r="O15" s="48">
         <v>2.0787200000000001</v>
       </c>
-      <c r="M15" s="48">
+      <c r="P15" s="48">
         <v>6.7506200000000002E-2</v>
       </c>
-      <c r="N15" s="71">
-        <f>M15*SQRT(I15)</f>
+      <c r="Q15" s="71">
+        <f>P15*SQRT(L15)</f>
         <v>0.19030762866815942</v>
       </c>
-      <c r="O15" t="s">
+      <c r="R15" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="16" spans="2:15" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="73" t="s">
+    <row r="16" spans="1:18" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>0.18</v>
+      </c>
+      <c r="B16">
+        <f t="shared" si="0"/>
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="C16" s="90">
+        <f t="shared" si="1"/>
+        <v>0.15305681410324079</v>
+      </c>
+      <c r="D16" s="90">
+        <f t="shared" si="2"/>
+        <v>4.0918684423863198E-2</v>
+      </c>
+      <c r="E16" s="73" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="74" t="s">
+      <c r="F16" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="D16" s="74">
-        <f>J16*L16</f>
+      <c r="G16" s="74">
+        <f>M16*O16</f>
         <v>0.37416959999999999</v>
       </c>
-      <c r="E16" s="75">
-        <f>D16*$D$29</f>
+      <c r="H16" s="75">
+        <f>G16*$G$29</f>
         <v>1.2141873629895492</v>
       </c>
-      <c r="F16" s="74"/>
-      <c r="G16" s="74">
-        <f>E16*SQRT(POWER(($E$29/$D$29),2)+POWER((N16/L16),2)+POWER((K16/J16),2))</f>
+      <c r="I16" s="74"/>
+      <c r="J16" s="74">
+        <f>H16*SQRT(POWER(($H$29/$G$29),2)+POWER((Q16/O16),2)+POWER((N16/M16),2))</f>
         <v>0.32460462364060161</v>
       </c>
-      <c r="H16" s="74">
+      <c r="K16" s="74">
         <v>55.631799999999998</v>
       </c>
-      <c r="I16" s="74">
+      <c r="L16" s="74">
         <v>7.9474</v>
       </c>
-      <c r="J16" s="74">
+      <c r="M16" s="74">
         <v>0.18</v>
       </c>
-      <c r="K16" s="74">
-        <f>0.2*J16</f>
+      <c r="N16" s="74">
+        <f>0.2*M16</f>
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="L16" s="74">
+      <c r="O16" s="74">
         <v>2.0787200000000001</v>
       </c>
-      <c r="M16" s="74">
+      <c r="P16" s="74">
         <v>6.7506200000000002E-2</v>
       </c>
-      <c r="N16" s="76">
-        <f t="shared" ref="N16:N21" si="5">M16*SQRT(I16)</f>
+      <c r="Q16" s="76">
+        <f t="shared" ref="Q16:Q21" si="6">P16*SQRT(L16)</f>
         <v>0.19030762866815942</v>
       </c>
     </row>
-    <row r="17" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="118" t="s">
+    <row r="17" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>0.17</v>
+      </c>
+      <c r="B17">
+        <f t="shared" si="0"/>
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="C17" s="90">
+        <f t="shared" si="1"/>
+        <v>0.15681294204581445</v>
+      </c>
+      <c r="D17" s="90">
+        <f t="shared" si="2"/>
+        <v>6.2524695841850123E-2</v>
+      </c>
+      <c r="E17" s="118" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="F17" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="D17" s="2">
-        <f>'18F norm Option 1'!D14</f>
-        <v>0.38335200000000003</v>
-      </c>
-      <c r="E17" s="35">
-        <f>'18F norm Option 1'!E14</f>
-        <v>1.2439844230444423</v>
-      </c>
-      <c r="F17" s="2">
-        <f>'18F norm Option 1'!F14</f>
-        <v>9.3142699999999995E-2</v>
       </c>
       <c r="G17" s="2">
         <f>'18F norm Option 1'!G14</f>
-        <v>0.49600336979921622</v>
-      </c>
-      <c r="H17" s="2">
+        <v>0.38335200000000003</v>
+      </c>
+      <c r="H17" s="35">
         <f>'18F norm Option 1'!H14</f>
-        <v>13.811199999999999</v>
+        <v>1.2439844230444423</v>
       </c>
       <c r="I17" s="2">
         <f>'18F norm Option 1'!I14</f>
+        <v>9.3142699999999995E-2</v>
+      </c>
+      <c r="J17" s="2">
+        <f>'18F norm Option 1'!J14</f>
+        <v>0.49600336979921622</v>
+      </c>
+      <c r="K17" s="2">
+        <f>'18F norm Option 1'!K14</f>
+        <v>13.811199999999999</v>
+      </c>
+      <c r="L17" s="2">
+        <f>'18F norm Option 1'!L14</f>
         <v>2.30186</v>
       </c>
-      <c r="J17" s="132"/>
-      <c r="K17" s="132"/>
-      <c r="L17" s="132"/>
       <c r="M17" s="132"/>
-      <c r="N17" s="153"/>
-      <c r="O17" t="s">
+      <c r="N17" s="132"/>
+      <c r="O17" s="132"/>
+      <c r="P17" s="132"/>
+      <c r="Q17" s="153"/>
+      <c r="R17" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="122"/>
-      <c r="C18" s="132" t="s">
+    <row r="18" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>0.51</v>
+      </c>
+      <c r="B18">
+        <f t="shared" si="0"/>
+        <v>0.10200000000000001</v>
+      </c>
+      <c r="C18" s="90">
+        <f t="shared" si="1"/>
+        <v>0.47113995038530559</v>
+      </c>
+      <c r="D18" s="90">
+        <f t="shared" si="2"/>
+        <v>0.10209210505229416</v>
+      </c>
+      <c r="E18" s="122"/>
+      <c r="F18" s="132" t="s">
         <v>11</v>
-      </c>
-      <c r="D18" s="2">
-        <f>'18F norm Option 1'!D15</f>
-        <v>1.15177</v>
-      </c>
-      <c r="E18" s="35">
-        <f>'18F norm Option 1'!E15</f>
-        <v>3.7375152312493403</v>
-      </c>
-      <c r="F18" s="2">
-        <f>'18F norm Option 1'!F15</f>
-        <v>0.117274</v>
       </c>
       <c r="G18" s="2">
         <f>'18F norm Option 1'!G15</f>
-        <v>0.80988843614557104</v>
-      </c>
-      <c r="H18" s="2">
+        <v>1.15177</v>
+      </c>
+      <c r="H18" s="35">
         <f>'18F norm Option 1'!H15</f>
-        <v>13.811199999999999</v>
+        <v>3.7375152312493403</v>
       </c>
       <c r="I18" s="2">
         <f>'18F norm Option 1'!I15</f>
+        <v>0.117274</v>
+      </c>
+      <c r="J18" s="2">
+        <f>'18F norm Option 1'!J15</f>
+        <v>0.80988843614557104</v>
+      </c>
+      <c r="K18" s="2">
+        <f>'18F norm Option 1'!K15</f>
+        <v>13.811199999999999</v>
+      </c>
+      <c r="L18" s="2">
+        <f>'18F norm Option 1'!L15</f>
         <v>2.30186</v>
       </c>
-      <c r="J18" s="132"/>
-      <c r="K18" s="132"/>
-      <c r="L18" s="132"/>
       <c r="M18" s="132"/>
-      <c r="N18" s="153"/>
-    </row>
-    <row r="19" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="81" t="s">
+      <c r="N18" s="132"/>
+      <c r="O18" s="132"/>
+      <c r="P18" s="132"/>
+      <c r="Q18" s="153"/>
+    </row>
+    <row r="19" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C19" s="90"/>
+      <c r="E19" s="81" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="58" t="s">
+      <c r="F19" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="D19" s="58">
+      <c r="G19" s="58">
         <f>0.2*1.42</f>
         <v>0.28399999999999997</v>
       </c>
-      <c r="E19" s="82">
-        <f t="shared" si="4"/>
+      <c r="H19" s="82">
+        <f>G19*$G$29</f>
         <v>0.9215853214398817</v>
       </c>
-      <c r="F19" s="58"/>
-      <c r="G19" s="58">
-        <f>E19*SQRT(POWER(($E$29/$D$29),2)+POWER((N19/L19),2)+POWER((K19/J19),2))</f>
+      <c r="I19" s="58"/>
+      <c r="J19" s="58">
+        <f>H19*SQRT(POWER(($H$29/$G$29),2)+POWER((Q19/O19),2)+POWER((N19/M19),2))</f>
         <v>0.25725005957972208</v>
       </c>
-      <c r="H19" s="58">
+      <c r="K19" s="58">
         <v>13.728</v>
       </c>
-      <c r="I19" s="58">
+      <c r="L19" s="58">
         <v>2.74559</v>
       </c>
-      <c r="J19" s="58">
+      <c r="M19" s="58">
         <v>0.16</v>
       </c>
-      <c r="K19" s="58">
-        <f>0.2*J19</f>
+      <c r="N19" s="58">
+        <f>0.2*M19</f>
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="L19" s="58">
+      <c r="O19" s="58">
         <v>2.4052099999999998</v>
       </c>
-      <c r="M19" s="58">
+      <c r="P19" s="58">
         <v>0.17675399999999999</v>
       </c>
-      <c r="N19" s="83">
-        <f t="shared" si="5"/>
+      <c r="Q19" s="83">
+        <f t="shared" si="6"/>
         <v>0.29287823118587092</v>
       </c>
-      <c r="O19" t="s">
+      <c r="R19" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="20" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="64" t="s">
+    <row r="20" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C20" s="90"/>
+      <c r="E20" s="64" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="157" t="s">
+      <c r="F20" s="157" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="157">
+      <c r="G20" s="157">
         <f>0.75*1.42</f>
         <v>1.0649999999999999</v>
       </c>
-      <c r="E20" s="168">
-        <f>D20*$D$29</f>
+      <c r="H20" s="168">
+        <f>G20*$G$29</f>
         <v>3.4559449553995565</v>
       </c>
-      <c r="F20" s="157"/>
-      <c r="G20" s="58">
-        <f t="shared" ref="G20:G21" si="6">E20*SQRT(POWER(($E$29/$D$29),2)+POWER((N20/L20),2)+POWER((K20/J20),2))</f>
+      <c r="I20" s="157"/>
+      <c r="J20" s="58">
+        <f t="shared" ref="J20:J21" si="7">H20*SQRT(POWER(($H$29/$G$29),2)+POWER((Q20/O20),2)+POWER((N20/M20),2))</f>
         <v>0.96468772342395792</v>
       </c>
-      <c r="H20" s="157">
+      <c r="K20" s="157">
         <v>13.728</v>
       </c>
-      <c r="I20" s="157">
+      <c r="L20" s="157">
         <v>2.74559</v>
       </c>
-      <c r="J20" s="157">
+      <c r="M20" s="157">
         <v>1.01</v>
       </c>
-      <c r="K20" s="157">
-        <f t="shared" ref="K20:K21" si="7">0.2*J20</f>
+      <c r="N20" s="157">
+        <f t="shared" ref="N20:N21" si="8">0.2*M20</f>
         <v>0.20200000000000001</v>
       </c>
-      <c r="L20" s="157">
+      <c r="O20" s="157">
         <v>2.4052099999999998</v>
       </c>
-      <c r="M20" s="157">
+      <c r="P20" s="157">
         <v>0.17675399999999999</v>
       </c>
-      <c r="N20" s="45">
-        <f t="shared" si="5"/>
+      <c r="Q20" s="45">
+        <f t="shared" si="6"/>
         <v>0.29287823118587092</v>
       </c>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B21" s="64" t="s">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="C21" s="90"/>
+      <c r="E21" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="C21" s="157" t="s">
+      <c r="F21" s="157" t="s">
         <v>10</v>
       </c>
-      <c r="D21" s="157">
+      <c r="G21" s="157">
         <v>0</v>
       </c>
-      <c r="E21" s="168">
-        <f t="shared" si="4"/>
+      <c r="H21" s="168">
+        <f>G21*$G$29</f>
         <v>0</v>
       </c>
-      <c r="F21" s="157"/>
-      <c r="G21" s="58">
+      <c r="I21" s="157"/>
+      <c r="J21" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="157">
+        <v>13.728</v>
+      </c>
+      <c r="L21" s="157">
+        <v>2.74559</v>
+      </c>
+      <c r="M21" s="157">
+        <v>0.35</v>
+      </c>
+      <c r="N21" s="157">
+        <f t="shared" si="8"/>
+        <v>6.9999999999999993E-2</v>
+      </c>
+      <c r="O21" s="157">
+        <v>2.4052099999999998</v>
+      </c>
+      <c r="P21" s="157">
+        <v>0.17675399999999999</v>
+      </c>
+      <c r="Q21" s="45">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H21" s="157">
-        <v>13.728</v>
-      </c>
-      <c r="I21" s="157">
-        <v>2.74559</v>
-      </c>
-      <c r="J21" s="157">
-        <v>0.35</v>
-      </c>
-      <c r="K21" s="157">
-        <f t="shared" si="7"/>
-        <v>6.9999999999999993E-2</v>
-      </c>
-      <c r="L21" s="157">
-        <v>2.4052099999999998</v>
-      </c>
-      <c r="M21" s="157">
-        <v>0.17675399999999999</v>
-      </c>
-      <c r="N21" s="45">
-        <f t="shared" si="5"/>
         <v>0.29287823118587092</v>
       </c>
     </row>
-    <row r="22" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="84" t="s">
+    <row r="22" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C22" s="90"/>
+      <c r="E22" s="84" t="s">
         <v>81</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="F22" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="D22" s="15">
+      <c r="G22" s="15">
         <v>0.03</v>
       </c>
-      <c r="E22" s="36"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
+      <c r="H22" s="36"/>
       <c r="I22" s="15"/>
       <c r="J22" s="15"/>
       <c r="K22" s="15"/>
       <c r="L22" s="15"/>
       <c r="M22" s="15"/>
-      <c r="N22" s="16"/>
-    </row>
-    <row r="23" spans="2:15" ht="35" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="65" t="s">
+      <c r="N22" s="15"/>
+      <c r="O22" s="15"/>
+      <c r="P22" s="15"/>
+      <c r="Q22" s="16"/>
+    </row>
+    <row r="23" spans="1:18" ht="35" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C23" s="90"/>
+      <c r="E23" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="C23" s="50" t="s">
+      <c r="F23" s="50" t="s">
         <v>13</v>
-      </c>
-      <c r="D23" s="50">
-        <f>'18F norm Option 1'!D20</f>
-        <v>0.80409799999999998</v>
-      </c>
-      <c r="E23" s="66">
-        <f>'18F norm Option 1'!E20</f>
-        <v>2.6093130767576271</v>
-      </c>
-      <c r="F23" s="50">
-        <f>'18F norm Option 1'!F20</f>
-        <v>0.103809</v>
       </c>
       <c r="G23" s="50">
         <f>'18F norm Option 1'!G20</f>
-        <v>0.43080050069535031</v>
-      </c>
-      <c r="H23" s="50">
+        <v>0.80409799999999998</v>
+      </c>
+      <c r="H23" s="66">
         <f>'18F norm Option 1'!H20</f>
-        <v>1.25024</v>
+        <v>2.6093130767576271</v>
       </c>
       <c r="I23" s="50">
         <f>'18F norm Option 1'!I20</f>
+        <v>0.103809</v>
+      </c>
+      <c r="J23" s="50">
+        <f>'18F norm Option 1'!J20</f>
+        <v>0.43080050069535031</v>
+      </c>
+      <c r="K23" s="50">
+        <f>'18F norm Option 1'!K20</f>
+        <v>1.25024</v>
+      </c>
+      <c r="L23" s="50">
+        <f>'18F norm Option 1'!L20</f>
         <v>0.25004900000000002</v>
       </c>
-      <c r="J23" s="132"/>
-      <c r="K23" s="132"/>
-      <c r="L23" s="132"/>
       <c r="M23" s="132"/>
       <c r="N23" s="132"/>
-      <c r="O23" t="s">
+      <c r="O23" s="132"/>
+      <c r="P23" s="132"/>
+      <c r="Q23" s="132"/>
+      <c r="R23" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="2:15" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="174" t="s">
+    <row r="24" spans="1:18" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C24" s="90">
+        <f t="shared" si="1"/>
+        <v>0.24543439248390164</v>
+      </c>
+      <c r="E24" s="174" t="s">
         <v>96</v>
       </c>
-      <c r="C24" s="136" t="s">
+      <c r="F24" s="136" t="s">
         <v>97</v>
       </c>
-      <c r="D24" s="136">
+      <c r="G24" s="136">
         <v>0.6</v>
       </c>
-      <c r="E24" s="136">
-        <f>D24*D29</f>
+      <c r="H24" s="136">
+        <f>G24*G29</f>
         <v>1.9470112424786234</v>
       </c>
-      <c r="F24" s="136"/>
-      <c r="G24" s="136"/>
-      <c r="H24" s="136"/>
-      <c r="I24" s="175"/>
-      <c r="J24" s="155"/>
-      <c r="K24" s="155"/>
-      <c r="L24" s="155"/>
+      <c r="I24" s="136"/>
+      <c r="J24" s="136"/>
+      <c r="K24" s="136"/>
+      <c r="L24" s="175"/>
       <c r="M24" s="155"/>
       <c r="N24" s="155"/>
-    </row>
-    <row r="25" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="176"/>
-      <c r="C25" s="173" t="s">
+      <c r="O24" s="155"/>
+      <c r="P24" s="155"/>
+      <c r="Q24" s="155"/>
+    </row>
+    <row r="25" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C25" s="90">
+        <f t="shared" si="1"/>
+        <v>0.85386625145149375</v>
+      </c>
+      <c r="D25">
+        <f>J25*$A$9/$H$9</f>
+        <v>2.8640149967164186E-2</v>
+      </c>
+      <c r="E25" s="176"/>
+      <c r="F25" s="173" t="s">
         <v>98</v>
       </c>
-      <c r="D25" s="173">
+      <c r="G25" s="173">
         <f>1.47*1.42</f>
         <v>2.0873999999999997</v>
       </c>
-      <c r="E25" s="173">
-        <f>D25*D29</f>
+      <c r="H25" s="173">
+        <f>G25*G29</f>
         <v>6.7736521125831306</v>
       </c>
-      <c r="F25" s="173">
+      <c r="I25" s="173">
         <v>0.16</v>
       </c>
-      <c r="G25" s="173"/>
-      <c r="H25" s="173"/>
-      <c r="I25" s="177"/>
-      <c r="J25" s="155"/>
-      <c r="K25" s="155"/>
-      <c r="L25" s="155"/>
+      <c r="J25" s="173">
+        <f>I25*1.42</f>
+        <v>0.22719999999999999</v>
+      </c>
+      <c r="K25" s="173"/>
+      <c r="L25" s="177"/>
       <c r="M25" s="155"/>
       <c r="N25" s="155"/>
-    </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B26" s="156"/>
-      <c r="C26" s="153"/>
-      <c r="D26" s="153"/>
-      <c r="E26" s="154"/>
+      <c r="O25" s="155"/>
+      <c r="P25" s="155"/>
+      <c r="Q25" s="155"/>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="E26" s="156"/>
       <c r="F26" s="153"/>
       <c r="G26" s="153"/>
-      <c r="H26" s="153"/>
-      <c r="I26" s="155"/>
-    </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B28" t="s">
+      <c r="H26" s="154"/>
+      <c r="I26" s="153"/>
+      <c r="J26" s="153"/>
+      <c r="K26" s="153"/>
+      <c r="L26" s="155"/>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="E28" t="s">
         <v>45</v>
       </c>
-      <c r="D28" t="s">
+      <c r="G28" t="s">
         <v>61</v>
       </c>
-      <c r="E28" t="s">
+      <c r="H28" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B29">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="E29">
         <v>3.6014013985414599</v>
       </c>
-      <c r="D29">
-        <f>'18F norm Option 1'!D23</f>
+      <c r="G29">
+        <f>'18F norm Option 1'!G23</f>
         <v>3.2450187374643726</v>
       </c>
-      <c r="E29">
-        <f>'18F norm Option 1'!E23</f>
+      <c r="H29">
+        <f>'18F norm Option 1'!H23</f>
         <v>0.4931026033780847</v>
       </c>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B30" t="s">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="E30" t="s">
         <v>62</v>
       </c>
-      <c r="D30" t="s">
+      <c r="G30" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="39" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E39" t="s">
+    <row r="39" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H39" t="s">
         <v>91</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="E4:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9762,12 +10610,12 @@
         <v>20</v>
       </c>
       <c r="N4" s="92">
-        <f>'18F norm Option 2 lit'!E3</f>
+        <f>'18F norm Option 2 lit'!H3</f>
         <v>7.4353114331521173</v>
       </c>
       <c r="O4" s="92">
-        <f>'18F norm Option 2 lit'!F3</f>
-        <v>0.32842500000000002</v>
+        <f>'18F norm Option 2 lit'!I3</f>
+        <v>0.19059799999999999</v>
       </c>
       <c r="P4" s="92">
         <v>0.18529999999999999</v>
@@ -9778,7 +10626,7 @@
       </c>
       <c r="R4">
         <f>O4*$P$12/$N$12</f>
-        <v>3.8341991619242809E-2</v>
+        <v>2.2251372211751361E-2</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.2">
@@ -9804,11 +10652,11 @@
         <v>1.084420518072289</v>
       </c>
       <c r="G5" s="109">
-        <f>'18O Option 2 lit'!D3</f>
+        <f>'18O Option 2 lit'!G3</f>
         <v>6.1960600000000001</v>
       </c>
       <c r="H5" s="109">
-        <f>'18O Option 2 lit'!F3</f>
+        <f>'18O Option 2 lit'!I3</f>
         <v>0.84551640881286871</v>
       </c>
       <c r="I5" s="109">
@@ -9851,11 +10699,11 @@
         <v>7</v>
       </c>
       <c r="N6" s="92">
-        <f>'18F norm Option 2 lit'!E4</f>
+        <f>'18F norm Option 2 lit'!H4</f>
         <v>1.0227947949460308</v>
       </c>
       <c r="O6" s="92">
-        <f>'18F norm Option 2 lit'!G4</f>
+        <f>'18F norm Option 2 lit'!J4</f>
         <v>0.28840956313475286</v>
       </c>
       <c r="P6" s="92">
@@ -9891,7 +10739,7 @@
         <v>60</v>
       </c>
       <c r="O7" s="92">
-        <f>'18F norm Option 2 lit'!G5</f>
+        <f>'18F norm Option 2 lit'!J5</f>
         <v>0.86522868940425868</v>
       </c>
       <c r="P7">
@@ -9921,11 +10769,11 @@
         <v>58</v>
       </c>
       <c r="N8">
-        <f>'18F norm Option 2 lit'!E5</f>
+        <f>'18F norm Option 2 lit'!H5</f>
         <v>3.0683843848380925</v>
       </c>
       <c r="O8">
-        <f>'18F norm Option 2 lit'!G5</f>
+        <f>'18F norm Option 2 lit'!J5</f>
         <v>0.86522868940425868</v>
       </c>
       <c r="P8">
@@ -9963,11 +10811,11 @@
         <v>8</v>
       </c>
       <c r="N9">
-        <f>'18F norm Option 2 lit'!E6</f>
+        <f>'18F norm Option 2 lit'!H6</f>
         <v>9.626303952433231</v>
       </c>
       <c r="O9">
-        <f>'18F norm Option 2 lit'!G6</f>
+        <f>'18F norm Option 2 lit'!J6</f>
         <v>2.7144429471506153</v>
       </c>
       <c r="P9">
@@ -10009,11 +10857,11 @@
         <v>9</v>
       </c>
       <c r="N10" s="98">
-        <f>'18F norm Option 2 lit'!E7</f>
+        <f>'18F norm Option 2 lit'!H7</f>
         <v>8.9243859559016432</v>
       </c>
       <c r="O10">
-        <f>'18F norm Option 2 lit'!G7</f>
+        <f>'18F norm Option 2 lit'!J7</f>
         <v>2.5165148155875503</v>
       </c>
       <c r="P10" s="98">
@@ -10058,11 +10906,11 @@
         <v>0.18666254819277109</v>
       </c>
       <c r="G11" s="111">
-        <f>'18O Option 2 lit'!D4</f>
+        <f>'18O Option 2 lit'!G4</f>
         <v>0.74325399999999997</v>
       </c>
       <c r="H11" s="111">
-        <f>'18O Option 2 lit'!F4</f>
+        <f>'18O Option 2 lit'!I4</f>
         <v>0.10717148336994237</v>
       </c>
       <c r="I11" s="111">
@@ -10083,12 +10931,12 @@
         <v>10</v>
       </c>
       <c r="N11" s="92">
-        <f>'18F norm Option 2 lit'!E8</f>
+        <f>'18F norm Option 2 lit'!H8</f>
         <v>0.50502875614905518</v>
       </c>
       <c r="O11" s="92">
-        <f>'18F norm Option 2 lit'!G8</f>
-        <v>9.4693203252016286E-2</v>
+        <f>'18F norm Option 2 lit'!J8</f>
+        <v>0.31671937986543069</v>
       </c>
       <c r="P11" s="92">
         <v>0.14710000000000001</v>
@@ -10099,7 +10947,7 @@
       </c>
       <c r="R11">
         <f t="shared" si="1"/>
-        <v>1.1054962336874672E-2</v>
+        <v>3.6975418462212445E-2</v>
       </c>
       <c r="S11">
         <v>0.21</v>
@@ -10110,7 +10958,7 @@
       </c>
       <c r="V11">
         <f>(G11-N11)/SQRT(H11*H11+O11*O11)</f>
-        <v>1.6657670429023756</v>
+        <v>0.71248038794399471</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.2">
@@ -10134,11 +10982,11 @@
         <v>0.73776149999999996</v>
       </c>
       <c r="G12" s="113">
-        <f>'18O Option 2 lit'!D5</f>
+        <f>'18O Option 2 lit'!G5</f>
         <v>4.9184099999999997</v>
       </c>
       <c r="H12" s="111">
-        <f>'18O Option 2 lit'!F5</f>
+        <f>'18O Option 2 lit'!I5</f>
         <v>0.24445529131853752</v>
       </c>
       <c r="I12" s="113">
@@ -10157,12 +11005,12 @@
         <v>11</v>
       </c>
       <c r="N12" s="98">
-        <f>'18F norm Option 2 lit'!E9</f>
+        <f>'18F norm Option 2 lit'!H9</f>
         <v>4.9184099999999997</v>
       </c>
       <c r="O12" s="92">
-        <f>'18F norm Option 2 lit'!G9</f>
-        <v>0.21764956340798039</v>
+        <f>'18F norm Option 2 lit'!J9</f>
+        <v>1.0283056650510694</v>
       </c>
       <c r="P12" s="98">
         <v>0.57420000000000004</v>
@@ -10173,7 +11021,7 @@
       </c>
       <c r="R12">
         <f t="shared" si="1"/>
-        <v>2.5409508216855115E-2</v>
+        <v>0.12004959181368045</v>
       </c>
       <c r="S12">
         <v>0.62</v>
@@ -10246,12 +11094,12 @@
         <v>10</v>
       </c>
       <c r="N15">
-        <f>'18F norm Option 1'!E8</f>
+        <f>'18F norm Option 1'!H8</f>
         <v>2.2567190758009605</v>
       </c>
       <c r="O15">
-        <f>'18F norm Option 1'!F8</f>
-        <v>0.11036899999999999</v>
+        <f>'18F norm Option 1'!J8</f>
+        <v>0.49585053737747803</v>
       </c>
       <c r="P15">
         <v>0.33560000000000001</v>
@@ -10262,7 +11110,7 @@
       </c>
       <c r="R15">
         <f t="shared" si="1"/>
-        <v>1.2885033943896505E-2</v>
+        <v>5.7888093624189105E-2</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.2">
@@ -10297,12 +11145,12 @@
         <v>11</v>
       </c>
       <c r="N17" s="98">
-        <f>'18F norm Option 1'!E9</f>
+        <f>'18F norm Option 1'!H9</f>
         <v>4.4950648555103978</v>
       </c>
       <c r="O17" s="98">
-        <f>'18F norm Option 1'!F9</f>
-        <v>0.206014</v>
+        <f>'18F norm Option 1'!J9</f>
+        <v>0.95576303443071298</v>
       </c>
       <c r="P17" s="98">
         <v>9.4999999999999998E-3</v>
@@ -10313,7 +11161,7 @@
       </c>
       <c r="R17">
         <f t="shared" si="1"/>
-        <v>2.4051113835568814E-2</v>
+        <v>0.11158059908997327</v>
       </c>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.2">
@@ -10332,12 +11180,12 @@
         <v>7</v>
       </c>
       <c r="N18" s="92">
-        <f>'18F norm Option 2 lit'!E12</f>
+        <f>'18F norm Option 2 lit'!H12</f>
         <v>1.169099125639977</v>
       </c>
       <c r="O18" s="92">
-        <f>'18F norm Option 2 lit'!F12</f>
-        <v>6.9371299999999997E-2</v>
+        <f>'18F norm Option 2 lit'!J12</f>
+        <v>0.39200123718697127</v>
       </c>
       <c r="P18" s="92">
         <v>0.13789999999999999</v>
@@ -10348,7 +11196,7 @@
       </c>
       <c r="R18">
         <f t="shared" si="1"/>
-        <v>8.0987555856465825E-3</v>
+        <v>4.5764202332208771E-2</v>
       </c>
       <c r="S18">
         <v>0.17</v>
@@ -10390,12 +11238,12 @@
         <v>6</v>
       </c>
       <c r="N20" s="98">
-        <f>'18F norm Option 2 lit'!E13</f>
+        <f>'18F norm Option 2 lit'!H13</f>
         <v>6.181890495619129</v>
       </c>
       <c r="O20" s="98">
-        <f>'18F norm Option 2 lit'!F13</f>
-        <v>0.117092</v>
+        <f>'18F norm Option 2 lit'!J13</f>
+        <v>1.1091946835077204</v>
       </c>
       <c r="P20" s="98">
         <v>0.65269999999999995</v>
@@ -10406,7 +11254,7 @@
       </c>
       <c r="R20">
         <f t="shared" si="1"/>
-        <v>1.3669910885835057E-2</v>
+        <v>0.12949298396639017</v>
       </c>
       <c r="S20">
         <v>0.68</v>
@@ -10452,12 +11300,12 @@
         <v>5</v>
       </c>
       <c r="N22" s="98">
-        <f>'18F norm Option 2 lit'!E14</f>
+        <f>'18F norm Option 2 lit'!H14</f>
         <v>1.3781042924825821</v>
       </c>
       <c r="O22" s="98">
-        <f>'18F norm Option 2 lit'!F14</f>
-        <v>8.5518999999999998E-2</v>
+        <f>'18F norm Option 2 lit'!J14</f>
+        <v>0.46289723602264254</v>
       </c>
       <c r="P22" s="98">
         <v>0.186</v>
@@ -10468,7 +11316,7 @@
       </c>
       <c r="R22">
         <f t="shared" si="1"/>
-        <v>9.9839195593697978E-3</v>
+        <v>5.4040958953035914E-2</v>
       </c>
       <c r="S22">
         <v>7.3999999999999996E-2</v>
@@ -10523,11 +11371,11 @@
         <v>1.3955247650602411</v>
       </c>
       <c r="G24" s="111">
-        <f>'18O Option 2 lit'!D6</f>
+        <f>'18O Option 2 lit'!G6</f>
         <v>8.2684207000000001</v>
       </c>
       <c r="H24" s="111">
-        <f>'18O Option 2 lit'!F6</f>
+        <f>'18O Option 2 lit'!I6</f>
         <v>1.3220240957837115</v>
       </c>
       <c r="I24" s="111">
@@ -10546,11 +11394,11 @@
         <v>12</v>
       </c>
       <c r="N24">
-        <f>'18F norm Option 2 lit'!E15</f>
+        <f>'18F norm Option 2 lit'!H15</f>
         <v>7.0153047639396187</v>
       </c>
       <c r="O24">
-        <f>'18F norm Option 2 lit'!G15</f>
+        <f>'18F norm Option 2 lit'!J15</f>
         <v>1.875493381034588</v>
       </c>
       <c r="P24">
@@ -10599,11 +11447,11 @@
         <v>0.24888339759036149</v>
       </c>
       <c r="G25" s="113">
-        <f>'18O Option 2 lit'!D7</f>
+        <f>'18O Option 2 lit'!G7</f>
         <v>1.4746228000000001</v>
       </c>
       <c r="H25" s="111">
-        <f>'18O Option 2 lit'!F7</f>
+        <f>'18O Option 2 lit'!I7</f>
         <v>0.23577499797416512</v>
       </c>
       <c r="I25" s="113"/>
@@ -10622,11 +11470,11 @@
         <v>8</v>
       </c>
       <c r="N25" s="98">
-        <f>'18F norm Option 2 lit'!E16</f>
+        <f>'18F norm Option 2 lit'!H16</f>
         <v>1.2141873629895492</v>
       </c>
       <c r="O25" s="98">
-        <f>'18F norm Option 2 lit'!G16</f>
+        <f>'18F norm Option 2 lit'!J16</f>
         <v>0.32460462364060161</v>
       </c>
       <c r="P25" s="98">
@@ -10675,11 +11523,11 @@
         <v>0.3111042469879518</v>
       </c>
       <c r="G26" s="111">
-        <f>'18O Option 2 lit'!D8</f>
+        <f>'18O Option 2 lit'!G8</f>
         <v>1.2651399999999999</v>
       </c>
       <c r="H26" s="111">
-        <f>'18O Option 2 lit'!F8</f>
+        <f>'18O Option 2 lit'!I8</f>
         <v>0.43678576450431567</v>
       </c>
       <c r="I26" s="111">
@@ -10700,11 +11548,11 @@
         <v>10</v>
       </c>
       <c r="N26" s="92">
-        <f>'18F norm Option 2 lit'!E17</f>
+        <f>'18F norm Option 2 lit'!H17</f>
         <v>1.2439844230444423</v>
       </c>
       <c r="O26" s="92">
-        <f>'18F norm Option 2 lit'!G17</f>
+        <f>'18F norm Option 2 lit'!J17</f>
         <v>0.49600336979921622</v>
       </c>
       <c r="P26" s="92">
@@ -10751,11 +11599,11 @@
         <v>0.58665372289156625</v>
       </c>
       <c r="G27" s="113">
-        <f>'18O Option 2 lit'!D9</f>
+        <f>'18O Option 2 lit'!G9</f>
         <v>3.4860899999999999</v>
       </c>
       <c r="H27" s="111">
-        <f>'18O Option 2 lit'!F9</f>
+        <f>'18O Option 2 lit'!I9</f>
         <v>0.55106232587730664</v>
       </c>
       <c r="I27" s="113">
@@ -10774,11 +11622,11 @@
         <v>11</v>
       </c>
       <c r="N27" s="98">
-        <f>'18F norm Option 2 lit'!E18</f>
+        <f>'18F norm Option 2 lit'!H18</f>
         <v>3.7375152312493403</v>
       </c>
       <c r="O27" s="98">
-        <f>'18F norm Option 2 lit'!G18</f>
+        <f>'18F norm Option 2 lit'!J18</f>
         <v>0.80988843614557104</v>
       </c>
       <c r="P27" s="98">
@@ -10827,11 +11675,11 @@
         <v>0.3111042469879518</v>
       </c>
       <c r="G28" s="111">
-        <f>'18O Option 2 lit'!D10</f>
+        <f>'18O Option 2 lit'!G10</f>
         <v>1.5525124999999997</v>
       </c>
       <c r="H28" s="111">
-        <f>'18O Option 2 lit'!F10</f>
+        <f>'18O Option 2 lit'!I10</f>
         <v>0.24245367754888389</v>
       </c>
       <c r="I28" s="111"/>
@@ -10895,11 +11743,11 @@
         <v>0.14221908433734939</v>
       </c>
       <c r="G31" s="90">
-        <f>'18O Option 2 lit'!D11</f>
+        <f>'18O Option 2 lit'!G11</f>
         <v>0.70971999999999991</v>
       </c>
       <c r="H31" s="90">
-        <f>'18O Option 2 lit'!F11</f>
+        <f>'18O Option 2 lit'!I11</f>
         <v>0.11083596687948978</v>
       </c>
       <c r="I31" s="90"/>
@@ -10918,11 +11766,11 @@
         <v>8</v>
       </c>
       <c r="N31" s="92">
-        <f>'18F norm Option 2 lit'!E24</f>
+        <f>'18F norm Option 2 lit'!H24</f>
         <v>1.9470112424786234</v>
       </c>
       <c r="O31" s="92">
-        <f>'18F norm Option 2 lit'!G19</f>
+        <f>'18F norm Option 2 lit'!J19</f>
         <v>0.25725005957972208</v>
       </c>
       <c r="P31" s="92">
@@ -10967,11 +11815,11 @@
         <v>0.89775796987951806</v>
       </c>
       <c r="G32" s="113">
-        <f>'18O Option 2 lit'!D12</f>
+        <f>'18O Option 2 lit'!G12</f>
         <v>4.4801074999999999</v>
       </c>
       <c r="H32" s="113">
-        <f>'18O Option 2 lit'!F12</f>
+        <f>'18O Option 2 lit'!I12</f>
         <v>0.69965204092677924</v>
       </c>
       <c r="I32" s="113">
@@ -10989,11 +11837,11 @@
         <v>7</v>
       </c>
       <c r="N32">
-        <f>'18F norm Option 2 lit'!E25</f>
+        <f>'18F norm Option 2 lit'!H25</f>
         <v>6.7736521125831306</v>
       </c>
       <c r="O32">
-        <f>'18F norm Option 2 lit'!F25</f>
+        <f>'18F norm Option 2 lit'!I25</f>
         <v>0.16</v>
       </c>
       <c r="P32">
@@ -11068,11 +11916,11 @@
         <v>10</v>
       </c>
       <c r="N35" s="98">
-        <f>'18F norm Option 2 lit'!E21</f>
+        <f>'18F norm Option 2 lit'!H21</f>
         <v>0</v>
       </c>
       <c r="O35" s="98">
-        <f>'18F norm Option 2 lit'!G21</f>
+        <f>'18F norm Option 2 lit'!J21</f>
         <v>0</v>
       </c>
       <c r="P35" s="98"/>
@@ -11127,11 +11975,11 @@
       <c r="E37" s="106"/>
       <c r="F37" s="106"/>
       <c r="G37" s="111">
-        <f>'18O Option 2 lit'!D13</f>
+        <f>'18O Option 2 lit'!G13</f>
         <v>0.28774300000000003</v>
       </c>
       <c r="H37" s="111">
-        <f>'18O Option 2 lit'!E13</f>
+        <f>'18O Option 2 lit'!H13</f>
         <v>3.6374200000000002E-2</v>
       </c>
       <c r="I37" s="111"/>
@@ -11187,11 +12035,11 @@
       <c r="E39" s="106"/>
       <c r="F39" s="106"/>
       <c r="G39" s="109">
-        <f>'18O Option 2 lit'!D14</f>
+        <f>'18O Option 2 lit'!G14</f>
         <v>0.28167199999999998</v>
       </c>
       <c r="H39" s="109">
-        <f>'18O Option 2 lit'!E14</f>
+        <f>'18O Option 2 lit'!H14</f>
         <v>2.2748000000000001E-2</v>
       </c>
       <c r="I39" s="109">
@@ -11293,11 +12141,11 @@
       <c r="E44" s="153"/>
       <c r="F44" s="153"/>
       <c r="G44" s="153">
-        <f>'18O Option 1'!D6</f>
+        <f>'18O Option 1'!G6</f>
         <v>8.4322099999999995</v>
       </c>
       <c r="H44" s="153">
-        <f>'18O Option 1'!F6</f>
+        <f>'18O Option 1'!I6</f>
         <v>0.46677488986783022</v>
       </c>
       <c r="I44" s="153"/>
@@ -11309,11 +12157,11 @@
         <v>12</v>
       </c>
       <c r="N44" s="155">
-        <f>'18F norm Option 1'!E13</f>
+        <f>'18F norm Option 1'!H13</f>
         <v>7.1501067363163733</v>
       </c>
       <c r="O44" s="155">
-        <f>'18F norm Option 1'!G13</f>
+        <f>'18F norm Option 1'!J13</f>
         <v>1.2684673643870159</v>
       </c>
       <c r="P44" s="155"/>
@@ -11524,7 +12372,7 @@
       <c r="E2">
         <v>5.6494999999999997</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="33">
         <v>5.3994999999999997</v>
       </c>
       <c r="G2">
@@ -11562,7 +12410,7 @@
       <c r="E3">
         <v>0</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="33">
         <v>0.48862899999999998</v>
       </c>
       <c r="G3">
@@ -11600,7 +12448,7 @@
       <c r="E4">
         <v>2.3946399999999999</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="33">
         <v>1.2217899999999999</v>
       </c>
       <c r="G4">
@@ -11638,7 +12486,7 @@
       <c r="E5">
         <v>0.27462799999999998</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="33">
         <v>0</v>
       </c>
       <c r="G5">
@@ -11661,6 +12509,14 @@
       </c>
       <c r="M5">
         <v>9.1579400000000005E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>90</v>
+      </c>
+      <c r="F6" s="33">
+        <v>0.16</v>
       </c>
     </row>
     <row r="51" spans="2:13" x14ac:dyDescent="0.2">
@@ -11676,7 +12532,7 @@
       <c r="E51">
         <v>5.6494999999999997</v>
       </c>
-      <c r="F51">
+      <c r="F51" s="33">
         <v>5.3994999999999997</v>
       </c>
       <c r="G51">
@@ -11714,7 +12570,7 @@
       <c r="E52">
         <v>1.05064</v>
       </c>
-      <c r="F52">
+      <c r="F52" s="33">
         <v>0.49790699999999999</v>
       </c>
       <c r="G52">
@@ -11752,7 +12608,7 @@
       <c r="E53">
         <v>2.5909900000000001</v>
       </c>
-      <c r="F53">
+      <c r="F53" s="33">
         <v>1.22211</v>
       </c>
       <c r="G53">
@@ -11790,7 +12646,7 @@
       <c r="E54">
         <v>0.27</v>
       </c>
-      <c r="F54">
+      <c r="F54" s="33">
         <v>0.53800000000000003</v>
       </c>
       <c r="G54">
@@ -11828,7 +12684,7 @@
       <c r="E55">
         <v>0.36</v>
       </c>
-      <c r="F55">
+      <c r="F55" s="33">
         <v>0.16575200000000001</v>
       </c>
       <c r="G55">
@@ -11866,7 +12722,7 @@
       <c r="E66">
         <v>5.6494999999999997</v>
       </c>
-      <c r="F66">
+      <c r="F66" s="33">
         <v>5.3994999999999997</v>
       </c>
       <c r="G66">
@@ -11904,7 +12760,7 @@
       <c r="E67">
         <v>2.3949600000000002</v>
       </c>
-      <c r="F67">
+      <c r="F67" s="33">
         <v>1.2212499999999999</v>
       </c>
       <c r="G67">
@@ -11942,7 +12798,7 @@
       <c r="E68">
         <v>0.27</v>
       </c>
-      <c r="F68">
+      <c r="F68" s="33">
         <v>3.7118199999999997E-2</v>
       </c>
       <c r="G68">
@@ -11980,7 +12836,7 @@
       <c r="E69">
         <v>0.38479999999999998</v>
       </c>
-      <c r="F69">
+      <c r="F69" s="33">
         <v>0.16</v>
       </c>
       <c r="G69">
@@ -12018,7 +12874,7 @@
       <c r="E70">
         <v>6.7000000000000004E-2</v>
       </c>
-      <c r="F70">
+      <c r="F70" s="33">
         <v>0.04</v>
       </c>
       <c r="G70">

--- a/analysis/final_working/free_lit_SM_SF_18F_18O.xlsx
+++ b/analysis/final_working/free_lit_SM_SF_18F_18O.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kawecka/digios/analysis/final_working/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AC726B1-0169-0E4B-84A0-CD6C27B2ECB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F5842D7-886E-DA48-8541-DD4646745B29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="17240" activeTab="4" xr2:uid="{FC3CEAA1-A762-5643-8C2C-8E9D51254AD0}"/>
+    <workbookView xWindow="980" yWindow="1000" windowWidth="29400" windowHeight="17160" activeTab="5" xr2:uid="{FC3CEAA1-A762-5643-8C2C-8E9D51254AD0}"/>
   </bookViews>
   <sheets>
     <sheet name="18O Option 1" sheetId="6" r:id="rId1"/>
@@ -18,8 +18,8 @@
     <sheet name="18O Option 2 SM" sheetId="9" r:id="rId3"/>
     <sheet name="18F norm Option 1" sheetId="7" r:id="rId4"/>
     <sheet name="18F norm Option 2 lit" sheetId="10" r:id="rId5"/>
-    <sheet name="18F norm Option 2 SM" sheetId="11" r:id="rId6"/>
-    <sheet name="18O &amp; 18F" sheetId="12" r:id="rId7"/>
+    <sheet name="18O &amp; 18F" sheetId="12" r:id="rId6"/>
+    <sheet name="18F norm Option 2 SM" sheetId="11" r:id="rId7"/>
     <sheet name="6.136 MeV in 18F" sheetId="14" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="122">
   <si>
     <t>unc</t>
   </si>
@@ -352,9 +352,6 @@
     <t>some of the states are not reproduced with SM so I wouldn't trust this too much</t>
   </si>
   <si>
-    <t>&lt;- upper limit rather than a real value</t>
-  </si>
-  <si>
     <t>(SF_O - SF_F)/sqrt(unc_O^2+unc_F^2)</t>
   </si>
   <si>
@@ -404,6 +401,21 @@
   </si>
   <si>
     <t>unc lit</t>
+  </si>
+  <si>
+    <t>epsilon</t>
+  </si>
+  <si>
+    <t>unc eps</t>
+  </si>
+  <si>
+    <t>ratio</t>
+  </si>
+  <si>
+    <t>unc frac</t>
+  </si>
+  <si>
+    <t>unc/SF</t>
   </si>
 </sst>
 </file>
@@ -1817,7 +1829,17 @@
   <c:chart>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="4.1634550915626463E-2"/>
+          <c:y val="1.6593726902771538E-2"/>
+          <c:w val="0.93931557531847676"/>
+          <c:h val="0.86442552829093056"/>
+        </c:manualLayout>
+      </c:layout>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
@@ -5928,16 +5950,16 @@
   <sheetData>
     <row r="2" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="183" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B2" s="183" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C2" s="183" t="s">
+        <v>112</v>
+      </c>
+      <c r="D2" s="183" t="s">
         <v>113</v>
-      </c>
-      <c r="D2" s="183" t="s">
-        <v>114</v>
       </c>
       <c r="G2" t="s">
         <v>47</v>
@@ -5946,7 +5968,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J2" t="s">
         <v>1</v>
@@ -6122,7 +6144,7 @@
         <v>51</v>
       </c>
       <c r="T6" s="187" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -6402,16 +6424,16 @@
   <sheetData>
     <row r="2" spans="1:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D2" t="s">
         <v>113</v>
-      </c>
-      <c r="D2" t="s">
-        <v>114</v>
       </c>
       <c r="G2" t="s">
         <v>47</v>
@@ -6420,7 +6442,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J2" t="s">
         <v>1</v>
@@ -6432,16 +6454,16 @@
         <v>32</v>
       </c>
       <c r="M2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N2" t="s">
         <v>3</v>
       </c>
       <c r="O2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q2" t="s">
         <v>46</v>
@@ -7623,25 +7645,25 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7253C9-71CE-6148-AA2F-0D73ACAD915E}">
-  <dimension ref="A2:O24"/>
+  <dimension ref="A2:Q28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="13.1640625" customWidth="1"/>
     <col min="4" max="4" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="183" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B2" s="183" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C2" s="183" t="s">
+        <v>112</v>
+      </c>
+      <c r="D2" s="183" t="s">
         <v>113</v>
-      </c>
-      <c r="D2" s="183" t="s">
-        <v>114</v>
       </c>
       <c r="G2" t="s">
         <v>47</v>
@@ -7650,10 +7672,10 @@
         <v>54</v>
       </c>
       <c r="I2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K2" t="s">
         <v>1</v>
@@ -7662,13 +7684,13 @@
         <v>76</v>
       </c>
       <c r="M2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C3" s="185">
         <f>H3*A$7/H$7</f>
         <v>0.93727303916393978</v>
@@ -7710,8 +7732,12 @@
       <c r="N3" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" ht="35" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="Q3">
+        <f>J3/H3</f>
+        <v>0.17323490542408537</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="35" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>0.10199999999999999</v>
       </c>
@@ -7757,22 +7783,26 @@
         <f>I4*SQRT(L4)</f>
         <v>0.28592844085343383</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="Q4">
+        <f t="shared" ref="Q4:Q20" si="1">J4/H4</f>
+        <v>3.6618441060157774</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>0.306+0.96+0.89</f>
         <v>2.1560000000000001</v>
       </c>
       <c r="B5">
-        <f t="shared" ref="B5:B15" si="1">0.2*A5</f>
+        <f t="shared" ref="B5:B15" si="2">0.2*A5</f>
         <v>0.43120000000000003</v>
       </c>
       <c r="C5" s="185">
-        <f t="shared" ref="C5:C15" si="2">H5*A$7/H$7</f>
+        <f t="shared" ref="C5:C15" si="3">H5*A$7/H$7</f>
         <v>1.8565557373588095</v>
       </c>
       <c r="D5" s="184">
-        <f t="shared" ref="D5:D15" si="3">J5*A$7/H$7</f>
+        <f t="shared" ref="D5:D15" si="4">J5*A$7/H$7</f>
         <v>0.56335248394980864</v>
       </c>
       <c r="E5" s="59" t="s">
@@ -7802,24 +7832,28 @@
         <v>8.0688099999999991</v>
       </c>
       <c r="M5" s="27">
-        <f t="shared" ref="M5:M20" si="4">I5*SQRT(L5)</f>
+        <f t="shared" ref="M5:M20" si="5">I5*SQRT(L5)</f>
         <v>1.1920658622842499</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="Q5">
+        <f t="shared" si="1"/>
+        <v>0.30343957502253632</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>0.21</v>
       </c>
       <c r="B6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.2000000000000003E-2</v>
       </c>
       <c r="C6" s="185">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.3662408951757635E-2</v>
       </c>
       <c r="D6" s="184">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.9924694264318557E-2</v>
       </c>
       <c r="E6" s="118" t="s">
@@ -7849,23 +7883,27 @@
         <v>3.04813</v>
       </c>
       <c r="M6" s="155">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>9.4693203252016286E-2</v>
       </c>
       <c r="N6" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="Q6">
+        <f t="shared" si="1"/>
+        <v>0.62713137818226239</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>0.62</v>
       </c>
       <c r="B7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.124</v>
       </c>
       <c r="C7" s="185">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.62</v>
       </c>
       <c r="D7" s="184">
@@ -7887,7 +7925,7 @@
         <v>0.124664</v>
       </c>
       <c r="J7" s="180">
-        <f t="shared" ref="J7" si="5">I7*SQRT(L7)</f>
+        <f t="shared" ref="J7" si="6">I7*SQRT(L7)</f>
         <v>0.21764956340798039</v>
       </c>
       <c r="K7" s="7">
@@ -7897,21 +7935,25 @@
         <v>3.04813</v>
       </c>
       <c r="M7" s="155">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.21764956340798039</v>
       </c>
       <c r="O7">
         <f>H7*SQRT(POWER(($H$23/$G$23),2)+POWER((M7/G7),2))</f>
         <v>1.0283056650510694</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="Q7">
+        <f>O7/H7</f>
+        <v>0.20907278267795271</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C8" s="185">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.28447523223899501</v>
       </c>
       <c r="D8" s="184">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6.250543024555423E-2</v>
       </c>
       <c r="E8" s="125" t="s">
@@ -7944,14 +7986,18 @@
         <f>I8</f>
         <v>0.11036899999999999</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="Q8">
+        <f t="shared" si="1"/>
+        <v>0.21972187087641357</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C9" s="185">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.56663438192758364</v>
       </c>
       <c r="D9" s="184">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.12048061901042045</v>
       </c>
       <c r="E9" s="120"/>
@@ -7982,21 +8028,25 @@
         <f>I9</f>
         <v>0.206014</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="Q9">
+        <f t="shared" si="1"/>
+        <v>0.21262497097434863</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>0.17</v>
       </c>
       <c r="B10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.4000000000000002E-2</v>
       </c>
       <c r="C10" s="185">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.14737312625356278</v>
       </c>
       <c r="D10" s="184">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.9414499209281496E-2</v>
       </c>
       <c r="E10" s="118" t="s">
@@ -8016,7 +8066,7 @@
         <v>6.9371299999999997E-2</v>
       </c>
       <c r="J10" s="181">
-        <f t="shared" ref="J10:J17" si="6">H10*SQRT(POWER(($H$23/$G$23),2)+POWER((M10/G10),2))</f>
+        <f t="shared" ref="J10:J17" si="7">H10*SQRT(POWER(($H$23/$G$23),2)+POWER((M10/G10),2))</f>
         <v>0.39200123718697127</v>
       </c>
       <c r="K10" s="3">
@@ -8026,27 +8076,31 @@
         <v>2.4095599999999999</v>
       </c>
       <c r="M10" s="155">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.10768338664574435</v>
       </c>
       <c r="N10" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="Q10">
+        <f t="shared" si="1"/>
+        <v>0.33530196763459708</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>0.68</v>
       </c>
       <c r="B11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.13600000000000001</v>
       </c>
       <c r="C11" s="185">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.77927055842921999</v>
       </c>
       <c r="D11" s="184">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.1398217521058201</v>
       </c>
       <c r="E11" s="119"/>
@@ -8064,7 +8118,7 @@
         <v>0.117092</v>
       </c>
       <c r="J11" s="181">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.1091946835077204</v>
       </c>
       <c r="K11" s="7">
@@ -8074,24 +8128,28 @@
         <v>2.4095599999999999</v>
       </c>
       <c r="M11" s="155">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.18175907196669946</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="Q11">
+        <f t="shared" si="1"/>
+        <v>0.17942645284541428</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>7.3999999999999996E-2</v>
       </c>
       <c r="B12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.4800000000000001E-2</v>
       </c>
       <c r="C12" s="185">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.17371969017206801</v>
       </c>
       <c r="D12" s="184">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.8351435999446651E-2</v>
       </c>
       <c r="E12" s="46" t="s">
@@ -8111,7 +8169,7 @@
         <v>8.5518999999999998E-2</v>
       </c>
       <c r="J12" s="181">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.46289723602264254</v>
       </c>
       <c r="K12" s="10">
@@ -8121,27 +8179,31 @@
         <v>2.2128999999999999</v>
       </c>
       <c r="M12" s="155">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.12721651911586365</v>
       </c>
       <c r="N12" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" ht="35" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="Q12">
+        <f t="shared" si="1"/>
+        <v>0.33589419795562614</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="35" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>1.22</v>
       </c>
       <c r="B13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.24399999999999999</v>
       </c>
       <c r="C13" s="185">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.90132099123825615</v>
       </c>
       <c r="D13" s="184">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.1598991881359931</v>
       </c>
       <c r="E13" s="61" t="s">
@@ -8161,7 +8223,7 @@
         <v>7.1556900000000007E-2</v>
       </c>
       <c r="J13" s="181">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.2684673643870159</v>
       </c>
       <c r="K13" s="53">
@@ -8171,24 +8233,28 @@
         <v>7.9474</v>
       </c>
       <c r="M13" s="155">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.20172701105742313</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="Q13">
+        <f t="shared" si="1"/>
+        <v>0.1774053746560588</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>0.17</v>
       </c>
       <c r="B14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.4000000000000002E-2</v>
       </c>
       <c r="C14" s="185">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.15681294204581445</v>
       </c>
       <c r="D14" s="184">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6.2524695841850123E-2</v>
       </c>
       <c r="E14" s="118" t="s">
@@ -8208,7 +8274,7 @@
         <v>9.3142699999999995E-2</v>
       </c>
       <c r="J14" s="181">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.49600336979921622</v>
       </c>
       <c r="K14" s="3">
@@ -8218,27 +8284,31 @@
         <v>2.30186</v>
       </c>
       <c r="M14" s="155">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.14131500430575206</v>
       </c>
       <c r="N14" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="Q14">
+        <f t="shared" si="1"/>
+        <v>0.39872152786715087</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>0.51</v>
       </c>
       <c r="B15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.10200000000000001</v>
       </c>
       <c r="C15" s="185">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.47113995038530559</v>
       </c>
       <c r="D15" s="184">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.10209210505229416</v>
       </c>
       <c r="E15" s="119"/>
@@ -8256,7 +8326,7 @@
         <v>0.117274</v>
       </c>
       <c r="J15" s="181">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.80988843614557104</v>
       </c>
       <c r="K15" s="7">
@@ -8266,11 +8336,15 @@
         <v>2.30186</v>
       </c>
       <c r="M15" s="155">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.1779267276442788</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="Q15">
+        <f t="shared" si="1"/>
+        <v>0.21669167509314721</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="E16" s="42" t="s">
         <v>29</v>
       </c>
@@ -8295,11 +8369,15 @@
         <v>2.0387900000000001</v>
       </c>
       <c r="M16" s="155">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.0964980949592529</v>
       </c>
-    </row>
-    <row r="17" spans="5:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="Q16" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="17" spans="5:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="E17" s="64" t="s">
         <v>30</v>
       </c>
@@ -8317,7 +8395,7 @@
         <v>0.27806199999999998</v>
       </c>
       <c r="J17" s="181">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.7628245835591634</v>
       </c>
       <c r="K17" s="45">
@@ -8327,11 +8405,15 @@
         <v>2.0387900000000001</v>
       </c>
       <c r="M17" s="155">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.39703417405305141</v>
       </c>
-    </row>
-    <row r="18" spans="5:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="Q17">
+        <f t="shared" si="1"/>
+        <v>0.22263942062385086</v>
+      </c>
+    </row>
+    <row r="18" spans="5:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="E18" s="64" t="s">
         <v>83</v>
       </c>
@@ -8342,7 +8424,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="44">
-        <f t="shared" ref="H18:H19" si="7">G18*$G$23</f>
+        <f t="shared" ref="H18:H19" si="8">G18*$G$23</f>
         <v>0</v>
       </c>
       <c r="I18" s="43"/>
@@ -8350,11 +8432,15 @@
       <c r="K18" s="45"/>
       <c r="L18" s="43"/>
       <c r="M18" s="155">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="5:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="Q18" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="19" spans="5:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="E19" s="64" t="s">
         <v>84</v>
       </c>
@@ -8365,7 +8451,7 @@
         <v>0.26</v>
       </c>
       <c r="H19" s="44">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.84370487174073694</v>
       </c>
       <c r="I19" s="43"/>
@@ -8373,11 +8459,15 @@
       <c r="K19" s="45"/>
       <c r="L19" s="43"/>
       <c r="M19" s="155">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="5:13" ht="35" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="Q19">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="5:17" ht="35" thickBot="1" x14ac:dyDescent="0.25">
       <c r="E20" s="65" t="s">
         <v>31</v>
       </c>
@@ -8388,15 +8478,15 @@
         <v>0.80409799999999998</v>
       </c>
       <c r="H20" s="66">
-        <f>G20*$G$23</f>
-        <v>2.6093130767576271</v>
+        <f>G20*$G$23*G28</f>
+        <v>3.6530383074606778</v>
       </c>
       <c r="I20" s="50">
         <v>0.103809</v>
       </c>
       <c r="J20" s="182">
-        <f t="shared" ref="J15:J20" si="8">H20*SQRT(POWER((H$23/G$23),2)+POWER((M20/G20),2))</f>
-        <v>0.43080050069535031</v>
+        <f>H20*SQRT(POWER((H$23/G$23),2)+POWER((M20/G20),2)+POWER((H28/G28),2))</f>
+        <v>0.79755574679409624</v>
       </c>
       <c r="K20" s="67">
         <v>1.25024</v>
@@ -8405,19 +8495,23 @@
         <v>0.25004900000000002</v>
       </c>
       <c r="M20" s="155">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5.1909586391779013E-2</v>
       </c>
-    </row>
-    <row r="22" spans="5:13" x14ac:dyDescent="0.2">
+      <c r="Q20">
+        <f t="shared" si="1"/>
+        <v>0.21832668580705306</v>
+      </c>
+    </row>
+    <row r="22" spans="5:17" x14ac:dyDescent="0.2">
       <c r="G22" t="s">
         <v>61</v>
       </c>
       <c r="H22" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="23" spans="5:13" x14ac:dyDescent="0.2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="23" spans="5:17" x14ac:dyDescent="0.2">
       <c r="G23">
         <f>'18O Option 1'!G5/G7</f>
         <v>3.2450187374643726</v>
@@ -8427,9 +8521,25 @@
         <v>0.4931026033780847</v>
       </c>
     </row>
-    <row r="24" spans="5:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="5:17" x14ac:dyDescent="0.2">
       <c r="G24" t="s">
         <v>63</v>
+      </c>
+    </row>
+    <row r="27" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="G27" s="183" t="s">
+        <v>117</v>
+      </c>
+      <c r="H27" s="183" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="28" spans="5:17" x14ac:dyDescent="0.2">
+      <c r="G28" s="183">
+        <v>1.4</v>
+      </c>
+      <c r="H28" s="183">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -8445,1033 +8555,1155 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{821ECE62-53CE-CB41-9599-014ED0A08C45}">
-  <dimension ref="A2:R39"/>
+  <dimension ref="A2:X39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="183" t="s">
-        <v>115</v>
+    <row r="2" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>121</v>
       </c>
       <c r="B2" s="183" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C2" s="183" t="s">
+        <v>116</v>
+      </c>
+      <c r="D2" s="183" t="s">
+        <v>112</v>
+      </c>
+      <c r="E2" s="183" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="183" t="s">
-        <v>114</v>
-      </c>
-      <c r="E2" s="132"/>
       <c r="F2" s="132"/>
-      <c r="G2" s="132" t="s">
+      <c r="G2" s="132"/>
+      <c r="H2" s="132" t="s">
         <v>47</v>
       </c>
-      <c r="H2" s="132" t="s">
+      <c r="I2" s="132" t="s">
         <v>54</v>
       </c>
-      <c r="I2" s="132" t="s">
-        <v>112</v>
-      </c>
       <c r="J2" s="132" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K2" s="132" t="s">
+        <v>109</v>
+      </c>
+      <c r="L2" s="132" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="132" t="s">
+      <c r="M2" s="132" t="s">
         <v>76</v>
       </c>
-      <c r="M2" s="132" t="s">
+      <c r="N2" s="132" t="s">
         <v>32</v>
       </c>
-      <c r="N2" s="132" t="s">
+      <c r="O2" s="132" t="s">
+        <v>103</v>
+      </c>
+      <c r="P2" s="132" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q2" s="132" t="s">
         <v>104</v>
       </c>
-      <c r="O2" s="132" t="s">
-        <v>3</v>
-      </c>
-      <c r="P2" s="132" t="s">
+      <c r="R2" s="132" t="s">
         <v>105</v>
       </c>
-      <c r="Q2" s="132" t="s">
-        <v>106</v>
-      </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C3" s="90">
-        <f>H3*$A$9/$H$9</f>
+    <row r="3" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <f>E3/D3</f>
+        <v>0.17323490542408534</v>
+      </c>
+      <c r="D3" s="90">
+        <f>I3*$B$9/$I$9</f>
         <v>0.93727303916393978</v>
       </c>
-      <c r="D3" s="90">
-        <f>J3*$A$9/$H$9</f>
+      <c r="E3" s="90">
+        <f>K3*$B$9/$I$9</f>
         <v>0.16236840629611016</v>
       </c>
-      <c r="E3" s="69" t="s">
+      <c r="F3" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="2">
+      <c r="H3" s="2">
         <f>'18F norm Option 1'!G3</f>
         <v>2.2913000000000001</v>
       </c>
-      <c r="H3" s="35">
+      <c r="I3" s="35">
         <f>'18F norm Option 1'!H3</f>
         <v>7.4353114331521173</v>
       </c>
-      <c r="I3" s="134">
+      <c r="J3" s="134">
         <f>'18F norm Option 1'!I3</f>
         <v>0.19059799999999999</v>
       </c>
-      <c r="J3" s="134">
+      <c r="K3" s="134">
         <f>'18F norm Option 1'!J3</f>
         <v>1.2880554729207276</v>
       </c>
-      <c r="K3" s="134">
+      <c r="L3" s="134">
         <f>'18F norm Option 1'!K3</f>
         <v>2.3610099999999998</v>
       </c>
-      <c r="L3" s="134">
+      <c r="M3" s="134">
         <f>'18F norm Option 1'!L3</f>
         <v>0.78700300000000001</v>
       </c>
-      <c r="M3" s="132"/>
       <c r="N3" s="132"/>
       <c r="O3" s="132"/>
       <c r="P3" s="132"/>
       <c r="Q3" s="132"/>
-      <c r="R3" t="s">
+      <c r="R3" s="132"/>
+      <c r="S3" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="X3">
+        <f>K3/I3</f>
+        <v>0.17323490542408537</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4">
+        <f t="shared" ref="A4:A25" si="0">E4/D4</f>
+        <v>0.2819818448039435</v>
+      </c>
+      <c r="B4">
         <v>0.10199999999999999</v>
       </c>
-      <c r="B4">
-        <f>0.2*A4</f>
+      <c r="C4">
+        <f>0.2*B4</f>
         <v>2.0400000000000001E-2</v>
       </c>
-      <c r="C4" s="90">
-        <f>H4*$A$9/$H$9</f>
+      <c r="D4" s="90">
+        <f>I4*$B$9/$I$9</f>
         <v>0.12893044151799851</v>
       </c>
-      <c r="D4" s="90">
-        <f>J4*$A$9/$H$9</f>
+      <c r="E4" s="90">
+        <f>K4*$B$9/$I$9</f>
         <v>3.6356043750632172E-2</v>
       </c>
-      <c r="E4" s="124" t="s">
+      <c r="F4" s="124" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="54" t="s">
+      <c r="G4" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="54">
-        <f>M4*O4</f>
+      <c r="H4" s="54">
+        <f>N4*P4</f>
         <v>0.31518917999999996</v>
       </c>
-      <c r="H4" s="55">
-        <f>G4*$G$29</f>
+      <c r="I4" s="55">
+        <f>H4*$H$29</f>
         <v>1.0227947949460308</v>
       </c>
-      <c r="I4" s="54"/>
-      <c r="J4" s="54">
-        <f>H4*SQRT(POWER(($H$29/$G$29),2)+POWER((Q4/O4),2)+POWER((N4/M4),2))</f>
+      <c r="J4" s="54"/>
+      <c r="K4" s="54">
+        <f>I4*SQRT(POWER(($I$29/$H$29),2)+POWER((R4/P4),2)+POWER((O4/N4),2))</f>
         <v>0.28840956313475286</v>
       </c>
-      <c r="K4" s="54">
+      <c r="L4" s="54">
         <v>86.371700000000004</v>
       </c>
-      <c r="L4" s="54">
+      <c r="M4" s="54">
         <v>7.8519699999999997</v>
       </c>
-      <c r="M4" s="54">
+      <c r="N4" s="54">
         <v>0.10199999999999999</v>
       </c>
-      <c r="N4" s="54">
-        <f>0.2*M4</f>
+      <c r="O4" s="54">
+        <f>0.2*N4</f>
         <v>2.0400000000000001E-2</v>
       </c>
-      <c r="O4" s="54">
+      <c r="P4" s="54">
         <v>3.09009</v>
       </c>
-      <c r="P4" s="54">
+      <c r="Q4" s="54">
         <v>0.141321</v>
       </c>
-      <c r="Q4" s="56">
-        <f>P4*SQRT(L4)</f>
+      <c r="R4" s="56">
+        <f>Q4*SQRT(M4)</f>
         <v>0.39600075842500704</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="X4">
+        <f t="shared" ref="X4:X25" si="1">K4/I4</f>
+        <v>0.2819818448039435</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5">
+        <f t="shared" si="0"/>
+        <v>0.2819818448039435</v>
+      </c>
+      <c r="B5">
         <v>0.30599999999999999</v>
       </c>
-      <c r="B5">
-        <f t="shared" ref="B5:B18" si="0">0.2*A5</f>
+      <c r="C5">
+        <f t="shared" ref="C5:C18" si="2">0.2*B5</f>
         <v>6.1200000000000004E-2</v>
       </c>
-      <c r="C5" s="90">
-        <f t="shared" ref="C5:C25" si="1">H5*$A$9/$H$9</f>
+      <c r="D5" s="90">
+        <f t="shared" ref="D5:D25" si="3">I5*$B$9/$I$9</f>
         <v>0.38679132455399562</v>
       </c>
-      <c r="D5" s="90">
-        <f t="shared" ref="D5:D18" si="2">J5*$A$9/$H$9</f>
+      <c r="E5" s="90">
+        <f t="shared" ref="E5:E18" si="4">K5*$B$9/$I$9</f>
         <v>0.10906813125189653</v>
       </c>
-      <c r="E5" s="126"/>
-      <c r="F5" s="161" t="s">
+      <c r="F5" s="126"/>
+      <c r="G5" s="161" t="s">
         <v>58</v>
       </c>
-      <c r="G5" s="161">
-        <f>M5*O5</f>
+      <c r="H5" s="161">
+        <f>N5*P5</f>
         <v>0.94556753999999998</v>
       </c>
-      <c r="H5" s="166">
-        <f>G5*$G$29</f>
+      <c r="I5" s="166">
+        <f>H5*$H$29</f>
         <v>3.0683843848380925</v>
       </c>
-      <c r="I5" s="161"/>
-      <c r="J5" s="161">
-        <f>H5*SQRT(POWER(($H$29/$G$29),2)+POWER((Q5/O5),2)+POWER((N5/M5),2))</f>
+      <c r="J5" s="161"/>
+      <c r="K5" s="161">
+        <f>I5*SQRT(POWER(($I$29/$H$29),2)+POWER((R5/P5),2)+POWER((O5/N5),2))</f>
         <v>0.86522868940425868</v>
       </c>
-      <c r="K5" s="161">
+      <c r="L5" s="161">
         <v>86.371700000000004</v>
       </c>
-      <c r="L5" s="161">
+      <c r="M5" s="161">
         <v>7.8519699999999997</v>
       </c>
-      <c r="M5" s="161">
+      <c r="N5" s="161">
         <v>0.30599999999999999</v>
       </c>
-      <c r="N5" s="161">
-        <f t="shared" ref="N5:N7" si="3">0.2*M5</f>
+      <c r="O5" s="161">
+        <f t="shared" ref="O5:O7" si="5">0.2*N5</f>
         <v>6.1200000000000004E-2</v>
       </c>
-      <c r="O5" s="161">
+      <c r="P5" s="161">
         <v>3.09009</v>
       </c>
-      <c r="P5" s="161">
+      <c r="Q5" s="161">
         <v>0.141321</v>
       </c>
-      <c r="Q5" s="28">
-        <f t="shared" ref="Q5:Q7" si="4">P5*SQRT(L5)</f>
+      <c r="R5" s="28">
+        <f t="shared" ref="R5:R7" si="6">Q5*SQRT(M5)</f>
         <v>0.39600075842500704</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" ht="17" x14ac:dyDescent="0.2">
+      <c r="X5">
+        <f t="shared" si="1"/>
+        <v>0.2819818448039435</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" ht="17" x14ac:dyDescent="0.2">
       <c r="A6">
+        <f t="shared" si="0"/>
+        <v>0.2819818448039435</v>
+      </c>
+      <c r="B6">
         <v>0.96</v>
       </c>
-      <c r="B6">
+      <c r="C6">
+        <f t="shared" si="2"/>
+        <v>0.192</v>
+      </c>
+      <c r="D6" s="90">
+        <f t="shared" si="3"/>
+        <v>1.2134629789929272</v>
+      </c>
+      <c r="E6" s="90">
+        <f t="shared" si="4"/>
+        <v>0.34217452941771459</v>
+      </c>
+      <c r="F6" s="62" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="161" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" s="161">
+        <f>N6*P6</f>
+        <v>2.9664864</v>
+      </c>
+      <c r="I6" s="166">
+        <f>H6*$H$29</f>
+        <v>9.626303952433231</v>
+      </c>
+      <c r="J6" s="161"/>
+      <c r="K6" s="161">
+        <f>I6*SQRT(POWER(($I$29/$H$29),2)+POWER((R6/P6),2)+POWER((O6/N6),2))</f>
+        <v>2.7144429471506153</v>
+      </c>
+      <c r="L6" s="161">
+        <v>86.371700000000004</v>
+      </c>
+      <c r="M6" s="161">
+        <v>7.8519699999999997</v>
+      </c>
+      <c r="N6" s="161">
+        <v>0.96</v>
+      </c>
+      <c r="O6" s="161">
+        <f t="shared" si="5"/>
+        <v>0.192</v>
+      </c>
+      <c r="P6" s="161">
+        <v>3.09009</v>
+      </c>
+      <c r="Q6" s="161">
+        <v>0.141321</v>
+      </c>
+      <c r="R6" s="28">
+        <f t="shared" si="6"/>
+        <v>0.39600075842500704</v>
+      </c>
+      <c r="X6">
+        <f t="shared" si="1"/>
+        <v>0.2819818448039435</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7">
         <f t="shared" si="0"/>
-        <v>0.192</v>
-      </c>
-      <c r="C6" s="90">
+        <v>0.2819818448039435</v>
+      </c>
+      <c r="B7">
+        <v>0.89</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="2"/>
+        <v>0.17800000000000002</v>
+      </c>
+      <c r="D7" s="90">
+        <f t="shared" si="3"/>
+        <v>1.12498130344136</v>
+      </c>
+      <c r="E7" s="90">
+        <f t="shared" si="4"/>
+        <v>0.31722430331433965</v>
+      </c>
+      <c r="F7" s="59" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="30">
+        <f>N7*P7</f>
+        <v>2.7501801000000001</v>
+      </c>
+      <c r="I7" s="41">
+        <f>H7*$H$29</f>
+        <v>8.9243859559016432</v>
+      </c>
+      <c r="J7" s="30"/>
+      <c r="K7" s="30">
+        <f>I7*SQRT(POWER(($I$29/$H$29),2)+POWER((R7/P7),2)+POWER((O7/N7),2))</f>
+        <v>2.5165148155875503</v>
+      </c>
+      <c r="L7" s="30">
+        <v>86.371700000000004</v>
+      </c>
+      <c r="M7" s="30">
+        <v>7.8519699999999997</v>
+      </c>
+      <c r="N7" s="30">
+        <v>0.89</v>
+      </c>
+      <c r="O7" s="30">
+        <f t="shared" si="5"/>
+        <v>0.17800000000000002</v>
+      </c>
+      <c r="P7" s="30">
+        <v>3.09009</v>
+      </c>
+      <c r="Q7" s="30">
+        <v>0.141321</v>
+      </c>
+      <c r="R7" s="31">
+        <f t="shared" si="6"/>
+        <v>0.39600075842500704</v>
+      </c>
+      <c r="X7">
         <f t="shared" si="1"/>
-        <v>1.2134629789929272</v>
-      </c>
-      <c r="D6" s="90">
+        <v>0.2819818448039435</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <f t="shared" si="0"/>
+        <v>0.62713137818226228</v>
+      </c>
+      <c r="B8">
+        <v>0.21</v>
+      </c>
+      <c r="C8">
         <f t="shared" si="2"/>
-        <v>0.34217452941771459</v>
-      </c>
-      <c r="E6" s="62" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" s="161" t="s">
-        <v>8</v>
-      </c>
-      <c r="G6" s="161">
-        <f>M6*O6</f>
-        <v>2.9664864</v>
-      </c>
-      <c r="H6" s="166">
-        <f>G6*$G$29</f>
-        <v>9.626303952433231</v>
-      </c>
-      <c r="I6" s="161"/>
-      <c r="J6" s="161">
-        <f>H6*SQRT(POWER(($H$29/$G$29),2)+POWER((Q6/O6),2)+POWER((N6/M6),2))</f>
-        <v>2.7144429471506153</v>
-      </c>
-      <c r="K6" s="161">
-        <v>86.371700000000004</v>
-      </c>
-      <c r="L6" s="161">
-        <v>7.8519699999999997</v>
-      </c>
-      <c r="M6" s="161">
-        <v>0.96</v>
-      </c>
-      <c r="N6" s="161">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="D8" s="90">
         <f t="shared" si="3"/>
-        <v>0.192</v>
-      </c>
-      <c r="O6" s="161">
-        <v>3.09009</v>
-      </c>
-      <c r="P6" s="161">
-        <v>0.141321</v>
-      </c>
-      <c r="Q6" s="28">
+        <v>6.3662408951757635E-2</v>
+      </c>
+      <c r="E8" s="90">
         <f t="shared" si="4"/>
-        <v>0.39600075842500704</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>0.89</v>
-      </c>
-      <c r="B7">
-        <f t="shared" si="0"/>
-        <v>0.17800000000000002</v>
-      </c>
-      <c r="C7" s="90">
-        <f t="shared" si="1"/>
-        <v>1.12498130344136</v>
-      </c>
-      <c r="D7" s="90">
-        <f t="shared" si="2"/>
-        <v>0.31722430331433965</v>
-      </c>
-      <c r="E7" s="59" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7" s="30">
-        <f>M7*O7</f>
-        <v>2.7501801000000001</v>
-      </c>
-      <c r="H7" s="41">
-        <f>G7*$G$29</f>
-        <v>8.9243859559016432</v>
-      </c>
-      <c r="I7" s="30"/>
-      <c r="J7" s="30">
-        <f>H7*SQRT(POWER(($H$29/$G$29),2)+POWER((Q7/O7),2)+POWER((N7/M7),2))</f>
-        <v>2.5165148155875503</v>
-      </c>
-      <c r="K7" s="30">
-        <v>86.371700000000004</v>
-      </c>
-      <c r="L7" s="30">
-        <v>7.8519699999999997</v>
-      </c>
-      <c r="M7" s="30">
-        <v>0.89</v>
-      </c>
-      <c r="N7" s="30">
-        <f t="shared" si="3"/>
-        <v>0.17800000000000002</v>
-      </c>
-      <c r="O7" s="30">
-        <v>3.09009</v>
-      </c>
-      <c r="P7" s="30">
-        <v>0.141321</v>
-      </c>
-      <c r="Q7" s="31">
-        <f t="shared" si="4"/>
-        <v>0.39600075842500704</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>0.21</v>
-      </c>
-      <c r="B8">
-        <f t="shared" si="0"/>
-        <v>4.2000000000000003E-2</v>
-      </c>
-      <c r="C8" s="90">
-        <f t="shared" si="1"/>
-        <v>6.3662408951757635E-2</v>
-      </c>
-      <c r="D8" s="90">
-        <f t="shared" si="2"/>
         <v>3.9924694264318557E-2</v>
       </c>
-      <c r="E8" s="118" t="s">
+      <c r="F8" s="118" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="2">
+      <c r="H8" s="2">
         <f>'18F norm Option 1'!G6</f>
         <v>0.15563199999999999</v>
       </c>
-      <c r="H8" s="35">
+      <c r="I8" s="35">
         <f>'18F norm Option 1'!H6</f>
         <v>0.50502875614905518</v>
       </c>
-      <c r="I8" s="134">
+      <c r="J8" s="134">
         <f>'18F norm Option 1'!I6</f>
         <v>5.4237800000000003E-2</v>
       </c>
-      <c r="J8" s="169">
+      <c r="K8" s="169">
         <f>'18F norm Option 1'!J6</f>
         <v>0.31671937986543069</v>
       </c>
-      <c r="K8" s="134">
+      <c r="L8" s="134">
         <f>'18F norm Option 1'!K6</f>
         <v>24.385100000000001</v>
       </c>
-      <c r="L8" s="170">
+      <c r="M8" s="170">
         <f>'18F norm Option 1'!L6</f>
         <v>3.04813</v>
       </c>
-      <c r="M8" s="132"/>
       <c r="N8" s="132"/>
       <c r="O8" s="132"/>
       <c r="P8" s="132"/>
       <c r="Q8" s="132"/>
-      <c r="R8" t="s">
+      <c r="R8" s="132"/>
+      <c r="S8" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="X8">
+        <f t="shared" si="1"/>
+        <v>0.62713137818226239</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9">
+        <f t="shared" si="0"/>
+        <v>0.20907278267795271</v>
+      </c>
+      <c r="B9">
         <v>0.62</v>
       </c>
-      <c r="B9">
-        <f t="shared" si="0"/>
+      <c r="C9">
+        <f t="shared" si="2"/>
         <v>0.124</v>
       </c>
-      <c r="C9" s="90">
-        <f t="shared" si="1"/>
+      <c r="D9" s="90">
+        <f t="shared" si="3"/>
         <v>0.62</v>
       </c>
-      <c r="D9" s="90">
-        <f t="shared" si="2"/>
+      <c r="E9" s="90">
+        <f t="shared" si="4"/>
         <v>0.12962512526033068</v>
       </c>
-      <c r="E9" s="119"/>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="119"/>
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="G9" s="6">
+      <c r="H9" s="6">
         <f>'18F norm Option 1'!G7</f>
         <v>1.5156799999999999</v>
       </c>
-      <c r="H9" s="34">
+      <c r="I9" s="34">
         <f>'18F norm Option 1'!H7</f>
         <v>4.9184099999999997</v>
       </c>
-      <c r="I9" s="135">
+      <c r="J9" s="135">
         <f>'18F norm Option 1'!I7</f>
         <v>0.124664</v>
       </c>
-      <c r="J9" s="171">
+      <c r="K9" s="171">
         <f>'18F norm Option 1'!O7</f>
         <v>1.0283056650510694</v>
       </c>
-      <c r="K9" s="135">
+      <c r="L9" s="135">
         <f>'18F norm Option 1'!K7</f>
         <v>24.385100000000001</v>
       </c>
-      <c r="L9" s="172">
+      <c r="M9" s="172">
         <f>'18F norm Option 1'!L7</f>
         <v>3.04813</v>
       </c>
-      <c r="M9" s="132"/>
       <c r="N9" s="132"/>
       <c r="O9" s="132"/>
       <c r="P9" s="132"/>
       <c r="Q9" s="132"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="C10" s="90"/>
+      <c r="R9" s="132"/>
+      <c r="X9">
+        <f t="shared" si="1"/>
+        <v>0.20907278267795271</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D10" s="90"/>
-      <c r="E10" s="125" t="s">
+      <c r="E10" s="90"/>
+      <c r="F10" s="125" t="s">
         <v>55</v>
       </c>
-      <c r="F10" s="17" t="s">
+      <c r="G10" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="35"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="136">
-        <f t="shared" ref="J10:J11" si="5">I10*SQRT(L10)</f>
+      <c r="H10" s="2"/>
+      <c r="I10" s="35"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="136">
+        <f t="shared" ref="K10:K11" si="7">J10*SQRT(M10)</f>
         <v>0</v>
       </c>
-      <c r="K10" s="2"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="132"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="3"/>
       <c r="N10" s="132"/>
       <c r="O10" s="132"/>
       <c r="P10" s="132"/>
       <c r="Q10" s="132"/>
-      <c r="R10" t="s">
+      <c r="R10" s="132"/>
+      <c r="S10" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C11" s="90"/>
+    <row r="11" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D11" s="90"/>
-      <c r="E11" s="121"/>
-      <c r="F11" s="22" t="s">
+      <c r="E11" s="90"/>
+      <c r="F11" s="121"/>
+      <c r="G11" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="G11" s="6"/>
-      <c r="H11" s="34"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="173">
-        <f t="shared" si="5"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="34"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="173">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="K11" s="6"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="132"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="7"/>
       <c r="N11" s="132"/>
       <c r="O11" s="132"/>
       <c r="P11" s="132"/>
       <c r="Q11" s="132"/>
-    </row>
-    <row r="12" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="R11" s="132"/>
+    </row>
+    <row r="12" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12">
+        <f t="shared" si="0"/>
+        <v>0.33530196763459708</v>
+      </c>
+      <c r="B12">
         <v>0.17</v>
       </c>
-      <c r="B12">
-        <f t="shared" si="0"/>
+      <c r="C12">
+        <f t="shared" si="2"/>
         <v>3.4000000000000002E-2</v>
       </c>
-      <c r="C12" s="90">
-        <f t="shared" si="1"/>
+      <c r="D12" s="90">
+        <f t="shared" si="3"/>
         <v>0.14737312625356278</v>
       </c>
-      <c r="D12" s="90">
-        <f t="shared" si="2"/>
+      <c r="E12" s="90">
+        <f t="shared" si="4"/>
         <v>4.9414499209281496E-2</v>
       </c>
-      <c r="E12" s="118" t="s">
+      <c r="F12" s="118" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="G12" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G12" s="2">
+      <c r="H12" s="2">
         <f>'18F norm Option 1'!G10</f>
         <v>0.36027500000000001</v>
       </c>
-      <c r="H12" s="35">
-        <f>G12*$G$29</f>
+      <c r="I12" s="35">
+        <f>H12*$H$29</f>
         <v>1.169099125639977</v>
       </c>
-      <c r="I12" s="2">
+      <c r="J12" s="2">
         <f>'18F norm Option 1'!I10</f>
         <v>6.9371299999999997E-2</v>
       </c>
-      <c r="J12" s="2">
+      <c r="K12" s="2">
         <f>'18F norm Option 1'!J10</f>
         <v>0.39200123718697127</v>
       </c>
-      <c r="K12" s="2">
+      <c r="L12" s="2">
         <f>'18F norm Option 1'!K10</f>
         <v>14.4574</v>
       </c>
-      <c r="L12" s="2">
+      <c r="M12" s="2">
         <f>'18F norm Option 1'!L10</f>
         <v>2.4095599999999999</v>
       </c>
-      <c r="M12" s="132"/>
       <c r="N12" s="132"/>
       <c r="O12" s="132"/>
       <c r="P12" s="132"/>
       <c r="Q12" s="132"/>
-      <c r="R12" t="s">
+      <c r="R12" s="132"/>
+      <c r="S12" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="X12">
+        <f t="shared" si="1"/>
+        <v>0.33530196763459708</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13">
+        <f t="shared" si="0"/>
+        <v>0.17942645284541428</v>
+      </c>
+      <c r="B13">
         <v>0.68</v>
       </c>
-      <c r="B13">
-        <f t="shared" si="0"/>
+      <c r="C13">
+        <f t="shared" si="2"/>
         <v>0.13600000000000001</v>
       </c>
-      <c r="C13" s="90">
-        <f t="shared" si="1"/>
+      <c r="D13" s="90">
+        <f t="shared" si="3"/>
         <v>0.77927055842921999</v>
       </c>
-      <c r="D13" s="90">
-        <f t="shared" si="2"/>
+      <c r="E13" s="90">
+        <f t="shared" si="4"/>
         <v>0.1398217521058201</v>
       </c>
-      <c r="E13" s="119"/>
-      <c r="F13" s="6" t="s">
+      <c r="F13" s="119"/>
+      <c r="G13" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G13" s="6">
+      <c r="H13" s="6">
         <f>'18F norm Option 1'!G11</f>
         <v>1.9050400000000001</v>
       </c>
-      <c r="H13" s="34">
-        <f>G13*$G$29</f>
+      <c r="I13" s="34">
+        <f>H13*$H$29</f>
         <v>6.181890495619129</v>
       </c>
-      <c r="I13" s="2">
+      <c r="J13" s="2">
         <f>'18F norm Option 1'!I11</f>
         <v>0.117092</v>
       </c>
-      <c r="J13" s="2">
+      <c r="K13" s="2">
         <f>'18F norm Option 1'!J11</f>
         <v>1.1091946835077204</v>
       </c>
-      <c r="K13" s="2">
+      <c r="L13" s="2">
         <f>'18F norm Option 1'!K11</f>
         <v>14.4574</v>
       </c>
-      <c r="L13" s="2">
+      <c r="M13" s="2">
         <f>'18F norm Option 1'!L11</f>
         <v>2.4095599999999999</v>
       </c>
-      <c r="M13" s="132"/>
       <c r="N13" s="132"/>
       <c r="O13" s="132"/>
       <c r="P13" s="132"/>
       <c r="Q13" s="132"/>
-    </row>
-    <row r="14" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="R13" s="132"/>
+      <c r="X13">
+        <f t="shared" si="1"/>
+        <v>0.17942645284541428</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14">
+        <f t="shared" si="0"/>
+        <v>0.33589419795562614</v>
+      </c>
+      <c r="B14">
         <v>7.3999999999999996E-2</v>
       </c>
-      <c r="B14">
-        <f t="shared" si="0"/>
+      <c r="C14">
+        <f t="shared" si="2"/>
         <v>1.4800000000000001E-2</v>
       </c>
-      <c r="C14" s="90">
-        <f t="shared" si="1"/>
+      <c r="D14" s="90">
+        <f t="shared" si="3"/>
         <v>0.17371969017206801</v>
       </c>
-      <c r="D14" s="90">
-        <f t="shared" si="2"/>
+      <c r="E14" s="90">
+        <f t="shared" si="4"/>
         <v>5.8351435999446651E-2</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="F14" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="G14" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="6">
+      <c r="H14" s="6">
         <f>'18F norm Option 1'!G12</f>
         <v>0.42468299999999998</v>
       </c>
-      <c r="H14" s="35">
-        <f>G14*$G$29</f>
+      <c r="I14" s="35">
+        <f>H14*$H$29</f>
         <v>1.3781042924825821</v>
       </c>
-      <c r="I14" s="2">
+      <c r="J14" s="2">
         <f>'18F norm Option 1'!I12</f>
         <v>8.5518999999999998E-2</v>
       </c>
-      <c r="J14" s="2">
+      <c r="K14" s="2">
         <f>'18F norm Option 1'!J12</f>
         <v>0.46289723602264254</v>
       </c>
-      <c r="K14" s="2">
+      <c r="L14" s="2">
         <f>'18F norm Option 1'!K12</f>
         <v>11.064500000000001</v>
       </c>
-      <c r="L14" s="2">
+      <c r="M14" s="2">
         <f>'18F norm Option 1'!L12</f>
         <v>2.2128999999999999</v>
       </c>
-      <c r="M14" s="132"/>
       <c r="N14" s="132"/>
       <c r="O14" s="132"/>
       <c r="P14" s="132"/>
       <c r="Q14" s="132"/>
-      <c r="R14" t="s">
+      <c r="R14" s="132"/>
+      <c r="S14" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="X14">
+        <f t="shared" si="1"/>
+        <v>0.33589419795562614</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15">
+        <f t="shared" si="0"/>
+        <v>0.26734310826738167</v>
+      </c>
+      <c r="B15">
         <v>1.04</v>
       </c>
-      <c r="B15">
+      <c r="C15">
+        <f t="shared" si="2"/>
+        <v>0.20800000000000002</v>
+      </c>
+      <c r="D15" s="90">
+        <f t="shared" si="3"/>
+        <v>0.88432825926316905</v>
+      </c>
+      <c r="E15" s="90">
+        <f t="shared" si="4"/>
+        <v>0.23641906556009859</v>
+      </c>
+      <c r="F15" s="70" t="s">
+        <v>25</v>
+      </c>
+      <c r="G15" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" s="48">
+        <f>N15*P15</f>
+        <v>2.1618688000000001</v>
+      </c>
+      <c r="I15" s="57">
+        <f>H15*$H$29</f>
+        <v>7.0153047639396187</v>
+      </c>
+      <c r="J15" s="48"/>
+      <c r="K15" s="48">
+        <f>I15*SQRT(POWER(($I$29/$H$29),2)+POWER((R15/P15),2)+POWER((O15/N15),2))</f>
+        <v>1.875493381034588</v>
+      </c>
+      <c r="L15" s="48">
+        <v>55.631799999999998</v>
+      </c>
+      <c r="M15" s="48">
+        <v>7.9474</v>
+      </c>
+      <c r="N15" s="48">
+        <v>1.04</v>
+      </c>
+      <c r="O15" s="48">
+        <f>0.2*N15</f>
+        <v>0.20800000000000002</v>
+      </c>
+      <c r="P15" s="48">
+        <v>2.0787200000000001</v>
+      </c>
+      <c r="Q15" s="48">
+        <v>6.7506200000000002E-2</v>
+      </c>
+      <c r="R15" s="71">
+        <f>Q15*SQRT(M15)</f>
+        <v>0.19030762866815942</v>
+      </c>
+      <c r="S15" t="s">
+        <v>95</v>
+      </c>
+      <c r="X15">
+        <f t="shared" si="1"/>
+        <v>0.26734310826738167</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16">
         <f t="shared" si="0"/>
-        <v>0.20800000000000002</v>
-      </c>
-      <c r="C15" s="90">
+        <v>0.26734310826738156</v>
+      </c>
+      <c r="B16">
+        <v>0.18</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="2"/>
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="D16" s="90">
+        <f t="shared" si="3"/>
+        <v>0.15305681410324079</v>
+      </c>
+      <c r="E16" s="90">
+        <f t="shared" si="4"/>
+        <v>4.0918684423863198E-2</v>
+      </c>
+      <c r="F16" s="73" t="s">
+        <v>27</v>
+      </c>
+      <c r="G16" s="74" t="s">
+        <v>8</v>
+      </c>
+      <c r="H16" s="74">
+        <f>N16*P16</f>
+        <v>0.37416959999999999</v>
+      </c>
+      <c r="I16" s="75">
+        <f>H16*$H$29</f>
+        <v>1.2141873629895492</v>
+      </c>
+      <c r="J16" s="74"/>
+      <c r="K16" s="74">
+        <f>I16*SQRT(POWER(($I$29/$H$29),2)+POWER((R16/P16),2)+POWER((O16/N16),2))</f>
+        <v>0.32460462364060161</v>
+      </c>
+      <c r="L16" s="74">
+        <v>55.631799999999998</v>
+      </c>
+      <c r="M16" s="74">
+        <v>7.9474</v>
+      </c>
+      <c r="N16" s="74">
+        <v>0.18</v>
+      </c>
+      <c r="O16" s="74">
+        <f>0.2*N16</f>
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="P16" s="74">
+        <v>2.0787200000000001</v>
+      </c>
+      <c r="Q16" s="74">
+        <v>6.7506200000000002E-2</v>
+      </c>
+      <c r="R16" s="76">
+        <f t="shared" ref="R16:R21" si="8">Q16*SQRT(M16)</f>
+        <v>0.19030762866815942</v>
+      </c>
+      <c r="X16">
         <f t="shared" si="1"/>
-        <v>0.88432825926316905</v>
-      </c>
-      <c r="D15" s="90">
+        <v>0.26734310826738161</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <f t="shared" si="0"/>
+        <v>0.39872152786715087</v>
+      </c>
+      <c r="B17">
+        <v>0.17</v>
+      </c>
+      <c r="C17">
         <f t="shared" si="2"/>
-        <v>0.23641906556009859</v>
-      </c>
-      <c r="E15" s="70" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="48" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15" s="48">
-        <f>M15*O15</f>
-        <v>2.1618688000000001</v>
-      </c>
-      <c r="H15" s="57">
-        <f>G15*$G$29</f>
-        <v>7.0153047639396187</v>
-      </c>
-      <c r="I15" s="48"/>
-      <c r="J15" s="48">
-        <f>H15*SQRT(POWER(($H$29/$G$29),2)+POWER((Q15/O15),2)+POWER((N15/M15),2))</f>
-        <v>1.875493381034588</v>
-      </c>
-      <c r="K15" s="48">
-        <v>55.631799999999998</v>
-      </c>
-      <c r="L15" s="48">
-        <v>7.9474</v>
-      </c>
-      <c r="M15" s="48">
-        <v>1.04</v>
-      </c>
-      <c r="N15" s="48">
-        <f>0.2*M15</f>
-        <v>0.20800000000000002</v>
-      </c>
-      <c r="O15" s="48">
-        <v>2.0787200000000001</v>
-      </c>
-      <c r="P15" s="48">
-        <v>6.7506200000000002E-2</v>
-      </c>
-      <c r="Q15" s="71">
-        <f>P15*SQRT(L15)</f>
-        <v>0.19030762866815942</v>
-      </c>
-      <c r="R15" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>0.18</v>
-      </c>
-      <c r="B16">
-        <f t="shared" si="0"/>
-        <v>3.5999999999999997E-2</v>
-      </c>
-      <c r="C16" s="90">
-        <f t="shared" si="1"/>
-        <v>0.15305681410324079</v>
-      </c>
-      <c r="D16" s="90">
-        <f t="shared" si="2"/>
-        <v>4.0918684423863198E-2</v>
-      </c>
-      <c r="E16" s="73" t="s">
-        <v>27</v>
-      </c>
-      <c r="F16" s="74" t="s">
-        <v>8</v>
-      </c>
-      <c r="G16" s="74">
-        <f>M16*O16</f>
-        <v>0.37416959999999999</v>
-      </c>
-      <c r="H16" s="75">
-        <f>G16*$G$29</f>
-        <v>1.2141873629895492</v>
-      </c>
-      <c r="I16" s="74"/>
-      <c r="J16" s="74">
-        <f>H16*SQRT(POWER(($H$29/$G$29),2)+POWER((Q16/O16),2)+POWER((N16/M16),2))</f>
-        <v>0.32460462364060161</v>
-      </c>
-      <c r="K16" s="74">
-        <v>55.631799999999998</v>
-      </c>
-      <c r="L16" s="74">
-        <v>7.9474</v>
-      </c>
-      <c r="M16" s="74">
-        <v>0.18</v>
-      </c>
-      <c r="N16" s="74">
-        <f>0.2*M16</f>
-        <v>3.5999999999999997E-2</v>
-      </c>
-      <c r="O16" s="74">
-        <v>2.0787200000000001</v>
-      </c>
-      <c r="P16" s="74">
-        <v>6.7506200000000002E-2</v>
-      </c>
-      <c r="Q16" s="76">
-        <f t="shared" ref="Q16:Q21" si="6">P16*SQRT(L16)</f>
-        <v>0.19030762866815942</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>0.17</v>
-      </c>
-      <c r="B17">
-        <f t="shared" si="0"/>
         <v>3.4000000000000002E-2</v>
       </c>
-      <c r="C17" s="90">
-        <f t="shared" si="1"/>
+      <c r="D17" s="90">
+        <f t="shared" si="3"/>
         <v>0.15681294204581445</v>
       </c>
-      <c r="D17" s="90">
-        <f t="shared" si="2"/>
+      <c r="E17" s="90">
+        <f t="shared" si="4"/>
         <v>6.2524695841850123E-2</v>
       </c>
-      <c r="E17" s="118" t="s">
+      <c r="F17" s="118" t="s">
         <v>28</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="G17" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G17" s="2">
+      <c r="H17" s="2">
         <f>'18F norm Option 1'!G14</f>
         <v>0.38335200000000003</v>
       </c>
-      <c r="H17" s="35">
+      <c r="I17" s="35">
         <f>'18F norm Option 1'!H14</f>
         <v>1.2439844230444423</v>
       </c>
-      <c r="I17" s="2">
+      <c r="J17" s="2">
         <f>'18F norm Option 1'!I14</f>
         <v>9.3142699999999995E-2</v>
       </c>
-      <c r="J17" s="2">
+      <c r="K17" s="2">
         <f>'18F norm Option 1'!J14</f>
         <v>0.49600336979921622</v>
       </c>
-      <c r="K17" s="2">
+      <c r="L17" s="2">
         <f>'18F norm Option 1'!K14</f>
         <v>13.811199999999999</v>
       </c>
-      <c r="L17" s="2">
+      <c r="M17" s="2">
         <f>'18F norm Option 1'!L14</f>
         <v>2.30186</v>
       </c>
-      <c r="M17" s="132"/>
       <c r="N17" s="132"/>
       <c r="O17" s="132"/>
       <c r="P17" s="132"/>
-      <c r="Q17" s="153"/>
-      <c r="R17" t="s">
+      <c r="Q17" s="132"/>
+      <c r="R17" s="153"/>
+      <c r="S17" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="18" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="X17">
+        <f t="shared" si="1"/>
+        <v>0.39872152786715087</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18">
+        <f t="shared" si="0"/>
+        <v>0.21669167509314727</v>
+      </c>
+      <c r="B18">
         <v>0.51</v>
       </c>
-      <c r="B18">
-        <f t="shared" si="0"/>
+      <c r="C18">
+        <f t="shared" si="2"/>
         <v>0.10200000000000001</v>
       </c>
-      <c r="C18" s="90">
-        <f t="shared" si="1"/>
+      <c r="D18" s="90">
+        <f t="shared" si="3"/>
         <v>0.47113995038530559</v>
       </c>
-      <c r="D18" s="90">
-        <f t="shared" si="2"/>
+      <c r="E18" s="90">
+        <f t="shared" si="4"/>
         <v>0.10209210505229416</v>
       </c>
-      <c r="E18" s="122"/>
-      <c r="F18" s="132" t="s">
+      <c r="F18" s="122"/>
+      <c r="G18" s="132" t="s">
         <v>11</v>
       </c>
-      <c r="G18" s="2">
+      <c r="H18" s="2">
         <f>'18F norm Option 1'!G15</f>
         <v>1.15177</v>
       </c>
-      <c r="H18" s="35">
+      <c r="I18" s="35">
         <f>'18F norm Option 1'!H15</f>
         <v>3.7375152312493403</v>
       </c>
-      <c r="I18" s="2">
+      <c r="J18" s="2">
         <f>'18F norm Option 1'!I15</f>
         <v>0.117274</v>
       </c>
-      <c r="J18" s="2">
+      <c r="K18" s="2">
         <f>'18F norm Option 1'!J15</f>
         <v>0.80988843614557104</v>
       </c>
-      <c r="K18" s="2">
+      <c r="L18" s="2">
         <f>'18F norm Option 1'!K15</f>
         <v>13.811199999999999</v>
       </c>
-      <c r="L18" s="2">
+      <c r="M18" s="2">
         <f>'18F norm Option 1'!L15</f>
         <v>2.30186</v>
       </c>
-      <c r="M18" s="132"/>
       <c r="N18" s="132"/>
       <c r="O18" s="132"/>
       <c r="P18" s="132"/>
-      <c r="Q18" s="153"/>
-    </row>
-    <row r="19" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C19" s="90"/>
-      <c r="E19" s="81" t="s">
+      <c r="Q18" s="132"/>
+      <c r="R18" s="153"/>
+      <c r="X18">
+        <f t="shared" si="1"/>
+        <v>0.21669167509314721</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="D19" s="90"/>
+      <c r="F19" s="81" t="s">
         <v>29</v>
       </c>
-      <c r="F19" s="58" t="s">
+      <c r="G19" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="G19" s="58">
+      <c r="H19" s="58">
         <f>0.2*1.42</f>
         <v>0.28399999999999997</v>
       </c>
-      <c r="H19" s="82">
-        <f>G19*$G$29</f>
+      <c r="I19" s="82">
+        <f>H19*$H$29</f>
         <v>0.9215853214398817</v>
       </c>
-      <c r="I19" s="58"/>
-      <c r="J19" s="58">
-        <f>H19*SQRT(POWER(($H$29/$G$29),2)+POWER((Q19/O19),2)+POWER((N19/M19),2))</f>
+      <c r="J19" s="58"/>
+      <c r="K19" s="58">
+        <f>I19*SQRT(POWER(($I$29/$H$29),2)+POWER((R19/P19),2)+POWER((O19/N19),2))</f>
         <v>0.25725005957972208</v>
       </c>
-      <c r="K19" s="58">
+      <c r="L19" s="58">
         <v>13.728</v>
       </c>
-      <c r="L19" s="58">
+      <c r="M19" s="58">
         <v>2.74559</v>
       </c>
-      <c r="M19" s="58">
+      <c r="N19" s="58">
         <v>0.16</v>
       </c>
-      <c r="N19" s="58">
-        <f>0.2*M19</f>
+      <c r="O19" s="58">
+        <f>0.2*N19</f>
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="O19" s="58">
+      <c r="P19" s="58">
         <v>2.4052099999999998</v>
       </c>
-      <c r="P19" s="58">
+      <c r="Q19" s="58">
         <v>0.17675399999999999</v>
       </c>
-      <c r="Q19" s="83">
-        <f t="shared" si="6"/>
+      <c r="R19" s="83">
+        <f t="shared" si="8"/>
         <v>0.29287823118587092</v>
       </c>
-      <c r="R19" t="s">
+      <c r="S19" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="20" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C20" s="90"/>
-      <c r="E20" s="64" t="s">
+      <c r="X19">
+        <f t="shared" si="1"/>
+        <v>0.27913862514411086</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="D20" s="90"/>
+      <c r="F20" s="64" t="s">
         <v>30</v>
       </c>
-      <c r="F20" s="157" t="s">
+      <c r="G20" s="157" t="s">
         <v>7</v>
       </c>
-      <c r="G20" s="157">
+      <c r="H20" s="157">
         <f>0.75*1.42</f>
         <v>1.0649999999999999</v>
       </c>
-      <c r="H20" s="168">
-        <f>G20*$G$29</f>
+      <c r="I20" s="168">
+        <f>H20*$H$29</f>
         <v>3.4559449553995565</v>
       </c>
-      <c r="I20" s="157"/>
-      <c r="J20" s="58">
-        <f t="shared" ref="J20:J21" si="7">H20*SQRT(POWER(($H$29/$G$29),2)+POWER((Q20/O20),2)+POWER((N20/M20),2))</f>
+      <c r="J20" s="157"/>
+      <c r="K20" s="58">
+        <f t="shared" ref="K20:K21" si="9">I20*SQRT(POWER(($I$29/$H$29),2)+POWER((R20/P20),2)+POWER((O20/N20),2))</f>
         <v>0.96468772342395792</v>
       </c>
-      <c r="K20" s="157">
+      <c r="L20" s="157">
         <v>13.728</v>
       </c>
-      <c r="L20" s="157">
+      <c r="M20" s="157">
         <v>2.74559</v>
       </c>
-      <c r="M20" s="157">
+      <c r="N20" s="157">
         <v>1.01</v>
       </c>
-      <c r="N20" s="157">
-        <f t="shared" ref="N20:N21" si="8">0.2*M20</f>
+      <c r="O20" s="157">
+        <f t="shared" ref="O20:O21" si="10">0.2*N20</f>
         <v>0.20200000000000001</v>
       </c>
-      <c r="O20" s="157">
+      <c r="P20" s="157">
         <v>2.4052099999999998</v>
       </c>
-      <c r="P20" s="157">
+      <c r="Q20" s="157">
         <v>0.17675399999999999</v>
       </c>
-      <c r="Q20" s="45">
-        <f t="shared" si="6"/>
+      <c r="R20" s="45">
+        <f t="shared" si="8"/>
         <v>0.29287823118587092</v>
       </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="C21" s="90"/>
-      <c r="E21" s="64" t="s">
+      <c r="X20">
+        <f t="shared" si="1"/>
+        <v>0.27913862514411092</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="D21" s="90"/>
+      <c r="F21" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="F21" s="157" t="s">
+      <c r="G21" s="157" t="s">
         <v>10</v>
       </c>
-      <c r="G21" s="157">
+      <c r="H21" s="157">
         <v>0</v>
       </c>
-      <c r="H21" s="168">
-        <f>G21*$G$29</f>
+      <c r="I21" s="168">
+        <f>H21*$H$29</f>
         <v>0</v>
       </c>
-      <c r="I21" s="157"/>
-      <c r="J21" s="58">
-        <f t="shared" si="7"/>
+      <c r="J21" s="157"/>
+      <c r="K21" s="58">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="K21" s="157">
+      <c r="L21" s="157">
         <v>13.728</v>
       </c>
-      <c r="L21" s="157">
+      <c r="M21" s="157">
         <v>2.74559</v>
       </c>
-      <c r="M21" s="157">
+      <c r="N21" s="157">
         <v>0.35</v>
       </c>
-      <c r="N21" s="157">
+      <c r="O21" s="157">
+        <f t="shared" si="10"/>
+        <v>6.9999999999999993E-2</v>
+      </c>
+      <c r="P21" s="157">
+        <v>2.4052099999999998</v>
+      </c>
+      <c r="Q21" s="157">
+        <v>0.17675399999999999</v>
+      </c>
+      <c r="R21" s="45">
         <f t="shared" si="8"/>
-        <v>6.9999999999999993E-2</v>
-      </c>
-      <c r="O21" s="157">
-        <v>2.4052099999999998</v>
-      </c>
-      <c r="P21" s="157">
-        <v>0.17675399999999999</v>
-      </c>
-      <c r="Q21" s="45">
-        <f t="shared" si="6"/>
         <v>0.29287823118587092</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C22" s="90"/>
-      <c r="E22" s="84" t="s">
+    <row r="22" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="D22" s="90"/>
+      <c r="F22" s="84" t="s">
         <v>81</v>
       </c>
-      <c r="F22" s="15" t="s">
+      <c r="G22" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="G22" s="15">
+      <c r="H22" s="15">
         <v>0.03</v>
       </c>
-      <c r="H22" s="36"/>
-      <c r="I22" s="15"/>
+      <c r="I22" s="36"/>
       <c r="J22" s="15"/>
       <c r="K22" s="15"/>
       <c r="L22" s="15"/>
@@ -9479,1050 +9711,204 @@
       <c r="N22" s="15"/>
       <c r="O22" s="15"/>
       <c r="P22" s="15"/>
-      <c r="Q22" s="16"/>
-    </row>
-    <row r="23" spans="1:18" ht="35" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C23" s="90"/>
-      <c r="E23" s="65" t="s">
+      <c r="Q22" s="15"/>
+      <c r="R22" s="16"/>
+    </row>
+    <row r="23" spans="1:24" ht="35" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="D23" s="90"/>
+      <c r="F23" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="F23" s="50" t="s">
+      <c r="G23" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="G23" s="50">
+      <c r="H23" s="50">
         <f>'18F norm Option 1'!G20</f>
         <v>0.80409799999999998</v>
       </c>
-      <c r="H23" s="66">
+      <c r="I23" s="66">
         <f>'18F norm Option 1'!H20</f>
-        <v>2.6093130767576271</v>
-      </c>
-      <c r="I23" s="50">
+        <v>3.6530383074606778</v>
+      </c>
+      <c r="J23" s="50">
         <f>'18F norm Option 1'!I20</f>
         <v>0.103809</v>
       </c>
-      <c r="J23" s="50">
+      <c r="K23" s="50">
         <f>'18F norm Option 1'!J20</f>
-        <v>0.43080050069535031</v>
-      </c>
-      <c r="K23" s="50">
+        <v>0.79755574679409624</v>
+      </c>
+      <c r="L23" s="50">
         <f>'18F norm Option 1'!K20</f>
         <v>1.25024</v>
       </c>
-      <c r="L23" s="50">
+      <c r="M23" s="50">
         <f>'18F norm Option 1'!L20</f>
         <v>0.25004900000000002</v>
       </c>
-      <c r="M23" s="132"/>
       <c r="N23" s="132"/>
       <c r="O23" s="132"/>
       <c r="P23" s="132"/>
       <c r="Q23" s="132"/>
-      <c r="R23" t="s">
+      <c r="R23" s="132"/>
+      <c r="S23" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="24" spans="1:18" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C24" s="90">
+      <c r="X23">
         <f t="shared" si="1"/>
+        <v>0.21832668580705306</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D24" s="90">
+        <f t="shared" si="3"/>
         <v>0.24543439248390164</v>
       </c>
-      <c r="E24" s="174" t="s">
+      <c r="F24" s="174" t="s">
         <v>96</v>
       </c>
-      <c r="F24" s="136" t="s">
+      <c r="G24" s="136" t="s">
         <v>97</v>
       </c>
-      <c r="G24" s="136">
+      <c r="H24" s="136">
         <v>0.6</v>
       </c>
-      <c r="H24" s="136">
-        <f>G24*G29</f>
+      <c r="I24" s="136">
+        <f>H24*H29</f>
         <v>1.9470112424786234</v>
       </c>
-      <c r="I24" s="136"/>
       <c r="J24" s="136"/>
       <c r="K24" s="136"/>
-      <c r="L24" s="175"/>
-      <c r="M24" s="155"/>
+      <c r="L24" s="136"/>
+      <c r="M24" s="175"/>
       <c r="N24" s="155"/>
       <c r="O24" s="155"/>
       <c r="P24" s="155"/>
       <c r="Q24" s="155"/>
-    </row>
-    <row r="25" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C25" s="90">
-        <f t="shared" si="1"/>
-        <v>0.85386625145149375</v>
-      </c>
-      <c r="D25">
-        <f>J25*$A$9/$H$9</f>
-        <v>2.8640149967164186E-2</v>
-      </c>
-      <c r="E25" s="176"/>
-      <c r="F25" s="173" t="s">
+      <c r="R24" s="155"/>
+    </row>
+    <row r="25" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <f t="shared" si="0"/>
+        <v>0.23525718343534233</v>
+      </c>
+      <c r="D25" s="90">
+        <f t="shared" si="3"/>
+        <v>0.84183996621978252</v>
+      </c>
+      <c r="E25">
+        <f>K25*$B$9/$I$9</f>
+        <v>0.19804889935616976</v>
+      </c>
+      <c r="F25" s="176"/>
+      <c r="G25" s="173" t="s">
         <v>98</v>
       </c>
-      <c r="G25" s="173">
-        <f>1.47*1.42</f>
-        <v>2.0873999999999997</v>
-      </c>
       <c r="H25" s="173">
-        <f>G25*G29</f>
-        <v>6.7736521125831306</v>
+        <f>1.47*H34</f>
+        <v>2.0579999999999998</v>
       </c>
       <c r="I25" s="173">
+        <f>H25*H29</f>
+        <v>6.678248561701678</v>
+      </c>
+      <c r="J25" s="173">
+        <f>0.16</f>
         <v>0.16</v>
       </c>
-      <c r="J25" s="173">
-        <f>I25*1.42</f>
-        <v>0.22719999999999999</v>
-      </c>
-      <c r="K25" s="173"/>
-      <c r="L25" s="177"/>
-      <c r="M25" s="155"/>
+      <c r="K25" s="173">
+        <f>I25*SQRT(POWER((J25/1.47),2)+POWER((I34/H34),2)+POWER((I29/H29),2))</f>
+        <v>1.5711059469070627</v>
+      </c>
+      <c r="L25" s="173"/>
+      <c r="M25" s="177"/>
       <c r="N25" s="155"/>
       <c r="O25" s="155"/>
       <c r="P25" s="155"/>
       <c r="Q25" s="155"/>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="E26" s="156"/>
-      <c r="F26" s="153"/>
+      <c r="R25" s="155"/>
+      <c r="X25">
+        <f t="shared" si="1"/>
+        <v>0.23525718343534233</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="F26" s="156"/>
       <c r="G26" s="153"/>
-      <c r="H26" s="154"/>
-      <c r="I26" s="153"/>
+      <c r="H26" s="153"/>
+      <c r="I26" s="154"/>
       <c r="J26" s="153"/>
       <c r="K26" s="153"/>
-      <c r="L26" s="155"/>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="E28" t="s">
+      <c r="L26" s="153"/>
+      <c r="M26" s="155"/>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="F28" t="s">
         <v>45</v>
       </c>
-      <c r="G28" t="s">
+      <c r="H28" t="s">
         <v>61</v>
       </c>
-      <c r="H28" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="E29">
+      <c r="I28" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="F29">
         <v>3.6014013985414599</v>
       </c>
-      <c r="G29">
+      <c r="H29">
         <f>'18F norm Option 1'!G23</f>
         <v>3.2450187374643726</v>
       </c>
-      <c r="H29">
+      <c r="I29">
         <f>'18F norm Option 1'!H23</f>
         <v>0.4931026033780847</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="E30" t="s">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="F30" t="s">
         <v>62</v>
       </c>
-      <c r="G30" t="s">
+      <c r="H30" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="39" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H39" t="s">
+    <row r="33" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="H33" t="s">
+        <v>117</v>
+      </c>
+      <c r="I33" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="34" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="H34">
+        <v>1.4</v>
+      </c>
+      <c r="I34">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="39" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="I39" t="s">
         <v>91</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="F4:F5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C43407E-2C20-1145-AC1B-F17AB55E2580}">
-  <dimension ref="B2:L34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="2" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I2" t="s">
-        <v>33</v>
-      </c>
-      <c r="J2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K2" t="s">
-        <v>0</v>
-      </c>
-      <c r="L2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="69" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="2">
-        <v>2.3270200000000001</v>
-      </c>
-      <c r="E3" s="35">
-        <f t="shared" ref="E3:E27" si="0">D3*$D$31</f>
-        <v>7.9657627397373192</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0.32842500000000002</v>
-      </c>
-      <c r="G3" s="3">
-        <v>0.870116</v>
-      </c>
-      <c r="L3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="124" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="54" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="54">
-        <f>I4*J4</f>
-        <v>0.53477599500000006</v>
-      </c>
-      <c r="E4" s="55">
-        <f t="shared" si="0"/>
-        <v>1.8306240148674919</v>
-      </c>
-      <c r="F4" s="54">
-        <f>I4*K4</f>
-        <v>2.4061307399999999E-2</v>
-      </c>
-      <c r="G4" s="54">
-        <v>158.19300000000001</v>
-      </c>
-      <c r="H4" s="54">
-        <v>14.3811</v>
-      </c>
-      <c r="I4" s="54">
-        <v>0.3211</v>
-      </c>
-      <c r="J4" s="54">
-        <v>1.6654500000000001</v>
-      </c>
-      <c r="K4" s="56">
-        <v>7.4934000000000001E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="126"/>
-      <c r="C5" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="D5" s="27">
-        <f t="shared" ref="D5:D8" si="1">I5*J5</f>
-        <v>4.8964230000000004E-2</v>
-      </c>
-      <c r="E5" s="40">
-        <f t="shared" si="0"/>
-        <v>0.16761241369387811</v>
-      </c>
-      <c r="F5" s="27">
-        <f t="shared" ref="F5:F8" si="2">I5*K5</f>
-        <v>2.2030596E-3</v>
-      </c>
-      <c r="G5" s="27">
-        <v>158.19300000000001</v>
-      </c>
-      <c r="H5" s="54">
-        <v>14.3811</v>
-      </c>
-      <c r="I5" s="27">
-        <v>2.9399999999999999E-2</v>
-      </c>
-      <c r="J5" s="27">
-        <v>1.6654500000000001</v>
-      </c>
-      <c r="K5" s="28">
-        <v>7.4934000000000001E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="126"/>
-      <c r="C6" s="27" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="27">
-        <f t="shared" si="1"/>
-        <v>0.43967880000000004</v>
-      </c>
-      <c r="E6" s="40">
-        <f t="shared" si="0"/>
-        <v>1.5050910617409463</v>
-      </c>
-      <c r="F6" s="27">
-        <f t="shared" si="2"/>
-        <v>1.9782576E-2</v>
-      </c>
-      <c r="G6" s="27">
-        <v>158.19300000000001</v>
-      </c>
-      <c r="H6" s="54">
-        <v>14.3811</v>
-      </c>
-      <c r="I6" s="27">
-        <v>0.26400000000000001</v>
-      </c>
-      <c r="J6" s="27">
-        <v>1.6654500000000001</v>
-      </c>
-      <c r="K6" s="28">
-        <v>7.4934000000000001E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="62" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="27">
-        <f t="shared" si="1"/>
-        <v>1.2514191299999999</v>
-      </c>
-      <c r="E7" s="40">
-        <f t="shared" si="0"/>
-        <v>4.2838084234551017</v>
-      </c>
-      <c r="F7" s="27">
-        <f t="shared" si="2"/>
-        <v>5.6305407599999996E-2</v>
-      </c>
-      <c r="G7" s="27">
-        <v>158.19300000000001</v>
-      </c>
-      <c r="H7" s="54">
-        <v>14.3811</v>
-      </c>
-      <c r="I7" s="27">
-        <v>0.75139999999999996</v>
-      </c>
-      <c r="J7" s="27">
-        <v>1.6654500000000001</v>
-      </c>
-      <c r="K7" s="28">
-        <v>7.4934000000000001E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="59" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="30">
-        <f t="shared" si="1"/>
-        <v>1.6654500000000001</v>
-      </c>
-      <c r="E8" s="41">
-        <f t="shared" si="0"/>
-        <v>5.701102506594494</v>
-      </c>
-      <c r="F8" s="30">
-        <f t="shared" si="2"/>
-        <v>7.4934000000000001E-2</v>
-      </c>
-      <c r="G8" s="30">
-        <v>158.19300000000001</v>
-      </c>
-      <c r="H8" s="54">
-        <v>14.3811</v>
-      </c>
-      <c r="I8" s="30">
-        <v>1</v>
-      </c>
-      <c r="J8" s="30">
-        <v>1.6654500000000001</v>
-      </c>
-      <c r="K8" s="31">
-        <v>7.4934000000000001E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B9" s="122" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9">
-        <v>0.17736399999999999</v>
-      </c>
-      <c r="E9" s="33">
-        <f t="shared" si="0"/>
-        <v>0.60714542314667252</v>
-      </c>
-      <c r="F9">
-        <v>4.4671700000000002E-2</v>
-      </c>
-      <c r="G9" s="4">
-        <v>31.5443</v>
-      </c>
-      <c r="H9">
-        <v>4.3747400000000001</v>
-      </c>
-      <c r="L9" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="122"/>
-      <c r="C10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10">
-        <v>1.4557599999999999</v>
-      </c>
-      <c r="E10" s="33">
-        <f t="shared" si="0"/>
-        <v>4.9832999999999998</v>
-      </c>
-      <c r="F10">
-        <v>0.12048</v>
-      </c>
-      <c r="G10" s="4">
-        <v>31.5443</v>
-      </c>
-      <c r="H10">
-        <v>4.3747400000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="60" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="17">
-        <f>I11*J11</f>
-        <v>0.25210164000000002</v>
-      </c>
-      <c r="E11" s="37">
-        <f t="shared" si="0"/>
-        <v>0.86298435361048531</v>
-      </c>
-      <c r="F11" s="17">
-        <f>I11*K11</f>
-        <v>1.5407612999999999E-2</v>
-      </c>
-      <c r="G11" s="17">
-        <v>21.929400000000001</v>
-      </c>
-      <c r="H11" s="17">
-        <v>2.7411699999999999</v>
-      </c>
-      <c r="I11" s="17">
-        <v>8.6999999999999994E-2</v>
-      </c>
-      <c r="J11" s="17">
-        <v>2.8977200000000001</v>
-      </c>
-      <c r="K11" s="18">
-        <v>0.17709900000000001</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="86"/>
-      <c r="C12" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="D12" s="19">
-        <f t="shared" ref="D12:D15" si="3">I12*J12</f>
-        <v>0.28600496399999997</v>
-      </c>
-      <c r="E12" s="38">
-        <f t="shared" si="0"/>
-        <v>0.97904087013051588</v>
-      </c>
-      <c r="F12" s="19">
-        <f t="shared" ref="F12:F15" si="4">I12*K12</f>
-        <v>1.7479671299999999E-2</v>
-      </c>
-      <c r="G12" s="19">
-        <v>21.929400000000001</v>
-      </c>
-      <c r="H12" s="17">
-        <v>2.7411699999999999</v>
-      </c>
-      <c r="I12" s="19">
-        <v>9.8699999999999996E-2</v>
-      </c>
-      <c r="J12" s="19">
-        <v>2.8977200000000001</v>
-      </c>
-      <c r="K12" s="20">
-        <v>0.17709900000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="85" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" s="19">
-        <f t="shared" si="3"/>
-        <v>0.97247483200000007</v>
-      </c>
-      <c r="E13" s="38">
-        <f t="shared" si="0"/>
-        <v>3.328937345651481</v>
-      </c>
-      <c r="F13" s="19">
-        <f t="shared" si="4"/>
-        <v>5.9434424400000005E-2</v>
-      </c>
-      <c r="G13" s="19">
-        <v>21.929400000000001</v>
-      </c>
-      <c r="H13" s="17">
-        <v>2.7411699999999999</v>
-      </c>
-      <c r="I13" s="19">
-        <v>0.33560000000000001</v>
-      </c>
-      <c r="J13" s="19">
-        <v>2.8977200000000001</v>
-      </c>
-      <c r="K13" s="20">
-        <v>0.17709900000000001</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="85"/>
-      <c r="C14" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" s="19">
-        <f t="shared" si="3"/>
-        <v>0.20370971600000001</v>
-      </c>
-      <c r="E14" s="38">
-        <f t="shared" si="0"/>
-        <v>0.69733103515881745</v>
-      </c>
-      <c r="F14" s="19">
-        <f t="shared" si="4"/>
-        <v>1.24500597E-2</v>
-      </c>
-      <c r="G14" s="19">
-        <v>21.929400000000001</v>
-      </c>
-      <c r="H14" s="17">
-        <v>2.7411699999999999</v>
-      </c>
-      <c r="I14" s="19">
-        <v>7.0300000000000001E-2</v>
-      </c>
-      <c r="J14" s="19">
-        <v>2.8977200000000001</v>
-      </c>
-      <c r="K14" s="20">
-        <v>0.17709900000000001</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="21"/>
-      <c r="C15" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="D15" s="22">
-        <f t="shared" si="3"/>
-        <v>2.7528339999999998E-2</v>
-      </c>
-      <c r="E15" s="39">
-        <f t="shared" si="0"/>
-        <v>9.423392367011045E-2</v>
-      </c>
-      <c r="F15" s="22">
-        <f t="shared" si="4"/>
-        <v>1.6824405000000001E-3</v>
-      </c>
-      <c r="G15" s="22">
-        <v>21.929400000000001</v>
-      </c>
-      <c r="H15" s="17">
-        <v>2.7411699999999999</v>
-      </c>
-      <c r="I15" s="22">
-        <v>9.4999999999999998E-3</v>
-      </c>
-      <c r="J15" s="22">
-        <v>2.8977200000000001</v>
-      </c>
-      <c r="K15" s="23">
-        <v>0.17709900000000001</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B16" s="122" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16">
-        <v>0.36342999999999998</v>
-      </c>
-      <c r="E16" s="33">
-        <f t="shared" si="0"/>
-        <v>1.244079188190361</v>
-      </c>
-      <c r="F16">
-        <v>5.6393199999999997E-2</v>
-      </c>
-      <c r="G16" s="4">
-        <v>21.1067</v>
-      </c>
-      <c r="H16">
-        <v>3.02854</v>
-      </c>
-      <c r="L16" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="17" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="119"/>
-      <c r="C17" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D17" s="6">
-        <v>1.8707499999999999</v>
-      </c>
-      <c r="E17" s="34">
-        <f t="shared" si="0"/>
-        <v>6.4038773389844472</v>
-      </c>
-      <c r="F17" s="6">
-        <v>0.114702</v>
-      </c>
-      <c r="G17" s="7">
-        <v>21.1067</v>
-      </c>
-      <c r="H17">
-        <v>3.02854</v>
-      </c>
-    </row>
-    <row r="18" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D18" s="2">
-        <v>0.45706400000000003</v>
-      </c>
-      <c r="E18" s="35">
-        <f t="shared" si="0"/>
-        <v>1.5646033901192504</v>
-      </c>
-      <c r="F18" s="2">
-        <v>8.3333199999999996E-2</v>
-      </c>
-      <c r="G18" s="3">
-        <v>15.232100000000001</v>
-      </c>
-      <c r="H18">
-        <v>3.06196</v>
-      </c>
-      <c r="L18" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="19" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="70" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="48" t="s">
-        <v>26</v>
-      </c>
-      <c r="D19" s="48">
-        <f>I19*J19</f>
-        <v>8.0849340000000006E-2</v>
-      </c>
-      <c r="E19" s="57">
-        <f t="shared" si="0"/>
-        <v>0.27676025994806835</v>
-      </c>
-      <c r="F19" s="48">
-        <f>I19*K19</f>
-        <v>2.4430000000000003E-3</v>
-      </c>
-      <c r="G19" s="48">
-        <v>58.458599999999997</v>
-      </c>
-      <c r="H19" s="48">
-        <v>8.3512299999999993</v>
-      </c>
-      <c r="I19" s="48">
-        <v>3.49E-2</v>
-      </c>
-      <c r="J19" s="48">
-        <v>2.3166000000000002</v>
-      </c>
-      <c r="K19" s="71">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="87"/>
-      <c r="C20" s="68" t="s">
-        <v>12</v>
-      </c>
-      <c r="D20" s="68">
-        <f t="shared" ref="D20:D21" si="5">I20*J20</f>
-        <v>2.1407700600000004</v>
-      </c>
-      <c r="E20" s="72">
-        <f t="shared" si="0"/>
-        <v>7.3281993185676217</v>
-      </c>
-      <c r="F20" s="68">
-        <f t="shared" ref="F20:F21" si="6">I20*K20</f>
-        <v>6.4687000000000008E-2</v>
-      </c>
-      <c r="G20" s="68">
-        <v>58.458599999999997</v>
-      </c>
-      <c r="H20" s="48">
-        <v>8.3512299999999993</v>
-      </c>
-      <c r="I20" s="68">
-        <v>0.92410000000000003</v>
-      </c>
-      <c r="J20" s="68">
-        <v>2.3166000000000002</v>
-      </c>
-      <c r="K20" s="88">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="2:12" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="73" t="s">
-        <v>27</v>
-      </c>
-      <c r="C21" s="74" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="74">
-        <f t="shared" si="5"/>
-        <v>0.41559804000000006</v>
-      </c>
-      <c r="E21" s="75">
-        <f t="shared" si="0"/>
-        <v>1.4226587574407872</v>
-      </c>
-      <c r="F21" s="74">
-        <f t="shared" si="6"/>
-        <v>1.2558000000000001E-2</v>
-      </c>
-      <c r="G21" s="74">
-        <v>58.458599999999997</v>
-      </c>
-      <c r="H21" s="48">
-        <v>8.3512299999999993</v>
-      </c>
-      <c r="I21" s="74">
-        <v>0.1794</v>
-      </c>
-      <c r="J21" s="74">
-        <v>2.3166000000000002</v>
-      </c>
-      <c r="K21" s="76">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B22" s="122" t="s">
-        <v>28</v>
-      </c>
-      <c r="C22" t="s">
-        <v>10</v>
-      </c>
-      <c r="D22">
-        <v>0.43999500000000002</v>
-      </c>
-      <c r="E22" s="33">
-        <f t="shared" si="0"/>
-        <v>1.5061734650629226</v>
-      </c>
-      <c r="F22">
-        <v>7.8331999999999999E-2</v>
-      </c>
-      <c r="G22" s="4">
-        <v>17.810700000000001</v>
-      </c>
-      <c r="H22">
-        <v>4.02874</v>
-      </c>
-      <c r="L22" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="23" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="122"/>
-      <c r="C23" t="s">
-        <v>11</v>
-      </c>
-      <c r="D23">
-        <v>1.1331500000000001</v>
-      </c>
-      <c r="E23" s="33">
-        <f t="shared" si="0"/>
-        <v>3.8789542197889766</v>
-      </c>
-      <c r="F23">
-        <v>0.112195</v>
-      </c>
-      <c r="G23" s="4">
-        <v>17.810700000000001</v>
-      </c>
-      <c r="H23">
-        <v>4.02874</v>
-      </c>
-    </row>
-    <row r="24" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="81" t="s">
-        <v>29</v>
-      </c>
-      <c r="C24" s="58" t="s">
-        <v>8</v>
-      </c>
-      <c r="D24" s="58">
-        <f>I24*J24</f>
-        <v>0.38584674400000002</v>
-      </c>
-      <c r="E24" s="82">
-        <f t="shared" si="0"/>
-        <v>1.3208152987959554</v>
-      </c>
-      <c r="F24" s="58">
-        <f>I24*K24</f>
-        <v>2.8167167999999999E-2</v>
-      </c>
-      <c r="G24" s="58">
-        <v>11.266400000000001</v>
-      </c>
-      <c r="H24" s="58">
-        <v>2.2532800000000002</v>
-      </c>
-      <c r="I24" s="58">
-        <v>6.9199999999999998E-2</v>
-      </c>
-      <c r="J24" s="82">
-        <v>5.5758200000000002</v>
-      </c>
-      <c r="K24" s="83">
-        <v>0.40704000000000001</v>
-      </c>
-    </row>
-    <row r="25" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="42"/>
-      <c r="C25" s="43" t="s">
-        <v>7</v>
-      </c>
-      <c r="D25" s="43">
-        <f t="shared" ref="D25:D27" si="7">I25*J25</f>
-        <v>2.9496087800000002</v>
-      </c>
-      <c r="E25" s="44">
-        <f t="shared" si="0"/>
-        <v>10.096984003801451</v>
-      </c>
-      <c r="F25" s="43">
-        <f t="shared" ref="F25:F27" si="8">I25*K25</f>
-        <v>0.21532416000000001</v>
-      </c>
-      <c r="G25" s="43">
-        <v>11.266400000000001</v>
-      </c>
-      <c r="H25" s="58">
-        <v>2.2532800000000002</v>
-      </c>
-      <c r="I25" s="43">
-        <v>0.52900000000000003</v>
-      </c>
-      <c r="J25" s="44">
-        <v>5.5758200000000002</v>
-      </c>
-      <c r="K25" s="45">
-        <v>0.40704000000000001</v>
-      </c>
-    </row>
-    <row r="26" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="42"/>
-      <c r="C26" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="D26" s="43">
-        <f t="shared" si="7"/>
-        <v>2.0630534000000002E-2</v>
-      </c>
-      <c r="E26" s="44">
-        <f t="shared" si="0"/>
-        <v>7.0621627247760624E-2</v>
-      </c>
-      <c r="F26" s="43">
-        <f t="shared" si="8"/>
-        <v>1.5060480000000001E-3</v>
-      </c>
-      <c r="G26" s="43">
-        <v>11.266400000000001</v>
-      </c>
-      <c r="H26" s="58">
-        <v>2.2532800000000002</v>
-      </c>
-      <c r="I26" s="43">
-        <v>3.7000000000000002E-3</v>
-      </c>
-      <c r="J26" s="44">
-        <v>5.5758200000000002</v>
-      </c>
-      <c r="K26" s="45">
-        <v>0.40704000000000001</v>
-      </c>
-    </row>
-    <row r="27" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="84" t="s">
-        <v>30</v>
-      </c>
-      <c r="C27" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="D27" s="15">
-        <f t="shared" si="7"/>
-        <v>1.6727459999999999E-3</v>
-      </c>
-      <c r="E27" s="36">
-        <f t="shared" si="0"/>
-        <v>5.7260778849535631E-3</v>
-      </c>
-      <c r="F27" s="15">
-        <f t="shared" si="8"/>
-        <v>1.2211199999999999E-4</v>
-      </c>
-      <c r="G27" s="15">
-        <v>11.266400000000001</v>
-      </c>
-      <c r="H27" s="58">
-        <v>2.2532800000000002</v>
-      </c>
-      <c r="I27" s="15">
-        <v>2.9999999999999997E-4</v>
-      </c>
-      <c r="J27" s="36">
-        <v>5.5758200000000002</v>
-      </c>
-      <c r="K27" s="16">
-        <v>0.40704000000000001</v>
-      </c>
-    </row>
-    <row r="28" spans="2:12" ht="35" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="77" t="s">
-        <v>31</v>
-      </c>
-      <c r="C28" s="78" t="s">
-        <v>13</v>
-      </c>
-      <c r="D28" s="78">
-        <v>0.80409799999999998</v>
-      </c>
-      <c r="E28" s="79">
-        <f>D28*D31</f>
-        <v>2.7525564402099247</v>
-      </c>
-      <c r="F28" s="78">
-        <v>0.103809</v>
-      </c>
-      <c r="G28" s="80">
-        <v>1.25024</v>
-      </c>
-      <c r="H28" s="58"/>
-      <c r="L28" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B30" t="s">
-        <v>45</v>
-      </c>
-      <c r="D30" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B31">
-        <v>3.6014013985414599</v>
-      </c>
-      <c r="D31">
-        <v>3.4231604110567675</v>
-      </c>
-    </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B32" t="s">
-        <v>62</v>
-      </c>
-      <c r="D32" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B34" t="s">
-        <v>99</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="B22:B23"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E379A37-1643-1048-AB5D-38CA5C6FAEF5}">
   <dimension ref="A1:Y56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -10571,8 +9957,11 @@
       <c r="T2" t="s">
         <v>2</v>
       </c>
+      <c r="U2" t="s">
+        <v>120</v>
+      </c>
       <c r="V2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.2">
@@ -10589,7 +9978,7 @@
         <v>72</v>
       </c>
       <c r="H3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I3" t="s">
         <v>71</v>
@@ -10598,7 +9987,7 @@
         <v>72</v>
       </c>
       <c r="O3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P3" t="s">
         <v>71</v>
@@ -10610,12 +9999,12 @@
         <v>20</v>
       </c>
       <c r="N4" s="92">
-        <f>'18F norm Option 2 lit'!H3</f>
+        <f>'18F norm Option 2 lit'!I3</f>
         <v>7.4353114331521173</v>
       </c>
       <c r="O4" s="92">
-        <f>'18F norm Option 2 lit'!I3</f>
-        <v>0.19059799999999999</v>
+        <f>'18F norm Option 2 lit'!K3</f>
+        <v>1.2880554729207276</v>
       </c>
       <c r="P4" s="92">
         <v>0.18529999999999999</v>
@@ -10626,7 +10015,11 @@
       </c>
       <c r="R4">
         <f>O4*$P$12/$N$12</f>
-        <v>2.2251372211751361E-2</v>
+        <v>0.15037409499230076</v>
+      </c>
+      <c r="U4">
+        <f>O4/N4</f>
+        <v>0.17323490542408537</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.2">
@@ -10699,11 +10092,11 @@
         <v>7</v>
       </c>
       <c r="N6" s="92">
-        <f>'18F norm Option 2 lit'!H4</f>
+        <f>'18F norm Option 2 lit'!I4</f>
         <v>1.0227947949460308</v>
       </c>
       <c r="O6" s="92">
-        <f>'18F norm Option 2 lit'!J4</f>
+        <f>'18F norm Option 2 lit'!K4</f>
         <v>0.28840956313475286</v>
       </c>
       <c r="P6" s="92">
@@ -10723,6 +10116,10 @@
       <c r="T6">
         <f>$N$12/$S$12*S6</f>
         <v>0.80915777419354828</v>
+      </c>
+      <c r="U6">
+        <f t="shared" ref="U5:U36" si="2">O6/N6</f>
+        <v>0.2819818448039435</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.2">
@@ -10739,7 +10136,7 @@
         <v>60</v>
       </c>
       <c r="O7" s="92">
-        <f>'18F norm Option 2 lit'!J5</f>
+        <f>'18F norm Option 2 lit'!K5</f>
         <v>0.86522868940425868</v>
       </c>
       <c r="P7">
@@ -10751,7 +10148,7 @@
         <v>0.1010111628465145</v>
       </c>
       <c r="T7">
-        <f t="shared" ref="T7:T11" si="2">$N$12/$S$12*S7</f>
+        <f t="shared" ref="T7:T11" si="3">$N$12/$S$12*S7</f>
         <v>0</v>
       </c>
     </row>
@@ -10769,11 +10166,11 @@
         <v>58</v>
       </c>
       <c r="N8">
-        <f>'18F norm Option 2 lit'!H5</f>
+        <f>'18F norm Option 2 lit'!I5</f>
         <v>3.0683843848380925</v>
       </c>
       <c r="O8">
-        <f>'18F norm Option 2 lit'!J5</f>
+        <f>'18F norm Option 2 lit'!K5</f>
         <v>0.86522868940425868</v>
       </c>
       <c r="P8">
@@ -10791,8 +10188,18 @@
         <v>0.30599999999999999</v>
       </c>
       <c r="T8">
+        <f t="shared" si="3"/>
+        <v>2.4274733225806453</v>
+      </c>
+      <c r="U8">
         <f t="shared" si="2"/>
-        <v>2.4274733225806453</v>
+        <v>0.2819818448039435</v>
+      </c>
+      <c r="W8" t="s">
+        <v>119</v>
+      </c>
+      <c r="X8" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:25" ht="17" x14ac:dyDescent="0.2">
@@ -10811,11 +10218,11 @@
         <v>8</v>
       </c>
       <c r="N9">
-        <f>'18F norm Option 2 lit'!H6</f>
+        <f>'18F norm Option 2 lit'!I6</f>
         <v>9.626303952433231</v>
       </c>
       <c r="O9">
-        <f>'18F norm Option 2 lit'!J6</f>
+        <f>'18F norm Option 2 lit'!K6</f>
         <v>2.7144429471506153</v>
       </c>
       <c r="P9">
@@ -10833,12 +10240,20 @@
         <v>0.96</v>
       </c>
       <c r="T9">
+        <f t="shared" si="3"/>
+        <v>7.6156025806451613</v>
+      </c>
+      <c r="U9">
         <f t="shared" si="2"/>
-        <v>7.6156025806451613</v>
+        <v>0.2819818448039435</v>
       </c>
       <c r="V9">
         <f>(G5-N9)/SQRT(H5*H5+O9*O9)</f>
         <v>-1.2065242951441306</v>
+      </c>
+      <c r="W9">
+        <f>N9/G5</f>
+        <v>1.5536169682722942</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.2">
@@ -10857,11 +10272,11 @@
         <v>9</v>
       </c>
       <c r="N10" s="98">
-        <f>'18F norm Option 2 lit'!H7</f>
+        <f>'18F norm Option 2 lit'!I7</f>
         <v>8.9243859559016432</v>
       </c>
       <c r="O10">
-        <f>'18F norm Option 2 lit'!J7</f>
+        <f>'18F norm Option 2 lit'!K7</f>
         <v>2.5165148155875503</v>
       </c>
       <c r="P10" s="98">
@@ -10879,8 +10294,12 @@
         <v>0.89</v>
       </c>
       <c r="T10">
+        <f t="shared" si="3"/>
+        <v>7.0602982258064513</v>
+      </c>
+      <c r="U10">
         <f t="shared" si="2"/>
-        <v>7.0602982258064513</v>
+        <v>0.2819818448039435</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.2">
@@ -10894,7 +10313,7 @@
         <v>0.21</v>
       </c>
       <c r="D11" s="106">
-        <f t="shared" ref="D11:D32" si="3">0.15*C11</f>
+        <f t="shared" ref="D11:D32" si="4">0.15*C11</f>
         <v>3.15E-2</v>
       </c>
       <c r="E11" s="106">
@@ -10902,7 +10321,7 @@
         <v>1.2444169879518072</v>
       </c>
       <c r="F11" s="106">
-        <f t="shared" ref="F11:F32" si="4">0.15*E11</f>
+        <f t="shared" ref="F11:F32" si="5">0.15*E11</f>
         <v>0.18666254819277109</v>
       </c>
       <c r="G11" s="111">
@@ -10921,7 +10340,7 @@
         <v>0.18567711715778065</v>
       </c>
       <c r="K11" s="113">
-        <f t="shared" ref="K11:K39" si="5">H11*$I$12/$G$12</f>
+        <f t="shared" ref="K11:K39" si="6">H11*$I$12/$G$12</f>
         <v>2.6773205490524008E-2</v>
       </c>
       <c r="L11" s="127" t="s">
@@ -10931,11 +10350,11 @@
         <v>10</v>
       </c>
       <c r="N11" s="92">
-        <f>'18F norm Option 2 lit'!H8</f>
+        <f>'18F norm Option 2 lit'!I8</f>
         <v>0.50502875614905518</v>
       </c>
       <c r="O11" s="92">
-        <f>'18F norm Option 2 lit'!J8</f>
+        <f>'18F norm Option 2 lit'!K8</f>
         <v>0.31671937986543069</v>
       </c>
       <c r="P11" s="92">
@@ -10953,12 +10372,24 @@
         <v>0.21</v>
       </c>
       <c r="T11">
+        <f t="shared" si="3"/>
+        <v>1.6659130645161289</v>
+      </c>
+      <c r="U11">
         <f t="shared" si="2"/>
-        <v>1.6659130645161289</v>
+        <v>0.62713137818226239</v>
       </c>
       <c r="V11">
         <f>(G11-N11)/SQRT(H11*H11+O11*O11)</f>
         <v>0.71248038794399471</v>
+      </c>
+      <c r="W11">
+        <f>N11/G11</f>
+        <v>0.67948340156804432</v>
+      </c>
+      <c r="X11">
+        <f>W11*SQRT(POWER((O11/N11),2)+POWER((H11/G11),2))</f>
+        <v>0.43724383462485572</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.2">
@@ -10970,7 +10401,7 @@
         <v>0.83</v>
       </c>
       <c r="D12" s="106">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.12449999999999999</v>
       </c>
       <c r="E12" s="106">
@@ -10978,7 +10409,7 @@
         <v>4.9184099999999997</v>
       </c>
       <c r="F12" s="106">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.73776149999999996</v>
       </c>
       <c r="G12" s="113">
@@ -10997,7 +10428,7 @@
         <v>1.2286999999999999</v>
       </c>
       <c r="K12" s="113">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>6.1068966687016141E-2</v>
       </c>
       <c r="L12" s="131"/>
@@ -11005,11 +10436,11 @@
         <v>11</v>
       </c>
       <c r="N12" s="98">
-        <f>'18F norm Option 2 lit'!H9</f>
+        <f>'18F norm Option 2 lit'!I9</f>
         <v>4.9184099999999997</v>
       </c>
       <c r="O12" s="92">
-        <f>'18F norm Option 2 lit'!J9</f>
+        <f>'18F norm Option 2 lit'!K9</f>
         <v>1.0283056650510694</v>
       </c>
       <c r="P12" s="98">
@@ -11030,9 +10461,21 @@
         <f>$N$12/$S$12*S12</f>
         <v>4.9184099999999997</v>
       </c>
+      <c r="U12">
+        <f t="shared" si="2"/>
+        <v>0.20907278267795271</v>
+      </c>
       <c r="V12">
         <f>(G12-N12)/SQRT(H12*H12+O12*O12)</f>
         <v>0</v>
+      </c>
+      <c r="W12">
+        <f t="shared" ref="W12:W32" si="7">N12/G12</f>
+        <v>1</v>
+      </c>
+      <c r="X12">
+        <f t="shared" ref="X12:X44" si="8">W12*SQRT(POWER((O12/N12),2)+POWER((H12/G12),2))</f>
+        <v>0.21489934134669222</v>
       </c>
     </row>
     <row r="13" spans="1:25" ht="17" x14ac:dyDescent="0.2">
@@ -11112,6 +10555,10 @@
         <f t="shared" si="1"/>
         <v>5.7888093624189105E-2</v>
       </c>
+      <c r="U15">
+        <f t="shared" si="2"/>
+        <v>0.21972187087641357</v>
+      </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="106"/>
@@ -11131,7 +10578,7 @@
       </c>
       <c r="Q16" s="95"/>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D17" s="106"/>
       <c r="E17" s="106"/>
       <c r="F17" s="106"/>
@@ -11163,8 +10610,12 @@
         <f t="shared" si="1"/>
         <v>0.11158059908997327</v>
       </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="U17">
+        <f t="shared" si="2"/>
+        <v>0.21262497097434863</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D18" s="106"/>
       <c r="E18" s="106"/>
       <c r="F18" s="106"/>
@@ -11180,11 +10631,11 @@
         <v>7</v>
       </c>
       <c r="N18" s="92">
-        <f>'18F norm Option 2 lit'!H12</f>
+        <f>'18F norm Option 2 lit'!I12</f>
         <v>1.169099125639977</v>
       </c>
       <c r="O18" s="92">
-        <f>'18F norm Option 2 lit'!J12</f>
+        <f>'18F norm Option 2 lit'!K12</f>
         <v>0.39200123718697127</v>
       </c>
       <c r="P18" s="92">
@@ -11205,8 +10656,12 @@
         <f>$N$12/$S$12*S18</f>
         <v>1.3485962903225808</v>
       </c>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="U18">
+        <f t="shared" si="2"/>
+        <v>0.33530196763459708</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D19" s="106"/>
       <c r="E19" s="106"/>
       <c r="F19" s="106"/>
@@ -11224,7 +10679,7 @@
       </c>
       <c r="Q19" s="95"/>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D20" s="106"/>
       <c r="E20" s="106"/>
       <c r="F20" s="106"/>
@@ -11238,11 +10693,11 @@
         <v>6</v>
       </c>
       <c r="N20" s="98">
-        <f>'18F norm Option 2 lit'!H13</f>
+        <f>'18F norm Option 2 lit'!I13</f>
         <v>6.181890495619129</v>
       </c>
       <c r="O20" s="98">
-        <f>'18F norm Option 2 lit'!J13</f>
+        <f>'18F norm Option 2 lit'!K13</f>
         <v>1.1091946835077204</v>
       </c>
       <c r="P20" s="98">
@@ -11263,8 +10718,12 @@
         <f>$N$12/$S$12*S20</f>
         <v>5.3943851612903231</v>
       </c>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="U20">
+        <f t="shared" si="2"/>
+        <v>0.17942645284541428</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D21" s="106"/>
       <c r="E21" s="106"/>
       <c r="F21" s="106"/>
@@ -11284,7 +10743,7 @@
       </c>
       <c r="Q21" s="93"/>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D22" s="106"/>
       <c r="E22" s="106"/>
       <c r="F22" s="106"/>
@@ -11300,11 +10759,11 @@
         <v>5</v>
       </c>
       <c r="N22" s="98">
-        <f>'18F norm Option 2 lit'!H14</f>
+        <f>'18F norm Option 2 lit'!I14</f>
         <v>1.3781042924825821</v>
       </c>
       <c r="O22" s="98">
-        <f>'18F norm Option 2 lit'!J14</f>
+        <f>'18F norm Option 2 lit'!K14</f>
         <v>0.46289723602264254</v>
       </c>
       <c r="P22" s="98">
@@ -11325,8 +10784,12 @@
         <f>$N$12/$S$12*S22</f>
         <v>0.58703603225806444</v>
       </c>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="U22">
+        <f t="shared" si="2"/>
+        <v>0.33589419795562614</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D23" s="106"/>
       <c r="E23" s="106"/>
       <c r="F23" s="106"/>
@@ -11348,7 +10811,7 @@
       </c>
       <c r="Q23" s="93"/>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" s="102" t="s">
         <v>34</v>
       </c>
@@ -11359,7 +10822,7 @@
         <v>1.57</v>
       </c>
       <c r="D24" s="106">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.23549999999999999</v>
       </c>
       <c r="E24" s="106">
@@ -11367,7 +10830,7 @@
         <v>9.3034984337349407</v>
       </c>
       <c r="F24" s="106">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.3955247650602411</v>
       </c>
       <c r="G24" s="111">
@@ -11386,7 +10849,7 @@
         <v>2.0655879672678772</v>
       </c>
       <c r="K24" s="113">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.33026344011366399</v>
       </c>
       <c r="L24" s="103"/>
@@ -11394,11 +10857,11 @@
         <v>12</v>
       </c>
       <c r="N24">
-        <f>'18F norm Option 2 lit'!H15</f>
+        <f>'18F norm Option 2 lit'!I15</f>
         <v>7.0153047639396187</v>
       </c>
       <c r="O24">
-        <f>'18F norm Option 2 lit'!J15</f>
+        <f>'18F norm Option 2 lit'!K15</f>
         <v>1.875493381034588</v>
       </c>
       <c r="P24">
@@ -11419,12 +10882,24 @@
         <f>$N$12/$S$12*S24</f>
         <v>8.2502361290322579</v>
       </c>
+      <c r="U24">
+        <f t="shared" si="2"/>
+        <v>0.26734310826738167</v>
+      </c>
       <c r="V24">
-        <f t="shared" ref="V24:V31" si="6">(G24-N24)/SQRT(H24*H24+O24*O24)</f>
+        <f t="shared" ref="V24:V31" si="9">(G24-N24)/SQRT(H24*H24+O24*O24)</f>
         <v>0.54611343737150353</v>
       </c>
-    </row>
-    <row r="25" spans="1:23" ht="17" x14ac:dyDescent="0.2">
+      <c r="W24">
+        <f t="shared" si="7"/>
+        <v>0.84844555187420723</v>
+      </c>
+      <c r="X24">
+        <f t="shared" si="8"/>
+        <v>0.26429674096855549</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" ht="17" x14ac:dyDescent="0.2">
       <c r="A25" s="100" t="s">
         <v>35</v>
       </c>
@@ -11435,7 +10910,7 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="D25" s="106">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.2000000000000003E-2</v>
       </c>
       <c r="E25" s="106">
@@ -11443,7 +10918,7 @@
         <v>1.6592226506024099</v>
       </c>
       <c r="F25" s="106">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.24888339759036149</v>
       </c>
       <c r="G25" s="113">
@@ -11460,7 +10935,7 @@
         <v>0.36838511518153222</v>
       </c>
       <c r="K25" s="113">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5.8900486134920972E-2</v>
       </c>
       <c r="L25" s="104" t="s">
@@ -11470,11 +10945,11 @@
         <v>8</v>
       </c>
       <c r="N25" s="98">
-        <f>'18F norm Option 2 lit'!H16</f>
+        <f>'18F norm Option 2 lit'!I16</f>
         <v>1.2141873629895492</v>
       </c>
       <c r="O25" s="98">
-        <f>'18F norm Option 2 lit'!J16</f>
+        <f>'18F norm Option 2 lit'!K16</f>
         <v>0.32460462364060161</v>
       </c>
       <c r="P25" s="98">
@@ -11495,12 +10970,24 @@
         <f>$N$12/$S$12*S25</f>
         <v>1.4279254838709676</v>
       </c>
+      <c r="U25">
+        <f t="shared" si="2"/>
+        <v>0.26734310826738161</v>
+      </c>
       <c r="V25">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0.64914808281115821</v>
       </c>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="W25">
+        <f t="shared" si="7"/>
+        <v>0.82338843736143852</v>
+      </c>
+      <c r="X25">
+        <f t="shared" si="8"/>
+        <v>0.25649127403061039</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26" s="127" t="s">
         <v>36</v>
       </c>
@@ -11511,7 +10998,7 @@
         <v>0.35</v>
       </c>
       <c r="D26" s="106">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.2499999999999998E-2</v>
       </c>
       <c r="E26" s="106">
@@ -11519,7 +11006,7 @@
         <v>2.0740283132530122</v>
       </c>
       <c r="F26" s="106">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.3111042469879518</v>
       </c>
       <c r="G26" s="111">
@@ -11538,7 +11025,7 @@
         <v>0.31605285407275929</v>
       </c>
       <c r="K26" s="113">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.10911629344573809</v>
       </c>
       <c r="L26" s="127" t="s">
@@ -11548,11 +11035,11 @@
         <v>10</v>
       </c>
       <c r="N26" s="92">
-        <f>'18F norm Option 2 lit'!H17</f>
+        <f>'18F norm Option 2 lit'!I17</f>
         <v>1.2439844230444423</v>
       </c>
       <c r="O26" s="92">
-        <f>'18F norm Option 2 lit'!J17</f>
+        <f>'18F norm Option 2 lit'!K17</f>
         <v>0.49600336979921622</v>
       </c>
       <c r="P26" s="92">
@@ -11573,12 +11060,24 @@
         <f>$N$12/$S$12*S26</f>
         <v>1.3485962903225808</v>
       </c>
+      <c r="U26">
+        <f t="shared" si="2"/>
+        <v>0.39872152786715087</v>
+      </c>
       <c r="V26">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>3.2009802082717455E-2</v>
       </c>
-    </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="W26">
+        <f t="shared" si="7"/>
+        <v>0.98327807439844006</v>
+      </c>
+      <c r="X26">
+        <f t="shared" si="8"/>
+        <v>0.51860283161046616</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="131"/>
       <c r="B27" s="98" t="s">
         <v>11</v>
@@ -11587,7 +11086,7 @@
         <v>0.66</v>
       </c>
       <c r="D27" s="106">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>9.9000000000000005E-2</v>
       </c>
       <c r="E27" s="106">
@@ -11595,7 +11094,7 @@
         <v>3.9110248192771087</v>
       </c>
       <c r="F27" s="106">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.58665372289156625</v>
       </c>
       <c r="G27" s="113">
@@ -11614,7 +11113,7 @@
         <v>0.87088282249751447</v>
       </c>
       <c r="K27" s="113">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.13766446469599863</v>
       </c>
       <c r="L27" s="131"/>
@@ -11622,11 +11121,11 @@
         <v>11</v>
       </c>
       <c r="N27" s="98">
-        <f>'18F norm Option 2 lit'!H18</f>
+        <f>'18F norm Option 2 lit'!I18</f>
         <v>3.7375152312493403</v>
       </c>
       <c r="O27" s="98">
-        <f>'18F norm Option 2 lit'!J18</f>
+        <f>'18F norm Option 2 lit'!K18</f>
         <v>0.80988843614557104</v>
       </c>
       <c r="P27" s="98">
@@ -11647,12 +11146,24 @@
         <f>$N$12/$S$12*S27</f>
         <v>4.0457888709677423</v>
       </c>
+      <c r="U27">
+        <f t="shared" si="2"/>
+        <v>0.21669167509314721</v>
+      </c>
       <c r="V27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>-0.25666475481903567</v>
       </c>
-    </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="W27">
+        <f t="shared" si="7"/>
+        <v>1.0721224154423266</v>
+      </c>
+      <c r="X27">
+        <f t="shared" si="8"/>
+        <v>0.28756646653896967</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="127" t="s">
         <v>39</v>
       </c>
@@ -11663,7 +11174,7 @@
         <v>0.35</v>
       </c>
       <c r="D28" s="106">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.2499999999999998E-2</v>
       </c>
       <c r="E28" s="106">
@@ -11671,7 +11182,7 @@
         <v>2.0740283132530122</v>
       </c>
       <c r="F28" s="106">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.3111042469879518</v>
       </c>
       <c r="G28" s="111">
@@ -11688,11 +11199,11 @@
         <v>0.38784324786872171</v>
       </c>
       <c r="K28" s="113">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>6.0568930529238847E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" s="128"/>
       <c r="B29" t="s">
         <v>18</v>
@@ -11706,7 +11217,7 @@
       <c r="J29" s="115"/>
       <c r="K29" s="113"/>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="128"/>
       <c r="B30" t="s">
         <v>11</v>
@@ -11720,7 +11231,7 @@
       <c r="J30" s="115"/>
       <c r="K30" s="113"/>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="94" t="s">
         <v>40</v>
       </c>
@@ -11731,7 +11242,7 @@
         <v>0.16</v>
       </c>
       <c r="D31" s="106">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.4E-2</v>
       </c>
       <c r="E31" s="106">
@@ -11739,7 +11250,7 @@
         <v>0.9481272289156627</v>
       </c>
       <c r="F31" s="106">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.14221908433734939</v>
       </c>
       <c r="G31" s="90">
@@ -11756,7 +11267,7 @@
         <v>0.17729977045427281</v>
       </c>
       <c r="K31" s="113">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.7688653956223469E-2</v>
       </c>
       <c r="L31" s="92" t="s">
@@ -11766,11 +11277,11 @@
         <v>8</v>
       </c>
       <c r="N31" s="92">
-        <f>'18F norm Option 2 lit'!H24</f>
+        <f>'18F norm Option 2 lit'!I24</f>
         <v>1.9470112424786234</v>
       </c>
       <c r="O31" s="92">
-        <f>'18F norm Option 2 lit'!J19</f>
+        <f>'18F norm Option 2 lit'!K19</f>
         <v>0.25725005957972208</v>
       </c>
       <c r="P31" s="92">
@@ -11784,15 +11295,24 @@
         <f t="shared" si="1"/>
         <v>3.0032669950385685E-2</v>
       </c>
+      <c r="U31">
+        <f t="shared" si="2"/>
+        <v>0.13212561590154581</v>
+      </c>
       <c r="V31">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>-4.4171452999701799</v>
       </c>
-      <c r="W31" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="W31">
+        <f t="shared" si="7"/>
+        <v>2.7433512405999885</v>
+      </c>
+      <c r="X31">
+        <f t="shared" si="8"/>
+        <v>0.56118671006773435</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A32" s="97" t="s">
         <v>41</v>
       </c>
@@ -11803,7 +11323,7 @@
         <v>1.01</v>
       </c>
       <c r="D32" s="106">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.1515</v>
       </c>
       <c r="E32" s="106">
@@ -11811,7 +11331,7 @@
         <v>5.9850531325301208</v>
       </c>
       <c r="F32" s="106">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.89775796987951806</v>
       </c>
       <c r="G32" s="113">
@@ -11830,37 +11350,49 @@
         <v>1.1192048009925972</v>
       </c>
       <c r="K32" s="113">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.17478462809866069</v>
       </c>
       <c r="M32" t="s">
         <v>7</v>
       </c>
       <c r="N32">
-        <f>'18F norm Option 2 lit'!H25</f>
-        <v>6.7736521125831306</v>
+        <f>'18F norm Option 2 lit'!I25</f>
+        <v>6.678248561701678</v>
       </c>
       <c r="O32">
-        <f>'18F norm Option 2 lit'!I25</f>
-        <v>0.16</v>
+        <f>'18F norm Option 2 lit'!K25</f>
+        <v>1.5711059469070627</v>
       </c>
       <c r="P32">
         <v>0.52900000000000003</v>
       </c>
       <c r="Q32" s="95">
         <f t="shared" si="0"/>
-        <v>0.79079032513459302</v>
+        <v>0.77965243323128897</v>
       </c>
       <c r="R32">
         <f t="shared" si="1"/>
-        <v>1.8679207304799723E-2</v>
+        <v>0.18341883550050433</v>
+      </c>
+      <c r="U32">
+        <f t="shared" si="2"/>
+        <v>0.23525718343534233</v>
       </c>
       <c r="V32">
         <f>(G32-N32)/SQRT(H32*H32+O32*O32)</f>
-        <v>-3.1956260009000808</v>
-      </c>
-    </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.2">
+        <v>-1.2780998353761297</v>
+      </c>
+      <c r="W32">
+        <f>N32/G32</f>
+        <v>1.4906447137042309</v>
+      </c>
+      <c r="X32">
+        <f t="shared" si="8"/>
+        <v>0.42091797181039392</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D33" s="106"/>
       <c r="E33" s="106"/>
       <c r="F33" s="106"/>
@@ -11878,7 +11410,7 @@
       </c>
       <c r="Q33" s="95"/>
     </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D34" s="106"/>
       <c r="E34" s="106"/>
       <c r="F34" s="106"/>
@@ -11900,7 +11432,7 @@
       </c>
       <c r="Q34" s="99"/>
     </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D35" s="106"/>
       <c r="E35" s="106"/>
       <c r="F35" s="106"/>
@@ -11916,11 +11448,11 @@
         <v>10</v>
       </c>
       <c r="N35" s="98">
-        <f>'18F norm Option 2 lit'!H21</f>
+        <f>'18F norm Option 2 lit'!I21</f>
         <v>0</v>
       </c>
       <c r="O35" s="98">
-        <f>'18F norm Option 2 lit'!J21</f>
+        <f>'18F norm Option 2 lit'!K21</f>
         <v>0</v>
       </c>
       <c r="P35" s="98"/>
@@ -11930,7 +11462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:22" ht="34" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:24" ht="34" x14ac:dyDescent="0.2">
       <c r="D36" s="106"/>
       <c r="E36" s="106"/>
       <c r="F36" s="106"/>
@@ -11962,8 +11494,12 @@
         <f t="shared" si="1"/>
         <v>1.2119186444399717E-2</v>
       </c>
-    </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="U36">
+        <f t="shared" si="2"/>
+        <v>3.7713668095424403E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A37" s="102" t="s">
         <v>43</v>
       </c>
@@ -11988,7 +11524,7 @@
         <v>7.1882950811339441E-2</v>
       </c>
       <c r="K37" s="113">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>9.0868755431125093E-3</v>
       </c>
       <c r="Q37" s="107">
@@ -11996,7 +11532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A38" s="97"/>
       <c r="B38" s="98" t="s">
         <v>26</v>
@@ -12023,7 +11559,7 @@
         <v>3.3027173415799006E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A39" s="108" t="s">
         <v>44</v>
       </c>
@@ -12050,7 +11586,7 @@
         <v>7.0366314804987784E-2</v>
       </c>
       <c r="K39" s="113">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5.6828258725889055E-3</v>
       </c>
       <c r="L39" t="s">
@@ -12064,7 +11600,7 @@
         <v>3.8525865066149433E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
       <c r="L41" s="155"/>
       <c r="M41" s="155"/>
       <c r="N41" s="155"/>
@@ -12074,9 +11610,9 @@
       <c r="R41" s="155"/>
       <c r="S41" s="155"/>
     </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A42" s="153" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B42" s="153"/>
       <c r="C42" s="153"/>
@@ -12097,7 +11633,7 @@
       <c r="R42" s="155"/>
       <c r="S42" s="155"/>
     </row>
-    <row r="43" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:24" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="158"/>
       <c r="B43" s="153"/>
       <c r="C43" s="153"/>
@@ -12126,10 +11662,10 @@
       <c r="R43" s="155"/>
       <c r="S43" s="155"/>
       <c r="V43" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A44" s="102" t="s">
         <v>34</v>
       </c>
@@ -12172,8 +11708,16 @@
         <f>(G44-N44)/SQRT(H44*H44+O44*O44)</f>
         <v>0.94856482107387652</v>
       </c>
-    </row>
-    <row r="45" spans="1:22" ht="17" x14ac:dyDescent="0.2">
+      <c r="W44">
+        <f>N44/G44</f>
+        <v>0.84795169194272602</v>
+      </c>
+      <c r="X44">
+        <f>W44*SQRT(POWER((O44/N44),2)+POWER((H44/G44),2))</f>
+        <v>0.15758440883278385</v>
+      </c>
+    </row>
+    <row r="45" spans="1:24" ht="17" x14ac:dyDescent="0.2">
       <c r="A45" s="100" t="s">
         <v>35</v>
       </c>
@@ -12197,7 +11741,7 @@
       <c r="R45" s="155"/>
       <c r="S45" s="155"/>
     </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A46" s="153"/>
       <c r="B46" s="153"/>
       <c r="C46" s="153"/>
@@ -12210,7 +11754,7 @@
       <c r="J46" s="153"/>
       <c r="K46" s="153"/>
     </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A47" s="160"/>
       <c r="B47" s="153"/>
       <c r="C47" s="153"/>
@@ -12223,7 +11767,7 @@
       <c r="J47" s="159"/>
       <c r="K47" s="159"/>
     </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A48" s="160"/>
       <c r="B48" s="153"/>
       <c r="C48" s="153"/>
@@ -12354,6 +11898,882 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C43407E-2C20-1145-AC1B-F17AB55E2580}">
+  <dimension ref="B2:L34"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="2" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J2" t="s">
+        <v>3</v>
+      </c>
+      <c r="K2" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="2">
+        <v>2.3270200000000001</v>
+      </c>
+      <c r="E3" s="35">
+        <f t="shared" ref="E3:E27" si="0">D3*$D$31</f>
+        <v>7.9657627397373192</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0.32842500000000002</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0.870116</v>
+      </c>
+      <c r="L3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="124" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="54">
+        <f>I4*J4</f>
+        <v>0.53477599500000006</v>
+      </c>
+      <c r="E4" s="55">
+        <f t="shared" si="0"/>
+        <v>1.8306240148674919</v>
+      </c>
+      <c r="F4" s="54">
+        <f>I4*K4</f>
+        <v>2.4061307399999999E-2</v>
+      </c>
+      <c r="G4" s="54">
+        <v>158.19300000000001</v>
+      </c>
+      <c r="H4" s="54">
+        <v>14.3811</v>
+      </c>
+      <c r="I4" s="54">
+        <v>0.3211</v>
+      </c>
+      <c r="J4" s="54">
+        <v>1.6654500000000001</v>
+      </c>
+      <c r="K4" s="56">
+        <v>7.4934000000000001E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="126"/>
+      <c r="C5" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="27">
+        <f t="shared" ref="D5:D8" si="1">I5*J5</f>
+        <v>4.8964230000000004E-2</v>
+      </c>
+      <c r="E5" s="40">
+        <f t="shared" si="0"/>
+        <v>0.16761241369387811</v>
+      </c>
+      <c r="F5" s="27">
+        <f t="shared" ref="F5:F8" si="2">I5*K5</f>
+        <v>2.2030596E-3</v>
+      </c>
+      <c r="G5" s="27">
+        <v>158.19300000000001</v>
+      </c>
+      <c r="H5" s="54">
+        <v>14.3811</v>
+      </c>
+      <c r="I5" s="27">
+        <v>2.9399999999999999E-2</v>
+      </c>
+      <c r="J5" s="27">
+        <v>1.6654500000000001</v>
+      </c>
+      <c r="K5" s="28">
+        <v>7.4934000000000001E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="126"/>
+      <c r="C6" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="27">
+        <f t="shared" si="1"/>
+        <v>0.43967880000000004</v>
+      </c>
+      <c r="E6" s="40">
+        <f t="shared" si="0"/>
+        <v>1.5050910617409463</v>
+      </c>
+      <c r="F6" s="27">
+        <f t="shared" si="2"/>
+        <v>1.9782576E-2</v>
+      </c>
+      <c r="G6" s="27">
+        <v>158.19300000000001</v>
+      </c>
+      <c r="H6" s="54">
+        <v>14.3811</v>
+      </c>
+      <c r="I6" s="27">
+        <v>0.26400000000000001</v>
+      </c>
+      <c r="J6" s="27">
+        <v>1.6654500000000001</v>
+      </c>
+      <c r="K6" s="28">
+        <v>7.4934000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="62" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="27">
+        <f t="shared" si="1"/>
+        <v>1.2514191299999999</v>
+      </c>
+      <c r="E7" s="40">
+        <f t="shared" si="0"/>
+        <v>4.2838084234551017</v>
+      </c>
+      <c r="F7" s="27">
+        <f t="shared" si="2"/>
+        <v>5.6305407599999996E-2</v>
+      </c>
+      <c r="G7" s="27">
+        <v>158.19300000000001</v>
+      </c>
+      <c r="H7" s="54">
+        <v>14.3811</v>
+      </c>
+      <c r="I7" s="27">
+        <v>0.75139999999999996</v>
+      </c>
+      <c r="J7" s="27">
+        <v>1.6654500000000001</v>
+      </c>
+      <c r="K7" s="28">
+        <v>7.4934000000000001E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="59" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="30">
+        <f t="shared" si="1"/>
+        <v>1.6654500000000001</v>
+      </c>
+      <c r="E8" s="41">
+        <f t="shared" si="0"/>
+        <v>5.701102506594494</v>
+      </c>
+      <c r="F8" s="30">
+        <f t="shared" si="2"/>
+        <v>7.4934000000000001E-2</v>
+      </c>
+      <c r="G8" s="30">
+        <v>158.19300000000001</v>
+      </c>
+      <c r="H8" s="54">
+        <v>14.3811</v>
+      </c>
+      <c r="I8" s="30">
+        <v>1</v>
+      </c>
+      <c r="J8" s="30">
+        <v>1.6654500000000001</v>
+      </c>
+      <c r="K8" s="31">
+        <v>7.4934000000000001E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B9" s="122" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9">
+        <v>0.17736399999999999</v>
+      </c>
+      <c r="E9" s="33">
+        <f t="shared" si="0"/>
+        <v>0.60714542314667252</v>
+      </c>
+      <c r="F9">
+        <v>4.4671700000000002E-2</v>
+      </c>
+      <c r="G9" s="4">
+        <v>31.5443</v>
+      </c>
+      <c r="H9">
+        <v>4.3747400000000001</v>
+      </c>
+      <c r="L9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="122"/>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10">
+        <v>1.4557599999999999</v>
+      </c>
+      <c r="E10" s="33">
+        <f t="shared" si="0"/>
+        <v>4.9832999999999998</v>
+      </c>
+      <c r="F10">
+        <v>0.12048</v>
+      </c>
+      <c r="G10" s="4">
+        <v>31.5443</v>
+      </c>
+      <c r="H10">
+        <v>4.3747400000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="60" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="17">
+        <f>I11*J11</f>
+        <v>0.25210164000000002</v>
+      </c>
+      <c r="E11" s="37">
+        <f t="shared" si="0"/>
+        <v>0.86298435361048531</v>
+      </c>
+      <c r="F11" s="17">
+        <f>I11*K11</f>
+        <v>1.5407612999999999E-2</v>
+      </c>
+      <c r="G11" s="17">
+        <v>21.929400000000001</v>
+      </c>
+      <c r="H11" s="17">
+        <v>2.7411699999999999</v>
+      </c>
+      <c r="I11" s="17">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="J11" s="17">
+        <v>2.8977200000000001</v>
+      </c>
+      <c r="K11" s="18">
+        <v>0.17709900000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="86"/>
+      <c r="C12" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="19">
+        <f t="shared" ref="D12:D15" si="3">I12*J12</f>
+        <v>0.28600496399999997</v>
+      </c>
+      <c r="E12" s="38">
+        <f t="shared" si="0"/>
+        <v>0.97904087013051588</v>
+      </c>
+      <c r="F12" s="19">
+        <f t="shared" ref="F12:F15" si="4">I12*K12</f>
+        <v>1.7479671299999999E-2</v>
+      </c>
+      <c r="G12" s="19">
+        <v>21.929400000000001</v>
+      </c>
+      <c r="H12" s="17">
+        <v>2.7411699999999999</v>
+      </c>
+      <c r="I12" s="19">
+        <v>9.8699999999999996E-2</v>
+      </c>
+      <c r="J12" s="19">
+        <v>2.8977200000000001</v>
+      </c>
+      <c r="K12" s="20">
+        <v>0.17709900000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="85" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="19">
+        <f t="shared" si="3"/>
+        <v>0.97247483200000007</v>
+      </c>
+      <c r="E13" s="38">
+        <f t="shared" si="0"/>
+        <v>3.328937345651481</v>
+      </c>
+      <c r="F13" s="19">
+        <f t="shared" si="4"/>
+        <v>5.9434424400000005E-2</v>
+      </c>
+      <c r="G13" s="19">
+        <v>21.929400000000001</v>
+      </c>
+      <c r="H13" s="17">
+        <v>2.7411699999999999</v>
+      </c>
+      <c r="I13" s="19">
+        <v>0.33560000000000001</v>
+      </c>
+      <c r="J13" s="19">
+        <v>2.8977200000000001</v>
+      </c>
+      <c r="K13" s="20">
+        <v>0.17709900000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="85"/>
+      <c r="C14" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="19">
+        <f t="shared" si="3"/>
+        <v>0.20370971600000001</v>
+      </c>
+      <c r="E14" s="38">
+        <f t="shared" si="0"/>
+        <v>0.69733103515881745</v>
+      </c>
+      <c r="F14" s="19">
+        <f t="shared" si="4"/>
+        <v>1.24500597E-2</v>
+      </c>
+      <c r="G14" s="19">
+        <v>21.929400000000001</v>
+      </c>
+      <c r="H14" s="17">
+        <v>2.7411699999999999</v>
+      </c>
+      <c r="I14" s="19">
+        <v>7.0300000000000001E-2</v>
+      </c>
+      <c r="J14" s="19">
+        <v>2.8977200000000001</v>
+      </c>
+      <c r="K14" s="20">
+        <v>0.17709900000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="21"/>
+      <c r="C15" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="22">
+        <f t="shared" si="3"/>
+        <v>2.7528339999999998E-2</v>
+      </c>
+      <c r="E15" s="39">
+        <f t="shared" si="0"/>
+        <v>9.423392367011045E-2</v>
+      </c>
+      <c r="F15" s="22">
+        <f t="shared" si="4"/>
+        <v>1.6824405000000001E-3</v>
+      </c>
+      <c r="G15" s="22">
+        <v>21.929400000000001</v>
+      </c>
+      <c r="H15" s="17">
+        <v>2.7411699999999999</v>
+      </c>
+      <c r="I15" s="22">
+        <v>9.4999999999999998E-3</v>
+      </c>
+      <c r="J15" s="22">
+        <v>2.8977200000000001</v>
+      </c>
+      <c r="K15" s="23">
+        <v>0.17709900000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B16" s="122" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16">
+        <v>0.36342999999999998</v>
+      </c>
+      <c r="E16" s="33">
+        <f t="shared" si="0"/>
+        <v>1.244079188190361</v>
+      </c>
+      <c r="F16">
+        <v>5.6393199999999997E-2</v>
+      </c>
+      <c r="G16" s="4">
+        <v>21.1067</v>
+      </c>
+      <c r="H16">
+        <v>3.02854</v>
+      </c>
+      <c r="L16" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="119"/>
+      <c r="C17" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" s="6">
+        <v>1.8707499999999999</v>
+      </c>
+      <c r="E17" s="34">
+        <f t="shared" si="0"/>
+        <v>6.4038773389844472</v>
+      </c>
+      <c r="F17" s="6">
+        <v>0.114702</v>
+      </c>
+      <c r="G17" s="7">
+        <v>21.1067</v>
+      </c>
+      <c r="H17">
+        <v>3.02854</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0.45706400000000003</v>
+      </c>
+      <c r="E18" s="35">
+        <f t="shared" si="0"/>
+        <v>1.5646033901192504</v>
+      </c>
+      <c r="F18" s="2">
+        <v>8.3333199999999996E-2</v>
+      </c>
+      <c r="G18" s="3">
+        <v>15.232100000000001</v>
+      </c>
+      <c r="H18">
+        <v>3.06196</v>
+      </c>
+      <c r="L18" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="70" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="48" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" s="48">
+        <f>I19*J19</f>
+        <v>8.0849340000000006E-2</v>
+      </c>
+      <c r="E19" s="57">
+        <f t="shared" si="0"/>
+        <v>0.27676025994806835</v>
+      </c>
+      <c r="F19" s="48">
+        <f>I19*K19</f>
+        <v>2.4430000000000003E-3</v>
+      </c>
+      <c r="G19" s="48">
+        <v>58.458599999999997</v>
+      </c>
+      <c r="H19" s="48">
+        <v>8.3512299999999993</v>
+      </c>
+      <c r="I19" s="48">
+        <v>3.49E-2</v>
+      </c>
+      <c r="J19" s="48">
+        <v>2.3166000000000002</v>
+      </c>
+      <c r="K19" s="71">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="87"/>
+      <c r="C20" s="68" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" s="68">
+        <f t="shared" ref="D20:D21" si="5">I20*J20</f>
+        <v>2.1407700600000004</v>
+      </c>
+      <c r="E20" s="72">
+        <f t="shared" si="0"/>
+        <v>7.3281993185676217</v>
+      </c>
+      <c r="F20" s="68">
+        <f t="shared" ref="F20:F21" si="6">I20*K20</f>
+        <v>6.4687000000000008E-2</v>
+      </c>
+      <c r="G20" s="68">
+        <v>58.458599999999997</v>
+      </c>
+      <c r="H20" s="48">
+        <v>8.3512299999999993</v>
+      </c>
+      <c r="I20" s="68">
+        <v>0.92410000000000003</v>
+      </c>
+      <c r="J20" s="68">
+        <v>2.3166000000000002</v>
+      </c>
+      <c r="K20" s="88">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="73" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="74" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="74">
+        <f t="shared" si="5"/>
+        <v>0.41559804000000006</v>
+      </c>
+      <c r="E21" s="75">
+        <f t="shared" si="0"/>
+        <v>1.4226587574407872</v>
+      </c>
+      <c r="F21" s="74">
+        <f t="shared" si="6"/>
+        <v>1.2558000000000001E-2</v>
+      </c>
+      <c r="G21" s="74">
+        <v>58.458599999999997</v>
+      </c>
+      <c r="H21" s="48">
+        <v>8.3512299999999993</v>
+      </c>
+      <c r="I21" s="74">
+        <v>0.1794</v>
+      </c>
+      <c r="J21" s="74">
+        <v>2.3166000000000002</v>
+      </c>
+      <c r="K21" s="76">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B22" s="122" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22">
+        <v>0.43999500000000002</v>
+      </c>
+      <c r="E22" s="33">
+        <f t="shared" si="0"/>
+        <v>1.5061734650629226</v>
+      </c>
+      <c r="F22">
+        <v>7.8331999999999999E-2</v>
+      </c>
+      <c r="G22" s="4">
+        <v>17.810700000000001</v>
+      </c>
+      <c r="H22">
+        <v>4.02874</v>
+      </c>
+      <c r="L22" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="122"/>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23">
+        <v>1.1331500000000001</v>
+      </c>
+      <c r="E23" s="33">
+        <f t="shared" si="0"/>
+        <v>3.8789542197889766</v>
+      </c>
+      <c r="F23">
+        <v>0.112195</v>
+      </c>
+      <c r="G23" s="4">
+        <v>17.810700000000001</v>
+      </c>
+      <c r="H23">
+        <v>4.02874</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="58" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="58">
+        <f>I24*J24</f>
+        <v>0.38584674400000002</v>
+      </c>
+      <c r="E24" s="82">
+        <f t="shared" si="0"/>
+        <v>1.3208152987959554</v>
+      </c>
+      <c r="F24" s="58">
+        <f>I24*K24</f>
+        <v>2.8167167999999999E-2</v>
+      </c>
+      <c r="G24" s="58">
+        <v>11.266400000000001</v>
+      </c>
+      <c r="H24" s="58">
+        <v>2.2532800000000002</v>
+      </c>
+      <c r="I24" s="58">
+        <v>6.9199999999999998E-2</v>
+      </c>
+      <c r="J24" s="82">
+        <v>5.5758200000000002</v>
+      </c>
+      <c r="K24" s="83">
+        <v>0.40704000000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="42"/>
+      <c r="C25" s="43" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="43">
+        <f t="shared" ref="D25:D27" si="7">I25*J25</f>
+        <v>2.9496087800000002</v>
+      </c>
+      <c r="E25" s="44">
+        <f t="shared" si="0"/>
+        <v>10.096984003801451</v>
+      </c>
+      <c r="F25" s="43">
+        <f t="shared" ref="F25:F27" si="8">I25*K25</f>
+        <v>0.21532416000000001</v>
+      </c>
+      <c r="G25" s="43">
+        <v>11.266400000000001</v>
+      </c>
+      <c r="H25" s="58">
+        <v>2.2532800000000002</v>
+      </c>
+      <c r="I25" s="43">
+        <v>0.52900000000000003</v>
+      </c>
+      <c r="J25" s="44">
+        <v>5.5758200000000002</v>
+      </c>
+      <c r="K25" s="45">
+        <v>0.40704000000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="42"/>
+      <c r="C26" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="D26" s="43">
+        <f t="shared" si="7"/>
+        <v>2.0630534000000002E-2</v>
+      </c>
+      <c r="E26" s="44">
+        <f t="shared" si="0"/>
+        <v>7.0621627247760624E-2</v>
+      </c>
+      <c r="F26" s="43">
+        <f t="shared" si="8"/>
+        <v>1.5060480000000001E-3</v>
+      </c>
+      <c r="G26" s="43">
+        <v>11.266400000000001</v>
+      </c>
+      <c r="H26" s="58">
+        <v>2.2532800000000002</v>
+      </c>
+      <c r="I26" s="43">
+        <v>3.7000000000000002E-3</v>
+      </c>
+      <c r="J26" s="44">
+        <v>5.5758200000000002</v>
+      </c>
+      <c r="K26" s="45">
+        <v>0.40704000000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="84" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="15">
+        <f t="shared" si="7"/>
+        <v>1.6727459999999999E-3</v>
+      </c>
+      <c r="E27" s="36">
+        <f t="shared" si="0"/>
+        <v>5.7260778849535631E-3</v>
+      </c>
+      <c r="F27" s="15">
+        <f t="shared" si="8"/>
+        <v>1.2211199999999999E-4</v>
+      </c>
+      <c r="G27" s="15">
+        <v>11.266400000000001</v>
+      </c>
+      <c r="H27" s="58">
+        <v>2.2532800000000002</v>
+      </c>
+      <c r="I27" s="15">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="J27" s="36">
+        <v>5.5758200000000002</v>
+      </c>
+      <c r="K27" s="16">
+        <v>0.40704000000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" ht="35" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="77" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="78" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="78">
+        <v>0.80409799999999998</v>
+      </c>
+      <c r="E28" s="79">
+        <f>D28*D31</f>
+        <v>2.7525564402099247</v>
+      </c>
+      <c r="F28" s="78">
+        <v>0.103809</v>
+      </c>
+      <c r="G28" s="80">
+        <v>1.25024</v>
+      </c>
+      <c r="H28" s="58"/>
+      <c r="L28" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B30" t="s">
+        <v>45</v>
+      </c>
+      <c r="D30" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B31">
+        <v>3.6014013985414599</v>
+      </c>
+      <c r="D31">
+        <v>3.4231604110567675</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B32" t="s">
+        <v>62</v>
+      </c>
+      <c r="D32" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B34" t="s">
+        <v>99</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="B22:B23"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2614BEC-FF13-A745-8162-474477D90294}">
   <dimension ref="B2:M70"/>
@@ -12709,6 +13129,40 @@
         <v>0.12610299999999999</v>
       </c>
     </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="F65">
+        <f>F69/F67</f>
+        <v>0.13101330603889458</v>
+      </c>
+      <c r="G65">
+        <f t="shared" ref="G65:M65" si="0">G69/G67</f>
+        <v>0.13793103448275865</v>
+      </c>
+      <c r="H65">
+        <f t="shared" si="0"/>
+        <v>0.13756527562832035</v>
+      </c>
+      <c r="I65">
+        <f t="shared" si="0"/>
+        <v>0.13674304652112396</v>
+      </c>
+      <c r="J65">
+        <f t="shared" si="0"/>
+        <v>0.13234972894616653</v>
+      </c>
+      <c r="K65">
+        <f t="shared" si="0"/>
+        <v>0.13402061855670103</v>
+      </c>
+      <c r="L65">
+        <f t="shared" si="0"/>
+        <v>0.13653460836913314</v>
+      </c>
+      <c r="M65">
+        <f t="shared" si="0"/>
+        <v>0.1324503311258278</v>
+      </c>
+    </row>
     <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B66" t="s">
         <v>87</v>
